--- a/outputs/benchmark-beaters/Benchmark_Beaters_2026-07-21.xlsx
+++ b/outputs/benchmark-beaters/Benchmark_Beaters_2026-07-21.xlsx
@@ -1260,7 +1260,7 @@
     <row r="2" ht="15.6" customHeight="1">
       <c r="A2" s="22" t="n"/>
       <c r="B2" s="21" t="n">
-        <v>46224.78932113852</v>
+        <v>46224.81394085352</v>
       </c>
       <c r="C2" s="22" t="n"/>
     </row>
@@ -1454,7 +1454,7 @@
         </is>
       </c>
       <c r="G8" s="89" t="n">
-        <v>1.59</v>
+        <v>1.632</v>
       </c>
       <c r="H8" s="90" t="n">
         <v>2358.79</v>
@@ -1492,7 +1492,7 @@
         </is>
       </c>
       <c r="G9" s="89" t="n">
-        <v>1.181</v>
+        <v>1.175</v>
       </c>
       <c r="H9" s="91" t="n">
         <v>555.83</v>
@@ -1530,7 +1530,7 @@
         </is>
       </c>
       <c r="G10" s="89" t="n">
-        <v>1.147</v>
+        <v>1.157</v>
       </c>
       <c r="H10" s="90" t="n">
         <v>284.57</v>
@@ -1568,7 +1568,7 @@
         </is>
       </c>
       <c r="G11" s="89" t="n">
-        <v>0.696</v>
+        <v>0.725</v>
       </c>
       <c r="H11" s="91" t="n">
         <v>2258.51</v>
@@ -1606,7 +1606,7 @@
         </is>
       </c>
       <c r="G12" s="89" t="n">
-        <v>0.576</v>
+        <v>0.5610000000000001</v>
       </c>
       <c r="H12" s="90" t="n">
         <v>1565.38</v>
@@ -1644,7 +1644,7 @@
         </is>
       </c>
       <c r="G13" s="89" t="n">
-        <v>0.54</v>
+        <v>0.547</v>
       </c>
       <c r="H13" s="91" t="n">
         <v>1892.54</v>
@@ -1682,7 +1682,7 @@
         </is>
       </c>
       <c r="G14" s="89" t="n">
-        <v>0.453</v>
+        <v>0.451</v>
       </c>
       <c r="H14" s="90" t="n">
         <v>53011.04</v>
@@ -1720,7 +1720,7 @@
         </is>
       </c>
       <c r="G15" s="89" t="n">
-        <v>0.439</v>
+        <v>0.437</v>
       </c>
       <c r="H15" s="91" t="n">
         <v>2385.76</v>
@@ -1739,33 +1739,33 @@
       </c>
       <c r="C16" s="30" t="inlineStr">
         <is>
-          <t>ARG</t>
+          <t>KBL</t>
         </is>
       </c>
       <c r="D16" s="31" t="inlineStr">
         <is>
-          <t>Amerigo Resources Ltd.</t>
+          <t>K-Bro Linen Inc.</t>
         </is>
       </c>
       <c r="E16" s="32" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="F16" s="32" t="inlineStr">
         <is>
-          <t>Metals and Mining</t>
+          <t>Commercial Services and Supplies</t>
         </is>
       </c>
       <c r="G16" s="89" t="n">
-        <v>0.398</v>
+        <v>0.377</v>
       </c>
       <c r="H16" s="91" t="n">
-        <v>681.6799999999999</v>
+        <v>390.27</v>
       </c>
       <c r="I16" s="54" t="inlineStr">
         <is>
-          <t>Amerigo Resources Ltd through its subsidiary Minera Valle Central S</t>
+          <t>K-Bro Linen Inc together with its subsidiaries provides laundry and linen services to healthcare organizations hotels and other commercial accounts in Canada and the United Kingdom</t>
         </is>
       </c>
       <c r="J16" s="28" t="n"/>
@@ -1777,33 +1777,33 @@
       </c>
       <c r="C17" s="38" t="inlineStr">
         <is>
-          <t>KBL</t>
+          <t>BMO</t>
         </is>
       </c>
       <c r="D17" s="39" t="inlineStr">
         <is>
-          <t>K-Bro Linen Inc.</t>
+          <t>Bank of Montreal</t>
         </is>
       </c>
       <c r="E17" s="40" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="F17" s="40" t="inlineStr">
         <is>
-          <t>Commercial Services and Supplies</t>
+          <t>Banks</t>
         </is>
       </c>
       <c r="G17" s="89" t="n">
-        <v>0.373</v>
+        <v>0.357</v>
       </c>
       <c r="H17" s="90" t="n">
-        <v>390.27</v>
+        <v>116001.23</v>
       </c>
       <c r="I17" s="53" t="inlineStr">
         <is>
-          <t>K-Bro Linen Inc together with its subsidiaries provides laundry and linen services to healthcare organizations hotels and other commercial accounts in Canada and the United Kingdom</t>
+          <t>Bank of Montreal engages in the provision of diversified financial services primarily in North America</t>
         </is>
       </c>
       <c r="J17" s="36" t="n"/>
@@ -1815,33 +1815,33 @@
       </c>
       <c r="C18" s="30" t="inlineStr">
         <is>
-          <t>SLF</t>
+          <t>ARG</t>
         </is>
       </c>
       <c r="D18" s="31" t="inlineStr">
         <is>
-          <t>Sun Life Financial Inc.</t>
+          <t>Amerigo Resources Ltd.</t>
         </is>
       </c>
       <c r="E18" s="32" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Materials</t>
         </is>
       </c>
       <c r="F18" s="32" t="inlineStr">
         <is>
-          <t>Insurance</t>
+          <t>Metals and Mining</t>
         </is>
       </c>
       <c r="G18" s="89" t="n">
-        <v>0.348</v>
+        <v>0.341</v>
       </c>
       <c r="H18" s="91" t="n">
-        <v>41467.31</v>
+        <v>681.6799999999999</v>
       </c>
       <c r="I18" s="54" t="inlineStr">
         <is>
-          <t>Sun Life Financial Inc a financial services company provides asset management wealth insurance and health solutions to individual and institutional customers in Canada the United States the United Kingdom Ireland Hong Kong the Philippines Japan Indonesia India China Australia Singapore Vietnam Malaysia and Bermuda</t>
+          <t>Amerigo Resources Ltd through its subsidiary Minera Valle Central S</t>
         </is>
       </c>
       <c r="J18" s="28" t="n"/>
@@ -1853,12 +1853,12 @@
       </c>
       <c r="C19" s="38" t="inlineStr">
         <is>
-          <t>BMO</t>
+          <t>POW</t>
         </is>
       </c>
       <c r="D19" s="39" t="inlineStr">
         <is>
-          <t>Bank of Montreal</t>
+          <t>Power Corporation of Canada</t>
         </is>
       </c>
       <c r="E19" s="40" t="inlineStr">
@@ -1868,18 +1868,18 @@
       </c>
       <c r="F19" s="40" t="inlineStr">
         <is>
-          <t>Banks</t>
+          <t>Insurance</t>
         </is>
       </c>
       <c r="G19" s="89" t="n">
-        <v>0.341</v>
+        <v>0.337</v>
       </c>
       <c r="H19" s="90" t="n">
-        <v>116001.23</v>
+        <v>38174.66</v>
       </c>
       <c r="I19" s="53" t="inlineStr">
         <is>
-          <t>Bank of Montreal engages in the provision of diversified financial services primarily in North America</t>
+          <t>Power Corporation of Canada an international management and holding company provides financial services in North America Europe and Asia</t>
         </is>
       </c>
       <c r="J19" s="36" t="n"/>
@@ -1891,33 +1891,33 @@
       </c>
       <c r="C20" s="30" t="inlineStr">
         <is>
-          <t>PPL</t>
+          <t>SLF</t>
         </is>
       </c>
       <c r="D20" s="31" t="inlineStr">
         <is>
-          <t>Pembina Pipeline Corporation</t>
+          <t>Sun Life Financial Inc.</t>
         </is>
       </c>
       <c r="E20" s="32" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="F20" s="32" t="inlineStr">
         <is>
-          <t>Oil Gas and Consumable Fuels</t>
+          <t>Insurance</t>
         </is>
       </c>
       <c r="G20" s="89" t="n">
-        <v>0.331</v>
+        <v>0.333</v>
       </c>
       <c r="H20" s="91" t="n">
-        <v>28518.97</v>
+        <v>41467.31</v>
       </c>
       <c r="I20" s="54" t="inlineStr">
         <is>
-          <t>Pembina Pipeline Corporation provides energy transportation and midstream services</t>
+          <t>Sun Life Financial Inc a financial services company provides asset management wealth insurance and health solutions to individual and institutional customers in Canada the United States the United Kingdom Ireland Hong Kong the Philippines Japan Indonesia India China Australia Singapore Vietnam Malaysia and Bermuda</t>
         </is>
       </c>
       <c r="J20" s="28" t="n"/>
@@ -1929,33 +1929,33 @@
       </c>
       <c r="C21" s="38" t="inlineStr">
         <is>
-          <t>POW</t>
+          <t>CNR</t>
         </is>
       </c>
       <c r="D21" s="39" t="inlineStr">
         <is>
-          <t>Power Corporation of Canada</t>
+          <t>Canadian National Railway Company</t>
         </is>
       </c>
       <c r="E21" s="40" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="F21" s="40" t="inlineStr">
         <is>
-          <t>Insurance</t>
+          <t>Ground Transportation</t>
         </is>
       </c>
       <c r="G21" s="89" t="n">
-        <v>0.321</v>
+        <v>0.327</v>
       </c>
       <c r="H21" s="90" t="n">
-        <v>38174.66</v>
+        <v>72839.50999999999</v>
       </c>
       <c r="I21" s="53" t="inlineStr">
         <is>
-          <t>Power Corporation of Canada an international management and holding company provides financial services in North America Europe and Asia</t>
+          <t>Canadian National Railway Company together with its subsidiaries engages in the rail intermodal trucking and related transportation businesses in Canada and the United States</t>
         </is>
       </c>
       <c r="J21" s="36" t="n"/>
@@ -2043,33 +2043,33 @@
       </c>
       <c r="C24" s="38" t="inlineStr">
         <is>
-          <t>CNR</t>
+          <t>EQB</t>
         </is>
       </c>
       <c r="D24" s="39" t="inlineStr">
         <is>
-          <t>Canadian National Railway Company</t>
+          <t>EQB Inc.</t>
         </is>
       </c>
       <c r="E24" s="40" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="F24" s="40" t="inlineStr">
         <is>
-          <t>Ground Transportation</t>
+          <t>Banks</t>
         </is>
       </c>
       <c r="G24" s="89" t="n">
-        <v>0.318</v>
+        <v>0.314</v>
       </c>
       <c r="H24" s="90" t="n">
-        <v>72839.50999999999</v>
+        <v>3018.47</v>
       </c>
       <c r="I24" s="53" t="inlineStr">
         <is>
-          <t>Canadian National Railway Company together with its subsidiaries engages in the rail intermodal trucking and related transportation businesses in Canada and the United States</t>
+          <t>EQB Inc through its subsidiary Equitable Bank provides personal and commercial banking services to retail and commercial customers in Canada</t>
         </is>
       </c>
       <c r="J24" s="36" t="n"/>
@@ -2081,33 +2081,33 @@
       </c>
       <c r="C25" s="30" t="inlineStr">
         <is>
-          <t>CP</t>
+          <t>PPL</t>
         </is>
       </c>
       <c r="D25" s="31" t="inlineStr">
         <is>
-          <t>Canadian Pacific Kansas City Limited</t>
+          <t>Pembina Pipeline Corporation</t>
         </is>
       </c>
       <c r="E25" s="32" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="F25" s="32" t="inlineStr">
         <is>
-          <t>Ground Transportation</t>
+          <t>Oil Gas and Consumable Fuels</t>
         </is>
       </c>
       <c r="G25" s="89" t="n">
-        <v>0.301</v>
+        <v>0.31</v>
       </c>
       <c r="H25" s="91" t="n">
-        <v>79823.21000000001</v>
+        <v>28518.97</v>
       </c>
       <c r="I25" s="54" t="inlineStr">
         <is>
-          <t>Canadian Pacific Kansas City Limited together with its subsidiaries owns and operates a transcontinental freight railway in Canada the United States and Mexico</t>
+          <t>Pembina Pipeline Corporation provides energy transportation and midstream services</t>
         </is>
       </c>
       <c r="J25" s="28" t="n"/>
@@ -2119,12 +2119,12 @@
       </c>
       <c r="C26" s="38" t="inlineStr">
         <is>
-          <t>EQB</t>
+          <t>IGM</t>
         </is>
       </c>
       <c r="D26" s="39" t="inlineStr">
         <is>
-          <t>EQB Inc.</t>
+          <t>IGM Financial Inc.</t>
         </is>
       </c>
       <c r="E26" s="40" t="inlineStr">
@@ -2134,18 +2134,18 @@
       </c>
       <c r="F26" s="40" t="inlineStr">
         <is>
-          <t>Banks</t>
+          <t>Capital Markets</t>
         </is>
       </c>
       <c r="G26" s="89" t="n">
-        <v>0.3</v>
+        <v>0.305</v>
       </c>
       <c r="H26" s="90" t="n">
-        <v>3018.47</v>
+        <v>13303.41</v>
       </c>
       <c r="I26" s="53" t="inlineStr">
         <is>
-          <t>EQB Inc through its subsidiary Equitable Bank provides personal and commercial banking services to retail and commercial customers in Canada</t>
+          <t>IGM Financial Inc engages in the wealth and asset management business in Canada</t>
         </is>
       </c>
       <c r="J26" s="36" t="n"/>
@@ -2157,33 +2157,33 @@
       </c>
       <c r="C27" s="38" t="inlineStr">
         <is>
-          <t>RY</t>
+          <t>CP</t>
         </is>
       </c>
       <c r="D27" s="39" t="inlineStr">
         <is>
-          <t>Royal Bank of Canada</t>
+          <t>Canadian Pacific Kansas City Limited</t>
         </is>
       </c>
       <c r="E27" s="40" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="F27" s="40" t="inlineStr">
         <is>
-          <t>Banks</t>
+          <t>Ground Transportation</t>
         </is>
       </c>
       <c r="G27" s="89" t="n">
         <v>0.298</v>
       </c>
       <c r="H27" s="90" t="n">
-        <v>275998.42</v>
+        <v>79823.21000000001</v>
       </c>
       <c r="I27" s="53" t="inlineStr">
         <is>
-          <t>Royal Bank of Canada operates as a diversified financial service company worldwide</t>
+          <t>Canadian Pacific Kansas City Limited together with its subsidiaries owns and operates a transcontinental freight railway in Canada the United States and Mexico</t>
         </is>
       </c>
       <c r="J27" s="36" t="n"/>
@@ -2195,12 +2195,12 @@
       </c>
       <c r="C28" s="30" t="inlineStr">
         <is>
-          <t>CF</t>
+          <t>RY</t>
         </is>
       </c>
       <c r="D28" s="31" t="inlineStr">
         <is>
-          <t>Canaccord Genuity Group Inc.</t>
+          <t>Royal Bank of Canada</t>
         </is>
       </c>
       <c r="E28" s="32" t="inlineStr">
@@ -2210,18 +2210,18 @@
       </c>
       <c r="F28" s="32" t="inlineStr">
         <is>
-          <t>Capital Markets</t>
+          <t>Banks</t>
         </is>
       </c>
       <c r="G28" s="89" t="n">
-        <v>0.286</v>
+        <v>0.295</v>
       </c>
       <c r="H28" s="91" t="n">
-        <v>976.67</v>
+        <v>275998.42</v>
       </c>
       <c r="I28" s="54" t="inlineStr">
         <is>
-          <t>Canaccord Genuity Group Inc operates as a full-service investment dealer in Canada the United States the United Kingdom Europe Crown Dependencies and Australia</t>
+          <t>Royal Bank of Canada operates as a diversified financial service company worldwide</t>
         </is>
       </c>
       <c r="J28" s="28" t="n"/>
@@ -2233,12 +2233,12 @@
       </c>
       <c r="C29" s="38" t="inlineStr">
         <is>
-          <t>IGM</t>
+          <t>CF</t>
         </is>
       </c>
       <c r="D29" s="39" t="inlineStr">
         <is>
-          <t>IGM Financial Inc.</t>
+          <t>Canaccord Genuity Group Inc.</t>
         </is>
       </c>
       <c r="E29" s="40" t="inlineStr">
@@ -2252,14 +2252,14 @@
         </is>
       </c>
       <c r="G29" s="89" t="n">
-        <v>0.278</v>
+        <v>0.269</v>
       </c>
       <c r="H29" s="90" t="n">
-        <v>13303.41</v>
+        <v>976.67</v>
       </c>
       <c r="I29" s="53" t="inlineStr">
         <is>
-          <t>IGM Financial Inc engages in the wealth and asset management business in Canada</t>
+          <t>Canaccord Genuity Group Inc operates as a full-service investment dealer in Canada the United States the United Kingdom Europe Crown Dependencies and Australia</t>
         </is>
       </c>
       <c r="J29" s="36" t="n"/>
@@ -2290,7 +2290,7 @@
         </is>
       </c>
       <c r="G30" s="89" t="n">
-        <v>0.272</v>
+        <v>0.264</v>
       </c>
       <c r="H30" s="90" t="n">
         <v>10045.65</v>
@@ -2309,12 +2309,12 @@
       </c>
       <c r="C31" s="30" t="inlineStr">
         <is>
-          <t>DXT</t>
+          <t>BDGI</t>
         </is>
       </c>
       <c r="D31" s="31" t="inlineStr">
         <is>
-          <t>Dexterra Group Inc.</t>
+          <t>Badger Infrastructure Solutions Ltd.</t>
         </is>
       </c>
       <c r="E31" s="32" t="inlineStr">
@@ -2324,18 +2324,18 @@
       </c>
       <c r="F31" s="32" t="inlineStr">
         <is>
-          <t>Commercial Services and Supplies</t>
+          <t>Construction and Engineering</t>
         </is>
       </c>
       <c r="G31" s="89" t="n">
-        <v>0.231</v>
+        <v>0.252</v>
       </c>
       <c r="H31" s="91" t="n">
-        <v>576.85</v>
+        <v>2215.94</v>
       </c>
       <c r="I31" s="54" t="inlineStr">
         <is>
-          <t>Dexterra Group Inc engages in the provision of support services for the creation management and operation of infrastructure in Canada</t>
+          <t>Badger Infrastructure Solutions Ltd provides non-destructive excavating and related services to utilities industrial construction transportation and other industries in Canada and the United States</t>
         </is>
       </c>
       <c r="J31" s="28" t="n"/>
@@ -2347,33 +2347,33 @@
       </c>
       <c r="C32" s="38" t="inlineStr">
         <is>
-          <t>BNS</t>
+          <t>DXT</t>
         </is>
       </c>
       <c r="D32" s="39" t="inlineStr">
         <is>
-          <t>The Bank of Nova Scotia</t>
+          <t>Dexterra Group Inc.</t>
         </is>
       </c>
       <c r="E32" s="40" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="F32" s="40" t="inlineStr">
         <is>
-          <t>Banks</t>
+          <t>Commercial Services and Supplies</t>
         </is>
       </c>
       <c r="G32" s="89" t="n">
-        <v>0.226</v>
+        <v>0.234</v>
       </c>
       <c r="H32" s="90" t="n">
-        <v>100391.39</v>
+        <v>576.85</v>
       </c>
       <c r="I32" s="53" t="inlineStr">
         <is>
-          <t>The Bank of Nova Scotia provides various banking products and services in Canada the United States Mexico Peru Chile Colombia the Caribbean and Central America and internationally</t>
+          <t>Dexterra Group Inc engages in the provision of support services for the creation management and operation of infrastructure in Canada</t>
         </is>
       </c>
       <c r="J32" s="36" t="n"/>
@@ -2404,7 +2404,7 @@
         </is>
       </c>
       <c r="G33" s="89" t="n">
-        <v>0.225</v>
+        <v>0.234</v>
       </c>
       <c r="H33" s="91" t="n">
         <v>11282.66</v>
@@ -2423,33 +2423,33 @@
       </c>
       <c r="C34" s="38" t="inlineStr">
         <is>
-          <t>BDI</t>
+          <t>BNS</t>
         </is>
       </c>
       <c r="D34" s="39" t="inlineStr">
         <is>
-          <t>Black Diamond Group Limited</t>
+          <t>The Bank of Nova Scotia</t>
         </is>
       </c>
       <c r="E34" s="40" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="F34" s="40" t="inlineStr">
         <is>
-          <t>Commercial Services and Supplies</t>
+          <t>Banks</t>
         </is>
       </c>
       <c r="G34" s="89" t="n">
-        <v>0.221</v>
+        <v>0.223</v>
       </c>
       <c r="H34" s="90" t="n">
-        <v>927.72</v>
+        <v>100391.39</v>
       </c>
       <c r="I34" s="53" t="inlineStr">
         <is>
-          <t>Black Diamond Group Limited provides specialty rentals and industrial services in Canada the United States and Australia</t>
+          <t>The Bank of Nova Scotia provides various banking products and services in Canada the United States Mexico Peru Chile Colombia the Caribbean and Central America and internationally</t>
         </is>
       </c>
       <c r="J34" s="36" t="n"/>
@@ -2461,33 +2461,33 @@
       </c>
       <c r="C35" s="30" t="inlineStr">
         <is>
-          <t>MFC</t>
+          <t>BDI</t>
         </is>
       </c>
       <c r="D35" s="31" t="inlineStr">
         <is>
-          <t>Manulife Financial Corporation</t>
+          <t>Black Diamond Group Limited</t>
         </is>
       </c>
       <c r="E35" s="32" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="F35" s="32" t="inlineStr">
         <is>
-          <t>Insurance</t>
+          <t>Commercial Services and Supplies</t>
         </is>
       </c>
       <c r="G35" s="89" t="n">
-        <v>0.215</v>
+        <v>0.217</v>
       </c>
       <c r="H35" s="91" t="n">
-        <v>65572.44</v>
+        <v>927.72</v>
       </c>
       <c r="I35" s="54" t="inlineStr">
         <is>
-          <t>Manulife Financial Corporation together with its subsidiaries provides financial products and services in the United States Canada Asia and internationally</t>
+          <t>Black Diamond Group Limited provides specialty rentals and industrial services in Canada the United States and Australia</t>
         </is>
       </c>
       <c r="J35" s="28" t="n"/>
@@ -2499,33 +2499,33 @@
       </c>
       <c r="C36" s="38" t="inlineStr">
         <is>
-          <t>BDGI</t>
+          <t>MFC</t>
         </is>
       </c>
       <c r="D36" s="39" t="inlineStr">
         <is>
-          <t>Badger Infrastructure Solutions Ltd.</t>
+          <t>Manulife Financial Corporation</t>
         </is>
       </c>
       <c r="E36" s="40" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="F36" s="40" t="inlineStr">
         <is>
-          <t>Construction and Engineering</t>
+          <t>Insurance</t>
         </is>
       </c>
       <c r="G36" s="89" t="n">
-        <v>0.204</v>
+        <v>0.215</v>
       </c>
       <c r="H36" s="90" t="n">
-        <v>2215.94</v>
+        <v>65572.44</v>
       </c>
       <c r="I36" s="53" t="inlineStr">
         <is>
-          <t>Badger Infrastructure Solutions Ltd provides non-destructive excavating and related services to utilities industrial construction transportation and other industries in Canada and the United States</t>
+          <t>Manulife Financial Corporation together with its subsidiaries provides financial products and services in the United States Canada Asia and internationally</t>
         </is>
       </c>
       <c r="J36" s="36" t="n"/>
@@ -2556,7 +2556,7 @@
         </is>
       </c>
       <c r="G37" s="89" t="n">
-        <v>0.2</v>
+        <v>0.191</v>
       </c>
       <c r="H37" s="91" t="n">
         <v>501.72</v>
@@ -2594,7 +2594,7 @@
         </is>
       </c>
       <c r="G38" s="89" t="n">
-        <v>0.184</v>
+        <v>0.178</v>
       </c>
       <c r="H38" s="90" t="n">
         <v>1330.28</v>
@@ -2632,7 +2632,7 @@
         </is>
       </c>
       <c r="G39" s="89" t="n">
-        <v>0.155</v>
+        <v>0.14</v>
       </c>
       <c r="H39" s="91" t="n">
         <v>676.4400000000001</v>
@@ -2670,7 +2670,7 @@
         </is>
       </c>
       <c r="G40" s="89" t="n">
-        <v>0.079</v>
+        <v>0.076</v>
       </c>
       <c r="H40" s="90" t="n">
         <v>6226.62</v>
@@ -3958,7 +3958,7 @@
         </is>
       </c>
       <c r="G8" s="89" t="n">
-        <v>1.174</v>
+        <v>1.192</v>
       </c>
       <c r="H8" s="90" t="n">
         <v>12725.72</v>
@@ -3996,7 +3996,7 @@
         </is>
       </c>
       <c r="G9" s="89" t="n">
-        <v>0.859</v>
+        <v>0.899</v>
       </c>
       <c r="H9" s="91" t="n">
         <v>213908.98</v>
@@ -4034,7 +4034,7 @@
         </is>
       </c>
       <c r="G10" s="89" t="n">
-        <v>0.834</v>
+        <v>0.833</v>
       </c>
       <c r="H10" s="90" t="n">
         <v>77721.12</v>
@@ -4072,7 +4072,7 @@
         </is>
       </c>
       <c r="G11" s="89" t="n">
-        <v>0.697</v>
+        <v>0.6929999999999999</v>
       </c>
       <c r="H11" s="91" t="n">
         <v>77190.64999999999</v>
@@ -4110,7 +4110,7 @@
         </is>
       </c>
       <c r="G12" s="89" t="n">
-        <v>0.45</v>
+        <v>0.477</v>
       </c>
       <c r="H12" s="90" t="n">
         <v>44725.83</v>
@@ -4129,12 +4129,12 @@
       </c>
       <c r="C13" s="30" t="inlineStr">
         <is>
-          <t>CSX</t>
+          <t>JBHT</t>
         </is>
       </c>
       <c r="D13" s="31" t="inlineStr">
         <is>
-          <t>CSX Corporation</t>
+          <t>J.B. Hunt Transport Services Inc.</t>
         </is>
       </c>
       <c r="E13" s="32" t="inlineStr">
@@ -4148,14 +4148,14 @@
         </is>
       </c>
       <c r="G13" s="89" t="n">
-        <v>0.408</v>
+        <v>0.418</v>
       </c>
       <c r="H13" s="91" t="n">
-        <v>86617.14</v>
+        <v>26566.73</v>
       </c>
       <c r="I13" s="54" t="inlineStr">
         <is>
-          <t>CSX Corporation together with its subsidiaries provides rail-based freight transportation services in the United States and Canada</t>
+          <t>J</t>
         </is>
       </c>
       <c r="J13" s="28" t="n"/>
@@ -4167,12 +4167,12 @@
       </c>
       <c r="C14" s="38" t="inlineStr">
         <is>
-          <t>JBHT</t>
+          <t>CSX</t>
         </is>
       </c>
       <c r="D14" s="39" t="inlineStr">
         <is>
-          <t>J.B. Hunt Transport Services Inc.</t>
+          <t>CSX Corporation</t>
         </is>
       </c>
       <c r="E14" s="40" t="inlineStr">
@@ -4186,14 +4186,14 @@
         </is>
       </c>
       <c r="G14" s="89" t="n">
-        <v>0.393</v>
+        <v>0.375</v>
       </c>
       <c r="H14" s="90" t="n">
-        <v>26566.73</v>
+        <v>86617.14</v>
       </c>
       <c r="I14" s="53" t="inlineStr">
         <is>
-          <t>J</t>
+          <t>CSX Corporation together with its subsidiaries provides rail-based freight transportation services in the United States and Canada</t>
         </is>
       </c>
       <c r="J14" s="36" t="n"/>
@@ -4205,33 +4205,33 @@
       </c>
       <c r="C15" s="30" t="inlineStr">
         <is>
-          <t>WELL</t>
+          <t>GL</t>
         </is>
       </c>
       <c r="D15" s="31" t="inlineStr">
         <is>
-          <t>Welltower Inc.</t>
+          <t>Globe Life Inc.</t>
         </is>
       </c>
       <c r="E15" s="32" t="inlineStr">
         <is>
-          <t>Real Estate</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="F15" s="32" t="inlineStr">
         <is>
-          <t>Health Care REITs</t>
+          <t>Insurance</t>
         </is>
       </c>
       <c r="G15" s="89" t="n">
-        <v>0.358</v>
+        <v>0.355</v>
       </c>
       <c r="H15" s="91" t="n">
-        <v>148209.56</v>
+        <v>12644.53</v>
       </c>
       <c r="I15" s="54" t="inlineStr">
         <is>
-          <t>Welltower Inc is a S&amp;P 500 company is positioned at the center of the silver economy focusing on rental housing for aging seniors across the United States United Kingdom and Canada</t>
+          <t>Globe Life Inc through its subsidiaries provides various life and supplemental health insurance products to lower middle- and middle-income families in the United States</t>
         </is>
       </c>
       <c r="J15" s="28" t="n"/>
@@ -4243,12 +4243,12 @@
       </c>
       <c r="C16" s="38" t="inlineStr">
         <is>
-          <t>TRV</t>
+          <t>BNY</t>
         </is>
       </c>
       <c r="D16" s="39" t="inlineStr">
         <is>
-          <t>The Travelers Companies Inc.</t>
+          <t>The Bank of New York Mellon Corporation</t>
         </is>
       </c>
       <c r="E16" s="40" t="inlineStr">
@@ -4258,18 +4258,18 @@
       </c>
       <c r="F16" s="40" t="inlineStr">
         <is>
-          <t>Insurance</t>
+          <t>Capital Markets</t>
         </is>
       </c>
       <c r="G16" s="89" t="n">
-        <v>0.339</v>
+        <v>0.351</v>
       </c>
       <c r="H16" s="90" t="n">
-        <v>64533.41</v>
+        <v>96186.41</v>
       </c>
       <c r="I16" s="53" t="inlineStr">
         <is>
-          <t>The Travelers Companies Inc through its subsidiaries provides a range of commercial and personal property and casualty insurance products and services to businesses government units associations and individuals in the United States Canada and internationally</t>
+          <t>The Bank of New York Mellon Corporation provides a range of financial products and services in the United States and internationally</t>
         </is>
       </c>
       <c r="J16" s="36" t="n"/>
@@ -4281,33 +4281,33 @@
       </c>
       <c r="C17" s="30" t="inlineStr">
         <is>
-          <t>GL</t>
+          <t>WELL</t>
         </is>
       </c>
       <c r="D17" s="31" t="inlineStr">
         <is>
-          <t>Globe Life Inc.</t>
+          <t>Welltower Inc.</t>
         </is>
       </c>
       <c r="E17" s="32" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Real Estate</t>
         </is>
       </c>
       <c r="F17" s="32" t="inlineStr">
         <is>
-          <t>Insurance</t>
+          <t>Health Care REITs</t>
         </is>
       </c>
       <c r="G17" s="89" t="n">
-        <v>0.338</v>
+        <v>0.348</v>
       </c>
       <c r="H17" s="91" t="n">
-        <v>12644.53</v>
+        <v>148209.56</v>
       </c>
       <c r="I17" s="54" t="inlineStr">
         <is>
-          <t>Globe Life Inc through its subsidiaries provides various life and supplemental health insurance products to lower middle- and middle-income families in the United States</t>
+          <t>Welltower Inc is a S&amp;P 500 company is positioned at the center of the silver economy focusing on rental housing for aging seniors across the United States United Kingdom and Canada</t>
         </is>
       </c>
       <c r="J17" s="28" t="n"/>
@@ -4319,33 +4319,33 @@
       </c>
       <c r="C18" s="38" t="inlineStr">
         <is>
-          <t>CVS</t>
+          <t>TRV</t>
         </is>
       </c>
       <c r="D18" s="39" t="inlineStr">
         <is>
-          <t>CVS Health Corporation</t>
+          <t>The Travelers Companies Inc.</t>
         </is>
       </c>
       <c r="E18" s="40" t="inlineStr">
         <is>
-          <t>Health Care</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="F18" s="40" t="inlineStr">
         <is>
-          <t>Health Care Providers and Services</t>
+          <t>Insurance</t>
         </is>
       </c>
       <c r="G18" s="89" t="n">
-        <v>0.337</v>
+        <v>0.341</v>
       </c>
       <c r="H18" s="90" t="n">
-        <v>125211.85</v>
+        <v>64533.41</v>
       </c>
       <c r="I18" s="53" t="inlineStr">
         <is>
-          <t>CVS Health Corporation provides health solutions in the United States</t>
+          <t>The Travelers Companies Inc through its subsidiaries provides a range of commercial and personal property and casualty insurance products and services to businesses government units associations and individuals in the United States Canada and internationally</t>
         </is>
       </c>
       <c r="J18" s="36" t="n"/>
@@ -4357,33 +4357,33 @@
       </c>
       <c r="C19" s="30" t="inlineStr">
         <is>
-          <t>BNY</t>
+          <t>CVS</t>
         </is>
       </c>
       <c r="D19" s="31" t="inlineStr">
         <is>
-          <t>The Bank of New York Mellon Corporation</t>
+          <t>CVS Health Corporation</t>
         </is>
       </c>
       <c r="E19" s="32" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Health Care</t>
         </is>
       </c>
       <c r="F19" s="32" t="inlineStr">
         <is>
-          <t>Capital Markets</t>
+          <t>Health Care Providers and Services</t>
         </is>
       </c>
       <c r="G19" s="89" t="n">
-        <v>0.33</v>
+        <v>0.339</v>
       </c>
       <c r="H19" s="91" t="n">
-        <v>96186.41</v>
+        <v>125211.85</v>
       </c>
       <c r="I19" s="54" t="inlineStr">
         <is>
-          <t>The Bank of New York Mellon Corporation provides a range of financial products and services in the United States and internationally</t>
+          <t>CVS Health Corporation provides health solutions in the United States</t>
         </is>
       </c>
       <c r="J19" s="28" t="n"/>
@@ -4414,7 +4414,7 @@
         </is>
       </c>
       <c r="G20" s="89" t="n">
-        <v>0.323</v>
+        <v>0.324</v>
       </c>
       <c r="H20" s="90" t="n">
         <v>4309578.68</v>
@@ -4433,33 +4433,33 @@
       </c>
       <c r="C21" s="30" t="inlineStr">
         <is>
-          <t>ADM</t>
+          <t>BBY</t>
         </is>
       </c>
       <c r="D21" s="31" t="inlineStr">
         <is>
-          <t>Archer-Daniels-Midland Company</t>
+          <t>Best Buy Co. Inc.</t>
         </is>
       </c>
       <c r="E21" s="32" t="inlineStr">
         <is>
-          <t>Consumer Staples</t>
+          <t>Consumer Discretionary</t>
         </is>
       </c>
       <c r="F21" s="32" t="inlineStr">
         <is>
-          <t>Food Products</t>
+          <t>Specialty Retail</t>
         </is>
       </c>
       <c r="G21" s="89" t="n">
-        <v>0.305</v>
+        <v>0.3</v>
       </c>
       <c r="H21" s="91" t="n">
-        <v>39380.19</v>
+        <v>16078.79</v>
       </c>
       <c r="I21" s="54" t="inlineStr">
         <is>
-          <t>Archer-Daniels-Midland Company provides human and animal nutrition ingredients and solutions in the United States Switzerland the Cayman Islands Brazil Mexico Canada the United Kingdom and internationally</t>
+          <t>Best Buy Co</t>
         </is>
       </c>
       <c r="J21" s="28" t="n"/>
@@ -4471,33 +4471,33 @@
       </c>
       <c r="C22" s="38" t="inlineStr">
         <is>
-          <t>DOC</t>
+          <t>UNP</t>
         </is>
       </c>
       <c r="D22" s="39" t="inlineStr">
         <is>
-          <t>Healthpeak Properties Inc.</t>
+          <t>Union Pacific Corporation</t>
         </is>
       </c>
       <c r="E22" s="40" t="inlineStr">
         <is>
-          <t>Real Estate</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="F22" s="40" t="inlineStr">
         <is>
-          <t>Health Care REITs</t>
+          <t>Ground Transportation</t>
         </is>
       </c>
       <c r="G22" s="89" t="n">
-        <v>0.305</v>
+        <v>0.298</v>
       </c>
       <c r="H22" s="90" t="n">
-        <v>14353.95</v>
+        <v>158667.48</v>
       </c>
       <c r="I22" s="53" t="inlineStr">
         <is>
-          <t>Healthpeak Properties Inc is a Standard &amp; Poor’s 500 company that owns operates and develops high-quality real estate focused on healthcare discovery and delivery in the United States</t>
+          <t>Union Pacific Corporation through its subsidiary Union Pacific Railroad Company operates in the railroad business in the United States</t>
         </is>
       </c>
       <c r="J22" s="36" t="n"/>
@@ -4509,33 +4509,33 @@
       </c>
       <c r="C23" s="30" t="inlineStr">
         <is>
-          <t>BBY</t>
+          <t>ADM</t>
         </is>
       </c>
       <c r="D23" s="31" t="inlineStr">
         <is>
-          <t>Best Buy Co. Inc.</t>
+          <t>Archer-Daniels-Midland Company</t>
         </is>
       </c>
       <c r="E23" s="32" t="inlineStr">
         <is>
-          <t>Consumer Discretionary</t>
+          <t>Consumer Staples</t>
         </is>
       </c>
       <c r="F23" s="32" t="inlineStr">
         <is>
-          <t>Specialty Retail</t>
+          <t>Food Products</t>
         </is>
       </c>
       <c r="G23" s="89" t="n">
-        <v>0.299</v>
+        <v>0.295</v>
       </c>
       <c r="H23" s="91" t="n">
-        <v>16078.79</v>
+        <v>39380.19</v>
       </c>
       <c r="I23" s="54" t="inlineStr">
         <is>
-          <t>Best Buy Co</t>
+          <t>Archer-Daniels-Midland Company provides human and animal nutrition ingredients and solutions in the United States Switzerland the Cayman Islands Brazil Mexico Canada the United Kingdom and internationally</t>
         </is>
       </c>
       <c r="J23" s="28" t="n"/>
@@ -4547,12 +4547,12 @@
       </c>
       <c r="C24" s="38" t="inlineStr">
         <is>
-          <t>UNP</t>
+          <t>GWW</t>
         </is>
       </c>
       <c r="D24" s="39" t="inlineStr">
         <is>
-          <t>Union Pacific Corporation</t>
+          <t>W.W. Grainger Inc.</t>
         </is>
       </c>
       <c r="E24" s="40" t="inlineStr">
@@ -4562,18 +4562,18 @@
       </c>
       <c r="F24" s="40" t="inlineStr">
         <is>
-          <t>Ground Transportation</t>
+          <t>Trading Companies and Distributors</t>
         </is>
       </c>
       <c r="G24" s="89" t="n">
-        <v>0.288</v>
+        <v>0.294</v>
       </c>
       <c r="H24" s="90" t="n">
-        <v>158667.48</v>
+        <v>62147.38</v>
       </c>
       <c r="I24" s="53" t="inlineStr">
         <is>
-          <t>Union Pacific Corporation through its subsidiary Union Pacific Railroad Company operates in the railroad business in the United States</t>
+          <t>W</t>
         </is>
       </c>
       <c r="J24" s="36" t="n"/>
@@ -4585,33 +4585,33 @@
       </c>
       <c r="C25" s="30" t="inlineStr">
         <is>
-          <t>GWW</t>
+          <t>DOC</t>
         </is>
       </c>
       <c r="D25" s="31" t="inlineStr">
         <is>
-          <t>W.W. Grainger Inc.</t>
+          <t>Healthpeak Properties Inc.</t>
         </is>
       </c>
       <c r="E25" s="32" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Real Estate</t>
         </is>
       </c>
       <c r="F25" s="32" t="inlineStr">
         <is>
-          <t>Trading Companies and Distributors</t>
+          <t>Health Care REITs</t>
         </is>
       </c>
       <c r="G25" s="89" t="n">
-        <v>0.285</v>
+        <v>0.29</v>
       </c>
       <c r="H25" s="91" t="n">
-        <v>62147.38</v>
+        <v>14353.95</v>
       </c>
       <c r="I25" s="54" t="inlineStr">
         <is>
-          <t>W</t>
+          <t>Healthpeak Properties Inc is a Standard &amp; Poor’s 500 company that owns operates and develops high-quality real estate focused on healthcare discovery and delivery in the United States</t>
         </is>
       </c>
       <c r="J25" s="28" t="n"/>
@@ -4623,12 +4623,12 @@
       </c>
       <c r="C26" s="38" t="inlineStr">
         <is>
-          <t>MET</t>
+          <t>NTRS</t>
         </is>
       </c>
       <c r="D26" s="39" t="inlineStr">
         <is>
-          <t>MetLife Inc.</t>
+          <t>Northern Trust Corporation</t>
         </is>
       </c>
       <c r="E26" s="40" t="inlineStr">
@@ -4638,18 +4638,18 @@
       </c>
       <c r="F26" s="40" t="inlineStr">
         <is>
-          <t>Insurance</t>
+          <t>Capital Markets</t>
         </is>
       </c>
       <c r="G26" s="89" t="n">
-        <v>0.23</v>
+        <v>0.257</v>
       </c>
       <c r="H26" s="90" t="n">
-        <v>55851.6</v>
+        <v>30713.22</v>
       </c>
       <c r="I26" s="53" t="inlineStr">
         <is>
-          <t>MetLife Inc a financial services company provides insurance annuities employee benefits and asset management services worldwide</t>
+          <t>Northern Trust Corporation a financial holding company provides wealth management asset servicing asset management and banking solutions for corporations institutions families and individuals</t>
         </is>
       </c>
       <c r="J26" s="36" t="n"/>
@@ -4661,12 +4661,12 @@
       </c>
       <c r="C27" s="30" t="inlineStr">
         <is>
-          <t>XYZ</t>
+          <t>MET</t>
         </is>
       </c>
       <c r="D27" s="31" t="inlineStr">
         <is>
-          <t>Block Inc.</t>
+          <t>MetLife Inc.</t>
         </is>
       </c>
       <c r="E27" s="32" t="inlineStr">
@@ -4676,18 +4676,18 @@
       </c>
       <c r="F27" s="32" t="inlineStr">
         <is>
-          <t>Financial Services</t>
+          <t>Insurance</t>
         </is>
       </c>
       <c r="G27" s="89" t="n">
-        <v>0.23</v>
+        <v>0.248</v>
       </c>
       <c r="H27" s="91" t="n">
-        <v>40474.89</v>
+        <v>55851.6</v>
       </c>
       <c r="I27" s="54" t="inlineStr">
         <is>
-          <t>Block Inc together with its subsidiaries builds ecosystems focused on commerce and financial products and services in the United States and internationally</t>
+          <t>MetLife Inc a financial services company provides insurance annuities employee benefits and asset management services worldwide</t>
         </is>
       </c>
       <c r="J27" s="28" t="n"/>
@@ -4699,12 +4699,12 @@
       </c>
       <c r="C28" s="38" t="inlineStr">
         <is>
-          <t>NTRS</t>
+          <t>PFG</t>
         </is>
       </c>
       <c r="D28" s="39" t="inlineStr">
         <is>
-          <t>Northern Trust Corporation</t>
+          <t>Principal Financial Group Inc.</t>
         </is>
       </c>
       <c r="E28" s="40" t="inlineStr">
@@ -4714,18 +4714,18 @@
       </c>
       <c r="F28" s="40" t="inlineStr">
         <is>
-          <t>Capital Markets</t>
+          <t>Insurance</t>
         </is>
       </c>
       <c r="G28" s="89" t="n">
         <v>0.219</v>
       </c>
       <c r="H28" s="90" t="n">
-        <v>30713.22</v>
+        <v>23624.19</v>
       </c>
       <c r="I28" s="53" t="inlineStr">
         <is>
-          <t>Northern Trust Corporation a financial holding company provides wealth management asset servicing asset management and banking solutions for corporations institutions families and individuals</t>
+          <t>Principal Financial Group Inc provides retirement asset management and insurance products and services to businesses individuals and institutional clients worldwide</t>
         </is>
       </c>
       <c r="J28" s="36" t="n"/>
@@ -4737,12 +4737,12 @@
       </c>
       <c r="C29" s="30" t="inlineStr">
         <is>
-          <t>PFG</t>
+          <t>XYZ</t>
         </is>
       </c>
       <c r="D29" s="31" t="inlineStr">
         <is>
-          <t>Principal Financial Group Inc.</t>
+          <t>Block Inc.</t>
         </is>
       </c>
       <c r="E29" s="32" t="inlineStr">
@@ -4752,18 +4752,18 @@
       </c>
       <c r="F29" s="32" t="inlineStr">
         <is>
-          <t>Insurance</t>
+          <t>Financial Services</t>
         </is>
       </c>
       <c r="G29" s="89" t="n">
-        <v>0.209</v>
+        <v>0.202</v>
       </c>
       <c r="H29" s="91" t="n">
-        <v>23624.19</v>
+        <v>40474.89</v>
       </c>
       <c r="I29" s="54" t="inlineStr">
         <is>
-          <t>Principal Financial Group Inc provides retirement asset management and insurance products and services to businesses individuals and institutional clients worldwide</t>
+          <t>Block Inc together with its subsidiaries builds ecosystems focused on commerce and financial products and services in the United States and internationally</t>
         </is>
       </c>
       <c r="J29" s="28" t="n"/>
@@ -4775,12 +4775,12 @@
       </c>
       <c r="C30" s="38" t="inlineStr">
         <is>
-          <t>EG</t>
+          <t>BAC</t>
         </is>
       </c>
       <c r="D30" s="39" t="inlineStr">
         <is>
-          <t>Everest Group Ltd.</t>
+          <t>Bank of America Corporation</t>
         </is>
       </c>
       <c r="E30" s="40" t="inlineStr">
@@ -4790,18 +4790,18 @@
       </c>
       <c r="F30" s="40" t="inlineStr">
         <is>
-          <t>Insurance</t>
+          <t>Banks</t>
         </is>
       </c>
       <c r="G30" s="89" t="n">
-        <v>0.185</v>
+        <v>0.197</v>
       </c>
       <c r="H30" s="90" t="n">
-        <v>13320.91</v>
+        <v>388502.86</v>
       </c>
       <c r="I30" s="53" t="inlineStr">
         <is>
-          <t>Everest Group Ltd together with subsidiaries provides reinsurance and insurance products in the United States Europe and internationally</t>
+          <t>Bank of America Corporation through its subsidiaries provides various financial products and services for individual consumers small and middle-market businesses institutional investors large corporations and governments worldwide</t>
         </is>
       </c>
       <c r="J30" s="36" t="n"/>
@@ -4813,12 +4813,12 @@
       </c>
       <c r="C31" s="30" t="inlineStr">
         <is>
-          <t>BAC</t>
+          <t>GS</t>
         </is>
       </c>
       <c r="D31" s="31" t="inlineStr">
         <is>
-          <t>Bank of America Corporation</t>
+          <t>The Goldman Sachs Group Inc.</t>
         </is>
       </c>
       <c r="E31" s="32" t="inlineStr">
@@ -4828,18 +4828,18 @@
       </c>
       <c r="F31" s="32" t="inlineStr">
         <is>
-          <t>Banks</t>
+          <t>Capital Markets</t>
         </is>
       </c>
       <c r="G31" s="89" t="n">
-        <v>0.181</v>
+        <v>0.19</v>
       </c>
       <c r="H31" s="91" t="n">
-        <v>388502.86</v>
+        <v>308648.81</v>
       </c>
       <c r="I31" s="54" t="inlineStr">
         <is>
-          <t>Bank of America Corporation through its subsidiaries provides various financial products and services for individual consumers small and middle-market businesses institutional investors large corporations and governments worldwide</t>
+          <t>The Goldman Sachs Group Inc a financial institution provides a range of financial services for corporations financial institutions governments and individuals in the Americas Europe the Middle East Africa and Asia</t>
         </is>
       </c>
       <c r="J31" s="28" t="n"/>
@@ -4851,33 +4851,33 @@
       </c>
       <c r="C32" s="38" t="inlineStr">
         <is>
-          <t>MNST</t>
+          <t>EG</t>
         </is>
       </c>
       <c r="D32" s="39" t="inlineStr">
         <is>
-          <t>Monster Beverage Corporation</t>
+          <t>Everest Group Ltd.</t>
         </is>
       </c>
       <c r="E32" s="40" t="inlineStr">
         <is>
-          <t>Consumer Staples</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="F32" s="40" t="inlineStr">
         <is>
-          <t>Beverages</t>
+          <t>Insurance</t>
         </is>
       </c>
       <c r="G32" s="89" t="n">
-        <v>0.176</v>
+        <v>0.182</v>
       </c>
       <c r="H32" s="90" t="n">
-        <v>89144.46000000001</v>
+        <v>13320.91</v>
       </c>
       <c r="I32" s="53" t="inlineStr">
         <is>
-          <t>Monster Beverage Corporation through its subsidiaries engages in development marketing sale and distribution of energy drink beverages and concentrates in the United States and internationally</t>
+          <t>Everest Group Ltd together with subsidiaries provides reinsurance and insurance products in the United States Europe and internationally</t>
         </is>
       </c>
       <c r="J32" s="36" t="n"/>
@@ -4889,33 +4889,33 @@
       </c>
       <c r="C33" s="30" t="inlineStr">
         <is>
-          <t>FITB</t>
+          <t>MNST</t>
         </is>
       </c>
       <c r="D33" s="31" t="inlineStr">
         <is>
-          <t>Fifth Third Bancorp</t>
+          <t>Monster Beverage Corporation</t>
         </is>
       </c>
       <c r="E33" s="32" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Consumer Staples</t>
         </is>
       </c>
       <c r="F33" s="32" t="inlineStr">
         <is>
-          <t>Banks</t>
+          <t>Beverages</t>
         </is>
       </c>
       <c r="G33" s="89" t="n">
-        <v>0.148</v>
+        <v>0.159</v>
       </c>
       <c r="H33" s="91" t="n">
-        <v>47955.66</v>
+        <v>89144.46000000001</v>
       </c>
       <c r="I33" s="54" t="inlineStr">
         <is>
-          <t>Fifth Third Bancorp operates as the bank holding company for Fifth Third Bank National Association that provides a range of financial products and services in the United States</t>
+          <t>Monster Beverage Corporation through its subsidiaries engages in development marketing sale and distribution of energy drink beverages and concentrates in the United States and internationally</t>
         </is>
       </c>
       <c r="J33" s="28" t="n"/>
@@ -4927,12 +4927,12 @@
       </c>
       <c r="C34" s="38" t="inlineStr">
         <is>
-          <t>GS</t>
+          <t>CFG</t>
         </is>
       </c>
       <c r="D34" s="39" t="inlineStr">
         <is>
-          <t>The Goldman Sachs Group Inc.</t>
+          <t>Citizens Financial Group Inc.</t>
         </is>
       </c>
       <c r="E34" s="40" t="inlineStr">
@@ -4942,18 +4942,18 @@
       </c>
       <c r="F34" s="40" t="inlineStr">
         <is>
-          <t>Capital Markets</t>
+          <t>Banks</t>
         </is>
       </c>
       <c r="G34" s="89" t="n">
-        <v>0.145</v>
+        <v>0.158</v>
       </c>
       <c r="H34" s="90" t="n">
-        <v>308648.81</v>
+        <v>27585.86</v>
       </c>
       <c r="I34" s="53" t="inlineStr">
         <is>
-          <t>The Goldman Sachs Group Inc a financial institution provides a range of financial services for corporations financial institutions governments and individuals in the Americas Europe the Middle East Africa and Asia</t>
+          <t>Citizens Financial Group Inc operates as the bank holding company that provides retail and commercial banking products and services to individuals small businesses middle-market companies large corporations and institutions in the United States</t>
         </is>
       </c>
       <c r="J34" s="36" t="n"/>
@@ -4965,12 +4965,12 @@
       </c>
       <c r="C35" s="30" t="inlineStr">
         <is>
-          <t>CFG</t>
+          <t>FITB</t>
         </is>
       </c>
       <c r="D35" s="31" t="inlineStr">
         <is>
-          <t>Citizens Financial Group Inc.</t>
+          <t>Fifth Third Bancorp</t>
         </is>
       </c>
       <c r="E35" s="32" t="inlineStr">
@@ -4984,14 +4984,14 @@
         </is>
       </c>
       <c r="G35" s="89" t="n">
-        <v>0.131</v>
+        <v>0.152</v>
       </c>
       <c r="H35" s="91" t="n">
-        <v>27585.86</v>
+        <v>47955.66</v>
       </c>
       <c r="I35" s="54" t="inlineStr">
         <is>
-          <t>Citizens Financial Group Inc operates as the bank holding company that provides retail and commercial banking products and services to individuals small businesses middle-market companies large corporations and institutions in the United States</t>
+          <t>Fifth Third Bancorp operates as the bank holding company for Fifth Third Bank National Association that provides a range of financial products and services in the United States</t>
         </is>
       </c>
       <c r="J35" s="28" t="n"/>
@@ -5022,7 +5022,7 @@
         </is>
       </c>
       <c r="G36" s="89" t="n">
-        <v>0.12</v>
+        <v>0.13</v>
       </c>
       <c r="H36" s="90" t="n">
         <v>21453.67</v>
@@ -5060,7 +5060,7 @@
         </is>
       </c>
       <c r="G37" s="89" t="n">
-        <v>0.119</v>
+        <v>0.129</v>
       </c>
       <c r="H37" s="91" t="n">
         <v>36717.82</v>
@@ -5136,7 +5136,7 @@
         </is>
       </c>
       <c r="G39" s="89" t="n">
-        <v>0.07199999999999999</v>
+        <v>0.078</v>
       </c>
       <c r="H39" s="91" t="n">
         <v>36258.68</v>
@@ -5174,7 +5174,7 @@
         </is>
       </c>
       <c r="G40" s="89" t="n">
-        <v>0.067</v>
+        <v>0.068</v>
       </c>
       <c r="H40" s="90" t="n">
         <v>11826.25</v>

--- a/outputs/benchmark-beaters/Benchmark_Beaters_2026-07-21.xlsx
+++ b/outputs/benchmark-beaters/Benchmark_Beaters_2026-07-21.xlsx
@@ -17,9 +17,9 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Koyfin - US" sheetId="9" state="visible" r:id="rId9"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm.Print_Area" localSheetId="2">'Cdn Hardcoded'!$A$1:$J$49</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="2">'Cdn Hardcoded'!$A$1:$J$60</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="3">'Cdn'!$A$1:$J$48</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="6">'US Hardcoded'!$A$1:$J$49</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="6">'US Hardcoded'!$A$1:$J$60</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="7">'US'!$A$1:$J$54</definedName>
   </definedNames>
   <calcPr calcId="191029" fullCalcOnLoad="1"/>
@@ -1260,7 +1260,7 @@
     <row r="2" ht="15.6" customHeight="1">
       <c r="A2" s="22" t="n"/>
       <c r="B2" s="21" t="n">
-        <v>46224.81394085352</v>
+        <v>46224.8272040635</v>
       </c>
       <c r="C2" s="22" t="n"/>
     </row>
@@ -1282,7 +1282,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:J49"/>
+  <dimension ref="A1:J60"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="1.21875" customWidth="1" style="11" min="1" max="1"/>
@@ -1454,7 +1454,7 @@
         </is>
       </c>
       <c r="G8" s="89" t="n">
-        <v>1.632</v>
+        <v>1.631</v>
       </c>
       <c r="H8" s="90" t="n">
         <v>2358.79</v>
@@ -1530,7 +1530,7 @@
         </is>
       </c>
       <c r="G10" s="89" t="n">
-        <v>1.157</v>
+        <v>1.153</v>
       </c>
       <c r="H10" s="90" t="n">
         <v>284.57</v>
@@ -1568,7 +1568,7 @@
         </is>
       </c>
       <c r="G11" s="89" t="n">
-        <v>0.725</v>
+        <v>0.732</v>
       </c>
       <c r="H11" s="91" t="n">
         <v>2258.51</v>
@@ -1606,7 +1606,7 @@
         </is>
       </c>
       <c r="G12" s="89" t="n">
-        <v>0.5610000000000001</v>
+        <v>0.5679999999999999</v>
       </c>
       <c r="H12" s="90" t="n">
         <v>1565.38</v>
@@ -1644,7 +1644,7 @@
         </is>
       </c>
       <c r="G13" s="89" t="n">
-        <v>0.547</v>
+        <v>0.544</v>
       </c>
       <c r="H13" s="91" t="n">
         <v>1892.54</v>
@@ -1682,7 +1682,7 @@
         </is>
       </c>
       <c r="G14" s="89" t="n">
-        <v>0.451</v>
+        <v>0.456</v>
       </c>
       <c r="H14" s="90" t="n">
         <v>53011.04</v>
@@ -1720,7 +1720,7 @@
         </is>
       </c>
       <c r="G15" s="89" t="n">
-        <v>0.437</v>
+        <v>0.443</v>
       </c>
       <c r="H15" s="91" t="n">
         <v>2385.76</v>
@@ -1734,36 +1734,36 @@
     </row>
     <row r="16" ht="20.4" customHeight="1">
       <c r="A16" s="28" t="n"/>
-      <c r="B16" s="49" t="n">
+      <c r="B16" s="48" t="n">
         <v>9</v>
       </c>
-      <c r="C16" s="30" t="inlineStr">
+      <c r="C16" s="38" t="inlineStr">
         <is>
           <t>KBL</t>
         </is>
       </c>
-      <c r="D16" s="31" t="inlineStr">
+      <c r="D16" s="39" t="inlineStr">
         <is>
           <t>K-Bro Linen Inc.</t>
         </is>
       </c>
-      <c r="E16" s="32" t="inlineStr">
+      <c r="E16" s="40" t="inlineStr">
         <is>
           <t>Industrials</t>
         </is>
       </c>
-      <c r="F16" s="32" t="inlineStr">
+      <c r="F16" s="40" t="inlineStr">
         <is>
           <t>Commercial Services and Supplies</t>
         </is>
       </c>
       <c r="G16" s="89" t="n">
-        <v>0.377</v>
-      </c>
-      <c r="H16" s="91" t="n">
+        <v>0.376</v>
+      </c>
+      <c r="H16" s="90" t="n">
         <v>390.27</v>
       </c>
-      <c r="I16" s="54" t="inlineStr">
+      <c r="I16" s="53" t="inlineStr">
         <is>
           <t>K-Bro Linen Inc together with its subsidiaries provides laundry and linen services to healthcare organizations hotels and other commercial accounts in Canada and the United Kingdom</t>
         </is>
@@ -1772,36 +1772,36 @@
     </row>
     <row r="17" ht="40.8" customHeight="1">
       <c r="A17" s="36" t="n"/>
-      <c r="B17" s="48" t="n">
+      <c r="B17" s="49" t="n">
         <v>10</v>
       </c>
-      <c r="C17" s="38" t="inlineStr">
+      <c r="C17" s="30" t="inlineStr">
         <is>
           <t>BMO</t>
         </is>
       </c>
-      <c r="D17" s="39" t="inlineStr">
+      <c r="D17" s="31" t="inlineStr">
         <is>
           <t>Bank of Montreal</t>
         </is>
       </c>
-      <c r="E17" s="40" t="inlineStr">
+      <c r="E17" s="32" t="inlineStr">
         <is>
           <t>Financials</t>
         </is>
       </c>
-      <c r="F17" s="40" t="inlineStr">
+      <c r="F17" s="32" t="inlineStr">
         <is>
           <t>Banks</t>
         </is>
       </c>
       <c r="G17" s="89" t="n">
-        <v>0.357</v>
-      </c>
-      <c r="H17" s="90" t="n">
+        <v>0.36</v>
+      </c>
+      <c r="H17" s="91" t="n">
         <v>116001.23</v>
       </c>
-      <c r="I17" s="53" t="inlineStr">
+      <c r="I17" s="54" t="inlineStr">
         <is>
           <t>Bank of Montreal engages in the provision of diversified financial services primarily in North America</t>
         </is>
@@ -1810,36 +1810,36 @@
     </row>
     <row r="18" ht="24" customHeight="1">
       <c r="A18" s="28" t="n"/>
-      <c r="B18" s="49" t="n">
+      <c r="B18" s="48" t="n">
         <v>11</v>
       </c>
-      <c r="C18" s="30" t="inlineStr">
+      <c r="C18" s="38" t="inlineStr">
         <is>
           <t>ARG</t>
         </is>
       </c>
-      <c r="D18" s="31" t="inlineStr">
+      <c r="D18" s="39" t="inlineStr">
         <is>
           <t>Amerigo Resources Ltd.</t>
         </is>
       </c>
-      <c r="E18" s="32" t="inlineStr">
+      <c r="E18" s="40" t="inlineStr">
         <is>
           <t>Materials</t>
         </is>
       </c>
-      <c r="F18" s="32" t="inlineStr">
+      <c r="F18" s="40" t="inlineStr">
         <is>
           <t>Metals and Mining</t>
         </is>
       </c>
       <c r="G18" s="89" t="n">
-        <v>0.341</v>
-      </c>
-      <c r="H18" s="91" t="n">
+        <v>0.34</v>
+      </c>
+      <c r="H18" s="90" t="n">
         <v>681.6799999999999</v>
       </c>
-      <c r="I18" s="54" t="inlineStr">
+      <c r="I18" s="53" t="inlineStr">
         <is>
           <t>Amerigo Resources Ltd through its subsidiary Minera Valle Central S</t>
         </is>
@@ -1848,36 +1848,36 @@
     </row>
     <row r="19" ht="30.6" customHeight="1">
       <c r="A19" s="36" t="n"/>
-      <c r="B19" s="48" t="n">
+      <c r="B19" s="49" t="n">
         <v>12</v>
       </c>
-      <c r="C19" s="38" t="inlineStr">
+      <c r="C19" s="30" t="inlineStr">
         <is>
           <t>POW</t>
         </is>
       </c>
-      <c r="D19" s="39" t="inlineStr">
+      <c r="D19" s="31" t="inlineStr">
         <is>
           <t>Power Corporation of Canada</t>
         </is>
       </c>
-      <c r="E19" s="40" t="inlineStr">
+      <c r="E19" s="32" t="inlineStr">
         <is>
           <t>Financials</t>
         </is>
       </c>
-      <c r="F19" s="40" t="inlineStr">
+      <c r="F19" s="32" t="inlineStr">
         <is>
           <t>Insurance</t>
         </is>
       </c>
       <c r="G19" s="89" t="n">
-        <v>0.337</v>
-      </c>
-      <c r="H19" s="90" t="n">
+        <v>0.339</v>
+      </c>
+      <c r="H19" s="91" t="n">
         <v>38174.66</v>
       </c>
-      <c r="I19" s="53" t="inlineStr">
+      <c r="I19" s="54" t="inlineStr">
         <is>
           <t>Power Corporation of Canada an international management and holding company provides financial services in North America Europe and Asia</t>
         </is>
@@ -1886,36 +1886,36 @@
     </row>
     <row r="20" ht="30.6" customHeight="1">
       <c r="A20" s="28" t="n"/>
-      <c r="B20" s="49" t="n">
+      <c r="B20" s="48" t="n">
         <v>13</v>
       </c>
-      <c r="C20" s="30" t="inlineStr">
+      <c r="C20" s="38" t="inlineStr">
         <is>
           <t>SLF</t>
         </is>
       </c>
-      <c r="D20" s="31" t="inlineStr">
+      <c r="D20" s="39" t="inlineStr">
         <is>
           <t>Sun Life Financial Inc.</t>
         </is>
       </c>
-      <c r="E20" s="32" t="inlineStr">
+      <c r="E20" s="40" t="inlineStr">
         <is>
           <t>Financials</t>
         </is>
       </c>
-      <c r="F20" s="32" t="inlineStr">
+      <c r="F20" s="40" t="inlineStr">
         <is>
           <t>Insurance</t>
         </is>
       </c>
       <c r="G20" s="89" t="n">
-        <v>0.333</v>
-      </c>
-      <c r="H20" s="91" t="n">
+        <v>0.334</v>
+      </c>
+      <c r="H20" s="90" t="n">
         <v>41467.31</v>
       </c>
-      <c r="I20" s="54" t="inlineStr">
+      <c r="I20" s="53" t="inlineStr">
         <is>
           <t>Sun Life Financial Inc a financial services company provides asset management wealth insurance and health solutions to individual and institutional customers in Canada the United States the United Kingdom Ireland Hong Kong the Philippines Japan Indonesia India China Australia Singapore Vietnam Malaysia and Bermuda</t>
         </is>
@@ -1924,36 +1924,36 @@
     </row>
     <row r="21" ht="30.6" customHeight="1">
       <c r="A21" s="36" t="n"/>
-      <c r="B21" s="48" t="n">
+      <c r="B21" s="49" t="n">
         <v>14</v>
       </c>
-      <c r="C21" s="38" t="inlineStr">
+      <c r="C21" s="30" t="inlineStr">
         <is>
           <t>CNR</t>
         </is>
       </c>
-      <c r="D21" s="39" t="inlineStr">
+      <c r="D21" s="31" t="inlineStr">
         <is>
           <t>Canadian National Railway Company</t>
         </is>
       </c>
-      <c r="E21" s="40" t="inlineStr">
+      <c r="E21" s="32" t="inlineStr">
         <is>
           <t>Industrials</t>
         </is>
       </c>
-      <c r="F21" s="40" t="inlineStr">
+      <c r="F21" s="32" t="inlineStr">
         <is>
           <t>Ground Transportation</t>
         </is>
       </c>
       <c r="G21" s="89" t="n">
-        <v>0.327</v>
-      </c>
-      <c r="H21" s="90" t="n">
+        <v>0.329</v>
+      </c>
+      <c r="H21" s="91" t="n">
         <v>72839.50999999999</v>
       </c>
-      <c r="I21" s="53" t="inlineStr">
+      <c r="I21" s="54" t="inlineStr">
         <is>
           <t>Canadian National Railway Company together with its subsidiaries engages in the rail intermodal trucking and related transportation businesses in Canada and the United States</t>
         </is>
@@ -1962,38 +1962,38 @@
     </row>
     <row r="22" ht="24" customHeight="1">
       <c r="A22" s="28" t="n"/>
-      <c r="B22" s="49" t="n">
+      <c r="B22" s="48" t="n">
         <v>15</v>
       </c>
-      <c r="C22" s="30" t="inlineStr">
-        <is>
-          <t>TD</t>
-        </is>
-      </c>
-      <c r="D22" s="31" t="inlineStr">
-        <is>
-          <t>The Toronto-Dominion Bank</t>
-        </is>
-      </c>
-      <c r="E22" s="32" t="inlineStr">
+      <c r="C22" s="38" t="inlineStr">
+        <is>
+          <t>CM</t>
+        </is>
+      </c>
+      <c r="D22" s="39" t="inlineStr">
+        <is>
+          <t>Canadian Imperial Bank of Commerce</t>
+        </is>
+      </c>
+      <c r="E22" s="40" t="inlineStr">
         <is>
           <t>Financials</t>
         </is>
       </c>
-      <c r="F22" s="32" t="inlineStr">
+      <c r="F22" s="40" t="inlineStr">
         <is>
           <t>Banks</t>
         </is>
       </c>
       <c r="G22" s="89" t="n">
-        <v>0.321</v>
-      </c>
-      <c r="H22" s="91" t="n">
-        <v>189567.97</v>
-      </c>
-      <c r="I22" s="54" t="inlineStr">
-        <is>
-          <t>The Toronto-Dominion Bank together with its subsidiaries provides various financial products and services in Canada the United States and internationally</t>
+        <v>0.324</v>
+      </c>
+      <c r="H22" s="90" t="n">
+        <v>101497.85</v>
+      </c>
+      <c r="I22" s="53" t="inlineStr">
+        <is>
+          <t>Canadian Imperial Bank of Commerce a diversified financial institution provides various financial products and services to personal business public sector and institutional clients in Canada the United States and internationally</t>
         </is>
       </c>
       <c r="J22" s="28" t="n"/>
@@ -2005,12 +2005,12 @@
       </c>
       <c r="C23" s="30" t="inlineStr">
         <is>
-          <t>CM</t>
+          <t>TD</t>
         </is>
       </c>
       <c r="D23" s="31" t="inlineStr">
         <is>
-          <t>Canadian Imperial Bank of Commerce</t>
+          <t>The Toronto-Dominion Bank</t>
         </is>
       </c>
       <c r="E23" s="32" t="inlineStr">
@@ -2024,14 +2024,14 @@
         </is>
       </c>
       <c r="G23" s="89" t="n">
-        <v>0.32</v>
+        <v>0.324</v>
       </c>
       <c r="H23" s="91" t="n">
-        <v>101497.85</v>
+        <v>189567.97</v>
       </c>
       <c r="I23" s="54" t="inlineStr">
         <is>
-          <t>Canadian Imperial Bank of Commerce a diversified financial institution provides various financial products and services to personal business public sector and institutional clients in Canada the United States and internationally</t>
+          <t>The Toronto-Dominion Bank together with its subsidiaries provides various financial products and services in Canada the United States and internationally</t>
         </is>
       </c>
       <c r="J23" s="28" t="n"/>
@@ -2062,7 +2062,7 @@
         </is>
       </c>
       <c r="G24" s="89" t="n">
-        <v>0.314</v>
+        <v>0.317</v>
       </c>
       <c r="H24" s="90" t="n">
         <v>3018.47</v>
@@ -2138,7 +2138,7 @@
         </is>
       </c>
       <c r="G26" s="89" t="n">
-        <v>0.305</v>
+        <v>0.309</v>
       </c>
       <c r="H26" s="90" t="n">
         <v>13303.41</v>
@@ -2152,112 +2152,112 @@
     </row>
     <row r="27" ht="24" customHeight="1">
       <c r="A27" s="36" t="n"/>
-      <c r="B27" s="48" t="n">
+      <c r="B27" s="49" t="n">
         <v>20</v>
       </c>
-      <c r="C27" s="38" t="inlineStr">
-        <is>
-          <t>CP</t>
-        </is>
-      </c>
-      <c r="D27" s="39" t="inlineStr">
-        <is>
-          <t>Canadian Pacific Kansas City Limited</t>
-        </is>
-      </c>
-      <c r="E27" s="40" t="inlineStr">
-        <is>
-          <t>Industrials</t>
-        </is>
-      </c>
-      <c r="F27" s="40" t="inlineStr">
-        <is>
-          <t>Ground Transportation</t>
+      <c r="C27" s="30" t="inlineStr">
+        <is>
+          <t>RY</t>
+        </is>
+      </c>
+      <c r="D27" s="31" t="inlineStr">
+        <is>
+          <t>Royal Bank of Canada</t>
+        </is>
+      </c>
+      <c r="E27" s="32" t="inlineStr">
+        <is>
+          <t>Financials</t>
+        </is>
+      </c>
+      <c r="F27" s="32" t="inlineStr">
+        <is>
+          <t>Banks</t>
         </is>
       </c>
       <c r="G27" s="89" t="n">
         <v>0.298</v>
       </c>
-      <c r="H27" s="90" t="n">
-        <v>79823.21000000001</v>
-      </c>
-      <c r="I27" s="53" t="inlineStr">
-        <is>
-          <t>Canadian Pacific Kansas City Limited together with its subsidiaries owns and operates a transcontinental freight railway in Canada the United States and Mexico</t>
+      <c r="H27" s="91" t="n">
+        <v>275998.42</v>
+      </c>
+      <c r="I27" s="54" t="inlineStr">
+        <is>
+          <t>Royal Bank of Canada operates as a diversified financial service company worldwide</t>
         </is>
       </c>
       <c r="J27" s="36" t="n"/>
     </row>
     <row r="28" ht="20.4" customHeight="1">
       <c r="A28" s="28" t="n"/>
-      <c r="B28" s="49" t="n">
+      <c r="B28" s="48" t="n">
         <v>21</v>
       </c>
-      <c r="C28" s="30" t="inlineStr">
-        <is>
-          <t>RY</t>
-        </is>
-      </c>
-      <c r="D28" s="31" t="inlineStr">
-        <is>
-          <t>Royal Bank of Canada</t>
-        </is>
-      </c>
-      <c r="E28" s="32" t="inlineStr">
-        <is>
-          <t>Financials</t>
-        </is>
-      </c>
-      <c r="F28" s="32" t="inlineStr">
-        <is>
-          <t>Banks</t>
+      <c r="C28" s="38" t="inlineStr">
+        <is>
+          <t>CP</t>
+        </is>
+      </c>
+      <c r="D28" s="39" t="inlineStr">
+        <is>
+          <t>Canadian Pacific Kansas City Limited</t>
+        </is>
+      </c>
+      <c r="E28" s="40" t="inlineStr">
+        <is>
+          <t>Industrials</t>
+        </is>
+      </c>
+      <c r="F28" s="40" t="inlineStr">
+        <is>
+          <t>Ground Transportation</t>
         </is>
       </c>
       <c r="G28" s="89" t="n">
-        <v>0.295</v>
-      </c>
-      <c r="H28" s="91" t="n">
-        <v>275998.42</v>
-      </c>
-      <c r="I28" s="54" t="inlineStr">
-        <is>
-          <t>Royal Bank of Canada operates as a diversified financial service company worldwide</t>
+        <v>0.296</v>
+      </c>
+      <c r="H28" s="90" t="n">
+        <v>79823.21000000001</v>
+      </c>
+      <c r="I28" s="53" t="inlineStr">
+        <is>
+          <t>Canadian Pacific Kansas City Limited together with its subsidiaries owns and operates a transcontinental freight railway in Canada the United States and Mexico</t>
         </is>
       </c>
       <c r="J28" s="28" t="n"/>
     </row>
     <row r="29" ht="24" customHeight="1">
       <c r="A29" s="36" t="n"/>
-      <c r="B29" s="48" t="n">
+      <c r="B29" s="49" t="n">
         <v>22</v>
       </c>
-      <c r="C29" s="38" t="inlineStr">
+      <c r="C29" s="30" t="inlineStr">
         <is>
           <t>CF</t>
         </is>
       </c>
-      <c r="D29" s="39" t="inlineStr">
+      <c r="D29" s="31" t="inlineStr">
         <is>
           <t>Canaccord Genuity Group Inc.</t>
         </is>
       </c>
-      <c r="E29" s="40" t="inlineStr">
+      <c r="E29" s="32" t="inlineStr">
         <is>
           <t>Financials</t>
         </is>
       </c>
-      <c r="F29" s="40" t="inlineStr">
+      <c r="F29" s="32" t="inlineStr">
         <is>
           <t>Capital Markets</t>
         </is>
       </c>
       <c r="G29" s="89" t="n">
-        <v>0.269</v>
-      </c>
-      <c r="H29" s="90" t="n">
+        <v>0.266</v>
+      </c>
+      <c r="H29" s="91" t="n">
         <v>976.67</v>
       </c>
-      <c r="I29" s="53" t="inlineStr">
+      <c r="I29" s="54" t="inlineStr">
         <is>
           <t>Canaccord Genuity Group Inc operates as a full-service investment dealer in Canada the United States the United Kingdom Europe Crown Dependencies and Australia</t>
         </is>
@@ -2290,7 +2290,7 @@
         </is>
       </c>
       <c r="G30" s="89" t="n">
-        <v>0.264</v>
+        <v>0.265</v>
       </c>
       <c r="H30" s="90" t="n">
         <v>10045.65</v>
@@ -2328,7 +2328,7 @@
         </is>
       </c>
       <c r="G31" s="89" t="n">
-        <v>0.252</v>
+        <v>0.257</v>
       </c>
       <c r="H31" s="91" t="n">
         <v>2215.94</v>
@@ -2347,33 +2347,33 @@
       </c>
       <c r="C32" s="38" t="inlineStr">
         <is>
-          <t>DXT</t>
+          <t>IAG</t>
         </is>
       </c>
       <c r="D32" s="39" t="inlineStr">
         <is>
-          <t>Dexterra Group Inc.</t>
+          <t>iA Financial Corporation Inc.</t>
         </is>
       </c>
       <c r="E32" s="40" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="F32" s="40" t="inlineStr">
         <is>
-          <t>Commercial Services and Supplies</t>
+          <t>Insurance</t>
         </is>
       </c>
       <c r="G32" s="89" t="n">
-        <v>0.234</v>
+        <v>0.237</v>
       </c>
       <c r="H32" s="90" t="n">
-        <v>576.85</v>
+        <v>11282.66</v>
       </c>
       <c r="I32" s="53" t="inlineStr">
         <is>
-          <t>Dexterra Group Inc engages in the provision of support services for the creation management and operation of infrastructure in Canada</t>
+          <t>iA Financial Corporation Inc provides insurance and wealth management services for individual and group basis in Canada and the United States</t>
         </is>
       </c>
       <c r="J32" s="36" t="n"/>
@@ -2385,33 +2385,33 @@
       </c>
       <c r="C33" s="30" t="inlineStr">
         <is>
-          <t>IAG</t>
+          <t>DXT</t>
         </is>
       </c>
       <c r="D33" s="31" t="inlineStr">
         <is>
-          <t>iA Financial Corporation Inc.</t>
+          <t>Dexterra Group Inc.</t>
         </is>
       </c>
       <c r="E33" s="32" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="F33" s="32" t="inlineStr">
         <is>
-          <t>Insurance</t>
+          <t>Commercial Services and Supplies</t>
         </is>
       </c>
       <c r="G33" s="89" t="n">
-        <v>0.234</v>
+        <v>0.236</v>
       </c>
       <c r="H33" s="91" t="n">
-        <v>11282.66</v>
+        <v>576.85</v>
       </c>
       <c r="I33" s="54" t="inlineStr">
         <is>
-          <t>iA Financial Corporation Inc provides insurance and wealth management services for individual and group basis in Canada and the United States</t>
+          <t>Dexterra Group Inc engages in the provision of support services for the creation management and operation of infrastructure in Canada</t>
         </is>
       </c>
       <c r="J33" s="28" t="n"/>
@@ -2442,7 +2442,7 @@
         </is>
       </c>
       <c r="G34" s="89" t="n">
-        <v>0.223</v>
+        <v>0.227</v>
       </c>
       <c r="H34" s="90" t="n">
         <v>100391.39</v>
@@ -2480,7 +2480,7 @@
         </is>
       </c>
       <c r="G35" s="89" t="n">
-        <v>0.217</v>
+        <v>0.219</v>
       </c>
       <c r="H35" s="91" t="n">
         <v>927.72</v>
@@ -2556,7 +2556,7 @@
         </is>
       </c>
       <c r="G37" s="89" t="n">
-        <v>0.191</v>
+        <v>0.201</v>
       </c>
       <c r="H37" s="91" t="n">
         <v>501.72</v>
@@ -2594,7 +2594,7 @@
         </is>
       </c>
       <c r="G38" s="89" t="n">
-        <v>0.178</v>
+        <v>0.174</v>
       </c>
       <c r="H38" s="90" t="n">
         <v>1330.28</v>
@@ -2632,7 +2632,7 @@
         </is>
       </c>
       <c r="G39" s="89" t="n">
-        <v>0.14</v>
+        <v>0.144</v>
       </c>
       <c r="H39" s="91" t="n">
         <v>676.4400000000001</v>
@@ -2670,7 +2670,7 @@
         </is>
       </c>
       <c r="G40" s="89" t="n">
-        <v>0.076</v>
+        <v>0.079</v>
       </c>
       <c r="H40" s="90" t="n">
         <v>6226.62</v>
@@ -2684,170 +2684,228 @@
     </row>
     <row r="41" ht="15.6" customHeight="1" thickBot="1">
       <c r="A41" s="68" t="n"/>
-      <c r="B41" s="69" t="n">
-        <v>34</v>
-      </c>
-      <c r="C41" s="70" t="inlineStr">
-        <is>
-          <t>ASCU</t>
-        </is>
-      </c>
-      <c r="D41" s="71" t="inlineStr">
-        <is>
-          <t>Arizona Sonoran Copper Company Inc.</t>
-        </is>
-      </c>
-      <c r="E41" s="72" t="inlineStr">
-        <is>
-          <t>Materials</t>
-        </is>
-      </c>
-      <c r="F41" s="72" t="inlineStr">
-        <is>
-          <t>Metals and Mining</t>
-        </is>
-      </c>
-      <c r="G41" s="92" t="n">
-        <v>0</v>
-      </c>
-      <c r="H41" s="93" t="n">
-        <v>1264.79</v>
-      </c>
-      <c r="I41" s="74" t="inlineStr">
-        <is>
-          <t>Arizona Sonoran Copper Company Inc engages in the identification acquisition exploration and development of base metal properties</t>
-        </is>
-      </c>
+      <c r="B41" s="49" t="n"/>
+      <c r="C41" s="30" t="n"/>
+      <c r="D41" s="31" t="n"/>
+      <c r="E41" s="32" t="n"/>
+      <c r="F41" s="32" t="n"/>
+      <c r="G41" s="89" t="n"/>
+      <c r="H41" s="91" t="n"/>
+      <c r="I41" s="54" t="n"/>
       <c r="J41" s="68" t="n"/>
     </row>
-    <row r="42">
+    <row r="42" ht="26.4" customHeight="1">
       <c r="A42" s="43" t="n"/>
-      <c r="B42" s="43" t="n">
-        <v>35</v>
-      </c>
-      <c r="C42" s="43" t="inlineStr">
-        <is>
-          <t>RUP</t>
-        </is>
-      </c>
-      <c r="D42" s="43" t="inlineStr">
-        <is>
-          <t>Rupert Resources Ltd.</t>
-        </is>
-      </c>
-      <c r="E42" s="43" t="inlineStr">
-        <is>
-          <t>Materials</t>
-        </is>
-      </c>
-      <c r="F42" s="43" t="inlineStr">
-        <is>
-          <t>Metals and Mining</t>
-        </is>
-      </c>
-      <c r="G42" s="43" t="n">
-        <v>0</v>
-      </c>
-      <c r="H42" s="43" t="n">
-        <v>1488.84</v>
-      </c>
-      <c r="I42" s="43" t="inlineStr">
-        <is>
-          <t>Rupert Resources Ltd together with its subsidiaries engages in the acquisition and exploration of mineral properties in Finland</t>
-        </is>
-      </c>
+      <c r="B42" s="48" t="n"/>
+      <c r="C42" s="38" t="n"/>
+      <c r="D42" s="39" t="n"/>
+      <c r="E42" s="40" t="n"/>
+      <c r="F42" s="40" t="n"/>
+      <c r="G42" s="89" t="n"/>
+      <c r="H42" s="90" t="n"/>
+      <c r="I42" s="53" t="n"/>
       <c r="J42" s="43" t="n"/>
     </row>
-    <row r="43" ht="15.6" customHeight="1" thickBot="1">
+    <row r="43" ht="26.4" customHeight="1" thickBot="1">
       <c r="A43" s="43" t="n"/>
-      <c r="B43" s="43" t="n"/>
-      <c r="C43" s="43" t="n"/>
-      <c r="D43" s="43" t="n"/>
-      <c r="E43" s="43" t="n"/>
-      <c r="F43" s="43" t="n"/>
-      <c r="G43" s="43" t="n"/>
-      <c r="H43" s="43" t="n"/>
-      <c r="I43" s="43" t="n"/>
+      <c r="B43" s="49" t="n"/>
+      <c r="C43" s="30" t="n"/>
+      <c r="D43" s="31" t="n"/>
+      <c r="E43" s="32" t="n"/>
+      <c r="F43" s="32" t="n"/>
+      <c r="G43" s="89" t="n"/>
+      <c r="H43" s="91" t="n"/>
+      <c r="I43" s="54" t="n"/>
       <c r="J43" s="43" t="n"/>
     </row>
-    <row r="44" ht="12" customHeight="1">
+    <row r="44" ht="26.4" customHeight="1">
       <c r="A44" s="43" t="n"/>
-      <c r="B44" s="58" t="n"/>
-      <c r="C44" s="59" t="n"/>
-      <c r="D44" s="59" t="n"/>
-      <c r="E44" s="59" t="n"/>
-      <c r="F44" s="59" t="n"/>
-      <c r="G44" s="59" t="n"/>
-      <c r="H44" s="59" t="n"/>
-      <c r="I44" s="60" t="n"/>
+      <c r="B44" s="48" t="n"/>
+      <c r="C44" s="38" t="n"/>
+      <c r="D44" s="39" t="n"/>
+      <c r="E44" s="40" t="n"/>
+      <c r="F44" s="40" t="n"/>
+      <c r="G44" s="89" t="n"/>
+      <c r="H44" s="90" t="n"/>
+      <c r="I44" s="53" t="n"/>
       <c r="J44" s="43" t="n"/>
     </row>
-    <row r="45" ht="15.6" customHeight="1">
+    <row r="45" ht="26.4" customHeight="1">
       <c r="A45" s="43" t="n"/>
-      <c r="B45" s="67" t="n"/>
-      <c r="C45" s="64" t="n"/>
-      <c r="D45" s="66" t="n"/>
-      <c r="E45" s="64" t="n"/>
-      <c r="F45" s="64" t="n"/>
-      <c r="G45" s="64" t="n"/>
-      <c r="H45" s="64" t="n"/>
-      <c r="I45" s="65" t="n"/>
+      <c r="B45" s="49" t="n"/>
+      <c r="C45" s="30" t="n"/>
+      <c r="D45" s="31" t="n"/>
+      <c r="E45" s="32" t="n"/>
+      <c r="F45" s="32" t="n"/>
+      <c r="G45" s="89" t="n"/>
+      <c r="H45" s="91" t="n"/>
+      <c r="I45" s="54" t="n"/>
       <c r="J45" s="43" t="n"/>
     </row>
-    <row r="46" ht="9.6" customHeight="1" thickBot="1">
+    <row r="46" ht="26.4" customHeight="1" thickBot="1">
       <c r="A46" s="43" t="n"/>
-      <c r="B46" s="61" t="n"/>
-      <c r="C46" s="62" t="n"/>
-      <c r="D46" s="62" t="n"/>
-      <c r="E46" s="62" t="n"/>
-      <c r="F46" s="62" t="n"/>
-      <c r="G46" s="62" t="n"/>
-      <c r="H46" s="62" t="n"/>
-      <c r="I46" s="63" t="n"/>
+      <c r="B46" s="48" t="n"/>
+      <c r="C46" s="38" t="n"/>
+      <c r="D46" s="39" t="n"/>
+      <c r="E46" s="40" t="n"/>
+      <c r="F46" s="40" t="n"/>
+      <c r="G46" s="89" t="n"/>
+      <c r="H46" s="90" t="n"/>
+      <c r="I46" s="53" t="n"/>
       <c r="J46" s="43" t="n"/>
     </row>
-    <row r="47">
+    <row r="47" ht="26.4" customHeight="1">
       <c r="A47" s="43" t="n"/>
-      <c r="B47" s="43" t="n"/>
-      <c r="C47" s="43" t="n"/>
-      <c r="D47" s="43" t="n"/>
-      <c r="E47" s="43" t="n"/>
-      <c r="F47" s="43" t="n"/>
-      <c r="G47" s="43" t="n"/>
-      <c r="H47" s="43" t="n"/>
-      <c r="I47" s="43" t="n"/>
+      <c r="B47" s="49" t="n"/>
+      <c r="C47" s="30" t="n"/>
+      <c r="D47" s="31" t="n"/>
+      <c r="E47" s="32" t="n"/>
+      <c r="F47" s="32" t="n"/>
+      <c r="G47" s="89" t="n"/>
+      <c r="H47" s="91" t="n"/>
+      <c r="I47" s="54" t="n"/>
       <c r="J47" s="43" t="n"/>
     </row>
-    <row r="48">
+    <row r="48" ht="26.4" customHeight="1">
       <c r="A48" s="43" t="n"/>
-      <c r="B48" s="47" t="n"/>
-      <c r="C48" s="47" t="n"/>
-      <c r="D48" s="47" t="n"/>
-      <c r="E48" s="47" t="n"/>
-      <c r="F48" s="47" t="n"/>
-      <c r="G48" s="47" t="n"/>
-      <c r="H48" s="47" t="n"/>
-      <c r="I48" s="47" t="n"/>
+      <c r="B48" s="48" t="n"/>
+      <c r="C48" s="38" t="n"/>
+      <c r="D48" s="39" t="n"/>
+      <c r="E48" s="40" t="n"/>
+      <c r="F48" s="40" t="n"/>
+      <c r="G48" s="89" t="n"/>
+      <c r="H48" s="90" t="n"/>
+      <c r="I48" s="53" t="n"/>
       <c r="J48" s="43" t="n"/>
     </row>
-    <row r="49">
+    <row r="49" ht="26.4" customHeight="1">
       <c r="A49" s="43" t="n"/>
-      <c r="B49" s="43" t="n"/>
-      <c r="C49" s="43" t="n"/>
-      <c r="D49" s="43" t="n"/>
-      <c r="E49" s="43" t="n"/>
-      <c r="F49" s="43" t="n"/>
-      <c r="G49" s="43" t="n"/>
-      <c r="H49" s="43" t="n"/>
-      <c r="I49" s="43" t="n"/>
+      <c r="B49" s="49" t="n"/>
+      <c r="C49" s="30" t="n"/>
+      <c r="D49" s="31" t="n"/>
+      <c r="E49" s="32" t="n"/>
+      <c r="F49" s="32" t="n"/>
+      <c r="G49" s="89" t="n"/>
+      <c r="H49" s="91" t="n"/>
+      <c r="I49" s="54" t="n"/>
       <c r="J49" s="43" t="n"/>
+    </row>
+    <row r="50" ht="26.4" customHeight="1">
+      <c r="B50" s="48" t="n"/>
+      <c r="C50" s="38" t="n"/>
+      <c r="D50" s="39" t="n"/>
+      <c r="E50" s="40" t="n"/>
+      <c r="F50" s="40" t="n"/>
+      <c r="G50" s="89" t="n"/>
+      <c r="H50" s="90" t="n"/>
+      <c r="I50" s="53" t="n"/>
+    </row>
+    <row r="51" ht="26.4" customHeight="1">
+      <c r="B51" s="49" t="n"/>
+      <c r="C51" s="30" t="n"/>
+      <c r="D51" s="31" t="n"/>
+      <c r="E51" s="32" t="n"/>
+      <c r="F51" s="32" t="n"/>
+      <c r="G51" s="89" t="n"/>
+      <c r="H51" s="91" t="n"/>
+      <c r="I51" s="54" t="n"/>
+    </row>
+    <row r="52" ht="26.4" customHeight="1">
+      <c r="B52" s="48" t="n"/>
+      <c r="C52" s="38" t="n"/>
+      <c r="D52" s="39" t="n"/>
+      <c r="E52" s="40" t="n"/>
+      <c r="F52" s="40" t="n"/>
+      <c r="G52" s="89" t="n"/>
+      <c r="H52" s="90" t="n"/>
+      <c r="I52" s="53" t="n"/>
+    </row>
+    <row r="53" ht="26.4" customHeight="1">
+      <c r="B53" s="49" t="n"/>
+      <c r="C53" s="30" t="n"/>
+      <c r="D53" s="31" t="n"/>
+      <c r="E53" s="32" t="n"/>
+      <c r="F53" s="32" t="n"/>
+      <c r="G53" s="89" t="n"/>
+      <c r="H53" s="91" t="n"/>
+      <c r="I53" s="54" t="n"/>
+    </row>
+    <row r="54" ht="26.4" customHeight="1">
+      <c r="B54" s="48" t="n"/>
+      <c r="C54" s="38" t="n"/>
+      <c r="D54" s="39" t="n"/>
+      <c r="E54" s="40" t="n"/>
+      <c r="F54" s="40" t="n"/>
+      <c r="G54" s="89" t="n"/>
+      <c r="H54" s="90" t="n"/>
+      <c r="I54" s="53" t="n"/>
+    </row>
+    <row r="55" ht="26.4" customHeight="1">
+      <c r="B55" s="49" t="n"/>
+      <c r="C55" s="30" t="n"/>
+      <c r="D55" s="31" t="n"/>
+      <c r="E55" s="32" t="n"/>
+      <c r="F55" s="32" t="n"/>
+      <c r="G55" s="89" t="n"/>
+      <c r="H55" s="91" t="n"/>
+      <c r="I55" s="54" t="n"/>
+    </row>
+    <row r="56" ht="26.4" customHeight="1">
+      <c r="B56" s="48" t="n"/>
+      <c r="C56" s="38" t="n"/>
+      <c r="D56" s="39" t="n"/>
+      <c r="E56" s="40" t="n"/>
+      <c r="F56" s="40" t="n"/>
+      <c r="G56" s="89" t="n"/>
+      <c r="H56" s="90" t="n"/>
+      <c r="I56" s="53" t="n"/>
+    </row>
+    <row r="57" ht="26.4" customHeight="1">
+      <c r="B57" s="49" t="n"/>
+      <c r="C57" s="30" t="n"/>
+      <c r="D57" s="31" t="n"/>
+      <c r="E57" s="32" t="n"/>
+      <c r="F57" s="32" t="n"/>
+      <c r="G57" s="89" t="n"/>
+      <c r="H57" s="91" t="n"/>
+      <c r="I57" s="54" t="n"/>
+    </row>
+    <row r="58" ht="26.4" customHeight="1">
+      <c r="B58" s="48" t="n"/>
+      <c r="C58" s="38" t="n"/>
+      <c r="D58" s="39" t="n"/>
+      <c r="E58" s="40" t="n"/>
+      <c r="F58" s="40" t="n"/>
+      <c r="G58" s="89" t="n"/>
+      <c r="H58" s="90" t="n"/>
+      <c r="I58" s="53" t="n"/>
+    </row>
+    <row r="59" ht="26.4" customHeight="1">
+      <c r="B59" s="49" t="n"/>
+      <c r="C59" s="30" t="n"/>
+      <c r="D59" s="31" t="n"/>
+      <c r="E59" s="32" t="n"/>
+      <c r="F59" s="32" t="n"/>
+      <c r="G59" s="89" t="n"/>
+      <c r="H59" s="91" t="n"/>
+      <c r="I59" s="54" t="n"/>
+    </row>
+    <row r="60" ht="26.4" customHeight="1">
+      <c r="B60" s="48" t="n"/>
+      <c r="C60" s="38" t="n"/>
+      <c r="D60" s="39" t="n"/>
+      <c r="E60" s="40" t="n"/>
+      <c r="F60" s="40" t="n"/>
+      <c r="G60" s="89" t="n"/>
+      <c r="H60" s="90" t="n"/>
+      <c r="I60" s="53" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="2">
     <mergeCell ref="B2:G2"/>
     <mergeCell ref="H2:I2"/>
   </mergeCells>
-  <conditionalFormatting sqref="G8:G41">
+  <conditionalFormatting sqref="G8:G60">
     <cfRule type="colorScale" priority="1371">
       <colorScale>
         <cfvo type="min"/>
@@ -3786,7 +3844,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:J49"/>
+  <dimension ref="A1:J60"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="1.21875" customWidth="1" style="11" min="1" max="1"/>
@@ -3958,7 +4016,7 @@
         </is>
       </c>
       <c r="G8" s="89" t="n">
-        <v>1.192</v>
+        <v>1.193</v>
       </c>
       <c r="H8" s="90" t="n">
         <v>12725.72</v>
@@ -4034,7 +4092,7 @@
         </is>
       </c>
       <c r="G10" s="89" t="n">
-        <v>0.833</v>
+        <v>0.839</v>
       </c>
       <c r="H10" s="90" t="n">
         <v>77721.12</v>
@@ -4072,7 +4130,7 @@
         </is>
       </c>
       <c r="G11" s="89" t="n">
-        <v>0.6929999999999999</v>
+        <v>0.701</v>
       </c>
       <c r="H11" s="91" t="n">
         <v>77190.64999999999</v>
@@ -4110,7 +4168,7 @@
         </is>
       </c>
       <c r="G12" s="89" t="n">
-        <v>0.477</v>
+        <v>0.471</v>
       </c>
       <c r="H12" s="90" t="n">
         <v>44725.83</v>
@@ -4148,7 +4206,7 @@
         </is>
       </c>
       <c r="G13" s="89" t="n">
-        <v>0.418</v>
+        <v>0.424</v>
       </c>
       <c r="H13" s="91" t="n">
         <v>26566.73</v>
@@ -4186,7 +4244,7 @@
         </is>
       </c>
       <c r="G14" s="89" t="n">
-        <v>0.375</v>
+        <v>0.37</v>
       </c>
       <c r="H14" s="90" t="n">
         <v>86617.14</v>
@@ -4205,12 +4263,12 @@
       </c>
       <c r="C15" s="30" t="inlineStr">
         <is>
-          <t>GL</t>
+          <t>BNY</t>
         </is>
       </c>
       <c r="D15" s="31" t="inlineStr">
         <is>
-          <t>Globe Life Inc.</t>
+          <t>The Bank of New York Mellon Corporation</t>
         </is>
       </c>
       <c r="E15" s="32" t="inlineStr">
@@ -4220,18 +4278,18 @@
       </c>
       <c r="F15" s="32" t="inlineStr">
         <is>
-          <t>Insurance</t>
+          <t>Capital Markets</t>
         </is>
       </c>
       <c r="G15" s="89" t="n">
-        <v>0.355</v>
+        <v>0.356</v>
       </c>
       <c r="H15" s="91" t="n">
-        <v>12644.53</v>
+        <v>96186.41</v>
       </c>
       <c r="I15" s="54" t="inlineStr">
         <is>
-          <t>Globe Life Inc through its subsidiaries provides various life and supplemental health insurance products to lower middle- and middle-income families in the United States</t>
+          <t>The Bank of New York Mellon Corporation provides a range of financial products and services in the United States and internationally</t>
         </is>
       </c>
       <c r="J15" s="28" t="n"/>
@@ -4243,12 +4301,12 @@
       </c>
       <c r="C16" s="38" t="inlineStr">
         <is>
-          <t>BNY</t>
+          <t>GL</t>
         </is>
       </c>
       <c r="D16" s="39" t="inlineStr">
         <is>
-          <t>The Bank of New York Mellon Corporation</t>
+          <t>Globe Life Inc.</t>
         </is>
       </c>
       <c r="E16" s="40" t="inlineStr">
@@ -4258,18 +4316,18 @@
       </c>
       <c r="F16" s="40" t="inlineStr">
         <is>
-          <t>Capital Markets</t>
+          <t>Insurance</t>
         </is>
       </c>
       <c r="G16" s="89" t="n">
-        <v>0.351</v>
+        <v>0.356</v>
       </c>
       <c r="H16" s="90" t="n">
-        <v>96186.41</v>
+        <v>12644.53</v>
       </c>
       <c r="I16" s="53" t="inlineStr">
         <is>
-          <t>The Bank of New York Mellon Corporation provides a range of financial products and services in the United States and internationally</t>
+          <t>Globe Life Inc through its subsidiaries provides various life and supplemental health insurance products to lower middle- and middle-income families in the United States</t>
         </is>
       </c>
       <c r="J16" s="36" t="n"/>
@@ -4300,7 +4358,7 @@
         </is>
       </c>
       <c r="G17" s="89" t="n">
-        <v>0.348</v>
+        <v>0.351</v>
       </c>
       <c r="H17" s="91" t="n">
         <v>148209.56</v>
@@ -4319,33 +4377,33 @@
       </c>
       <c r="C18" s="38" t="inlineStr">
         <is>
-          <t>TRV</t>
+          <t>CVS</t>
         </is>
       </c>
       <c r="D18" s="39" t="inlineStr">
         <is>
-          <t>The Travelers Companies Inc.</t>
+          <t>CVS Health Corporation</t>
         </is>
       </c>
       <c r="E18" s="40" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Health Care</t>
         </is>
       </c>
       <c r="F18" s="40" t="inlineStr">
         <is>
-          <t>Insurance</t>
+          <t>Health Care Providers and Services</t>
         </is>
       </c>
       <c r="G18" s="89" t="n">
-        <v>0.341</v>
+        <v>0.343</v>
       </c>
       <c r="H18" s="90" t="n">
-        <v>64533.41</v>
+        <v>125211.85</v>
       </c>
       <c r="I18" s="53" t="inlineStr">
         <is>
-          <t>The Travelers Companies Inc through its subsidiaries provides a range of commercial and personal property and casualty insurance products and services to businesses government units associations and individuals in the United States Canada and internationally</t>
+          <t>CVS Health Corporation provides health solutions in the United States</t>
         </is>
       </c>
       <c r="J18" s="36" t="n"/>
@@ -4357,33 +4415,33 @@
       </c>
       <c r="C19" s="30" t="inlineStr">
         <is>
-          <t>CVS</t>
+          <t>TRV</t>
         </is>
       </c>
       <c r="D19" s="31" t="inlineStr">
         <is>
-          <t>CVS Health Corporation</t>
+          <t>The Travelers Companies Inc.</t>
         </is>
       </c>
       <c r="E19" s="32" t="inlineStr">
         <is>
-          <t>Health Care</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="F19" s="32" t="inlineStr">
         <is>
-          <t>Health Care Providers and Services</t>
+          <t>Insurance</t>
         </is>
       </c>
       <c r="G19" s="89" t="n">
-        <v>0.339</v>
+        <v>0.341</v>
       </c>
       <c r="H19" s="91" t="n">
-        <v>125211.85</v>
+        <v>64533.41</v>
       </c>
       <c r="I19" s="54" t="inlineStr">
         <is>
-          <t>CVS Health Corporation provides health solutions in the United States</t>
+          <t>The Travelers Companies Inc through its subsidiaries provides a range of commercial and personal property and casualty insurance products and services to businesses government units associations and individuals in the United States Canada and internationally</t>
         </is>
       </c>
       <c r="J19" s="28" t="n"/>
@@ -4452,7 +4510,7 @@
         </is>
       </c>
       <c r="G21" s="89" t="n">
-        <v>0.3</v>
+        <v>0.307</v>
       </c>
       <c r="H21" s="91" t="n">
         <v>16078.79</v>
@@ -4471,33 +4529,33 @@
       </c>
       <c r="C22" s="38" t="inlineStr">
         <is>
-          <t>UNP</t>
+          <t>ADM</t>
         </is>
       </c>
       <c r="D22" s="39" t="inlineStr">
         <is>
-          <t>Union Pacific Corporation</t>
+          <t>Archer-Daniels-Midland Company</t>
         </is>
       </c>
       <c r="E22" s="40" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Consumer Staples</t>
         </is>
       </c>
       <c r="F22" s="40" t="inlineStr">
         <is>
-          <t>Ground Transportation</t>
+          <t>Food Products</t>
         </is>
       </c>
       <c r="G22" s="89" t="n">
-        <v>0.298</v>
+        <v>0.295</v>
       </c>
       <c r="H22" s="90" t="n">
-        <v>158667.48</v>
+        <v>39380.19</v>
       </c>
       <c r="I22" s="53" t="inlineStr">
         <is>
-          <t>Union Pacific Corporation through its subsidiary Union Pacific Railroad Company operates in the railroad business in the United States</t>
+          <t>Archer-Daniels-Midland Company provides human and animal nutrition ingredients and solutions in the United States Switzerland the Cayman Islands Brazil Mexico Canada the United Kingdom and internationally</t>
         </is>
       </c>
       <c r="J22" s="36" t="n"/>
@@ -4509,33 +4567,33 @@
       </c>
       <c r="C23" s="30" t="inlineStr">
         <is>
-          <t>ADM</t>
+          <t>GWW</t>
         </is>
       </c>
       <c r="D23" s="31" t="inlineStr">
         <is>
-          <t>Archer-Daniels-Midland Company</t>
+          <t>W.W. Grainger Inc.</t>
         </is>
       </c>
       <c r="E23" s="32" t="inlineStr">
         <is>
-          <t>Consumer Staples</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="F23" s="32" t="inlineStr">
         <is>
-          <t>Food Products</t>
+          <t>Trading Companies and Distributors</t>
         </is>
       </c>
       <c r="G23" s="89" t="n">
-        <v>0.295</v>
+        <v>0.292</v>
       </c>
       <c r="H23" s="91" t="n">
-        <v>39380.19</v>
+        <v>62147.38</v>
       </c>
       <c r="I23" s="54" t="inlineStr">
         <is>
-          <t>Archer-Daniels-Midland Company provides human and animal nutrition ingredients and solutions in the United States Switzerland the Cayman Islands Brazil Mexico Canada the United Kingdom and internationally</t>
+          <t>W</t>
         </is>
       </c>
       <c r="J23" s="28" t="n"/>
@@ -4547,33 +4605,33 @@
       </c>
       <c r="C24" s="38" t="inlineStr">
         <is>
-          <t>GWW</t>
+          <t>DOC</t>
         </is>
       </c>
       <c r="D24" s="39" t="inlineStr">
         <is>
-          <t>W.W. Grainger Inc.</t>
+          <t>Healthpeak Properties Inc.</t>
         </is>
       </c>
       <c r="E24" s="40" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Real Estate</t>
         </is>
       </c>
       <c r="F24" s="40" t="inlineStr">
         <is>
-          <t>Trading Companies and Distributors</t>
+          <t>Health Care REITs</t>
         </is>
       </c>
       <c r="G24" s="89" t="n">
-        <v>0.294</v>
+        <v>0.291</v>
       </c>
       <c r="H24" s="90" t="n">
-        <v>62147.38</v>
+        <v>14353.95</v>
       </c>
       <c r="I24" s="53" t="inlineStr">
         <is>
-          <t>W</t>
+          <t>Healthpeak Properties Inc is a Standard &amp; Poor’s 500 company that owns operates and develops high-quality real estate focused on healthcare discovery and delivery in the United States</t>
         </is>
       </c>
       <c r="J24" s="36" t="n"/>
@@ -4585,33 +4643,33 @@
       </c>
       <c r="C25" s="30" t="inlineStr">
         <is>
-          <t>DOC</t>
+          <t>UNP</t>
         </is>
       </c>
       <c r="D25" s="31" t="inlineStr">
         <is>
-          <t>Healthpeak Properties Inc.</t>
+          <t>Union Pacific Corporation</t>
         </is>
       </c>
       <c r="E25" s="32" t="inlineStr">
         <is>
-          <t>Real Estate</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="F25" s="32" t="inlineStr">
         <is>
-          <t>Health Care REITs</t>
+          <t>Ground Transportation</t>
         </is>
       </c>
       <c r="G25" s="89" t="n">
-        <v>0.29</v>
+        <v>0.289</v>
       </c>
       <c r="H25" s="91" t="n">
-        <v>14353.95</v>
+        <v>158667.48</v>
       </c>
       <c r="I25" s="54" t="inlineStr">
         <is>
-          <t>Healthpeak Properties Inc is a Standard &amp; Poor’s 500 company that owns operates and develops high-quality real estate focused on healthcare discovery and delivery in the United States</t>
+          <t>Union Pacific Corporation through its subsidiary Union Pacific Railroad Company operates in the railroad business in the United States</t>
         </is>
       </c>
       <c r="J25" s="28" t="n"/>
@@ -4642,7 +4700,7 @@
         </is>
       </c>
       <c r="G26" s="89" t="n">
-        <v>0.257</v>
+        <v>0.258</v>
       </c>
       <c r="H26" s="90" t="n">
         <v>30713.22</v>
@@ -4680,7 +4738,7 @@
         </is>
       </c>
       <c r="G27" s="89" t="n">
-        <v>0.248</v>
+        <v>0.25</v>
       </c>
       <c r="H27" s="91" t="n">
         <v>55851.6</v>
@@ -4718,7 +4776,7 @@
         </is>
       </c>
       <c r="G28" s="89" t="n">
-        <v>0.219</v>
+        <v>0.222</v>
       </c>
       <c r="H28" s="90" t="n">
         <v>23624.19</v>
@@ -4756,7 +4814,7 @@
         </is>
       </c>
       <c r="G29" s="89" t="n">
-        <v>0.202</v>
+        <v>0.203</v>
       </c>
       <c r="H29" s="91" t="n">
         <v>40474.89</v>
@@ -4794,7 +4852,7 @@
         </is>
       </c>
       <c r="G30" s="89" t="n">
-        <v>0.197</v>
+        <v>0.196</v>
       </c>
       <c r="H30" s="90" t="n">
         <v>388502.86</v>
@@ -4832,7 +4890,7 @@
         </is>
       </c>
       <c r="G31" s="89" t="n">
-        <v>0.19</v>
+        <v>0.193</v>
       </c>
       <c r="H31" s="91" t="n">
         <v>308648.81</v>
@@ -4870,7 +4928,7 @@
         </is>
       </c>
       <c r="G32" s="89" t="n">
-        <v>0.182</v>
+        <v>0.18</v>
       </c>
       <c r="H32" s="90" t="n">
         <v>13320.91</v>
@@ -4889,33 +4947,33 @@
       </c>
       <c r="C33" s="30" t="inlineStr">
         <is>
-          <t>MNST</t>
+          <t>CFG</t>
         </is>
       </c>
       <c r="D33" s="31" t="inlineStr">
         <is>
-          <t>Monster Beverage Corporation</t>
+          <t>Citizens Financial Group Inc.</t>
         </is>
       </c>
       <c r="E33" s="32" t="inlineStr">
         <is>
-          <t>Consumer Staples</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="F33" s="32" t="inlineStr">
         <is>
-          <t>Beverages</t>
+          <t>Banks</t>
         </is>
       </c>
       <c r="G33" s="89" t="n">
-        <v>0.159</v>
+        <v>0.166</v>
       </c>
       <c r="H33" s="91" t="n">
-        <v>89144.46000000001</v>
+        <v>27585.86</v>
       </c>
       <c r="I33" s="54" t="inlineStr">
         <is>
-          <t>Monster Beverage Corporation through its subsidiaries engages in development marketing sale and distribution of energy drink beverages and concentrates in the United States and internationally</t>
+          <t>Citizens Financial Group Inc operates as the bank holding company that provides retail and commercial banking products and services to individuals small businesses middle-market companies large corporations and institutions in the United States</t>
         </is>
       </c>
       <c r="J33" s="28" t="n"/>
@@ -4927,12 +4985,12 @@
       </c>
       <c r="C34" s="38" t="inlineStr">
         <is>
-          <t>CFG</t>
+          <t>FITB</t>
         </is>
       </c>
       <c r="D34" s="39" t="inlineStr">
         <is>
-          <t>Citizens Financial Group Inc.</t>
+          <t>Fifth Third Bancorp</t>
         </is>
       </c>
       <c r="E34" s="40" t="inlineStr">
@@ -4946,14 +5004,14 @@
         </is>
       </c>
       <c r="G34" s="89" t="n">
-        <v>0.158</v>
+        <v>0.155</v>
       </c>
       <c r="H34" s="90" t="n">
-        <v>27585.86</v>
+        <v>47955.66</v>
       </c>
       <c r="I34" s="53" t="inlineStr">
         <is>
-          <t>Citizens Financial Group Inc operates as the bank holding company that provides retail and commercial banking products and services to individuals small businesses middle-market companies large corporations and institutions in the United States</t>
+          <t>Fifth Third Bancorp operates as the bank holding company for Fifth Third Bank National Association that provides a range of financial products and services in the United States</t>
         </is>
       </c>
       <c r="J34" s="36" t="n"/>
@@ -4965,33 +5023,33 @@
       </c>
       <c r="C35" s="30" t="inlineStr">
         <is>
-          <t>FITB</t>
+          <t>MNST</t>
         </is>
       </c>
       <c r="D35" s="31" t="inlineStr">
         <is>
-          <t>Fifth Third Bancorp</t>
+          <t>Monster Beverage Corporation</t>
         </is>
       </c>
       <c r="E35" s="32" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Consumer Staples</t>
         </is>
       </c>
       <c r="F35" s="32" t="inlineStr">
         <is>
-          <t>Banks</t>
+          <t>Beverages</t>
         </is>
       </c>
       <c r="G35" s="89" t="n">
         <v>0.152</v>
       </c>
       <c r="H35" s="91" t="n">
-        <v>47955.66</v>
+        <v>89144.46000000001</v>
       </c>
       <c r="I35" s="54" t="inlineStr">
         <is>
-          <t>Fifth Third Bancorp operates as the bank holding company for Fifth Third Bank National Association that provides a range of financial products and services in the United States</t>
+          <t>Monster Beverage Corporation through its subsidiaries engages in development marketing sale and distribution of energy drink beverages and concentrates in the United States and internationally</t>
         </is>
       </c>
       <c r="J35" s="28" t="n"/>
@@ -5003,33 +5061,33 @@
       </c>
       <c r="C36" s="38" t="inlineStr">
         <is>
-          <t>EXPD</t>
+          <t>PRU</t>
         </is>
       </c>
       <c r="D36" s="39" t="inlineStr">
         <is>
-          <t>Expeditors International of Washington Inc.</t>
+          <t>Prudential Financial Inc.</t>
         </is>
       </c>
       <c r="E36" s="40" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="F36" s="40" t="inlineStr">
         <is>
-          <t>Air Freight and Logistics</t>
+          <t>Insurance</t>
         </is>
       </c>
       <c r="G36" s="89" t="n">
-        <v>0.13</v>
+        <v>0.131</v>
       </c>
       <c r="H36" s="90" t="n">
-        <v>21453.67</v>
+        <v>36717.82</v>
       </c>
       <c r="I36" s="53" t="inlineStr">
         <is>
-          <t>Expeditors International of Washington Inc together with its subsidiaries provides logistics services in the Americas North Asia South Asia Europe and Middle East Africa and India</t>
+          <t>Prudential Financial Inc together with its subsidiaries provides financial products and services in the United States Japan and internationally</t>
         </is>
       </c>
       <c r="J36" s="36" t="n"/>
@@ -5041,33 +5099,33 @@
       </c>
       <c r="C37" s="30" t="inlineStr">
         <is>
-          <t>PRU</t>
+          <t>EXPD</t>
         </is>
       </c>
       <c r="D37" s="31" t="inlineStr">
         <is>
-          <t>Prudential Financial Inc.</t>
+          <t>Expeditors International of Washington Inc.</t>
         </is>
       </c>
       <c r="E37" s="32" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="F37" s="32" t="inlineStr">
         <is>
-          <t>Insurance</t>
+          <t>Air Freight and Logistics</t>
         </is>
       </c>
       <c r="G37" s="89" t="n">
-        <v>0.129</v>
+        <v>0.127</v>
       </c>
       <c r="H37" s="91" t="n">
-        <v>36717.82</v>
+        <v>21453.67</v>
       </c>
       <c r="I37" s="54" t="inlineStr">
         <is>
-          <t>Prudential Financial Inc together with its subsidiaries provides financial products and services in the United States Japan and internationally</t>
+          <t>Expeditors International of Washington Inc together with its subsidiaries provides logistics services in the Americas North Asia South Asia Europe and Middle East Africa and India</t>
         </is>
       </c>
       <c r="J37" s="28" t="n"/>
@@ -5098,7 +5156,7 @@
         </is>
       </c>
       <c r="G38" s="89" t="n">
-        <v>0.099</v>
+        <v>0.096</v>
       </c>
       <c r="H38" s="90" t="n">
         <v>612046.08</v>
@@ -5136,7 +5194,7 @@
         </is>
       </c>
       <c r="G39" s="89" t="n">
-        <v>0.078</v>
+        <v>0.075</v>
       </c>
       <c r="H39" s="91" t="n">
         <v>36258.68</v>
@@ -5198,108 +5256,218 @@
       <c r="I41" s="54" t="n"/>
       <c r="J41" s="28" t="n"/>
     </row>
-    <row r="42" ht="24.6" customHeight="1" thickBot="1">
+    <row r="42" ht="24" customHeight="1" thickBot="1">
       <c r="A42" s="75" t="n"/>
-      <c r="B42" s="76" t="n"/>
-      <c r="C42" s="77" t="n"/>
-      <c r="D42" s="78" t="n"/>
-      <c r="E42" s="79" t="n"/>
-      <c r="F42" s="79" t="n"/>
-      <c r="G42" s="92" t="n"/>
-      <c r="H42" s="96" t="n"/>
-      <c r="I42" s="81" t="n"/>
+      <c r="B42" s="48" t="n"/>
+      <c r="C42" s="38" t="n"/>
+      <c r="D42" s="39" t="n"/>
+      <c r="E42" s="40" t="n"/>
+      <c r="F42" s="40" t="n"/>
+      <c r="G42" s="89" t="n"/>
+      <c r="H42" s="90" t="n"/>
+      <c r="I42" s="53" t="n"/>
       <c r="J42" s="75" t="n"/>
     </row>
-    <row r="43">
+    <row r="43" ht="24" customHeight="1">
       <c r="A43" s="43" t="n"/>
-      <c r="B43" s="43" t="n"/>
-      <c r="C43" s="43" t="n"/>
-      <c r="D43" s="43" t="n"/>
-      <c r="E43" s="43" t="n"/>
-      <c r="F43" s="43" t="n"/>
-      <c r="G43" s="43" t="n"/>
-      <c r="H43" s="43" t="n"/>
-      <c r="I43" s="43" t="n"/>
+      <c r="B43" s="49" t="n"/>
+      <c r="C43" s="30" t="n"/>
+      <c r="D43" s="31" t="n"/>
+      <c r="E43" s="32" t="n"/>
+      <c r="F43" s="32" t="n"/>
+      <c r="G43" s="89" t="n"/>
+      <c r="H43" s="91" t="n"/>
+      <c r="I43" s="54" t="n"/>
       <c r="J43" s="43" t="n"/>
     </row>
-    <row r="44" ht="15.6" customHeight="1" thickBot="1">
+    <row r="44" ht="24" customHeight="1" thickBot="1">
       <c r="A44" s="43" t="n"/>
-      <c r="B44" s="43" t="n"/>
-      <c r="C44" s="43" t="n"/>
-      <c r="D44" s="43" t="n"/>
-      <c r="E44" s="43" t="n"/>
-      <c r="F44" s="43" t="n"/>
-      <c r="G44" s="43" t="n"/>
-      <c r="H44" s="43" t="n"/>
-      <c r="I44" s="43" t="n"/>
+      <c r="B44" s="48" t="n"/>
+      <c r="C44" s="38" t="n"/>
+      <c r="D44" s="39" t="n"/>
+      <c r="E44" s="40" t="n"/>
+      <c r="F44" s="40" t="n"/>
+      <c r="G44" s="89" t="n"/>
+      <c r="H44" s="90" t="n"/>
+      <c r="I44" s="53" t="n"/>
       <c r="J44" s="43" t="n"/>
     </row>
-    <row r="45" ht="10.2" customHeight="1">
+    <row r="45" ht="24" customHeight="1">
       <c r="A45" s="43" t="n"/>
-      <c r="B45" s="58" t="n"/>
-      <c r="C45" s="59" t="n"/>
-      <c r="D45" s="59" t="n"/>
-      <c r="E45" s="59" t="n"/>
-      <c r="F45" s="59" t="n"/>
-      <c r="G45" s="59" t="n"/>
-      <c r="H45" s="59" t="n"/>
-      <c r="I45" s="60" t="n"/>
+      <c r="B45" s="49" t="n"/>
+      <c r="C45" s="30" t="n"/>
+      <c r="D45" s="31" t="n"/>
+      <c r="E45" s="32" t="n"/>
+      <c r="F45" s="32" t="n"/>
+      <c r="G45" s="89" t="n"/>
+      <c r="H45" s="91" t="n"/>
+      <c r="I45" s="54" t="n"/>
       <c r="J45" s="43" t="n"/>
     </row>
-    <row r="46" ht="15.6" customHeight="1">
+    <row r="46" ht="24" customHeight="1">
       <c r="A46" s="43" t="n"/>
-      <c r="B46" s="67" t="n"/>
-      <c r="C46" s="64" t="n"/>
-      <c r="D46" s="64" t="n"/>
-      <c r="E46" s="64" t="n"/>
-      <c r="F46" s="64" t="n"/>
-      <c r="G46" s="64" t="n"/>
-      <c r="H46" s="64" t="n"/>
-      <c r="I46" s="65" t="n"/>
+      <c r="B46" s="48" t="n"/>
+      <c r="C46" s="38" t="n"/>
+      <c r="D46" s="39" t="n"/>
+      <c r="E46" s="40" t="n"/>
+      <c r="F46" s="40" t="n"/>
+      <c r="G46" s="89" t="n"/>
+      <c r="H46" s="90" t="n"/>
+      <c r="I46" s="53" t="n"/>
       <c r="J46" s="43" t="n"/>
     </row>
-    <row r="47" ht="10.8" customHeight="1" thickBot="1">
+    <row r="47" ht="24" customHeight="1" thickBot="1">
       <c r="A47" s="43" t="n"/>
-      <c r="B47" s="61" t="n"/>
-      <c r="C47" s="62" t="n"/>
-      <c r="D47" s="62" t="n"/>
-      <c r="E47" s="62" t="n"/>
-      <c r="F47" s="62" t="n"/>
-      <c r="G47" s="62" t="n"/>
-      <c r="H47" s="62" t="n"/>
-      <c r="I47" s="63" t="n"/>
+      <c r="B47" s="49" t="n"/>
+      <c r="C47" s="30" t="n"/>
+      <c r="D47" s="31" t="n"/>
+      <c r="E47" s="32" t="n"/>
+      <c r="F47" s="32" t="n"/>
+      <c r="G47" s="89" t="n"/>
+      <c r="H47" s="91" t="n"/>
+      <c r="I47" s="54" t="n"/>
       <c r="J47" s="43" t="n"/>
     </row>
-    <row r="48">
+    <row r="48" ht="24" customHeight="1">
       <c r="A48" s="43" t="n"/>
-      <c r="B48" s="43" t="n"/>
-      <c r="C48" s="43" t="n"/>
-      <c r="D48" s="43" t="n"/>
-      <c r="E48" s="43" t="n"/>
-      <c r="F48" s="43" t="n"/>
-      <c r="G48" s="43" t="n"/>
-      <c r="H48" s="43" t="n"/>
-      <c r="I48" s="43" t="n"/>
+      <c r="B48" s="48" t="n"/>
+      <c r="C48" s="38" t="n"/>
+      <c r="D48" s="39" t="n"/>
+      <c r="E48" s="40" t="n"/>
+      <c r="F48" s="40" t="n"/>
+      <c r="G48" s="89" t="n"/>
+      <c r="H48" s="90" t="n"/>
+      <c r="I48" s="53" t="n"/>
       <c r="J48" s="43" t="n"/>
     </row>
-    <row r="49">
+    <row r="49" ht="24" customHeight="1">
       <c r="A49" s="43" t="n"/>
-      <c r="B49" s="47" t="n"/>
-      <c r="C49" s="47" t="n"/>
-      <c r="D49" s="47" t="n"/>
-      <c r="E49" s="47" t="n"/>
-      <c r="F49" s="47" t="n"/>
-      <c r="G49" s="47" t="n"/>
-      <c r="H49" s="47" t="n"/>
-      <c r="I49" s="47" t="n"/>
+      <c r="B49" s="49" t="n"/>
+      <c r="C49" s="30" t="n"/>
+      <c r="D49" s="31" t="n"/>
+      <c r="E49" s="32" t="n"/>
+      <c r="F49" s="32" t="n"/>
+      <c r="G49" s="89" t="n"/>
+      <c r="H49" s="91" t="n"/>
+      <c r="I49" s="54" t="n"/>
       <c r="J49" s="43" t="n"/>
+    </row>
+    <row r="50" ht="24" customHeight="1">
+      <c r="B50" s="48" t="n"/>
+      <c r="C50" s="38" t="n"/>
+      <c r="D50" s="39" t="n"/>
+      <c r="E50" s="40" t="n"/>
+      <c r="F50" s="40" t="n"/>
+      <c r="G50" s="89" t="n"/>
+      <c r="H50" s="90" t="n"/>
+      <c r="I50" s="53" t="n"/>
+    </row>
+    <row r="51" ht="24" customHeight="1">
+      <c r="B51" s="49" t="n"/>
+      <c r="C51" s="30" t="n"/>
+      <c r="D51" s="31" t="n"/>
+      <c r="E51" s="32" t="n"/>
+      <c r="F51" s="32" t="n"/>
+      <c r="G51" s="89" t="n"/>
+      <c r="H51" s="91" t="n"/>
+      <c r="I51" s="54" t="n"/>
+    </row>
+    <row r="52" ht="24" customHeight="1">
+      <c r="B52" s="48" t="n"/>
+      <c r="C52" s="38" t="n"/>
+      <c r="D52" s="39" t="n"/>
+      <c r="E52" s="40" t="n"/>
+      <c r="F52" s="40" t="n"/>
+      <c r="G52" s="89" t="n"/>
+      <c r="H52" s="90" t="n"/>
+      <c r="I52" s="53" t="n"/>
+    </row>
+    <row r="53" ht="24" customHeight="1">
+      <c r="B53" s="49" t="n"/>
+      <c r="C53" s="30" t="n"/>
+      <c r="D53" s="31" t="n"/>
+      <c r="E53" s="32" t="n"/>
+      <c r="F53" s="32" t="n"/>
+      <c r="G53" s="89" t="n"/>
+      <c r="H53" s="91" t="n"/>
+      <c r="I53" s="54" t="n"/>
+    </row>
+    <row r="54" ht="24" customHeight="1">
+      <c r="B54" s="48" t="n"/>
+      <c r="C54" s="38" t="n"/>
+      <c r="D54" s="39" t="n"/>
+      <c r="E54" s="40" t="n"/>
+      <c r="F54" s="40" t="n"/>
+      <c r="G54" s="89" t="n"/>
+      <c r="H54" s="90" t="n"/>
+      <c r="I54" s="53" t="n"/>
+    </row>
+    <row r="55" ht="24" customHeight="1">
+      <c r="B55" s="49" t="n"/>
+      <c r="C55" s="30" t="n"/>
+      <c r="D55" s="31" t="n"/>
+      <c r="E55" s="32" t="n"/>
+      <c r="F55" s="32" t="n"/>
+      <c r="G55" s="89" t="n"/>
+      <c r="H55" s="91" t="n"/>
+      <c r="I55" s="54" t="n"/>
+    </row>
+    <row r="56" ht="24" customHeight="1">
+      <c r="B56" s="48" t="n"/>
+      <c r="C56" s="38" t="n"/>
+      <c r="D56" s="39" t="n"/>
+      <c r="E56" s="40" t="n"/>
+      <c r="F56" s="40" t="n"/>
+      <c r="G56" s="89" t="n"/>
+      <c r="H56" s="90" t="n"/>
+      <c r="I56" s="53" t="n"/>
+    </row>
+    <row r="57" ht="24" customHeight="1">
+      <c r="B57" s="49" t="n"/>
+      <c r="C57" s="30" t="n"/>
+      <c r="D57" s="31" t="n"/>
+      <c r="E57" s="32" t="n"/>
+      <c r="F57" s="32" t="n"/>
+      <c r="G57" s="89" t="n"/>
+      <c r="H57" s="91" t="n"/>
+      <c r="I57" s="54" t="n"/>
+    </row>
+    <row r="58" ht="24" customHeight="1">
+      <c r="B58" s="48" t="n"/>
+      <c r="C58" s="38" t="n"/>
+      <c r="D58" s="39" t="n"/>
+      <c r="E58" s="40" t="n"/>
+      <c r="F58" s="40" t="n"/>
+      <c r="G58" s="89" t="n"/>
+      <c r="H58" s="90" t="n"/>
+      <c r="I58" s="53" t="n"/>
+    </row>
+    <row r="59" ht="24" customHeight="1">
+      <c r="B59" s="49" t="n"/>
+      <c r="C59" s="30" t="n"/>
+      <c r="D59" s="31" t="n"/>
+      <c r="E59" s="32" t="n"/>
+      <c r="F59" s="32" t="n"/>
+      <c r="G59" s="89" t="n"/>
+      <c r="H59" s="91" t="n"/>
+      <c r="I59" s="54" t="n"/>
+    </row>
+    <row r="60" ht="24" customHeight="1">
+      <c r="B60" s="48" t="n"/>
+      <c r="C60" s="38" t="n"/>
+      <c r="D60" s="39" t="n"/>
+      <c r="E60" s="40" t="n"/>
+      <c r="F60" s="40" t="n"/>
+      <c r="G60" s="89" t="n"/>
+      <c r="H60" s="90" t="n"/>
+      <c r="I60" s="53" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="2">
     <mergeCell ref="B2:G2"/>
     <mergeCell ref="H2:I2"/>
   </mergeCells>
-  <conditionalFormatting sqref="G8:G42">
+  <conditionalFormatting sqref="G8:G60">
     <cfRule type="colorScale" priority="1351">
       <colorScale>
         <cfvo type="min"/>

--- a/outputs/benchmark-beaters/Benchmark_Beaters_2026-07-21.xlsx
+++ b/outputs/benchmark-beaters/Benchmark_Beaters_2026-07-21.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="30720" yWindow="0" windowWidth="21600" windowHeight="11235" tabRatio="600" firstSheet="0" activeTab="6" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="600" firstSheet="0" activeTab="8" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Instructions" sheetId="1" state="visible" r:id="rId1"/>
@@ -17,9 +17,9 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Koyfin - US" sheetId="9" state="visible" r:id="rId9"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm.Print_Area" localSheetId="2">'Cdn Hardcoded'!$A$1:$J$60</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="2">'Cdn Hardcoded'!$A$1:$K$43</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="3">'Cdn'!$A$1:$J$48</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="6">'US Hardcoded'!$A$1:$J$60</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="6">'US Hardcoded'!$A$1:$K$43</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="7">'US'!$A$1:$J$54</definedName>
   </definedNames>
   <calcPr calcId="191029" fullCalcOnLoad="1"/>
@@ -34,7 +34,7 @@
     <numFmt numFmtId="166" formatCode="[&gt;=1000]&quot;$&quot;#0.0,&quot;B&quot;;[&gt;=100]&quot;$&quot;#0.0,&quot;B&quot;;&quot;$&quot;#0.0"/>
     <numFmt numFmtId="167" formatCode="[$-F800]dddd\,\ mmmm\ dd\,\ yyyy"/>
   </numFmts>
-  <fonts count="26">
+  <fonts count="28">
     <font>
       <name val="Aptos Narrow"/>
       <family val="2"/>
@@ -214,8 +214,18 @@
       <sz val="12"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <b val="1"/>
+      <color rgb="FFC67A29"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <i val="1"/>
+      <color rgb="FF666666"/>
+      <sz val="10"/>
+    </font>
   </fonts>
-  <fills count="16">
+  <fills count="18">
     <fill>
       <patternFill/>
     </fill>
@@ -298,8 +308,18 @@
         <fgColor rgb="FFFFF3CD"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFCEFE0"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="15">
+  <borders count="19">
     <border>
       <left/>
       <right/>
@@ -453,11 +473,41 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium"/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFC67A29"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFC67A29"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFC67A29"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFC67A29"/>
+      </bottom>
+    </border>
+    <border/>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="FFD1DCE8"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="97">
+  <cellXfs count="118">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
@@ -686,25 +736,78 @@
     <xf numFmtId="164" fontId="20" fillId="11" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="19" fillId="8" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="166" fontId="19" fillId="8" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="19" fillId="10" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="166" fontId="19" fillId="10" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="164" fontId="20" fillId="11" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="19" fillId="10" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="166" fontId="19" fillId="10" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="12" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="19" fillId="15" borderId="7" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="19" fillId="15" borderId="10" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="centerContinuous"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="15" borderId="12" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="19" fillId="12" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="centerContinuous" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="5" fillId="2" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="19" fillId="8" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="166" fontId="19" fillId="8" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="15" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="8" borderId="15" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="8" borderId="15" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="8" borderId="15" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="20" fillId="11" borderId="15" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="8" borderId="15" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="19" fillId="8" borderId="15" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="8" borderId="15" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="16" borderId="16" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="16" borderId="16" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="27" fillId="17" borderId="17" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="17" borderId="17" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1260,7 +1363,7 @@
     <row r="2" ht="15.6" customHeight="1">
       <c r="A2" s="22" t="n"/>
       <c r="B2" s="21" t="n">
-        <v>46224.8272040635</v>
+        <v>46224.85673662008</v>
       </c>
       <c r="C2" s="22" t="n"/>
     </row>
@@ -1282,7 +1385,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:J60"/>
+  <dimension ref="A1:K49"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="1.21875" customWidth="1" style="11" min="1" max="1"/>
@@ -1292,10 +1395,10 @@
     <col width="16" customWidth="1" style="14" min="5" max="5"/>
     <col width="21" customWidth="1" style="14" min="6" max="6"/>
     <col width="13" customWidth="1" style="14" min="7" max="7"/>
-    <col width="14" customWidth="1" style="14" min="8" max="8"/>
-    <col width="56" customWidth="1" style="11" min="9" max="9"/>
-    <col width="1.21875" customWidth="1" style="11" min="10" max="10"/>
-    <col width="8.88671875" customWidth="1" style="11" min="11" max="11"/>
+    <col width="10" customWidth="1" style="14" min="8" max="8"/>
+    <col width="14" customWidth="1" style="11" min="9" max="9"/>
+    <col width="56" customWidth="1" style="11" min="10" max="10"/>
+    <col width="1.21875" customWidth="1" style="11" min="11" max="11"/>
     <col width="13.33203125" bestFit="1" customWidth="1" style="12" min="12" max="12"/>
     <col width="13.77734375" customWidth="1" style="11" min="13" max="13"/>
     <col width="8.88671875" customWidth="1" style="11" min="14" max="14"/>
@@ -1321,9 +1424,8 @@
           <t>Benchmark Beaters — Canadian Stocks</t>
         </is>
       </c>
-      <c r="H2" s="84">
-        <f>Date!B2</f>
-        <v/>
+      <c r="H2" s="84" t="n">
+        <v>46224.85673662008</v>
       </c>
       <c r="J2" s="83" t="n"/>
     </row>
@@ -1418,15 +1520,20 @@
       </c>
       <c r="H7" s="27" t="inlineStr">
         <is>
+          <t>Signal</t>
+        </is>
+      </c>
+      <c r="I7" s="27" t="inlineStr">
+        <is>
           <t>Mkt Cap ($M)</t>
         </is>
       </c>
-      <c r="I7" s="26" t="inlineStr">
+      <c r="J7" s="26" t="inlineStr">
         <is>
           <t>Business Description</t>
         </is>
       </c>
-      <c r="J7" s="26" t="n"/>
+      <c r="K7" s="26" t="n"/>
     </row>
     <row r="8" ht="24" customHeight="1">
       <c r="A8" s="36" t="n"/>
@@ -1454,17 +1561,22 @@
         </is>
       </c>
       <c r="G8" s="89" t="n">
-        <v>1.631</v>
-      </c>
-      <c r="H8" s="90" t="n">
+        <v>1.627</v>
+      </c>
+      <c r="H8" s="90" t="inlineStr">
+        <is>
+          <t>Streak</t>
+        </is>
+      </c>
+      <c r="I8" s="91" t="n">
         <v>2358.79</v>
       </c>
-      <c r="I8" s="53" t="inlineStr">
+      <c r="J8" s="53" t="inlineStr">
         <is>
           <t>Bird Construction Inc provides construction services in Canada</t>
         </is>
       </c>
-      <c r="J8" s="36" t="n"/>
+      <c r="K8" s="36" t="n"/>
     </row>
     <row r="9" ht="26.4" customHeight="1">
       <c r="A9" s="28" t="n"/>
@@ -1492,17 +1604,22 @@
         </is>
       </c>
       <c r="G9" s="89" t="n">
-        <v>1.175</v>
-      </c>
-      <c r="H9" s="91" t="n">
+        <v>1.172</v>
+      </c>
+      <c r="H9" s="92" t="inlineStr">
+        <is>
+          <t>Repeat</t>
+        </is>
+      </c>
+      <c r="I9" s="93" t="n">
         <v>555.83</v>
       </c>
-      <c r="I9" s="54" t="inlineStr">
+      <c r="J9" s="54" t="inlineStr">
         <is>
           <t>Mattr Corp operates as a materials technology company that serves the infrastructure markets including electrification transportation mining energy communication and water management markets in Canada the United States Europe the Middle East Africa and the Asia Pacific</t>
         </is>
       </c>
-      <c r="J9" s="28" t="n"/>
+      <c r="K9" s="28" t="n"/>
     </row>
     <row r="10" ht="20.4" customHeight="1">
       <c r="A10" s="36" t="n"/>
@@ -1530,17 +1647,22 @@
         </is>
       </c>
       <c r="G10" s="89" t="n">
-        <v>1.153</v>
-      </c>
-      <c r="H10" s="90" t="n">
+        <v>1.162</v>
+      </c>
+      <c r="H10" s="90" t="inlineStr">
+        <is>
+          <t>Streak</t>
+        </is>
+      </c>
+      <c r="I10" s="91" t="n">
         <v>284.57</v>
       </c>
-      <c r="I10" s="53" t="inlineStr">
+      <c r="J10" s="53" t="inlineStr">
         <is>
           <t>ADF Group Inc engages in the design and engineering of connections including industrial coatings in Canada and the United States</t>
         </is>
       </c>
-      <c r="J10" s="36" t="n"/>
+      <c r="K10" s="36" t="n"/>
     </row>
     <row r="11" ht="20.4" customHeight="1">
       <c r="A11" s="28" t="n"/>
@@ -1568,17 +1690,22 @@
         </is>
       </c>
       <c r="G11" s="89" t="n">
-        <v>0.732</v>
-      </c>
-      <c r="H11" s="91" t="n">
+        <v>0.735</v>
+      </c>
+      <c r="H11" s="92" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="I11" s="93" t="n">
         <v>2258.51</v>
       </c>
-      <c r="I11" s="54" t="inlineStr">
+      <c r="J11" s="54" t="inlineStr">
         <is>
           <t>Extendicare Inc through its subsidiaries provides care and services for seniors in Canada</t>
         </is>
       </c>
-      <c r="J11" s="28" t="n"/>
+      <c r="K11" s="28" t="n"/>
     </row>
     <row r="12" ht="20.4" customHeight="1">
       <c r="A12" s="36" t="n"/>
@@ -1608,15 +1735,20 @@
       <c r="G12" s="89" t="n">
         <v>0.5679999999999999</v>
       </c>
-      <c r="H12" s="90" t="n">
+      <c r="H12" s="90" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="I12" s="91" t="n">
         <v>1565.38</v>
       </c>
-      <c r="I12" s="53" t="inlineStr">
+      <c r="J12" s="53" t="inlineStr">
         <is>
           <t>Mullen Group Ltd provides a range of trucking and logistics services in Canada and the United States</t>
         </is>
       </c>
-      <c r="J12" s="36" t="n"/>
+      <c r="K12" s="36" t="n"/>
     </row>
     <row r="13" ht="24" customHeight="1">
       <c r="A13" s="28" t="n"/>
@@ -1644,17 +1776,22 @@
         </is>
       </c>
       <c r="G13" s="89" t="n">
-        <v>0.544</v>
-      </c>
-      <c r="H13" s="91" t="n">
+        <v>0.545</v>
+      </c>
+      <c r="H13" s="92" t="inlineStr">
+        <is>
+          <t>Repeat</t>
+        </is>
+      </c>
+      <c r="I13" s="93" t="n">
         <v>1892.54</v>
       </c>
-      <c r="I13" s="54" t="inlineStr">
+      <c r="J13" s="54" t="inlineStr">
         <is>
           <t>NFI Group Inc together with its subsidiaries manufactures and sells buses in North America the United Kingdom rest of Europe and the Asia Pacific</t>
         </is>
       </c>
-      <c r="J13" s="28" t="n"/>
+      <c r="K13" s="28" t="n"/>
     </row>
     <row r="14">
       <c r="A14" s="36" t="n"/>
@@ -1682,17 +1819,22 @@
         </is>
       </c>
       <c r="G14" s="89" t="n">
-        <v>0.456</v>
-      </c>
-      <c r="H14" s="90" t="n">
+        <v>0.458</v>
+      </c>
+      <c r="H14" s="90" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="I14" s="91" t="n">
         <v>53011.04</v>
       </c>
-      <c r="I14" s="53" t="inlineStr">
+      <c r="J14" s="53" t="inlineStr">
         <is>
           <t>Great-West Lifeco Inc engages in the life and health insurance retirement savings wealth and asset management and reinsurance businesses in Canada the United States and Europe</t>
         </is>
       </c>
-      <c r="J14" s="36" t="n"/>
+      <c r="K14" s="36" t="n"/>
     </row>
     <row r="15">
       <c r="A15" s="28" t="n"/>
@@ -1722,15 +1864,20 @@
       <c r="G15" s="89" t="n">
         <v>0.443</v>
       </c>
-      <c r="H15" s="91" t="n">
+      <c r="H15" s="92" t="inlineStr">
+        <is>
+          <t>Repeat</t>
+        </is>
+      </c>
+      <c r="I15" s="93" t="n">
         <v>2385.76</v>
       </c>
-      <c r="I15" s="54" t="inlineStr">
+      <c r="J15" s="54" t="inlineStr">
         <is>
           <t>Russel Metals Inc engages in the distribution of steel and other metal products in Canada and the United States</t>
         </is>
       </c>
-      <c r="J15" s="28" t="n"/>
+      <c r="K15" s="28" t="n"/>
     </row>
     <row r="16" ht="20.4" customHeight="1">
       <c r="A16" s="28" t="n"/>
@@ -1758,17 +1905,22 @@
         </is>
       </c>
       <c r="G16" s="89" t="n">
-        <v>0.376</v>
-      </c>
-      <c r="H16" s="90" t="n">
+        <v>0.38</v>
+      </c>
+      <c r="H16" s="90" t="inlineStr">
+        <is>
+          <t>Streak</t>
+        </is>
+      </c>
+      <c r="I16" s="91" t="n">
         <v>390.27</v>
       </c>
-      <c r="I16" s="53" t="inlineStr">
+      <c r="J16" s="53" t="inlineStr">
         <is>
           <t>K-Bro Linen Inc together with its subsidiaries provides laundry and linen services to healthcare organizations hotels and other commercial accounts in Canada and the United Kingdom</t>
         </is>
       </c>
-      <c r="J16" s="28" t="n"/>
+      <c r="K16" s="28" t="n"/>
     </row>
     <row r="17" ht="40.8" customHeight="1">
       <c r="A17" s="36" t="n"/>
@@ -1798,15 +1950,20 @@
       <c r="G17" s="89" t="n">
         <v>0.36</v>
       </c>
-      <c r="H17" s="91" t="n">
+      <c r="H17" s="92" t="inlineStr">
+        <is>
+          <t>Streak</t>
+        </is>
+      </c>
+      <c r="I17" s="93" t="n">
         <v>116001.23</v>
       </c>
-      <c r="I17" s="54" t="inlineStr">
+      <c r="J17" s="54" t="inlineStr">
         <is>
           <t>Bank of Montreal engages in the provision of diversified financial services primarily in North America</t>
         </is>
       </c>
-      <c r="J17" s="36" t="n"/>
+      <c r="K17" s="36" t="n"/>
     </row>
     <row r="18" ht="24" customHeight="1">
       <c r="A18" s="28" t="n"/>
@@ -1815,36 +1972,41 @@
       </c>
       <c r="C18" s="38" t="inlineStr">
         <is>
-          <t>ARG</t>
+          <t>POW</t>
         </is>
       </c>
       <c r="D18" s="39" t="inlineStr">
         <is>
-          <t>Amerigo Resources Ltd.</t>
+          <t>Power Corporation of Canada</t>
         </is>
       </c>
       <c r="E18" s="40" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="F18" s="40" t="inlineStr">
         <is>
-          <t>Metals and Mining</t>
+          <t>Insurance</t>
         </is>
       </c>
       <c r="G18" s="89" t="n">
         <v>0.34</v>
       </c>
-      <c r="H18" s="90" t="n">
-        <v>681.6799999999999</v>
-      </c>
-      <c r="I18" s="53" t="inlineStr">
-        <is>
-          <t>Amerigo Resources Ltd through its subsidiary Minera Valle Central S</t>
-        </is>
-      </c>
-      <c r="J18" s="28" t="n"/>
+      <c r="H18" s="90" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="I18" s="91" t="n">
+        <v>38174.66</v>
+      </c>
+      <c r="J18" s="53" t="inlineStr">
+        <is>
+          <t>Power Corporation of Canada an international management and holding company provides financial services in North America Europe and Asia</t>
+        </is>
+      </c>
+      <c r="K18" s="28" t="n"/>
     </row>
     <row r="19" ht="30.6" customHeight="1">
       <c r="A19" s="36" t="n"/>
@@ -1853,36 +2015,41 @@
       </c>
       <c r="C19" s="30" t="inlineStr">
         <is>
-          <t>POW</t>
+          <t>ARG</t>
         </is>
       </c>
       <c r="D19" s="31" t="inlineStr">
         <is>
-          <t>Power Corporation of Canada</t>
+          <t>Amerigo Resources Ltd.</t>
         </is>
       </c>
       <c r="E19" s="32" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Materials</t>
         </is>
       </c>
       <c r="F19" s="32" t="inlineStr">
         <is>
-          <t>Insurance</t>
+          <t>Metals and Mining</t>
         </is>
       </c>
       <c r="G19" s="89" t="n">
         <v>0.339</v>
       </c>
-      <c r="H19" s="91" t="n">
-        <v>38174.66</v>
-      </c>
-      <c r="I19" s="54" t="inlineStr">
-        <is>
-          <t>Power Corporation of Canada an international management and holding company provides financial services in North America Europe and Asia</t>
-        </is>
-      </c>
-      <c r="J19" s="36" t="n"/>
+      <c r="H19" s="92" t="inlineStr">
+        <is>
+          <t>Repeat</t>
+        </is>
+      </c>
+      <c r="I19" s="93" t="n">
+        <v>681.6799999999999</v>
+      </c>
+      <c r="J19" s="54" t="inlineStr">
+        <is>
+          <t>Amerigo Resources Ltd through its subsidiary Minera Valle Central S</t>
+        </is>
+      </c>
+      <c r="K19" s="36" t="n"/>
     </row>
     <row r="20" ht="30.6" customHeight="1">
       <c r="A20" s="28" t="n"/>
@@ -1910,17 +2077,22 @@
         </is>
       </c>
       <c r="G20" s="89" t="n">
-        <v>0.334</v>
-      </c>
-      <c r="H20" s="90" t="n">
+        <v>0.336</v>
+      </c>
+      <c r="H20" s="90" t="inlineStr">
+        <is>
+          <t>Streak</t>
+        </is>
+      </c>
+      <c r="I20" s="91" t="n">
         <v>41467.31</v>
       </c>
-      <c r="I20" s="53" t="inlineStr">
+      <c r="J20" s="53" t="inlineStr">
         <is>
           <t>Sun Life Financial Inc a financial services company provides asset management wealth insurance and health solutions to individual and institutional customers in Canada the United States the United Kingdom Ireland Hong Kong the Philippines Japan Indonesia India China Australia Singapore Vietnam Malaysia and Bermuda</t>
         </is>
       </c>
-      <c r="J20" s="28" t="n"/>
+      <c r="K20" s="28" t="n"/>
     </row>
     <row r="21" ht="30.6" customHeight="1">
       <c r="A21" s="36" t="n"/>
@@ -1948,17 +2120,22 @@
         </is>
       </c>
       <c r="G21" s="89" t="n">
-        <v>0.329</v>
-      </c>
-      <c r="H21" s="91" t="n">
+        <v>0.327</v>
+      </c>
+      <c r="H21" s="92" t="inlineStr">
+        <is>
+          <t>Streak</t>
+        </is>
+      </c>
+      <c r="I21" s="93" t="n">
         <v>72839.50999999999</v>
       </c>
-      <c r="I21" s="54" t="inlineStr">
+      <c r="J21" s="54" t="inlineStr">
         <is>
           <t>Canadian National Railway Company together with its subsidiaries engages in the rail intermodal trucking and related transportation businesses in Canada and the United States</t>
         </is>
       </c>
-      <c r="J21" s="36" t="n"/>
+      <c r="K21" s="36" t="n"/>
     </row>
     <row r="22" ht="24" customHeight="1">
       <c r="A22" s="28" t="n"/>
@@ -1988,15 +2165,20 @@
       <c r="G22" s="89" t="n">
         <v>0.324</v>
       </c>
-      <c r="H22" s="90" t="n">
+      <c r="H22" s="90" t="inlineStr">
+        <is>
+          <t>Streak</t>
+        </is>
+      </c>
+      <c r="I22" s="91" t="n">
         <v>101497.85</v>
       </c>
-      <c r="I22" s="53" t="inlineStr">
+      <c r="J22" s="53" t="inlineStr">
         <is>
           <t>Canadian Imperial Bank of Commerce a diversified financial institution provides various financial products and services to personal business public sector and institutional clients in Canada the United States and internationally</t>
         </is>
       </c>
-      <c r="J22" s="28" t="n"/>
+      <c r="K22" s="28" t="n"/>
     </row>
     <row r="23" ht="24" customHeight="1">
       <c r="A23" s="28" t="n"/>
@@ -2024,17 +2206,22 @@
         </is>
       </c>
       <c r="G23" s="89" t="n">
-        <v>0.324</v>
-      </c>
-      <c r="H23" s="91" t="n">
+        <v>0.323</v>
+      </c>
+      <c r="H23" s="92" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="I23" s="93" t="n">
         <v>189567.97</v>
       </c>
-      <c r="I23" s="54" t="inlineStr">
+      <c r="J23" s="54" t="inlineStr">
         <is>
           <t>The Toronto-Dominion Bank together with its subsidiaries provides various financial products and services in Canada the United States and internationally</t>
         </is>
       </c>
-      <c r="J23" s="28" t="n"/>
+      <c r="K23" s="28" t="n"/>
     </row>
     <row r="24" ht="24" customHeight="1">
       <c r="A24" s="36" t="n"/>
@@ -2064,15 +2251,20 @@
       <c r="G24" s="89" t="n">
         <v>0.317</v>
       </c>
-      <c r="H24" s="90" t="n">
+      <c r="H24" s="90" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="I24" s="91" t="n">
         <v>3018.47</v>
       </c>
-      <c r="I24" s="53" t="inlineStr">
+      <c r="J24" s="53" t="inlineStr">
         <is>
           <t>EQB Inc through its subsidiary Equitable Bank provides personal and commercial banking services to retail and commercial customers in Canada</t>
         </is>
       </c>
-      <c r="J24" s="36" t="n"/>
+      <c r="K24" s="36" t="n"/>
     </row>
     <row r="25" ht="24" customHeight="1">
       <c r="A25" s="28" t="n"/>
@@ -2102,15 +2294,20 @@
       <c r="G25" s="89" t="n">
         <v>0.31</v>
       </c>
-      <c r="H25" s="91" t="n">
+      <c r="H25" s="92" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="I25" s="93" t="n">
         <v>28518.97</v>
       </c>
-      <c r="I25" s="54" t="inlineStr">
+      <c r="J25" s="54" t="inlineStr">
         <is>
           <t>Pembina Pipeline Corporation provides energy transportation and midstream services</t>
         </is>
       </c>
-      <c r="J25" s="28" t="n"/>
+      <c r="K25" s="28" t="n"/>
     </row>
     <row r="26" ht="20.4" customHeight="1">
       <c r="A26" s="36" t="n"/>
@@ -2138,17 +2335,22 @@
         </is>
       </c>
       <c r="G26" s="89" t="n">
-        <v>0.309</v>
-      </c>
-      <c r="H26" s="90" t="n">
+        <v>0.308</v>
+      </c>
+      <c r="H26" s="90" t="inlineStr">
+        <is>
+          <t>Repeat</t>
+        </is>
+      </c>
+      <c r="I26" s="91" t="n">
         <v>13303.41</v>
       </c>
-      <c r="I26" s="53" t="inlineStr">
+      <c r="J26" s="53" t="inlineStr">
         <is>
           <t>IGM Financial Inc engages in the wealth and asset management business in Canada</t>
         </is>
       </c>
-      <c r="J26" s="36" t="n"/>
+      <c r="K26" s="36" t="n"/>
     </row>
     <row r="27" ht="24" customHeight="1">
       <c r="A27" s="36" t="n"/>
@@ -2176,17 +2378,22 @@
         </is>
       </c>
       <c r="G27" s="89" t="n">
-        <v>0.298</v>
-      </c>
-      <c r="H27" s="91" t="n">
+        <v>0.297</v>
+      </c>
+      <c r="H27" s="92" t="inlineStr">
+        <is>
+          <t>Streak</t>
+        </is>
+      </c>
+      <c r="I27" s="93" t="n">
         <v>275998.42</v>
       </c>
-      <c r="I27" s="54" t="inlineStr">
+      <c r="J27" s="54" t="inlineStr">
         <is>
           <t>Royal Bank of Canada operates as a diversified financial service company worldwide</t>
         </is>
       </c>
-      <c r="J27" s="36" t="n"/>
+      <c r="K27" s="36" t="n"/>
     </row>
     <row r="28" ht="20.4" customHeight="1">
       <c r="A28" s="28" t="n"/>
@@ -2214,17 +2421,22 @@
         </is>
       </c>
       <c r="G28" s="89" t="n">
-        <v>0.296</v>
-      </c>
-      <c r="H28" s="90" t="n">
+        <v>0.295</v>
+      </c>
+      <c r="H28" s="90" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="I28" s="91" t="n">
         <v>79823.21000000001</v>
       </c>
-      <c r="I28" s="53" t="inlineStr">
+      <c r="J28" s="53" t="inlineStr">
         <is>
           <t>Canadian Pacific Kansas City Limited together with its subsidiaries owns and operates a transcontinental freight railway in Canada the United States and Mexico</t>
         </is>
       </c>
-      <c r="J28" s="28" t="n"/>
+      <c r="K28" s="28" t="n"/>
     </row>
     <row r="29" ht="24" customHeight="1">
       <c r="A29" s="36" t="n"/>
@@ -2233,36 +2445,41 @@
       </c>
       <c r="C29" s="30" t="inlineStr">
         <is>
-          <t>CF</t>
+          <t>CU</t>
         </is>
       </c>
       <c r="D29" s="31" t="inlineStr">
         <is>
-          <t>Canaccord Genuity Group Inc.</t>
+          <t>Canadian Utilities Limited</t>
         </is>
       </c>
       <c r="E29" s="32" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Utilities</t>
         </is>
       </c>
       <c r="F29" s="32" t="inlineStr">
         <is>
-          <t>Capital Markets</t>
+          <t>Multi-Utilities</t>
         </is>
       </c>
       <c r="G29" s="89" t="n">
         <v>0.266</v>
       </c>
-      <c r="H29" s="91" t="n">
-        <v>976.67</v>
-      </c>
-      <c r="I29" s="54" t="inlineStr">
-        <is>
-          <t>Canaccord Genuity Group Inc operates as a full-service investment dealer in Canada the United States the United Kingdom Europe Crown Dependencies and Australia</t>
-        </is>
-      </c>
-      <c r="J29" s="36" t="n"/>
+      <c r="H29" s="92" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="I29" s="93" t="n">
+        <v>10045.65</v>
+      </c>
+      <c r="J29" s="54" t="inlineStr">
+        <is>
+          <t>Canadian Utilities Limited together with its subsidiaries engages in the electricity natural gas renewables pipelines and liquids businesses in Canada Australia and internationally</t>
+        </is>
+      </c>
+      <c r="K29" s="36" t="n"/>
     </row>
     <row r="30" ht="30.6" customHeight="1">
       <c r="A30" s="36" t="n"/>
@@ -2271,36 +2488,41 @@
       </c>
       <c r="C30" s="38" t="inlineStr">
         <is>
-          <t>CU</t>
+          <t>CF</t>
         </is>
       </c>
       <c r="D30" s="39" t="inlineStr">
         <is>
-          <t>Canadian Utilities Limited</t>
+          <t>Canaccord Genuity Group Inc.</t>
         </is>
       </c>
       <c r="E30" s="40" t="inlineStr">
         <is>
-          <t>Utilities</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="F30" s="40" t="inlineStr">
         <is>
-          <t>Multi-Utilities</t>
+          <t>Capital Markets</t>
         </is>
       </c>
       <c r="G30" s="89" t="n">
         <v>0.265</v>
       </c>
-      <c r="H30" s="90" t="n">
-        <v>10045.65</v>
-      </c>
-      <c r="I30" s="53" t="inlineStr">
-        <is>
-          <t>Canadian Utilities Limited together with its subsidiaries engages in the electricity natural gas renewables pipelines and liquids businesses in Canada Australia and internationally</t>
-        </is>
-      </c>
-      <c r="J30" s="36" t="n"/>
+      <c r="H30" s="90" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="I30" s="91" t="n">
+        <v>976.67</v>
+      </c>
+      <c r="J30" s="53" t="inlineStr">
+        <is>
+          <t>Canaccord Genuity Group Inc operates as a full-service investment dealer in Canada the United States the United Kingdom Europe Crown Dependencies and Australia</t>
+        </is>
+      </c>
+      <c r="K30" s="36" t="n"/>
     </row>
     <row r="31" ht="30.6" customHeight="1">
       <c r="A31" s="28" t="n"/>
@@ -2328,17 +2550,22 @@
         </is>
       </c>
       <c r="G31" s="89" t="n">
-        <v>0.257</v>
-      </c>
-      <c r="H31" s="91" t="n">
+        <v>0.254</v>
+      </c>
+      <c r="H31" s="92" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="I31" s="93" t="n">
         <v>2215.94</v>
       </c>
-      <c r="I31" s="54" t="inlineStr">
+      <c r="J31" s="54" t="inlineStr">
         <is>
           <t>Badger Infrastructure Solutions Ltd provides non-destructive excavating and related services to utilities industrial construction transportation and other industries in Canada and the United States</t>
         </is>
       </c>
-      <c r="J31" s="28" t="n"/>
+      <c r="K31" s="28" t="n"/>
     </row>
     <row r="32" ht="24" customHeight="1">
       <c r="A32" s="36" t="n"/>
@@ -2366,17 +2593,22 @@
         </is>
       </c>
       <c r="G32" s="89" t="n">
-        <v>0.237</v>
-      </c>
-      <c r="H32" s="90" t="n">
+        <v>0.238</v>
+      </c>
+      <c r="H32" s="90" t="inlineStr">
+        <is>
+          <t>Streak</t>
+        </is>
+      </c>
+      <c r="I32" s="91" t="n">
         <v>11282.66</v>
       </c>
-      <c r="I32" s="53" t="inlineStr">
+      <c r="J32" s="53" t="inlineStr">
         <is>
           <t>iA Financial Corporation Inc provides insurance and wealth management services for individual and group basis in Canada and the United States</t>
         </is>
       </c>
-      <c r="J32" s="36" t="n"/>
+      <c r="K32" s="36" t="n"/>
     </row>
     <row r="33" ht="20.4" customHeight="1">
       <c r="A33" s="28" t="n"/>
@@ -2404,17 +2636,22 @@
         </is>
       </c>
       <c r="G33" s="89" t="n">
-        <v>0.236</v>
-      </c>
-      <c r="H33" s="91" t="n">
+        <v>0.234</v>
+      </c>
+      <c r="H33" s="92" t="inlineStr">
+        <is>
+          <t>Repeat</t>
+        </is>
+      </c>
+      <c r="I33" s="93" t="n">
         <v>576.85</v>
       </c>
-      <c r="I33" s="54" t="inlineStr">
+      <c r="J33" s="54" t="inlineStr">
         <is>
           <t>Dexterra Group Inc engages in the provision of support services for the creation management and operation of infrastructure in Canada</t>
         </is>
       </c>
-      <c r="J33" s="28" t="n"/>
+      <c r="K33" s="28" t="n"/>
     </row>
     <row r="34" ht="30.6" customHeight="1">
       <c r="A34" s="36" t="n"/>
@@ -2444,15 +2681,20 @@
       <c r="G34" s="89" t="n">
         <v>0.227</v>
       </c>
-      <c r="H34" s="90" t="n">
+      <c r="H34" s="90" t="inlineStr">
+        <is>
+          <t>Repeat</t>
+        </is>
+      </c>
+      <c r="I34" s="91" t="n">
         <v>100391.39</v>
       </c>
-      <c r="I34" s="53" t="inlineStr">
+      <c r="J34" s="53" t="inlineStr">
         <is>
           <t>The Bank of Nova Scotia provides various banking products and services in Canada the United States Mexico Peru Chile Colombia the Caribbean and Central America and internationally</t>
         </is>
       </c>
-      <c r="J34" s="36" t="n"/>
+      <c r="K34" s="36" t="n"/>
     </row>
     <row r="35" ht="30.6" customHeight="1">
       <c r="A35" s="28" t="n"/>
@@ -2480,17 +2722,22 @@
         </is>
       </c>
       <c r="G35" s="89" t="n">
-        <v>0.219</v>
-      </c>
-      <c r="H35" s="91" t="n">
+        <v>0.22</v>
+      </c>
+      <c r="H35" s="92" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="I35" s="93" t="n">
         <v>927.72</v>
       </c>
-      <c r="I35" s="54" t="inlineStr">
+      <c r="J35" s="54" t="inlineStr">
         <is>
           <t>Black Diamond Group Limited provides specialty rentals and industrial services in Canada the United States and Australia</t>
         </is>
       </c>
-      <c r="J35" s="28" t="n"/>
+      <c r="K35" s="28" t="n"/>
     </row>
     <row r="36" ht="40.8" customHeight="1">
       <c r="A36" s="36" t="n"/>
@@ -2518,17 +2765,22 @@
         </is>
       </c>
       <c r="G36" s="89" t="n">
-        <v>0.215</v>
-      </c>
-      <c r="H36" s="90" t="n">
+        <v>0.216</v>
+      </c>
+      <c r="H36" s="90" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="I36" s="91" t="n">
         <v>65572.44</v>
       </c>
-      <c r="I36" s="53" t="inlineStr">
+      <c r="J36" s="53" t="inlineStr">
         <is>
           <t>Manulife Financial Corporation together with its subsidiaries provides financial products and services in the United States Canada Asia and internationally</t>
         </is>
       </c>
-      <c r="J36" s="36" t="n"/>
+      <c r="K36" s="36" t="n"/>
     </row>
     <row r="37" ht="24" customHeight="1">
       <c r="A37" s="28" t="n"/>
@@ -2556,17 +2808,22 @@
         </is>
       </c>
       <c r="G37" s="89" t="n">
-        <v>0.201</v>
-      </c>
-      <c r="H37" s="91" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="H37" s="92" t="inlineStr">
+        <is>
+          <t>Streak</t>
+        </is>
+      </c>
+      <c r="I37" s="93" t="n">
         <v>501.72</v>
       </c>
-      <c r="I37" s="54" t="inlineStr">
+      <c r="J37" s="54" t="inlineStr">
         <is>
           <t>Interfor Corporation together with its subsidiaries produces and sells wood products in Canada the United States Japan China Taiwan and internationally</t>
         </is>
       </c>
-      <c r="J37" s="28" t="n"/>
+      <c r="K37" s="28" t="n"/>
     </row>
     <row r="38" ht="20.4" customHeight="1">
       <c r="A38" s="36" t="n"/>
@@ -2596,15 +2853,20 @@
       <c r="G38" s="89" t="n">
         <v>0.174</v>
       </c>
-      <c r="H38" s="90" t="n">
+      <c r="H38" s="90" t="inlineStr">
+        <is>
+          <t>Repeat</t>
+        </is>
+      </c>
+      <c r="I38" s="91" t="n">
         <v>1330.28</v>
       </c>
-      <c r="I38" s="53" t="inlineStr">
+      <c r="J38" s="53" t="inlineStr">
         <is>
           <t>Spin Master Corp a children’s entertainment company engages in the creation design manufacture licensing and marketing of various toys entertainment products and digital games in North America Europe and internationally</t>
         </is>
       </c>
-      <c r="J38" s="36" t="n"/>
+      <c r="K38" s="36" t="n"/>
     </row>
     <row r="39" ht="24" customHeight="1">
       <c r="A39" s="28" t="n"/>
@@ -2632,280 +2894,199 @@
         </is>
       </c>
       <c r="G39" s="89" t="n">
-        <v>0.144</v>
-      </c>
-      <c r="H39" s="91" t="n">
+        <v>0.146</v>
+      </c>
+      <c r="H39" s="92" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="I39" s="93" t="n">
         <v>676.4400000000001</v>
       </c>
-      <c r="I39" s="54" t="inlineStr">
+      <c r="J39" s="54" t="inlineStr">
         <is>
           <t>Doman Building Materials Group Ltd through its subsidiaries engages in the wholesale distribution of building materials and home renovation products in the United States and Canada</t>
         </is>
       </c>
-      <c r="J39" s="28" t="n"/>
+      <c r="K39" s="28" t="n"/>
     </row>
     <row r="40" ht="20.4" customHeight="1">
       <c r="A40" s="36" t="n"/>
-      <c r="B40" s="48" t="n">
+      <c r="B40" s="106" t="n">
         <v>33</v>
       </c>
-      <c r="C40" s="38" t="inlineStr">
+      <c r="C40" s="107" t="inlineStr">
         <is>
           <t>DFY</t>
         </is>
       </c>
-      <c r="D40" s="39" t="inlineStr">
+      <c r="D40" s="108" t="inlineStr">
         <is>
           <t>Definity Financial Corporation</t>
         </is>
       </c>
-      <c r="E40" s="40" t="inlineStr">
+      <c r="E40" s="109" t="inlineStr">
         <is>
           <t>Financials</t>
         </is>
       </c>
-      <c r="F40" s="40" t="inlineStr">
+      <c r="F40" s="109" t="inlineStr">
         <is>
           <t>Insurance</t>
         </is>
       </c>
-      <c r="G40" s="89" t="n">
-        <v>0.079</v>
-      </c>
-      <c r="H40" s="90" t="n">
+      <c r="G40" s="110" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="H40" s="111" t="inlineStr">
+        <is>
+          <t>Repeat</t>
+        </is>
+      </c>
+      <c r="I40" s="112" t="n">
         <v>6226.62</v>
       </c>
-      <c r="I40" s="53" t="inlineStr">
+      <c r="J40" s="113" t="inlineStr">
         <is>
           <t>Definity Financial Corporation together with its subsidiaries offers property and casualty insurance products in Canada</t>
         </is>
       </c>
-      <c r="J40" s="36" t="n"/>
+      <c r="K40" s="36" t="n"/>
     </row>
     <row r="41" ht="15.6" customHeight="1" thickBot="1">
       <c r="A41" s="68" t="n"/>
-      <c r="B41" s="49" t="n"/>
-      <c r="C41" s="30" t="n"/>
-      <c r="D41" s="31" t="n"/>
-      <c r="E41" s="32" t="n"/>
-      <c r="F41" s="32" t="n"/>
-      <c r="G41" s="89" t="n"/>
-      <c r="H41" s="91" t="n"/>
-      <c r="I41" s="54" t="n"/>
-      <c r="J41" s="68" t="n"/>
-    </row>
-    <row r="42" ht="26.4" customHeight="1">
+      <c r="B41" s="69" t="n"/>
+      <c r="C41" s="70" t="n"/>
+      <c r="D41" s="71" t="n"/>
+      <c r="E41" s="72" t="n"/>
+      <c r="F41" s="72" t="n"/>
+      <c r="G41" s="94" t="n"/>
+      <c r="H41" s="95" t="n"/>
+      <c r="I41" s="96" t="n"/>
+      <c r="J41" s="74" t="n"/>
+      <c r="K41" s="68" t="n"/>
+    </row>
+    <row r="42" ht="34" customHeight="1">
       <c r="A42" s="43" t="n"/>
-      <c r="B42" s="48" t="n"/>
-      <c r="C42" s="38" t="n"/>
-      <c r="D42" s="39" t="n"/>
-      <c r="E42" s="40" t="n"/>
-      <c r="F42" s="40" t="n"/>
-      <c r="G42" s="89" t="n"/>
-      <c r="H42" s="90" t="n"/>
-      <c r="I42" s="53" t="n"/>
-      <c r="J42" s="43" t="n"/>
-    </row>
-    <row r="43" ht="26.4" customHeight="1" thickBot="1">
+      <c r="B42" s="114" t="inlineStr">
+        <is>
+          <t>🔓 Want to know which of these we would actually buy? Start your 14-Day Free Trial at www.5iresearch.ca/bb</t>
+        </is>
+      </c>
+      <c r="C42" s="115" t="n"/>
+      <c r="D42" s="115" t="n"/>
+      <c r="E42" s="115" t="n"/>
+      <c r="F42" s="115" t="n"/>
+      <c r="G42" s="115" t="n"/>
+      <c r="H42" s="115" t="n"/>
+      <c r="I42" s="115" t="n"/>
+      <c r="J42" s="115" t="n"/>
+      <c r="K42" s="43" t="n"/>
+    </row>
+    <row r="43" ht="28" customHeight="1" thickBot="1">
       <c r="A43" s="43" t="n"/>
-      <c r="B43" s="49" t="n"/>
-      <c r="C43" s="30" t="n"/>
-      <c r="D43" s="31" t="n"/>
-      <c r="E43" s="32" t="n"/>
-      <c r="F43" s="32" t="n"/>
-      <c r="G43" s="89" t="n"/>
-      <c r="H43" s="91" t="n"/>
-      <c r="I43" s="54" t="n"/>
-      <c r="J43" s="43" t="n"/>
-    </row>
-    <row r="44" ht="26.4" customHeight="1">
+      <c r="B43" s="116" t="inlineStr">
+        <is>
+          <t>Disclosure: While this table does not constitute any formal opinion on names presented, authors may own shares in non-Canadian securities listed above.</t>
+        </is>
+      </c>
+      <c r="C43" s="117" t="n"/>
+      <c r="D43" s="117" t="n"/>
+      <c r="E43" s="117" t="n"/>
+      <c r="F43" s="117" t="n"/>
+      <c r="G43" s="117" t="n"/>
+      <c r="H43" s="117" t="n"/>
+      <c r="I43" s="117" t="n"/>
+      <c r="J43" s="117" t="n"/>
+      <c r="K43" s="43" t="n"/>
+    </row>
+    <row r="44" ht="12" customHeight="1">
       <c r="A44" s="43" t="n"/>
-      <c r="B44" s="48" t="n"/>
-      <c r="C44" s="38" t="n"/>
-      <c r="D44" s="39" t="n"/>
-      <c r="E44" s="40" t="n"/>
-      <c r="F44" s="40" t="n"/>
-      <c r="G44" s="89" t="n"/>
-      <c r="H44" s="90" t="n"/>
-      <c r="I44" s="53" t="n"/>
-      <c r="J44" s="43" t="n"/>
-    </row>
-    <row r="45" ht="26.4" customHeight="1">
+      <c r="B44" s="58" t="n"/>
+      <c r="C44" s="59" t="n"/>
+      <c r="D44" s="59" t="n"/>
+      <c r="E44" s="59" t="n"/>
+      <c r="F44" s="59" t="n"/>
+      <c r="G44" s="59" t="n"/>
+      <c r="H44" s="98" t="n"/>
+      <c r="I44" s="59" t="n"/>
+      <c r="J44" s="60" t="n"/>
+      <c r="K44" s="43" t="n"/>
+    </row>
+    <row r="45" ht="15.6" customHeight="1">
       <c r="A45" s="43" t="n"/>
-      <c r="B45" s="49" t="n"/>
-      <c r="C45" s="30" t="n"/>
-      <c r="D45" s="31" t="n"/>
-      <c r="E45" s="32" t="n"/>
-      <c r="F45" s="32" t="n"/>
-      <c r="G45" s="89" t="n"/>
-      <c r="H45" s="91" t="n"/>
-      <c r="I45" s="54" t="n"/>
-      <c r="J45" s="43" t="n"/>
-    </row>
-    <row r="46" ht="26.4" customHeight="1" thickBot="1">
+      <c r="B45" s="67" t="n"/>
+      <c r="C45" s="64" t="n"/>
+      <c r="D45" s="66" t="n"/>
+      <c r="E45" s="64" t="n"/>
+      <c r="F45" s="64" t="n"/>
+      <c r="G45" s="64" t="n"/>
+      <c r="H45" s="99" t="n"/>
+      <c r="I45" s="64" t="n"/>
+      <c r="J45" s="65" t="n"/>
+      <c r="K45" s="43" t="n"/>
+    </row>
+    <row r="46" ht="9.6" customHeight="1" thickBot="1">
       <c r="A46" s="43" t="n"/>
-      <c r="B46" s="48" t="n"/>
-      <c r="C46" s="38" t="n"/>
-      <c r="D46" s="39" t="n"/>
-      <c r="E46" s="40" t="n"/>
-      <c r="F46" s="40" t="n"/>
-      <c r="G46" s="89" t="n"/>
-      <c r="H46" s="90" t="n"/>
-      <c r="I46" s="53" t="n"/>
-      <c r="J46" s="43" t="n"/>
-    </row>
-    <row r="47" ht="26.4" customHeight="1">
+      <c r="B46" s="61" t="n"/>
+      <c r="C46" s="62" t="n"/>
+      <c r="D46" s="62" t="n"/>
+      <c r="E46" s="62" t="n"/>
+      <c r="F46" s="62" t="n"/>
+      <c r="G46" s="62" t="n"/>
+      <c r="H46" s="100" t="n"/>
+      <c r="I46" s="62" t="n"/>
+      <c r="J46" s="63" t="n"/>
+      <c r="K46" s="43" t="n"/>
+    </row>
+    <row r="47">
       <c r="A47" s="43" t="n"/>
-      <c r="B47" s="49" t="n"/>
-      <c r="C47" s="30" t="n"/>
-      <c r="D47" s="31" t="n"/>
-      <c r="E47" s="32" t="n"/>
-      <c r="F47" s="32" t="n"/>
-      <c r="G47" s="89" t="n"/>
-      <c r="H47" s="91" t="n"/>
-      <c r="I47" s="54" t="n"/>
+      <c r="B47" s="43" t="n"/>
+      <c r="C47" s="43" t="n"/>
+      <c r="D47" s="43" t="n"/>
+      <c r="E47" s="43" t="n"/>
+      <c r="F47" s="43" t="n"/>
+      <c r="G47" s="43" t="n"/>
+      <c r="H47" s="97" t="n"/>
+      <c r="I47" s="43" t="n"/>
       <c r="J47" s="43" t="n"/>
-    </row>
-    <row r="48" ht="26.4" customHeight="1">
+      <c r="K47" s="43" t="n"/>
+    </row>
+    <row r="48">
       <c r="A48" s="43" t="n"/>
-      <c r="B48" s="48" t="n"/>
-      <c r="C48" s="38" t="n"/>
-      <c r="D48" s="39" t="n"/>
-      <c r="E48" s="40" t="n"/>
-      <c r="F48" s="40" t="n"/>
-      <c r="G48" s="89" t="n"/>
-      <c r="H48" s="90" t="n"/>
-      <c r="I48" s="53" t="n"/>
-      <c r="J48" s="43" t="n"/>
-    </row>
-    <row r="49" ht="26.4" customHeight="1">
+      <c r="B48" s="47" t="n"/>
+      <c r="C48" s="47" t="n"/>
+      <c r="D48" s="47" t="n"/>
+      <c r="E48" s="47" t="n"/>
+      <c r="F48" s="47" t="n"/>
+      <c r="G48" s="47" t="n"/>
+      <c r="H48" s="101" t="n"/>
+      <c r="I48" s="47" t="n"/>
+      <c r="J48" s="47" t="n"/>
+      <c r="K48" s="43" t="n"/>
+    </row>
+    <row r="49">
       <c r="A49" s="43" t="n"/>
-      <c r="B49" s="49" t="n"/>
-      <c r="C49" s="30" t="n"/>
-      <c r="D49" s="31" t="n"/>
-      <c r="E49" s="32" t="n"/>
-      <c r="F49" s="32" t="n"/>
-      <c r="G49" s="89" t="n"/>
-      <c r="H49" s="91" t="n"/>
-      <c r="I49" s="54" t="n"/>
+      <c r="B49" s="43" t="n"/>
+      <c r="C49" s="43" t="n"/>
+      <c r="D49" s="43" t="n"/>
+      <c r="E49" s="43" t="n"/>
+      <c r="F49" s="43" t="n"/>
+      <c r="G49" s="43" t="n"/>
+      <c r="H49" s="97" t="n"/>
+      <c r="I49" s="43" t="n"/>
       <c r="J49" s="43" t="n"/>
-    </row>
-    <row r="50" ht="26.4" customHeight="1">
-      <c r="B50" s="48" t="n"/>
-      <c r="C50" s="38" t="n"/>
-      <c r="D50" s="39" t="n"/>
-      <c r="E50" s="40" t="n"/>
-      <c r="F50" s="40" t="n"/>
-      <c r="G50" s="89" t="n"/>
-      <c r="H50" s="90" t="n"/>
-      <c r="I50" s="53" t="n"/>
-    </row>
-    <row r="51" ht="26.4" customHeight="1">
-      <c r="B51" s="49" t="n"/>
-      <c r="C51" s="30" t="n"/>
-      <c r="D51" s="31" t="n"/>
-      <c r="E51" s="32" t="n"/>
-      <c r="F51" s="32" t="n"/>
-      <c r="G51" s="89" t="n"/>
-      <c r="H51" s="91" t="n"/>
-      <c r="I51" s="54" t="n"/>
-    </row>
-    <row r="52" ht="26.4" customHeight="1">
-      <c r="B52" s="48" t="n"/>
-      <c r="C52" s="38" t="n"/>
-      <c r="D52" s="39" t="n"/>
-      <c r="E52" s="40" t="n"/>
-      <c r="F52" s="40" t="n"/>
-      <c r="G52" s="89" t="n"/>
-      <c r="H52" s="90" t="n"/>
-      <c r="I52" s="53" t="n"/>
-    </row>
-    <row r="53" ht="26.4" customHeight="1">
-      <c r="B53" s="49" t="n"/>
-      <c r="C53" s="30" t="n"/>
-      <c r="D53" s="31" t="n"/>
-      <c r="E53" s="32" t="n"/>
-      <c r="F53" s="32" t="n"/>
-      <c r="G53" s="89" t="n"/>
-      <c r="H53" s="91" t="n"/>
-      <c r="I53" s="54" t="n"/>
-    </row>
-    <row r="54" ht="26.4" customHeight="1">
-      <c r="B54" s="48" t="n"/>
-      <c r="C54" s="38" t="n"/>
-      <c r="D54" s="39" t="n"/>
-      <c r="E54" s="40" t="n"/>
-      <c r="F54" s="40" t="n"/>
-      <c r="G54" s="89" t="n"/>
-      <c r="H54" s="90" t="n"/>
-      <c r="I54" s="53" t="n"/>
-    </row>
-    <row r="55" ht="26.4" customHeight="1">
-      <c r="B55" s="49" t="n"/>
-      <c r="C55" s="30" t="n"/>
-      <c r="D55" s="31" t="n"/>
-      <c r="E55" s="32" t="n"/>
-      <c r="F55" s="32" t="n"/>
-      <c r="G55" s="89" t="n"/>
-      <c r="H55" s="91" t="n"/>
-      <c r="I55" s="54" t="n"/>
-    </row>
-    <row r="56" ht="26.4" customHeight="1">
-      <c r="B56" s="48" t="n"/>
-      <c r="C56" s="38" t="n"/>
-      <c r="D56" s="39" t="n"/>
-      <c r="E56" s="40" t="n"/>
-      <c r="F56" s="40" t="n"/>
-      <c r="G56" s="89" t="n"/>
-      <c r="H56" s="90" t="n"/>
-      <c r="I56" s="53" t="n"/>
-    </row>
-    <row r="57" ht="26.4" customHeight="1">
-      <c r="B57" s="49" t="n"/>
-      <c r="C57" s="30" t="n"/>
-      <c r="D57" s="31" t="n"/>
-      <c r="E57" s="32" t="n"/>
-      <c r="F57" s="32" t="n"/>
-      <c r="G57" s="89" t="n"/>
-      <c r="H57" s="91" t="n"/>
-      <c r="I57" s="54" t="n"/>
-    </row>
-    <row r="58" ht="26.4" customHeight="1">
-      <c r="B58" s="48" t="n"/>
-      <c r="C58" s="38" t="n"/>
-      <c r="D58" s="39" t="n"/>
-      <c r="E58" s="40" t="n"/>
-      <c r="F58" s="40" t="n"/>
-      <c r="G58" s="89" t="n"/>
-      <c r="H58" s="90" t="n"/>
-      <c r="I58" s="53" t="n"/>
-    </row>
-    <row r="59" ht="26.4" customHeight="1">
-      <c r="B59" s="49" t="n"/>
-      <c r="C59" s="30" t="n"/>
-      <c r="D59" s="31" t="n"/>
-      <c r="E59" s="32" t="n"/>
-      <c r="F59" s="32" t="n"/>
-      <c r="G59" s="89" t="n"/>
-      <c r="H59" s="91" t="n"/>
-      <c r="I59" s="54" t="n"/>
-    </row>
-    <row r="60" ht="26.4" customHeight="1">
-      <c r="B60" s="48" t="n"/>
-      <c r="C60" s="38" t="n"/>
-      <c r="D60" s="39" t="n"/>
-      <c r="E60" s="40" t="n"/>
-      <c r="F60" s="40" t="n"/>
-      <c r="G60" s="89" t="n"/>
-      <c r="H60" s="90" t="n"/>
-      <c r="I60" s="53" t="n"/>
+      <c r="K49" s="43" t="n"/>
     </row>
   </sheetData>
-  <mergeCells count="2">
+  <mergeCells count="4">
+    <mergeCell ref="B43:J43"/>
     <mergeCell ref="B2:G2"/>
     <mergeCell ref="H2:I2"/>
+    <mergeCell ref="B42:J42"/>
   </mergeCells>
-  <conditionalFormatting sqref="G8:G60">
+  <conditionalFormatting sqref="G8:G40">
     <cfRule type="colorScale" priority="1371">
       <colorScale>
         <cfvo type="min"/>
@@ -3032,14 +3213,14 @@
       </c>
     </row>
     <row r="11" ht="21" customHeight="1">
-      <c r="B11" s="94" t="n"/>
-      <c r="C11" s="94" t="n"/>
-      <c r="D11" s="94" t="n"/>
-      <c r="E11" s="94" t="n"/>
-      <c r="F11" s="94" t="n"/>
-      <c r="G11" s="94" t="n"/>
-      <c r="H11" s="94" t="n"/>
-      <c r="I11" s="94" t="n"/>
+      <c r="B11" s="102" t="n"/>
+      <c r="C11" s="102" t="n"/>
+      <c r="D11" s="102" t="n"/>
+      <c r="E11" s="102" t="n"/>
+      <c r="F11" s="102" t="n"/>
+      <c r="G11" s="102" t="n"/>
+      <c r="H11" s="102" t="n"/>
+      <c r="I11" s="102" t="n"/>
       <c r="J11" s="4" t="n"/>
       <c r="M11" s="19" t="inlineStr">
         <is>
@@ -3115,7 +3296,7 @@
     <row r="13" ht="15.6" customHeight="1" thickBot="1">
       <c r="A13" s="36" t="n"/>
       <c r="B13" s="48" t="n"/>
-      <c r="C13" s="95" t="n"/>
+      <c r="C13" s="103" t="n"/>
       <c r="D13" s="38" t="n"/>
       <c r="E13" s="39" t="n"/>
       <c r="F13" s="40" t="n"/>
@@ -3844,7 +4025,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:J60"/>
+  <dimension ref="A1:K49"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="1.21875" customWidth="1" style="11" min="1" max="1"/>
@@ -3854,10 +4035,10 @@
     <col width="16" customWidth="1" style="14" min="5" max="5"/>
     <col width="21" customWidth="1" style="14" min="6" max="6"/>
     <col width="13" customWidth="1" style="14" min="7" max="7"/>
-    <col width="14" customWidth="1" style="14" min="8" max="8"/>
-    <col width="56" customWidth="1" style="11" min="9" max="9"/>
-    <col width="1.21875" customWidth="1" style="11" min="10" max="10"/>
-    <col width="8.88671875" customWidth="1" style="11" min="11" max="11"/>
+    <col width="10" customWidth="1" style="14" min="8" max="8"/>
+    <col width="14" customWidth="1" style="11" min="9" max="9"/>
+    <col width="56" customWidth="1" style="11" min="10" max="10"/>
+    <col width="1.21875" customWidth="1" style="11" min="11" max="11"/>
     <col width="13.33203125" bestFit="1" customWidth="1" style="12" min="12" max="12"/>
     <col width="13.77734375" customWidth="1" style="11" min="13" max="13"/>
     <col width="8.88671875" customWidth="1" style="11" min="14" max="14"/>
@@ -3883,9 +4064,8 @@
           <t>Benchmark Beaters — U.S. Stocks</t>
         </is>
       </c>
-      <c r="H2" s="84">
-        <f>Date!B2</f>
-        <v/>
+      <c r="H2" s="84" t="n">
+        <v>46224.85673662008</v>
       </c>
       <c r="J2" s="83" t="n"/>
     </row>
@@ -3980,15 +4160,20 @@
       </c>
       <c r="H7" s="27" t="inlineStr">
         <is>
+          <t>Signal</t>
+        </is>
+      </c>
+      <c r="I7" s="27" t="inlineStr">
+        <is>
           <t>Mkt Cap ($M)</t>
         </is>
       </c>
-      <c r="I7" s="26" t="inlineStr">
+      <c r="J7" s="26" t="inlineStr">
         <is>
           <t>Business Description</t>
         </is>
       </c>
-      <c r="J7" s="26" t="n"/>
+      <c r="K7" s="26" t="n"/>
     </row>
     <row r="8" ht="24" customHeight="1">
       <c r="A8" s="36" t="n"/>
@@ -4016,17 +4201,22 @@
         </is>
       </c>
       <c r="G8" s="89" t="n">
-        <v>1.193</v>
-      </c>
-      <c r="H8" s="90" t="n">
+        <v>1.195</v>
+      </c>
+      <c r="H8" s="90" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="I8" s="91" t="n">
         <v>12725.72</v>
       </c>
-      <c r="I8" s="53" t="inlineStr">
+      <c r="J8" s="53" t="inlineStr">
         <is>
           <t>DaVita Inc provides kidney dialysis services for patients suffering from chronic kidney failure in the United States</t>
         </is>
       </c>
-      <c r="J8" s="36" t="n"/>
+      <c r="K8" s="36" t="n"/>
     </row>
     <row r="9" ht="24" customHeight="1">
       <c r="A9" s="28" t="n"/>
@@ -4056,15 +4246,20 @@
       <c r="G9" s="89" t="n">
         <v>0.899</v>
       </c>
-      <c r="H9" s="91" t="n">
+      <c r="H9" s="92" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="I9" s="93" t="n">
         <v>213908.98</v>
       </c>
-      <c r="I9" s="54" t="inlineStr">
+      <c r="J9" s="54" t="inlineStr">
         <is>
           <t>Palo Alto Networks Inc provides cybersecurity solutions in the Americas Europe the Middle East Africa the Asia Pacific and Japan</t>
         </is>
       </c>
-      <c r="J9" s="28" t="n"/>
+      <c r="K9" s="28" t="n"/>
     </row>
     <row r="10" ht="20.4" customHeight="1">
       <c r="A10" s="36" t="n"/>
@@ -4094,15 +4289,20 @@
       <c r="G10" s="89" t="n">
         <v>0.839</v>
       </c>
-      <c r="H10" s="90" t="n">
+      <c r="H10" s="90" t="inlineStr">
+        <is>
+          <t>Repeat</t>
+        </is>
+      </c>
+      <c r="I10" s="91" t="n">
         <v>77721.12</v>
       </c>
-      <c r="I10" s="53" t="inlineStr">
+      <c r="J10" s="53" t="inlineStr">
         <is>
           <t>Marathon Petroleum Corporation together with its subsidiaries operates as an integrated downstream energy company in the United States</t>
         </is>
       </c>
-      <c r="J10" s="36" t="n"/>
+      <c r="K10" s="36" t="n"/>
     </row>
     <row r="11" ht="24" customHeight="1">
       <c r="A11" s="28" t="n"/>
@@ -4132,15 +4332,20 @@
       <c r="G11" s="89" t="n">
         <v>0.701</v>
       </c>
-      <c r="H11" s="91" t="n">
+      <c r="H11" s="92" t="inlineStr">
+        <is>
+          <t>Repeat</t>
+        </is>
+      </c>
+      <c r="I11" s="93" t="n">
         <v>77190.64999999999</v>
       </c>
-      <c r="I11" s="54" t="inlineStr">
+      <c r="J11" s="54" t="inlineStr">
         <is>
           <t>Valero Energy Corporation manufactures markets and sells petroleum-based and low-carbon liquid transportation fuels and petrochemical products in the United States Canada the United Kingdom Ireland Latin America Mexico Peru and internationally</t>
         </is>
       </c>
-      <c r="J11" s="28" t="n"/>
+      <c r="K11" s="28" t="n"/>
     </row>
     <row r="12" ht="24" customHeight="1">
       <c r="A12" s="36" t="n"/>
@@ -4170,15 +4375,20 @@
       <c r="G12" s="89" t="n">
         <v>0.471</v>
       </c>
-      <c r="H12" s="90" t="n">
+      <c r="H12" s="90" t="inlineStr">
+        <is>
+          <t>Repeat</t>
+        </is>
+      </c>
+      <c r="I12" s="91" t="n">
         <v>44725.83</v>
       </c>
-      <c r="I12" s="53" t="inlineStr">
+      <c r="J12" s="53" t="inlineStr">
         <is>
           <t>State Street Corporation provides various financial products and services to institutional investors</t>
         </is>
       </c>
-      <c r="J12" s="36" t="n"/>
+      <c r="K12" s="36" t="n"/>
     </row>
     <row r="13" ht="20.4" customHeight="1">
       <c r="A13" s="28" t="n"/>
@@ -4208,15 +4418,20 @@
       <c r="G13" s="89" t="n">
         <v>0.424</v>
       </c>
-      <c r="H13" s="91" t="n">
+      <c r="H13" s="92" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="I13" s="93" t="n">
         <v>26566.73</v>
       </c>
-      <c r="I13" s="54" t="inlineStr">
+      <c r="J13" s="54" t="inlineStr">
         <is>
           <t>J</t>
         </is>
       </c>
-      <c r="J13" s="28" t="n"/>
+      <c r="K13" s="28" t="n"/>
     </row>
     <row r="14" ht="40.8" customHeight="1">
       <c r="A14" s="36" t="n"/>
@@ -4246,15 +4461,20 @@
       <c r="G14" s="89" t="n">
         <v>0.37</v>
       </c>
-      <c r="H14" s="90" t="n">
+      <c r="H14" s="90" t="inlineStr">
+        <is>
+          <t>Streak</t>
+        </is>
+      </c>
+      <c r="I14" s="91" t="n">
         <v>86617.14</v>
       </c>
-      <c r="I14" s="53" t="inlineStr">
+      <c r="J14" s="53" t="inlineStr">
         <is>
           <t>CSX Corporation together with its subsidiaries provides rail-based freight transportation services in the United States and Canada</t>
         </is>
       </c>
-      <c r="J14" s="36" t="n"/>
+      <c r="K14" s="36" t="n"/>
     </row>
     <row r="15" ht="30.6" customHeight="1">
       <c r="A15" s="28" t="n"/>
@@ -4284,15 +4504,20 @@
       <c r="G15" s="89" t="n">
         <v>0.356</v>
       </c>
-      <c r="H15" s="91" t="n">
+      <c r="H15" s="92" t="inlineStr">
+        <is>
+          <t>Repeat</t>
+        </is>
+      </c>
+      <c r="I15" s="93" t="n">
         <v>96186.41</v>
       </c>
-      <c r="I15" s="54" t="inlineStr">
+      <c r="J15" s="54" t="inlineStr">
         <is>
           <t>The Bank of New York Mellon Corporation provides a range of financial products and services in the United States and internationally</t>
         </is>
       </c>
-      <c r="J15" s="28" t="n"/>
+      <c r="K15" s="28" t="n"/>
     </row>
     <row r="16" ht="24" customHeight="1">
       <c r="A16" s="36" t="n"/>
@@ -4322,15 +4547,20 @@
       <c r="G16" s="89" t="n">
         <v>0.356</v>
       </c>
-      <c r="H16" s="90" t="n">
+      <c r="H16" s="90" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="I16" s="91" t="n">
         <v>12644.53</v>
       </c>
-      <c r="I16" s="53" t="inlineStr">
+      <c r="J16" s="53" t="inlineStr">
         <is>
           <t>Globe Life Inc through its subsidiaries provides various life and supplemental health insurance products to lower middle- and middle-income families in the United States</t>
         </is>
       </c>
-      <c r="J16" s="36" t="n"/>
+      <c r="K16" s="36" t="n"/>
     </row>
     <row r="17" ht="30.6" customHeight="1">
       <c r="A17" s="28" t="n"/>
@@ -4360,15 +4590,20 @@
       <c r="G17" s="89" t="n">
         <v>0.351</v>
       </c>
-      <c r="H17" s="91" t="n">
+      <c r="H17" s="92" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="I17" s="93" t="n">
         <v>148209.56</v>
       </c>
-      <c r="I17" s="54" t="inlineStr">
+      <c r="J17" s="54" t="inlineStr">
         <is>
           <t>Welltower Inc is a S&amp;P 500 company is positioned at the center of the silver economy focusing on rental housing for aging seniors across the United States United Kingdom and Canada</t>
         </is>
       </c>
-      <c r="J17" s="28" t="n"/>
+      <c r="K17" s="28" t="n"/>
     </row>
     <row r="18" ht="20.4" customHeight="1">
       <c r="A18" s="36" t="n"/>
@@ -4396,17 +4631,22 @@
         </is>
       </c>
       <c r="G18" s="89" t="n">
-        <v>0.343</v>
-      </c>
-      <c r="H18" s="90" t="n">
+        <v>0.344</v>
+      </c>
+      <c r="H18" s="90" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="I18" s="91" t="n">
         <v>125211.85</v>
       </c>
-      <c r="I18" s="53" t="inlineStr">
+      <c r="J18" s="53" t="inlineStr">
         <is>
           <t>CVS Health Corporation provides health solutions in the United States</t>
         </is>
       </c>
-      <c r="J18" s="36" t="n"/>
+      <c r="K18" s="36" t="n"/>
     </row>
     <row r="19" ht="20.4" customHeight="1">
       <c r="A19" s="28" t="n"/>
@@ -4436,15 +4676,20 @@
       <c r="G19" s="89" t="n">
         <v>0.341</v>
       </c>
-      <c r="H19" s="91" t="n">
+      <c r="H19" s="92" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="I19" s="93" t="n">
         <v>64533.41</v>
       </c>
-      <c r="I19" s="54" t="inlineStr">
+      <c r="J19" s="54" t="inlineStr">
         <is>
           <t>The Travelers Companies Inc through its subsidiaries provides a range of commercial and personal property and casualty insurance products and services to businesses government units associations and individuals in the United States Canada and internationally</t>
         </is>
       </c>
-      <c r="J19" s="28" t="n"/>
+      <c r="K19" s="28" t="n"/>
     </row>
     <row r="20" ht="24" customHeight="1">
       <c r="A20" s="36" t="n"/>
@@ -4474,15 +4719,20 @@
       <c r="G20" s="89" t="n">
         <v>0.324</v>
       </c>
-      <c r="H20" s="90" t="n">
+      <c r="H20" s="90" t="inlineStr">
+        <is>
+          <t>Repeat</t>
+        </is>
+      </c>
+      <c r="I20" s="91" t="n">
         <v>4309578.68</v>
       </c>
-      <c r="I20" s="53" t="inlineStr">
+      <c r="J20" s="53" t="inlineStr">
         <is>
           <t>Apple Inc designs manufactures and markets smartphones personal computers tablets wearables and accessories worldwide</t>
         </is>
       </c>
-      <c r="J20" s="36" t="n"/>
+      <c r="K20" s="36" t="n"/>
     </row>
     <row r="21" ht="20.4" customHeight="1">
       <c r="A21" s="28" t="n"/>
@@ -4510,17 +4760,22 @@
         </is>
       </c>
       <c r="G21" s="89" t="n">
-        <v>0.307</v>
-      </c>
-      <c r="H21" s="91" t="n">
+        <v>0.308</v>
+      </c>
+      <c r="H21" s="92" t="inlineStr">
+        <is>
+          <t>Repeat</t>
+        </is>
+      </c>
+      <c r="I21" s="93" t="n">
         <v>16078.79</v>
       </c>
-      <c r="I21" s="54" t="inlineStr">
+      <c r="J21" s="54" t="inlineStr">
         <is>
           <t>Best Buy Co</t>
         </is>
       </c>
-      <c r="J21" s="28" t="n"/>
+      <c r="K21" s="28" t="n"/>
     </row>
     <row r="22" ht="30.6" customHeight="1">
       <c r="A22" s="36" t="n"/>
@@ -4550,15 +4805,20 @@
       <c r="G22" s="89" t="n">
         <v>0.295</v>
       </c>
-      <c r="H22" s="90" t="n">
+      <c r="H22" s="90" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="I22" s="91" t="n">
         <v>39380.19</v>
       </c>
-      <c r="I22" s="53" t="inlineStr">
+      <c r="J22" s="53" t="inlineStr">
         <is>
           <t>Archer-Daniels-Midland Company provides human and animal nutrition ingredients and solutions in the United States Switzerland the Cayman Islands Brazil Mexico Canada the United Kingdom and internationally</t>
         </is>
       </c>
-      <c r="J22" s="36" t="n"/>
+      <c r="K22" s="36" t="n"/>
     </row>
     <row r="23" ht="20.4" customHeight="1">
       <c r="A23" s="28" t="n"/>
@@ -4588,15 +4848,20 @@
       <c r="G23" s="89" t="n">
         <v>0.292</v>
       </c>
-      <c r="H23" s="91" t="n">
+      <c r="H23" s="92" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="I23" s="93" t="n">
         <v>62147.38</v>
       </c>
-      <c r="I23" s="54" t="inlineStr">
+      <c r="J23" s="54" t="inlineStr">
         <is>
           <t>W</t>
         </is>
       </c>
-      <c r="J23" s="28" t="n"/>
+      <c r="K23" s="28" t="n"/>
     </row>
     <row r="24" ht="24" customHeight="1">
       <c r="A24" s="36" t="n"/>
@@ -4624,17 +4889,22 @@
         </is>
       </c>
       <c r="G24" s="89" t="n">
-        <v>0.291</v>
-      </c>
-      <c r="H24" s="90" t="n">
+        <v>0.292</v>
+      </c>
+      <c r="H24" s="90" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="I24" s="91" t="n">
         <v>14353.95</v>
       </c>
-      <c r="I24" s="53" t="inlineStr">
+      <c r="J24" s="53" t="inlineStr">
         <is>
           <t>Healthpeak Properties Inc is a Standard &amp; Poor’s 500 company that owns operates and develops high-quality real estate focused on healthcare discovery and delivery in the United States</t>
         </is>
       </c>
-      <c r="J24" s="36" t="n"/>
+      <c r="K24" s="36" t="n"/>
     </row>
     <row r="25" ht="30.6" customHeight="1">
       <c r="A25" s="28" t="n"/>
@@ -4662,17 +4932,22 @@
         </is>
       </c>
       <c r="G25" s="89" t="n">
-        <v>0.289</v>
-      </c>
-      <c r="H25" s="91" t="n">
+        <v>0.29</v>
+      </c>
+      <c r="H25" s="92" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="I25" s="93" t="n">
         <v>158667.48</v>
       </c>
-      <c r="I25" s="54" t="inlineStr">
+      <c r="J25" s="54" t="inlineStr">
         <is>
           <t>Union Pacific Corporation through its subsidiary Union Pacific Railroad Company operates in the railroad business in the United States</t>
         </is>
       </c>
-      <c r="J25" s="28" t="n"/>
+      <c r="K25" s="28" t="n"/>
     </row>
     <row r="26" ht="30.6" customHeight="1">
       <c r="A26" s="36" t="n"/>
@@ -4702,15 +4977,20 @@
       <c r="G26" s="89" t="n">
         <v>0.258</v>
       </c>
-      <c r="H26" s="90" t="n">
+      <c r="H26" s="90" t="inlineStr">
+        <is>
+          <t>Repeat</t>
+        </is>
+      </c>
+      <c r="I26" s="91" t="n">
         <v>30713.22</v>
       </c>
-      <c r="I26" s="53" t="inlineStr">
+      <c r="J26" s="53" t="inlineStr">
         <is>
           <t>Northern Trust Corporation a financial holding company provides wealth management asset servicing asset management and banking solutions for corporations institutions families and individuals</t>
         </is>
       </c>
-      <c r="J26" s="36" t="n"/>
+      <c r="K26" s="36" t="n"/>
     </row>
     <row r="27" ht="30.6" customHeight="1">
       <c r="A27" s="28" t="n"/>
@@ -4740,15 +5020,20 @@
       <c r="G27" s="89" t="n">
         <v>0.25</v>
       </c>
-      <c r="H27" s="91" t="n">
+      <c r="H27" s="92" t="inlineStr">
+        <is>
+          <t>Repeat</t>
+        </is>
+      </c>
+      <c r="I27" s="93" t="n">
         <v>55851.6</v>
       </c>
-      <c r="I27" s="54" t="inlineStr">
+      <c r="J27" s="54" t="inlineStr">
         <is>
           <t>MetLife Inc a financial services company provides insurance annuities employee benefits and asset management services worldwide</t>
         </is>
       </c>
-      <c r="J27" s="28" t="n"/>
+      <c r="K27" s="28" t="n"/>
     </row>
     <row r="28" ht="24" customHeight="1">
       <c r="A28" s="36" t="n"/>
@@ -4778,15 +5063,20 @@
       <c r="G28" s="89" t="n">
         <v>0.222</v>
       </c>
-      <c r="H28" s="90" t="n">
+      <c r="H28" s="90" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="I28" s="91" t="n">
         <v>23624.19</v>
       </c>
-      <c r="I28" s="53" t="inlineStr">
+      <c r="J28" s="53" t="inlineStr">
         <is>
           <t>Principal Financial Group Inc provides retirement asset management and insurance products and services to businesses individuals and institutional clients worldwide</t>
         </is>
       </c>
-      <c r="J28" s="36" t="n"/>
+      <c r="K28" s="36" t="n"/>
     </row>
     <row r="29" ht="20.4" customHeight="1">
       <c r="A29" s="28" t="n"/>
@@ -4816,15 +5106,20 @@
       <c r="G29" s="89" t="n">
         <v>0.203</v>
       </c>
-      <c r="H29" s="91" t="n">
+      <c r="H29" s="92" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="I29" s="93" t="n">
         <v>40474.89</v>
       </c>
-      <c r="I29" s="54" t="inlineStr">
+      <c r="J29" s="54" t="inlineStr">
         <is>
           <t>Block Inc together with its subsidiaries builds ecosystems focused on commerce and financial products and services in the United States and internationally</t>
         </is>
       </c>
-      <c r="J29" s="28" t="n"/>
+      <c r="K29" s="28" t="n"/>
     </row>
     <row r="30">
       <c r="A30" s="36" t="n"/>
@@ -4852,17 +5147,22 @@
         </is>
       </c>
       <c r="G30" s="89" t="n">
-        <v>0.196</v>
-      </c>
-      <c r="H30" s="90" t="n">
+        <v>0.197</v>
+      </c>
+      <c r="H30" s="90" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="I30" s="91" t="n">
         <v>388502.86</v>
       </c>
-      <c r="I30" s="53" t="inlineStr">
+      <c r="J30" s="53" t="inlineStr">
         <is>
           <t>Bank of America Corporation through its subsidiaries provides various financial products and services for individual consumers small and middle-market businesses institutional investors large corporations and governments worldwide</t>
         </is>
       </c>
-      <c r="J30" s="36" t="n"/>
+      <c r="K30" s="36" t="n"/>
     </row>
     <row r="31">
       <c r="A31" s="28" t="n"/>
@@ -4892,15 +5192,20 @@
       <c r="G31" s="89" t="n">
         <v>0.193</v>
       </c>
-      <c r="H31" s="91" t="n">
+      <c r="H31" s="92" t="inlineStr">
+        <is>
+          <t>Repeat</t>
+        </is>
+      </c>
+      <c r="I31" s="93" t="n">
         <v>308648.81</v>
       </c>
-      <c r="I31" s="54" t="inlineStr">
+      <c r="J31" s="54" t="inlineStr">
         <is>
           <t>The Goldman Sachs Group Inc a financial institution provides a range of financial services for corporations financial institutions governments and individuals in the Americas Europe the Middle East Africa and Asia</t>
         </is>
       </c>
-      <c r="J31" s="28" t="n"/>
+      <c r="K31" s="28" t="n"/>
     </row>
     <row r="32" ht="24" customHeight="1">
       <c r="A32" s="36" t="n"/>
@@ -4930,15 +5235,20 @@
       <c r="G32" s="89" t="n">
         <v>0.18</v>
       </c>
-      <c r="H32" s="90" t="n">
+      <c r="H32" s="90" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="I32" s="91" t="n">
         <v>13320.91</v>
       </c>
-      <c r="I32" s="53" t="inlineStr">
+      <c r="J32" s="53" t="inlineStr">
         <is>
           <t>Everest Group Ltd together with subsidiaries provides reinsurance and insurance products in the United States Europe and internationally</t>
         </is>
       </c>
-      <c r="J32" s="36" t="n"/>
+      <c r="K32" s="36" t="n"/>
     </row>
     <row r="33" ht="20.4" customHeight="1">
       <c r="A33" s="28" t="n"/>
@@ -4968,15 +5278,20 @@
       <c r="G33" s="89" t="n">
         <v>0.166</v>
       </c>
-      <c r="H33" s="91" t="n">
+      <c r="H33" s="92" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="I33" s="93" t="n">
         <v>27585.86</v>
       </c>
-      <c r="I33" s="54" t="inlineStr">
+      <c r="J33" s="54" t="inlineStr">
         <is>
           <t>Citizens Financial Group Inc operates as the bank holding company that provides retail and commercial banking products and services to individuals small businesses middle-market companies large corporations and institutions in the United States</t>
         </is>
       </c>
-      <c r="J33" s="28" t="n"/>
+      <c r="K33" s="28" t="n"/>
     </row>
     <row r="34" ht="24" customHeight="1">
       <c r="A34" s="36" t="n"/>
@@ -5006,15 +5321,20 @@
       <c r="G34" s="89" t="n">
         <v>0.155</v>
       </c>
-      <c r="H34" s="90" t="n">
+      <c r="H34" s="90" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="I34" s="91" t="n">
         <v>47955.66</v>
       </c>
-      <c r="I34" s="53" t="inlineStr">
+      <c r="J34" s="53" t="inlineStr">
         <is>
           <t>Fifth Third Bancorp operates as the bank holding company for Fifth Third Bank National Association that provides a range of financial products and services in the United States</t>
         </is>
       </c>
-      <c r="J34" s="36" t="n"/>
+      <c r="K34" s="36" t="n"/>
     </row>
     <row r="35" ht="20.4" customHeight="1">
       <c r="A35" s="28" t="n"/>
@@ -5044,15 +5364,20 @@
       <c r="G35" s="89" t="n">
         <v>0.152</v>
       </c>
-      <c r="H35" s="91" t="n">
+      <c r="H35" s="92" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="I35" s="93" t="n">
         <v>89144.46000000001</v>
       </c>
-      <c r="I35" s="54" t="inlineStr">
+      <c r="J35" s="54" t="inlineStr">
         <is>
           <t>Monster Beverage Corporation through its subsidiaries engages in development marketing sale and distribution of energy drink beverages and concentrates in the United States and internationally</t>
         </is>
       </c>
-      <c r="J35" s="28" t="n"/>
+      <c r="K35" s="28" t="n"/>
     </row>
     <row r="36" ht="30.6" customHeight="1">
       <c r="A36" s="36" t="n"/>
@@ -5082,15 +5407,20 @@
       <c r="G36" s="89" t="n">
         <v>0.131</v>
       </c>
-      <c r="H36" s="90" t="n">
+      <c r="H36" s="90" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="I36" s="91" t="n">
         <v>36717.82</v>
       </c>
-      <c r="I36" s="53" t="inlineStr">
+      <c r="J36" s="53" t="inlineStr">
         <is>
           <t>Prudential Financial Inc together with its subsidiaries provides financial products and services in the United States Japan and internationally</t>
         </is>
       </c>
-      <c r="J36" s="36" t="n"/>
+      <c r="K36" s="36" t="n"/>
     </row>
     <row r="37" ht="30.6" customHeight="1">
       <c r="A37" s="28" t="n"/>
@@ -5120,15 +5450,20 @@
       <c r="G37" s="89" t="n">
         <v>0.127</v>
       </c>
-      <c r="H37" s="91" t="n">
+      <c r="H37" s="92" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="I37" s="93" t="n">
         <v>21453.67</v>
       </c>
-      <c r="I37" s="54" t="inlineStr">
+      <c r="J37" s="54" t="inlineStr">
         <is>
           <t>Expeditors International of Washington Inc together with its subsidiaries provides logistics services in the Americas North Asia South Asia Europe and Middle East Africa and India</t>
         </is>
       </c>
-      <c r="J37" s="28" t="n"/>
+      <c r="K37" s="28" t="n"/>
     </row>
     <row r="38" ht="20.4" customHeight="1">
       <c r="A38" s="36" t="n"/>
@@ -5156,17 +5491,22 @@
         </is>
       </c>
       <c r="G38" s="89" t="n">
-        <v>0.096</v>
-      </c>
-      <c r="H38" s="90" t="n">
+        <v>0.095</v>
+      </c>
+      <c r="H38" s="90" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="I38" s="91" t="n">
         <v>612046.08</v>
       </c>
-      <c r="I38" s="53" t="inlineStr">
+      <c r="J38" s="53" t="inlineStr">
         <is>
           <t>Visa Inc operates as a payment technology company in the United States and internationally</t>
         </is>
       </c>
-      <c r="J38" s="36" t="n"/>
+      <c r="K38" s="36" t="n"/>
     </row>
     <row r="39" ht="24" customHeight="1">
       <c r="A39" s="28" t="n"/>
@@ -5196,53 +5536,63 @@
       <c r="G39" s="89" t="n">
         <v>0.075</v>
       </c>
-      <c r="H39" s="91" t="n">
+      <c r="H39" s="92" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="I39" s="93" t="n">
         <v>36258.68</v>
       </c>
-      <c r="I39" s="54" t="inlineStr">
+      <c r="J39" s="54" t="inlineStr">
         <is>
           <t>Paychex Inc together with its subsidiaries provides human capital management solutions (HCM) for payroll employee benefits human resources (HR) and insurance services for small to medium-sized businesses in the United States Europe and India</t>
         </is>
       </c>
-      <c r="J39" s="28" t="n"/>
+      <c r="K39" s="28" t="n"/>
     </row>
     <row r="40" ht="24" customHeight="1">
       <c r="A40" s="36" t="n"/>
-      <c r="B40" s="48" t="n">
+      <c r="B40" s="106" t="n">
         <v>33</v>
       </c>
-      <c r="C40" s="38" t="inlineStr">
+      <c r="C40" s="107" t="inlineStr">
         <is>
           <t>BXP</t>
         </is>
       </c>
-      <c r="D40" s="39" t="inlineStr">
+      <c r="D40" s="108" t="inlineStr">
         <is>
           <t>BXP Inc.</t>
         </is>
       </c>
-      <c r="E40" s="40" t="inlineStr">
+      <c r="E40" s="109" t="inlineStr">
         <is>
           <t>Real Estate</t>
         </is>
       </c>
-      <c r="F40" s="40" t="inlineStr">
+      <c r="F40" s="109" t="inlineStr">
         <is>
           <t>Office REITs</t>
         </is>
       </c>
-      <c r="G40" s="89" t="n">
+      <c r="G40" s="110" t="n">
         <v>0.068</v>
       </c>
-      <c r="H40" s="90" t="n">
+      <c r="H40" s="111" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="I40" s="112" t="n">
         <v>11826.25</v>
       </c>
-      <c r="I40" s="53" t="inlineStr">
+      <c r="J40" s="113" t="inlineStr">
         <is>
           <t>BXP Inc (BXP) is the largest publicly traded developer owner and manager of premier workplaces in the United States</t>
         </is>
       </c>
-      <c r="J40" s="36" t="n"/>
+      <c r="K40" s="36" t="n"/>
     </row>
     <row r="41" ht="30.6" customHeight="1">
       <c r="A41" s="28" t="n"/>
@@ -5252,222 +5602,131 @@
       <c r="E41" s="32" t="n"/>
       <c r="F41" s="32" t="n"/>
       <c r="G41" s="89" t="n"/>
-      <c r="H41" s="91" t="n"/>
-      <c r="I41" s="54" t="n"/>
-      <c r="J41" s="28" t="n"/>
-    </row>
-    <row r="42" ht="24" customHeight="1" thickBot="1">
+      <c r="H41" s="92" t="n"/>
+      <c r="I41" s="93" t="n"/>
+      <c r="J41" s="54" t="n"/>
+      <c r="K41" s="28" t="n"/>
+    </row>
+    <row r="42" ht="34" customHeight="1" thickBot="1">
       <c r="A42" s="75" t="n"/>
-      <c r="B42" s="48" t="n"/>
-      <c r="C42" s="38" t="n"/>
-      <c r="D42" s="39" t="n"/>
-      <c r="E42" s="40" t="n"/>
-      <c r="F42" s="40" t="n"/>
-      <c r="G42" s="89" t="n"/>
-      <c r="H42" s="90" t="n"/>
-      <c r="I42" s="53" t="n"/>
-      <c r="J42" s="75" t="n"/>
-    </row>
-    <row r="43" ht="24" customHeight="1">
+      <c r="B42" s="114" t="inlineStr">
+        <is>
+          <t>🔓 Want to know which of these we would actually buy? Start your 14-Day Free Trial at www.5iresearch.ca/bb</t>
+        </is>
+      </c>
+      <c r="C42" s="115" t="n"/>
+      <c r="D42" s="115" t="n"/>
+      <c r="E42" s="115" t="n"/>
+      <c r="F42" s="115" t="n"/>
+      <c r="G42" s="115" t="n"/>
+      <c r="H42" s="115" t="n"/>
+      <c r="I42" s="115" t="n"/>
+      <c r="J42" s="115" t="n"/>
+      <c r="K42" s="75" t="n"/>
+    </row>
+    <row r="43" ht="28" customHeight="1">
       <c r="A43" s="43" t="n"/>
-      <c r="B43" s="49" t="n"/>
-      <c r="C43" s="30" t="n"/>
-      <c r="D43" s="31" t="n"/>
-      <c r="E43" s="32" t="n"/>
-      <c r="F43" s="32" t="n"/>
-      <c r="G43" s="89" t="n"/>
-      <c r="H43" s="91" t="n"/>
-      <c r="I43" s="54" t="n"/>
-      <c r="J43" s="43" t="n"/>
-    </row>
-    <row r="44" ht="24" customHeight="1" thickBot="1">
+      <c r="B43" s="116" t="inlineStr">
+        <is>
+          <t>Disclosure: While this table does not constitute any formal opinion on names presented, authors may own shares in non-Canadian securities listed above.</t>
+        </is>
+      </c>
+      <c r="C43" s="117" t="n"/>
+      <c r="D43" s="117" t="n"/>
+      <c r="E43" s="117" t="n"/>
+      <c r="F43" s="117" t="n"/>
+      <c r="G43" s="117" t="n"/>
+      <c r="H43" s="117" t="n"/>
+      <c r="I43" s="117" t="n"/>
+      <c r="J43" s="117" t="n"/>
+      <c r="K43" s="43" t="n"/>
+    </row>
+    <row r="44" ht="15.6" customHeight="1" thickBot="1">
       <c r="A44" s="43" t="n"/>
-      <c r="B44" s="48" t="n"/>
-      <c r="C44" s="38" t="n"/>
-      <c r="D44" s="39" t="n"/>
-      <c r="E44" s="40" t="n"/>
-      <c r="F44" s="40" t="n"/>
-      <c r="G44" s="89" t="n"/>
-      <c r="H44" s="90" t="n"/>
-      <c r="I44" s="53" t="n"/>
+      <c r="B44" s="43" t="n"/>
+      <c r="C44" s="43" t="n"/>
+      <c r="D44" s="43" t="n"/>
+      <c r="E44" s="43" t="n"/>
+      <c r="F44" s="43" t="n"/>
+      <c r="G44" s="43" t="n"/>
+      <c r="H44" s="97" t="n"/>
+      <c r="I44" s="43" t="n"/>
       <c r="J44" s="43" t="n"/>
-    </row>
-    <row r="45" ht="24" customHeight="1">
+      <c r="K44" s="43" t="n"/>
+    </row>
+    <row r="45" ht="10.2" customHeight="1">
       <c r="A45" s="43" t="n"/>
-      <c r="B45" s="49" t="n"/>
-      <c r="C45" s="30" t="n"/>
-      <c r="D45" s="31" t="n"/>
-      <c r="E45" s="32" t="n"/>
-      <c r="F45" s="32" t="n"/>
-      <c r="G45" s="89" t="n"/>
-      <c r="H45" s="91" t="n"/>
-      <c r="I45" s="54" t="n"/>
-      <c r="J45" s="43" t="n"/>
-    </row>
-    <row r="46" ht="24" customHeight="1">
+      <c r="B45" s="58" t="n"/>
+      <c r="C45" s="59" t="n"/>
+      <c r="D45" s="59" t="n"/>
+      <c r="E45" s="59" t="n"/>
+      <c r="F45" s="59" t="n"/>
+      <c r="G45" s="59" t="n"/>
+      <c r="H45" s="98" t="n"/>
+      <c r="I45" s="59" t="n"/>
+      <c r="J45" s="60" t="n"/>
+      <c r="K45" s="43" t="n"/>
+    </row>
+    <row r="46" ht="15.6" customHeight="1">
       <c r="A46" s="43" t="n"/>
-      <c r="B46" s="48" t="n"/>
-      <c r="C46" s="38" t="n"/>
-      <c r="D46" s="39" t="n"/>
-      <c r="E46" s="40" t="n"/>
-      <c r="F46" s="40" t="n"/>
-      <c r="G46" s="89" t="n"/>
-      <c r="H46" s="90" t="n"/>
-      <c r="I46" s="53" t="n"/>
-      <c r="J46" s="43" t="n"/>
-    </row>
-    <row r="47" ht="24" customHeight="1" thickBot="1">
+      <c r="B46" s="67" t="n"/>
+      <c r="C46" s="64" t="n"/>
+      <c r="D46" s="64" t="n"/>
+      <c r="E46" s="64" t="n"/>
+      <c r="F46" s="64" t="n"/>
+      <c r="G46" s="64" t="n"/>
+      <c r="H46" s="99" t="n"/>
+      <c r="I46" s="64" t="n"/>
+      <c r="J46" s="65" t="n"/>
+      <c r="K46" s="43" t="n"/>
+    </row>
+    <row r="47" ht="10.8" customHeight="1" thickBot="1">
       <c r="A47" s="43" t="n"/>
-      <c r="B47" s="49" t="n"/>
-      <c r="C47" s="30" t="n"/>
-      <c r="D47" s="31" t="n"/>
-      <c r="E47" s="32" t="n"/>
-      <c r="F47" s="32" t="n"/>
-      <c r="G47" s="89" t="n"/>
-      <c r="H47" s="91" t="n"/>
-      <c r="I47" s="54" t="n"/>
-      <c r="J47" s="43" t="n"/>
-    </row>
-    <row r="48" ht="24" customHeight="1">
+      <c r="B47" s="61" t="n"/>
+      <c r="C47" s="62" t="n"/>
+      <c r="D47" s="62" t="n"/>
+      <c r="E47" s="62" t="n"/>
+      <c r="F47" s="62" t="n"/>
+      <c r="G47" s="62" t="n"/>
+      <c r="H47" s="100" t="n"/>
+      <c r="I47" s="62" t="n"/>
+      <c r="J47" s="63" t="n"/>
+      <c r="K47" s="43" t="n"/>
+    </row>
+    <row r="48">
       <c r="A48" s="43" t="n"/>
-      <c r="B48" s="48" t="n"/>
-      <c r="C48" s="38" t="n"/>
-      <c r="D48" s="39" t="n"/>
-      <c r="E48" s="40" t="n"/>
-      <c r="F48" s="40" t="n"/>
-      <c r="G48" s="89" t="n"/>
-      <c r="H48" s="90" t="n"/>
-      <c r="I48" s="53" t="n"/>
+      <c r="B48" s="43" t="n"/>
+      <c r="C48" s="43" t="n"/>
+      <c r="D48" s="43" t="n"/>
+      <c r="E48" s="43" t="n"/>
+      <c r="F48" s="43" t="n"/>
+      <c r="G48" s="43" t="n"/>
+      <c r="H48" s="97" t="n"/>
+      <c r="I48" s="43" t="n"/>
       <c r="J48" s="43" t="n"/>
-    </row>
-    <row r="49" ht="24" customHeight="1">
+      <c r="K48" s="43" t="n"/>
+    </row>
+    <row r="49">
       <c r="A49" s="43" t="n"/>
-      <c r="B49" s="49" t="n"/>
-      <c r="C49" s="30" t="n"/>
-      <c r="D49" s="31" t="n"/>
-      <c r="E49" s="32" t="n"/>
-      <c r="F49" s="32" t="n"/>
-      <c r="G49" s="89" t="n"/>
-      <c r="H49" s="91" t="n"/>
-      <c r="I49" s="54" t="n"/>
-      <c r="J49" s="43" t="n"/>
-    </row>
-    <row r="50" ht="24" customHeight="1">
-      <c r="B50" s="48" t="n"/>
-      <c r="C50" s="38" t="n"/>
-      <c r="D50" s="39" t="n"/>
-      <c r="E50" s="40" t="n"/>
-      <c r="F50" s="40" t="n"/>
-      <c r="G50" s="89" t="n"/>
-      <c r="H50" s="90" t="n"/>
-      <c r="I50" s="53" t="n"/>
-    </row>
-    <row r="51" ht="24" customHeight="1">
-      <c r="B51" s="49" t="n"/>
-      <c r="C51" s="30" t="n"/>
-      <c r="D51" s="31" t="n"/>
-      <c r="E51" s="32" t="n"/>
-      <c r="F51" s="32" t="n"/>
-      <c r="G51" s="89" t="n"/>
-      <c r="H51" s="91" t="n"/>
-      <c r="I51" s="54" t="n"/>
-    </row>
-    <row r="52" ht="24" customHeight="1">
-      <c r="B52" s="48" t="n"/>
-      <c r="C52" s="38" t="n"/>
-      <c r="D52" s="39" t="n"/>
-      <c r="E52" s="40" t="n"/>
-      <c r="F52" s="40" t="n"/>
-      <c r="G52" s="89" t="n"/>
-      <c r="H52" s="90" t="n"/>
-      <c r="I52" s="53" t="n"/>
-    </row>
-    <row r="53" ht="24" customHeight="1">
-      <c r="B53" s="49" t="n"/>
-      <c r="C53" s="30" t="n"/>
-      <c r="D53" s="31" t="n"/>
-      <c r="E53" s="32" t="n"/>
-      <c r="F53" s="32" t="n"/>
-      <c r="G53" s="89" t="n"/>
-      <c r="H53" s="91" t="n"/>
-      <c r="I53" s="54" t="n"/>
-    </row>
-    <row r="54" ht="24" customHeight="1">
-      <c r="B54" s="48" t="n"/>
-      <c r="C54" s="38" t="n"/>
-      <c r="D54" s="39" t="n"/>
-      <c r="E54" s="40" t="n"/>
-      <c r="F54" s="40" t="n"/>
-      <c r="G54" s="89" t="n"/>
-      <c r="H54" s="90" t="n"/>
-      <c r="I54" s="53" t="n"/>
-    </row>
-    <row r="55" ht="24" customHeight="1">
-      <c r="B55" s="49" t="n"/>
-      <c r="C55" s="30" t="n"/>
-      <c r="D55" s="31" t="n"/>
-      <c r="E55" s="32" t="n"/>
-      <c r="F55" s="32" t="n"/>
-      <c r="G55" s="89" t="n"/>
-      <c r="H55" s="91" t="n"/>
-      <c r="I55" s="54" t="n"/>
-    </row>
-    <row r="56" ht="24" customHeight="1">
-      <c r="B56" s="48" t="n"/>
-      <c r="C56" s="38" t="n"/>
-      <c r="D56" s="39" t="n"/>
-      <c r="E56" s="40" t="n"/>
-      <c r="F56" s="40" t="n"/>
-      <c r="G56" s="89" t="n"/>
-      <c r="H56" s="90" t="n"/>
-      <c r="I56" s="53" t="n"/>
-    </row>
-    <row r="57" ht="24" customHeight="1">
-      <c r="B57" s="49" t="n"/>
-      <c r="C57" s="30" t="n"/>
-      <c r="D57" s="31" t="n"/>
-      <c r="E57" s="32" t="n"/>
-      <c r="F57" s="32" t="n"/>
-      <c r="G57" s="89" t="n"/>
-      <c r="H57" s="91" t="n"/>
-      <c r="I57" s="54" t="n"/>
-    </row>
-    <row r="58" ht="24" customHeight="1">
-      <c r="B58" s="48" t="n"/>
-      <c r="C58" s="38" t="n"/>
-      <c r="D58" s="39" t="n"/>
-      <c r="E58" s="40" t="n"/>
-      <c r="F58" s="40" t="n"/>
-      <c r="G58" s="89" t="n"/>
-      <c r="H58" s="90" t="n"/>
-      <c r="I58" s="53" t="n"/>
-    </row>
-    <row r="59" ht="24" customHeight="1">
-      <c r="B59" s="49" t="n"/>
-      <c r="C59" s="30" t="n"/>
-      <c r="D59" s="31" t="n"/>
-      <c r="E59" s="32" t="n"/>
-      <c r="F59" s="32" t="n"/>
-      <c r="G59" s="89" t="n"/>
-      <c r="H59" s="91" t="n"/>
-      <c r="I59" s="54" t="n"/>
-    </row>
-    <row r="60" ht="24" customHeight="1">
-      <c r="B60" s="48" t="n"/>
-      <c r="C60" s="38" t="n"/>
-      <c r="D60" s="39" t="n"/>
-      <c r="E60" s="40" t="n"/>
-      <c r="F60" s="40" t="n"/>
-      <c r="G60" s="89" t="n"/>
-      <c r="H60" s="90" t="n"/>
-      <c r="I60" s="53" t="n"/>
+      <c r="B49" s="47" t="n"/>
+      <c r="C49" s="47" t="n"/>
+      <c r="D49" s="47" t="n"/>
+      <c r="E49" s="47" t="n"/>
+      <c r="F49" s="47" t="n"/>
+      <c r="G49" s="47" t="n"/>
+      <c r="H49" s="101" t="n"/>
+      <c r="I49" s="47" t="n"/>
+      <c r="J49" s="47" t="n"/>
+      <c r="K49" s="43" t="n"/>
     </row>
   </sheetData>
-  <mergeCells count="2">
+  <mergeCells count="4">
+    <mergeCell ref="B43:J43"/>
     <mergeCell ref="B2:G2"/>
     <mergeCell ref="H2:I2"/>
+    <mergeCell ref="B42:J42"/>
   </mergeCells>
-  <conditionalFormatting sqref="G8:G60">
+  <conditionalFormatting sqref="G8:G40">
     <cfRule type="colorScale" priority="1351">
       <colorScale>
         <cfvo type="min"/>
@@ -5594,14 +5853,14 @@
       </c>
     </row>
     <row r="11" ht="21" customHeight="1">
-      <c r="B11" s="94" t="n"/>
-      <c r="C11" s="94" t="n"/>
-      <c r="D11" s="94" t="n"/>
-      <c r="E11" s="94" t="n"/>
-      <c r="F11" s="94" t="n"/>
-      <c r="G11" s="94" t="n"/>
-      <c r="H11" s="94" t="n"/>
-      <c r="I11" s="94" t="n"/>
+      <c r="B11" s="102" t="n"/>
+      <c r="C11" s="102" t="n"/>
+      <c r="D11" s="102" t="n"/>
+      <c r="E11" s="102" t="n"/>
+      <c r="F11" s="102" t="n"/>
+      <c r="G11" s="102" t="n"/>
+      <c r="H11" s="102" t="n"/>
+      <c r="I11" s="102" t="n"/>
       <c r="J11" s="4" t="n"/>
       <c r="M11" s="19" t="inlineStr">
         <is>
@@ -5677,7 +5936,7 @@
     <row r="13" ht="45" customHeight="1" thickBot="1">
       <c r="A13" s="36" t="n"/>
       <c r="B13" s="48" t="n"/>
-      <c r="C13" s="95" t="n"/>
+      <c r="C13" s="103" t="n"/>
       <c r="D13" s="38" t="n"/>
       <c r="E13" s="39" t="n"/>
       <c r="F13" s="40" t="n"/>

--- a/outputs/benchmark-beaters/Benchmark_Beaters_2026-07-21.xlsx
+++ b/outputs/benchmark-beaters/Benchmark_Beaters_2026-07-21.xlsx
@@ -1363,7 +1363,7 @@
     <row r="2" ht="15.6" customHeight="1">
       <c r="A2" s="22" t="n"/>
       <c r="B2" s="21" t="n">
-        <v>46224.85673662008</v>
+        <v>46224.86266495839</v>
       </c>
       <c r="C2" s="22" t="n"/>
     </row>
@@ -1425,7 +1425,7 @@
         </is>
       </c>
       <c r="H2" s="84" t="n">
-        <v>46224.85673662008</v>
+        <v>46224.86266495839</v>
       </c>
       <c r="J2" s="83" t="n"/>
     </row>
@@ -4065,7 +4065,7 @@
         </is>
       </c>
       <c r="H2" s="84" t="n">
-        <v>46224.85673662008</v>
+        <v>46224.86266495839</v>
       </c>
       <c r="J2" s="83" t="n"/>
     </row>

--- a/outputs/benchmark-beaters/Benchmark_Beaters_2026-07-21.xlsx
+++ b/outputs/benchmark-beaters/Benchmark_Beaters_2026-07-21.xlsx
@@ -479,6 +479,7 @@
       <top/>
       <bottom style="medium"/>
     </border>
+    <border/>
     <border>
       <left style="thin">
         <color rgb="FFC67A29"/>
@@ -493,7 +494,6 @@
         <color rgb="FFC67A29"/>
       </bottom>
     </border>
-    <border/>
     <border>
       <left/>
       <right/>
@@ -507,7 +507,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="118">
+  <cellXfs count="126">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
@@ -800,14 +800,38 @@
     <xf numFmtId="0" fontId="22" fillId="8" borderId="15" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="16" borderId="16" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="16" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="16" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="16" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="16" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="16" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="16" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="16" borderId="16" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="27" fillId="17" borderId="17" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="16" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="16" borderId="17" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="17" borderId="17" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="16" borderId="17" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="27" fillId="17" borderId="16" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="17" borderId="16" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1363,7 +1387,7 @@
     <row r="2" ht="15.6" customHeight="1">
       <c r="A2" s="22" t="n"/>
       <c r="B2" s="21" t="n">
-        <v>46224.86266495839</v>
+        <v>46224.87725170761</v>
       </c>
       <c r="C2" s="22" t="n"/>
     </row>
@@ -1424,10 +1448,10 @@
           <t>Benchmark Beaters — Canadian Stocks</t>
         </is>
       </c>
-      <c r="H2" s="84" t="n">
-        <v>46224.86266495839</v>
-      </c>
-      <c r="J2" s="83" t="n"/>
+      <c r="H2" s="82" t="n"/>
+      <c r="I2" s="84" t="n">
+        <v>46224.87725170761</v>
+      </c>
     </row>
     <row r="3" ht="3" customHeight="1">
       <c r="A3" s="45" t="n"/>
@@ -1478,21 +1502,17 @@
       <c r="F6" s="24" t="n"/>
       <c r="G6" s="24" t="n"/>
       <c r="H6" s="24" t="n"/>
-      <c r="I6" s="55" t="inlineStr">
+      <c r="I6" s="24" t="n"/>
+      <c r="J6" s="55" t="inlineStr">
         <is>
           <t>Chris White, CFA
 Head of Research</t>
         </is>
       </c>
-      <c r="J6" s="24" t="n"/>
     </row>
     <row r="7" ht="28.05" customHeight="1" thickBot="1">
       <c r="A7" s="26" t="n"/>
-      <c r="B7" s="27" t="inlineStr">
-        <is>
-          <t>#</t>
-        </is>
-      </c>
+      <c r="B7" s="27" t="inlineStr"/>
       <c r="C7" s="27" t="inlineStr">
         <is>
           <t>Ticker</t>
@@ -1535,784 +1555,822 @@
       </c>
       <c r="K7" s="26" t="n"/>
     </row>
-    <row r="8" ht="24" customHeight="1">
+    <row r="8" ht="45" customHeight="1">
       <c r="A8" s="36" t="n"/>
-      <c r="B8" s="48" t="n">
-        <v>1</v>
+      <c r="B8" s="48" t="inlineStr">
+        <is>
+          <t>🆕</t>
+        </is>
       </c>
       <c r="C8" s="38" t="inlineStr">
         <is>
-          <t>BDT</t>
+          <t>EXE</t>
         </is>
       </c>
       <c r="D8" s="39" t="inlineStr">
         <is>
-          <t>Bird Construction Inc.</t>
+          <t>Extendicare Inc.</t>
         </is>
       </c>
       <c r="E8" s="40" t="inlineStr">
         <is>
+          <t>Health Care</t>
+        </is>
+      </c>
+      <c r="F8" s="40" t="inlineStr">
+        <is>
+          <t>Health Care Providers and Services</t>
+        </is>
+      </c>
+      <c r="G8" s="89" t="n">
+        <v>0.735</v>
+      </c>
+      <c r="H8" s="90" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="I8" s="91" t="n">
+        <v>2258.51</v>
+      </c>
+      <c r="J8" s="53" t="inlineStr">
+        <is>
+          <t>Extendicare Inc through its subsidiaries provides care and services for seniors in Canada</t>
+        </is>
+      </c>
+      <c r="K8" s="36" t="n"/>
+    </row>
+    <row r="9" ht="45" customHeight="1">
+      <c r="A9" s="28" t="n"/>
+      <c r="B9" s="49" t="inlineStr">
+        <is>
+          <t>🆕</t>
+        </is>
+      </c>
+      <c r="C9" s="30" t="inlineStr">
+        <is>
+          <t>MTL</t>
+        </is>
+      </c>
+      <c r="D9" s="31" t="inlineStr">
+        <is>
+          <t>Mullen Group Ltd.</t>
+        </is>
+      </c>
+      <c r="E9" s="32" t="inlineStr">
+        <is>
           <t>Industrials</t>
         </is>
       </c>
-      <c r="F8" s="40" t="inlineStr">
+      <c r="F9" s="32" t="inlineStr">
+        <is>
+          <t>Ground Transportation</t>
+        </is>
+      </c>
+      <c r="G9" s="89" t="n">
+        <v>0.5679999999999999</v>
+      </c>
+      <c r="H9" s="92" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="I9" s="93" t="n">
+        <v>1565.38</v>
+      </c>
+      <c r="J9" s="54" t="inlineStr">
+        <is>
+          <t>Mullen Group Ltd provides a range of trucking and logistics services in Canada and the United States</t>
+        </is>
+      </c>
+      <c r="K9" s="28" t="n"/>
+    </row>
+    <row r="10" ht="45" customHeight="1">
+      <c r="A10" s="36" t="n"/>
+      <c r="B10" s="48" t="inlineStr">
+        <is>
+          <t>🆕</t>
+        </is>
+      </c>
+      <c r="C10" s="38" t="inlineStr">
+        <is>
+          <t>GWO</t>
+        </is>
+      </c>
+      <c r="D10" s="39" t="inlineStr">
+        <is>
+          <t>Great-West Lifeco Inc.</t>
+        </is>
+      </c>
+      <c r="E10" s="40" t="inlineStr">
+        <is>
+          <t>Financials</t>
+        </is>
+      </c>
+      <c r="F10" s="40" t="inlineStr">
+        <is>
+          <t>Insurance</t>
+        </is>
+      </c>
+      <c r="G10" s="89" t="n">
+        <v>0.458</v>
+      </c>
+      <c r="H10" s="90" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="I10" s="91" t="n">
+        <v>53011.04</v>
+      </c>
+      <c r="J10" s="53" t="inlineStr">
+        <is>
+          <t>Great-West Lifeco Inc engages in the life and health insurance retirement savings wealth and asset management and reinsurance businesses in Canada the United States and Europe</t>
+        </is>
+      </c>
+      <c r="K10" s="36" t="n"/>
+    </row>
+    <row r="11" ht="45" customHeight="1">
+      <c r="A11" s="28" t="n"/>
+      <c r="B11" s="49" t="inlineStr">
+        <is>
+          <t>🆕</t>
+        </is>
+      </c>
+      <c r="C11" s="30" t="inlineStr">
+        <is>
+          <t>POW</t>
+        </is>
+      </c>
+      <c r="D11" s="31" t="inlineStr">
+        <is>
+          <t>Power Corporation of Canada</t>
+        </is>
+      </c>
+      <c r="E11" s="32" t="inlineStr">
+        <is>
+          <t>Financials</t>
+        </is>
+      </c>
+      <c r="F11" s="32" t="inlineStr">
+        <is>
+          <t>Insurance</t>
+        </is>
+      </c>
+      <c r="G11" s="89" t="n">
+        <v>0.34</v>
+      </c>
+      <c r="H11" s="92" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="I11" s="93" t="n">
+        <v>38174.66</v>
+      </c>
+      <c r="J11" s="54" t="inlineStr">
+        <is>
+          <t>Power Corporation of Canada an international management and holding company provides financial services in North America Europe and Asia</t>
+        </is>
+      </c>
+      <c r="K11" s="28" t="n"/>
+    </row>
+    <row r="12" ht="45" customHeight="1">
+      <c r="A12" s="36" t="n"/>
+      <c r="B12" s="48" t="inlineStr">
+        <is>
+          <t>🆕</t>
+        </is>
+      </c>
+      <c r="C12" s="38" t="inlineStr">
+        <is>
+          <t>TD</t>
+        </is>
+      </c>
+      <c r="D12" s="39" t="inlineStr">
+        <is>
+          <t>The Toronto-Dominion Bank</t>
+        </is>
+      </c>
+      <c r="E12" s="40" t="inlineStr">
+        <is>
+          <t>Financials</t>
+        </is>
+      </c>
+      <c r="F12" s="40" t="inlineStr">
+        <is>
+          <t>Banks</t>
+        </is>
+      </c>
+      <c r="G12" s="89" t="n">
+        <v>0.323</v>
+      </c>
+      <c r="H12" s="90" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="I12" s="91" t="n">
+        <v>189567.97</v>
+      </c>
+      <c r="J12" s="53" t="inlineStr">
+        <is>
+          <t>The Toronto-Dominion Bank together with its subsidiaries provides various financial products and services in Canada the United States and internationally</t>
+        </is>
+      </c>
+      <c r="K12" s="36" t="n"/>
+    </row>
+    <row r="13" ht="45" customHeight="1">
+      <c r="A13" s="28" t="n"/>
+      <c r="B13" s="49" t="inlineStr">
+        <is>
+          <t>🆕</t>
+        </is>
+      </c>
+      <c r="C13" s="30" t="inlineStr">
+        <is>
+          <t>EQB</t>
+        </is>
+      </c>
+      <c r="D13" s="31" t="inlineStr">
+        <is>
+          <t>EQB Inc.</t>
+        </is>
+      </c>
+      <c r="E13" s="32" t="inlineStr">
+        <is>
+          <t>Financials</t>
+        </is>
+      </c>
+      <c r="F13" s="32" t="inlineStr">
+        <is>
+          <t>Banks</t>
+        </is>
+      </c>
+      <c r="G13" s="89" t="n">
+        <v>0.317</v>
+      </c>
+      <c r="H13" s="92" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="I13" s="93" t="n">
+        <v>3018.47</v>
+      </c>
+      <c r="J13" s="54" t="inlineStr">
+        <is>
+          <t>EQB Inc through its subsidiary Equitable Bank provides personal and commercial banking services to retail and commercial customers in Canada</t>
+        </is>
+      </c>
+      <c r="K13" s="28" t="n"/>
+    </row>
+    <row r="14" ht="45" customHeight="1">
+      <c r="A14" s="36" t="n"/>
+      <c r="B14" s="48" t="inlineStr">
+        <is>
+          <t>🆕</t>
+        </is>
+      </c>
+      <c r="C14" s="38" t="inlineStr">
+        <is>
+          <t>PPL</t>
+        </is>
+      </c>
+      <c r="D14" s="39" t="inlineStr">
+        <is>
+          <t>Pembina Pipeline Corporation</t>
+        </is>
+      </c>
+      <c r="E14" s="40" t="inlineStr">
+        <is>
+          <t>Energy</t>
+        </is>
+      </c>
+      <c r="F14" s="40" t="inlineStr">
+        <is>
+          <t>Oil Gas and Consumable Fuels</t>
+        </is>
+      </c>
+      <c r="G14" s="89" t="n">
+        <v>0.31</v>
+      </c>
+      <c r="H14" s="90" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="I14" s="91" t="n">
+        <v>28518.97</v>
+      </c>
+      <c r="J14" s="53" t="inlineStr">
+        <is>
+          <t>Pembina Pipeline Corporation provides energy transportation and midstream services</t>
+        </is>
+      </c>
+      <c r="K14" s="36" t="n"/>
+    </row>
+    <row r="15" ht="45" customHeight="1">
+      <c r="A15" s="28" t="n"/>
+      <c r="B15" s="49" t="inlineStr">
+        <is>
+          <t>🆕</t>
+        </is>
+      </c>
+      <c r="C15" s="30" t="inlineStr">
+        <is>
+          <t>CP</t>
+        </is>
+      </c>
+      <c r="D15" s="31" t="inlineStr">
+        <is>
+          <t>Canadian Pacific Kansas City Limited</t>
+        </is>
+      </c>
+      <c r="E15" s="32" t="inlineStr">
+        <is>
+          <t>Industrials</t>
+        </is>
+      </c>
+      <c r="F15" s="32" t="inlineStr">
+        <is>
+          <t>Ground Transportation</t>
+        </is>
+      </c>
+      <c r="G15" s="89" t="n">
+        <v>0.295</v>
+      </c>
+      <c r="H15" s="92" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="I15" s="93" t="n">
+        <v>79823.21000000001</v>
+      </c>
+      <c r="J15" s="54" t="inlineStr">
+        <is>
+          <t>Canadian Pacific Kansas City Limited together with its subsidiaries owns and operates a transcontinental freight railway in Canada the United States and Mexico</t>
+        </is>
+      </c>
+      <c r="K15" s="28" t="n"/>
+    </row>
+    <row r="16" ht="45" customHeight="1">
+      <c r="A16" s="28" t="n"/>
+      <c r="B16" s="48" t="inlineStr">
+        <is>
+          <t>🆕</t>
+        </is>
+      </c>
+      <c r="C16" s="38" t="inlineStr">
+        <is>
+          <t>CU</t>
+        </is>
+      </c>
+      <c r="D16" s="39" t="inlineStr">
+        <is>
+          <t>Canadian Utilities Limited</t>
+        </is>
+      </c>
+      <c r="E16" s="40" t="inlineStr">
+        <is>
+          <t>Utilities</t>
+        </is>
+      </c>
+      <c r="F16" s="40" t="inlineStr">
+        <is>
+          <t>Multi-Utilities</t>
+        </is>
+      </c>
+      <c r="G16" s="89" t="n">
+        <v>0.266</v>
+      </c>
+      <c r="H16" s="90" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="I16" s="91" t="n">
+        <v>10045.65</v>
+      </c>
+      <c r="J16" s="53" t="inlineStr">
+        <is>
+          <t>Canadian Utilities Limited together with its subsidiaries engages in the electricity natural gas renewables pipelines and liquids businesses in Canada Australia and internationally</t>
+        </is>
+      </c>
+      <c r="K16" s="28" t="n"/>
+    </row>
+    <row r="17" ht="45" customHeight="1">
+      <c r="A17" s="36" t="n"/>
+      <c r="B17" s="49" t="inlineStr">
+        <is>
+          <t>🆕</t>
+        </is>
+      </c>
+      <c r="C17" s="30" t="inlineStr">
+        <is>
+          <t>CF</t>
+        </is>
+      </c>
+      <c r="D17" s="31" t="inlineStr">
+        <is>
+          <t>Canaccord Genuity Group Inc.</t>
+        </is>
+      </c>
+      <c r="E17" s="32" t="inlineStr">
+        <is>
+          <t>Financials</t>
+        </is>
+      </c>
+      <c r="F17" s="32" t="inlineStr">
+        <is>
+          <t>Capital Markets</t>
+        </is>
+      </c>
+      <c r="G17" s="89" t="n">
+        <v>0.265</v>
+      </c>
+      <c r="H17" s="92" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="I17" s="93" t="n">
+        <v>976.67</v>
+      </c>
+      <c r="J17" s="54" t="inlineStr">
+        <is>
+          <t>Canaccord Genuity Group Inc operates as a full-service investment dealer in Canada the United States the United Kingdom Europe Crown Dependencies and Australia</t>
+        </is>
+      </c>
+      <c r="K17" s="36" t="n"/>
+    </row>
+    <row r="18" ht="45" customHeight="1">
+      <c r="A18" s="28" t="n"/>
+      <c r="B18" s="48" t="inlineStr">
+        <is>
+          <t>🆕</t>
+        </is>
+      </c>
+      <c r="C18" s="38" t="inlineStr">
+        <is>
+          <t>BDGI</t>
+        </is>
+      </c>
+      <c r="D18" s="39" t="inlineStr">
+        <is>
+          <t>Badger Infrastructure Solutions Ltd.</t>
+        </is>
+      </c>
+      <c r="E18" s="40" t="inlineStr">
+        <is>
+          <t>Industrials</t>
+        </is>
+      </c>
+      <c r="F18" s="40" t="inlineStr">
         <is>
           <t>Construction and Engineering</t>
         </is>
       </c>
-      <c r="G8" s="89" t="n">
-        <v>1.627</v>
-      </c>
-      <c r="H8" s="90" t="inlineStr">
-        <is>
-          <t>Streak</t>
-        </is>
-      </c>
-      <c r="I8" s="91" t="n">
-        <v>2358.79</v>
-      </c>
-      <c r="J8" s="53" t="inlineStr">
-        <is>
-          <t>Bird Construction Inc provides construction services in Canada</t>
-        </is>
-      </c>
-      <c r="K8" s="36" t="n"/>
-    </row>
-    <row r="9" ht="26.4" customHeight="1">
-      <c r="A9" s="28" t="n"/>
-      <c r="B9" s="49" t="n">
-        <v>2</v>
-      </c>
-      <c r="C9" s="30" t="inlineStr">
+      <c r="G18" s="89" t="n">
+        <v>0.254</v>
+      </c>
+      <c r="H18" s="90" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="I18" s="91" t="n">
+        <v>2215.94</v>
+      </c>
+      <c r="J18" s="53" t="inlineStr">
+        <is>
+          <t>Badger Infrastructure Solutions Ltd provides non-destructive excavating and related services to utilities industrial construction transportation and other industries in Canada and the United States</t>
+        </is>
+      </c>
+      <c r="K18" s="28" t="n"/>
+    </row>
+    <row r="19" ht="45" customHeight="1">
+      <c r="A19" s="36" t="n"/>
+      <c r="B19" s="49" t="inlineStr">
+        <is>
+          <t>🆕</t>
+        </is>
+      </c>
+      <c r="C19" s="30" t="inlineStr">
+        <is>
+          <t>BDI</t>
+        </is>
+      </c>
+      <c r="D19" s="31" t="inlineStr">
+        <is>
+          <t>Black Diamond Group Limited</t>
+        </is>
+      </c>
+      <c r="E19" s="32" t="inlineStr">
+        <is>
+          <t>Industrials</t>
+        </is>
+      </c>
+      <c r="F19" s="32" t="inlineStr">
+        <is>
+          <t>Commercial Services and Supplies</t>
+        </is>
+      </c>
+      <c r="G19" s="89" t="n">
+        <v>0.22</v>
+      </c>
+      <c r="H19" s="92" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="I19" s="93" t="n">
+        <v>927.72</v>
+      </c>
+      <c r="J19" s="54" t="inlineStr">
+        <is>
+          <t>Black Diamond Group Limited provides specialty rentals and industrial services in Canada the United States and Australia</t>
+        </is>
+      </c>
+      <c r="K19" s="36" t="n"/>
+    </row>
+    <row r="20" ht="45" customHeight="1">
+      <c r="A20" s="28" t="n"/>
+      <c r="B20" s="48" t="inlineStr">
+        <is>
+          <t>🆕</t>
+        </is>
+      </c>
+      <c r="C20" s="38" t="inlineStr">
+        <is>
+          <t>MFC</t>
+        </is>
+      </c>
+      <c r="D20" s="39" t="inlineStr">
+        <is>
+          <t>Manulife Financial Corporation</t>
+        </is>
+      </c>
+      <c r="E20" s="40" t="inlineStr">
+        <is>
+          <t>Financials</t>
+        </is>
+      </c>
+      <c r="F20" s="40" t="inlineStr">
+        <is>
+          <t>Insurance</t>
+        </is>
+      </c>
+      <c r="G20" s="89" t="n">
+        <v>0.216</v>
+      </c>
+      <c r="H20" s="90" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="I20" s="91" t="n">
+        <v>65572.44</v>
+      </c>
+      <c r="J20" s="53" t="inlineStr">
+        <is>
+          <t>Manulife Financial Corporation together with its subsidiaries provides financial products and services in the United States Canada Asia and internationally</t>
+        </is>
+      </c>
+      <c r="K20" s="28" t="n"/>
+    </row>
+    <row r="21" ht="45" customHeight="1">
+      <c r="A21" s="36" t="n"/>
+      <c r="B21" s="49" t="inlineStr">
+        <is>
+          <t>🆕</t>
+        </is>
+      </c>
+      <c r="C21" s="30" t="inlineStr">
+        <is>
+          <t>DBM</t>
+        </is>
+      </c>
+      <c r="D21" s="31" t="inlineStr">
+        <is>
+          <t>Doman Building Materials Group Ltd.</t>
+        </is>
+      </c>
+      <c r="E21" s="32" t="inlineStr">
+        <is>
+          <t>Industrials</t>
+        </is>
+      </c>
+      <c r="F21" s="32" t="inlineStr">
+        <is>
+          <t>Trading Companies and Distributors</t>
+        </is>
+      </c>
+      <c r="G21" s="89" t="n">
+        <v>0.146</v>
+      </c>
+      <c r="H21" s="92" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="I21" s="93" t="n">
+        <v>676.4400000000001</v>
+      </c>
+      <c r="J21" s="54" t="inlineStr">
+        <is>
+          <t>Doman Building Materials Group Ltd through its subsidiaries engages in the wholesale distribution of building materials and home renovation products in the United States and Canada</t>
+        </is>
+      </c>
+      <c r="K21" s="36" t="n"/>
+    </row>
+    <row r="22" ht="45" customHeight="1">
+      <c r="A22" s="28" t="n"/>
+      <c r="B22" s="48" t="inlineStr">
+        <is>
+          <t>🔁</t>
+        </is>
+      </c>
+      <c r="C22" s="38" t="inlineStr">
         <is>
           <t>MATR</t>
         </is>
       </c>
-      <c r="D9" s="31" t="inlineStr">
+      <c r="D22" s="39" t="inlineStr">
         <is>
           <t>Mattr Corp.</t>
         </is>
       </c>
-      <c r="E9" s="32" t="inlineStr">
+      <c r="E22" s="40" t="inlineStr">
         <is>
           <t>Energy</t>
         </is>
       </c>
-      <c r="F9" s="32" t="inlineStr">
+      <c r="F22" s="40" t="inlineStr">
         <is>
           <t>Energy Equipment and Services</t>
         </is>
       </c>
-      <c r="G9" s="89" t="n">
+      <c r="G22" s="89" t="n">
         <v>1.172</v>
       </c>
-      <c r="H9" s="92" t="inlineStr">
+      <c r="H22" s="90" t="inlineStr">
         <is>
           <t>Repeat</t>
         </is>
       </c>
-      <c r="I9" s="93" t="n">
+      <c r="I22" s="91" t="n">
         <v>555.83</v>
       </c>
-      <c r="J9" s="54" t="inlineStr">
+      <c r="J22" s="53" t="inlineStr">
         <is>
           <t>Mattr Corp operates as a materials technology company that serves the infrastructure markets including electrification transportation mining energy communication and water management markets in Canada the United States Europe the Middle East Africa and the Asia Pacific</t>
         </is>
       </c>
-      <c r="K9" s="28" t="n"/>
-    </row>
-    <row r="10" ht="20.4" customHeight="1">
-      <c r="A10" s="36" t="n"/>
-      <c r="B10" s="48" t="n">
-        <v>3</v>
-      </c>
-      <c r="C10" s="38" t="inlineStr">
-        <is>
-          <t>DRX</t>
-        </is>
-      </c>
-      <c r="D10" s="39" t="inlineStr">
-        <is>
-          <t>ADF Group Inc.</t>
-        </is>
-      </c>
-      <c r="E10" s="40" t="inlineStr">
+      <c r="K22" s="28" t="n"/>
+    </row>
+    <row r="23" ht="45" customHeight="1">
+      <c r="A23" s="28" t="n"/>
+      <c r="B23" s="49" t="inlineStr">
+        <is>
+          <t>🔁</t>
+        </is>
+      </c>
+      <c r="C23" s="30" t="inlineStr">
+        <is>
+          <t>NFI</t>
+        </is>
+      </c>
+      <c r="D23" s="31" t="inlineStr">
+        <is>
+          <t>NFI Group Inc.</t>
+        </is>
+      </c>
+      <c r="E23" s="32" t="inlineStr">
+        <is>
+          <t>Industrials</t>
+        </is>
+      </c>
+      <c r="F23" s="32" t="inlineStr">
+        <is>
+          <t>Machinery</t>
+        </is>
+      </c>
+      <c r="G23" s="89" t="n">
+        <v>0.545</v>
+      </c>
+      <c r="H23" s="92" t="inlineStr">
+        <is>
+          <t>Repeat</t>
+        </is>
+      </c>
+      <c r="I23" s="93" t="n">
+        <v>1892.54</v>
+      </c>
+      <c r="J23" s="54" t="inlineStr">
+        <is>
+          <t>NFI Group Inc together with its subsidiaries manufactures and sells buses in North America the United Kingdom rest of Europe and the Asia Pacific</t>
+        </is>
+      </c>
+      <c r="K23" s="28" t="n"/>
+    </row>
+    <row r="24" ht="45" customHeight="1">
+      <c r="A24" s="36" t="n"/>
+      <c r="B24" s="48" t="inlineStr">
+        <is>
+          <t>🔁</t>
+        </is>
+      </c>
+      <c r="C24" s="38" t="inlineStr">
+        <is>
+          <t>RUS</t>
+        </is>
+      </c>
+      <c r="D24" s="39" t="inlineStr">
+        <is>
+          <t>Russel Metals Inc.</t>
+        </is>
+      </c>
+      <c r="E24" s="40" t="inlineStr">
+        <is>
+          <t>Industrials</t>
+        </is>
+      </c>
+      <c r="F24" s="40" t="inlineStr">
+        <is>
+          <t>Trading Companies and Distributors</t>
+        </is>
+      </c>
+      <c r="G24" s="89" t="n">
+        <v>0.443</v>
+      </c>
+      <c r="H24" s="90" t="inlineStr">
+        <is>
+          <t>Repeat</t>
+        </is>
+      </c>
+      <c r="I24" s="91" t="n">
+        <v>2385.76</v>
+      </c>
+      <c r="J24" s="53" t="inlineStr">
+        <is>
+          <t>Russel Metals Inc engages in the distribution of steel and other metal products in Canada and the United States</t>
+        </is>
+      </c>
+      <c r="K24" s="36" t="n"/>
+    </row>
+    <row r="25" ht="45" customHeight="1">
+      <c r="A25" s="28" t="n"/>
+      <c r="B25" s="49" t="inlineStr">
+        <is>
+          <t>🔁</t>
+        </is>
+      </c>
+      <c r="C25" s="30" t="inlineStr">
+        <is>
+          <t>ARG</t>
+        </is>
+      </c>
+      <c r="D25" s="31" t="inlineStr">
+        <is>
+          <t>Amerigo Resources Ltd.</t>
+        </is>
+      </c>
+      <c r="E25" s="32" t="inlineStr">
         <is>
           <t>Materials</t>
         </is>
       </c>
-      <c r="F10" s="40" t="inlineStr">
+      <c r="F25" s="32" t="inlineStr">
         <is>
           <t>Metals and Mining</t>
         </is>
       </c>
-      <c r="G10" s="89" t="n">
-        <v>1.162</v>
-      </c>
-      <c r="H10" s="90" t="inlineStr">
-        <is>
-          <t>Streak</t>
-        </is>
-      </c>
-      <c r="I10" s="91" t="n">
-        <v>284.57</v>
-      </c>
-      <c r="J10" s="53" t="inlineStr">
-        <is>
-          <t>ADF Group Inc engages in the design and engineering of connections including industrial coatings in Canada and the United States</t>
-        </is>
-      </c>
-      <c r="K10" s="36" t="n"/>
-    </row>
-    <row r="11" ht="20.4" customHeight="1">
-      <c r="A11" s="28" t="n"/>
-      <c r="B11" s="49" t="n">
-        <v>4</v>
-      </c>
-      <c r="C11" s="30" t="inlineStr">
-        <is>
-          <t>EXE</t>
-        </is>
-      </c>
-      <c r="D11" s="31" t="inlineStr">
-        <is>
-          <t>Extendicare Inc.</t>
-        </is>
-      </c>
-      <c r="E11" s="32" t="inlineStr">
-        <is>
-          <t>Health Care</t>
-        </is>
-      </c>
-      <c r="F11" s="32" t="inlineStr">
-        <is>
-          <t>Health Care Providers and Services</t>
-        </is>
-      </c>
-      <c r="G11" s="89" t="n">
-        <v>0.735</v>
-      </c>
-      <c r="H11" s="92" t="inlineStr">
-        <is>
-          <t>New</t>
-        </is>
-      </c>
-      <c r="I11" s="93" t="n">
-        <v>2258.51</v>
-      </c>
-      <c r="J11" s="54" t="inlineStr">
-        <is>
-          <t>Extendicare Inc through its subsidiaries provides care and services for seniors in Canada</t>
-        </is>
-      </c>
-      <c r="K11" s="28" t="n"/>
-    </row>
-    <row r="12" ht="20.4" customHeight="1">
-      <c r="A12" s="36" t="n"/>
-      <c r="B12" s="48" t="n">
-        <v>5</v>
-      </c>
-      <c r="C12" s="38" t="inlineStr">
-        <is>
-          <t>MTL</t>
-        </is>
-      </c>
-      <c r="D12" s="39" t="inlineStr">
-        <is>
-          <t>Mullen Group Ltd.</t>
-        </is>
-      </c>
-      <c r="E12" s="40" t="inlineStr">
-        <is>
-          <t>Industrials</t>
-        </is>
-      </c>
-      <c r="F12" s="40" t="inlineStr">
-        <is>
-          <t>Ground Transportation</t>
-        </is>
-      </c>
-      <c r="G12" s="89" t="n">
-        <v>0.5679999999999999</v>
-      </c>
-      <c r="H12" s="90" t="inlineStr">
-        <is>
-          <t>New</t>
-        </is>
-      </c>
-      <c r="I12" s="91" t="n">
-        <v>1565.38</v>
-      </c>
-      <c r="J12" s="53" t="inlineStr">
-        <is>
-          <t>Mullen Group Ltd provides a range of trucking and logistics services in Canada and the United States</t>
-        </is>
-      </c>
-      <c r="K12" s="36" t="n"/>
-    </row>
-    <row r="13" ht="24" customHeight="1">
-      <c r="A13" s="28" t="n"/>
-      <c r="B13" s="49" t="n">
-        <v>6</v>
-      </c>
-      <c r="C13" s="30" t="inlineStr">
-        <is>
-          <t>NFI</t>
-        </is>
-      </c>
-      <c r="D13" s="31" t="inlineStr">
-        <is>
-          <t>NFI Group Inc.</t>
-        </is>
-      </c>
-      <c r="E13" s="32" t="inlineStr">
-        <is>
-          <t>Industrials</t>
-        </is>
-      </c>
-      <c r="F13" s="32" t="inlineStr">
-        <is>
-          <t>Machinery</t>
-        </is>
-      </c>
-      <c r="G13" s="89" t="n">
-        <v>0.545</v>
-      </c>
-      <c r="H13" s="92" t="inlineStr">
+      <c r="G25" s="89" t="n">
+        <v>0.339</v>
+      </c>
+      <c r="H25" s="92" t="inlineStr">
         <is>
           <t>Repeat</t>
         </is>
       </c>
-      <c r="I13" s="93" t="n">
-        <v>1892.54</v>
-      </c>
-      <c r="J13" s="54" t="inlineStr">
-        <is>
-          <t>NFI Group Inc together with its subsidiaries manufactures and sells buses in North America the United Kingdom rest of Europe and the Asia Pacific</t>
-        </is>
-      </c>
-      <c r="K13" s="28" t="n"/>
-    </row>
-    <row r="14">
-      <c r="A14" s="36" t="n"/>
-      <c r="B14" s="48" t="n">
-        <v>7</v>
-      </c>
-      <c r="C14" s="38" t="inlineStr">
-        <is>
-          <t>GWO</t>
-        </is>
-      </c>
-      <c r="D14" s="39" t="inlineStr">
-        <is>
-          <t>Great-West Lifeco Inc.</t>
-        </is>
-      </c>
-      <c r="E14" s="40" t="inlineStr">
-        <is>
-          <t>Financials</t>
-        </is>
-      </c>
-      <c r="F14" s="40" t="inlineStr">
-        <is>
-          <t>Insurance</t>
-        </is>
-      </c>
-      <c r="G14" s="89" t="n">
-        <v>0.458</v>
-      </c>
-      <c r="H14" s="90" t="inlineStr">
-        <is>
-          <t>New</t>
-        </is>
-      </c>
-      <c r="I14" s="91" t="n">
-        <v>53011.04</v>
-      </c>
-      <c r="J14" s="53" t="inlineStr">
-        <is>
-          <t>Great-West Lifeco Inc engages in the life and health insurance retirement savings wealth and asset management and reinsurance businesses in Canada the United States and Europe</t>
-        </is>
-      </c>
-      <c r="K14" s="36" t="n"/>
-    </row>
-    <row r="15">
-      <c r="A15" s="28" t="n"/>
-      <c r="B15" s="49" t="n">
-        <v>8</v>
-      </c>
-      <c r="C15" s="30" t="inlineStr">
-        <is>
-          <t>RUS</t>
-        </is>
-      </c>
-      <c r="D15" s="31" t="inlineStr">
-        <is>
-          <t>Russel Metals Inc.</t>
-        </is>
-      </c>
-      <c r="E15" s="32" t="inlineStr">
-        <is>
-          <t>Industrials</t>
-        </is>
-      </c>
-      <c r="F15" s="32" t="inlineStr">
-        <is>
-          <t>Trading Companies and Distributors</t>
-        </is>
-      </c>
-      <c r="G15" s="89" t="n">
-        <v>0.443</v>
-      </c>
-      <c r="H15" s="92" t="inlineStr">
-        <is>
-          <t>Repeat</t>
-        </is>
-      </c>
-      <c r="I15" s="93" t="n">
-        <v>2385.76</v>
-      </c>
-      <c r="J15" s="54" t="inlineStr">
-        <is>
-          <t>Russel Metals Inc engages in the distribution of steel and other metal products in Canada and the United States</t>
-        </is>
-      </c>
-      <c r="K15" s="28" t="n"/>
-    </row>
-    <row r="16" ht="20.4" customHeight="1">
-      <c r="A16" s="28" t="n"/>
-      <c r="B16" s="48" t="n">
-        <v>9</v>
-      </c>
-      <c r="C16" s="38" t="inlineStr">
-        <is>
-          <t>KBL</t>
-        </is>
-      </c>
-      <c r="D16" s="39" t="inlineStr">
-        <is>
-          <t>K-Bro Linen Inc.</t>
-        </is>
-      </c>
-      <c r="E16" s="40" t="inlineStr">
-        <is>
-          <t>Industrials</t>
-        </is>
-      </c>
-      <c r="F16" s="40" t="inlineStr">
-        <is>
-          <t>Commercial Services and Supplies</t>
-        </is>
-      </c>
-      <c r="G16" s="89" t="n">
-        <v>0.38</v>
-      </c>
-      <c r="H16" s="90" t="inlineStr">
-        <is>
-          <t>Streak</t>
-        </is>
-      </c>
-      <c r="I16" s="91" t="n">
-        <v>390.27</v>
-      </c>
-      <c r="J16" s="53" t="inlineStr">
-        <is>
-          <t>K-Bro Linen Inc together with its subsidiaries provides laundry and linen services to healthcare organizations hotels and other commercial accounts in Canada and the United Kingdom</t>
-        </is>
-      </c>
-      <c r="K16" s="28" t="n"/>
-    </row>
-    <row r="17" ht="40.8" customHeight="1">
-      <c r="A17" s="36" t="n"/>
-      <c r="B17" s="49" t="n">
-        <v>10</v>
-      </c>
-      <c r="C17" s="30" t="inlineStr">
-        <is>
-          <t>BMO</t>
-        </is>
-      </c>
-      <c r="D17" s="31" t="inlineStr">
-        <is>
-          <t>Bank of Montreal</t>
-        </is>
-      </c>
-      <c r="E17" s="32" t="inlineStr">
-        <is>
-          <t>Financials</t>
-        </is>
-      </c>
-      <c r="F17" s="32" t="inlineStr">
-        <is>
-          <t>Banks</t>
-        </is>
-      </c>
-      <c r="G17" s="89" t="n">
-        <v>0.36</v>
-      </c>
-      <c r="H17" s="92" t="inlineStr">
-        <is>
-          <t>Streak</t>
-        </is>
-      </c>
-      <c r="I17" s="93" t="n">
-        <v>116001.23</v>
-      </c>
-      <c r="J17" s="54" t="inlineStr">
-        <is>
-          <t>Bank of Montreal engages in the provision of diversified financial services primarily in North America</t>
-        </is>
-      </c>
-      <c r="K17" s="36" t="n"/>
-    </row>
-    <row r="18" ht="24" customHeight="1">
-      <c r="A18" s="28" t="n"/>
-      <c r="B18" s="48" t="n">
-        <v>11</v>
-      </c>
-      <c r="C18" s="38" t="inlineStr">
-        <is>
-          <t>POW</t>
-        </is>
-      </c>
-      <c r="D18" s="39" t="inlineStr">
-        <is>
-          <t>Power Corporation of Canada</t>
-        </is>
-      </c>
-      <c r="E18" s="40" t="inlineStr">
-        <is>
-          <t>Financials</t>
-        </is>
-      </c>
-      <c r="F18" s="40" t="inlineStr">
-        <is>
-          <t>Insurance</t>
-        </is>
-      </c>
-      <c r="G18" s="89" t="n">
-        <v>0.34</v>
-      </c>
-      <c r="H18" s="90" t="inlineStr">
-        <is>
-          <t>New</t>
-        </is>
-      </c>
-      <c r="I18" s="91" t="n">
-        <v>38174.66</v>
-      </c>
-      <c r="J18" s="53" t="inlineStr">
-        <is>
-          <t>Power Corporation of Canada an international management and holding company provides financial services in North America Europe and Asia</t>
-        </is>
-      </c>
-      <c r="K18" s="28" t="n"/>
-    </row>
-    <row r="19" ht="30.6" customHeight="1">
-      <c r="A19" s="36" t="n"/>
-      <c r="B19" s="49" t="n">
-        <v>12</v>
-      </c>
-      <c r="C19" s="30" t="inlineStr">
-        <is>
-          <t>ARG</t>
-        </is>
-      </c>
-      <c r="D19" s="31" t="inlineStr">
-        <is>
-          <t>Amerigo Resources Ltd.</t>
-        </is>
-      </c>
-      <c r="E19" s="32" t="inlineStr">
-        <is>
-          <t>Materials</t>
-        </is>
-      </c>
-      <c r="F19" s="32" t="inlineStr">
-        <is>
-          <t>Metals and Mining</t>
-        </is>
-      </c>
-      <c r="G19" s="89" t="n">
-        <v>0.339</v>
-      </c>
-      <c r="H19" s="92" t="inlineStr">
-        <is>
-          <t>Repeat</t>
-        </is>
-      </c>
-      <c r="I19" s="93" t="n">
+      <c r="I25" s="93" t="n">
         <v>681.6799999999999</v>
       </c>
-      <c r="J19" s="54" t="inlineStr">
+      <c r="J25" s="54" t="inlineStr">
         <is>
           <t>Amerigo Resources Ltd through its subsidiary Minera Valle Central S</t>
         </is>
       </c>
-      <c r="K19" s="36" t="n"/>
-    </row>
-    <row r="20" ht="30.6" customHeight="1">
-      <c r="A20" s="28" t="n"/>
-      <c r="B20" s="48" t="n">
-        <v>13</v>
-      </c>
-      <c r="C20" s="38" t="inlineStr">
-        <is>
-          <t>SLF</t>
-        </is>
-      </c>
-      <c r="D20" s="39" t="inlineStr">
-        <is>
-          <t>Sun Life Financial Inc.</t>
-        </is>
-      </c>
-      <c r="E20" s="40" t="inlineStr">
-        <is>
-          <t>Financials</t>
-        </is>
-      </c>
-      <c r="F20" s="40" t="inlineStr">
-        <is>
-          <t>Insurance</t>
-        </is>
-      </c>
-      <c r="G20" s="89" t="n">
-        <v>0.336</v>
-      </c>
-      <c r="H20" s="90" t="inlineStr">
-        <is>
-          <t>Streak</t>
-        </is>
-      </c>
-      <c r="I20" s="91" t="n">
-        <v>41467.31</v>
-      </c>
-      <c r="J20" s="53" t="inlineStr">
-        <is>
-          <t>Sun Life Financial Inc a financial services company provides asset management wealth insurance and health solutions to individual and institutional customers in Canada the United States the United Kingdom Ireland Hong Kong the Philippines Japan Indonesia India China Australia Singapore Vietnam Malaysia and Bermuda</t>
-        </is>
-      </c>
-      <c r="K20" s="28" t="n"/>
-    </row>
-    <row r="21" ht="30.6" customHeight="1">
-      <c r="A21" s="36" t="n"/>
-      <c r="B21" s="49" t="n">
-        <v>14</v>
-      </c>
-      <c r="C21" s="30" t="inlineStr">
-        <is>
-          <t>CNR</t>
-        </is>
-      </c>
-      <c r="D21" s="31" t="inlineStr">
-        <is>
-          <t>Canadian National Railway Company</t>
-        </is>
-      </c>
-      <c r="E21" s="32" t="inlineStr">
-        <is>
-          <t>Industrials</t>
-        </is>
-      </c>
-      <c r="F21" s="32" t="inlineStr">
-        <is>
-          <t>Ground Transportation</t>
-        </is>
-      </c>
-      <c r="G21" s="89" t="n">
-        <v>0.327</v>
-      </c>
-      <c r="H21" s="92" t="inlineStr">
-        <is>
-          <t>Streak</t>
-        </is>
-      </c>
-      <c r="I21" s="93" t="n">
-        <v>72839.50999999999</v>
-      </c>
-      <c r="J21" s="54" t="inlineStr">
-        <is>
-          <t>Canadian National Railway Company together with its subsidiaries engages in the rail intermodal trucking and related transportation businesses in Canada and the United States</t>
-        </is>
-      </c>
-      <c r="K21" s="36" t="n"/>
-    </row>
-    <row r="22" ht="24" customHeight="1">
-      <c r="A22" s="28" t="n"/>
-      <c r="B22" s="48" t="n">
-        <v>15</v>
-      </c>
-      <c r="C22" s="38" t="inlineStr">
-        <is>
-          <t>CM</t>
-        </is>
-      </c>
-      <c r="D22" s="39" t="inlineStr">
-        <is>
-          <t>Canadian Imperial Bank of Commerce</t>
-        </is>
-      </c>
-      <c r="E22" s="40" t="inlineStr">
-        <is>
-          <t>Financials</t>
-        </is>
-      </c>
-      <c r="F22" s="40" t="inlineStr">
-        <is>
-          <t>Banks</t>
-        </is>
-      </c>
-      <c r="G22" s="89" t="n">
-        <v>0.324</v>
-      </c>
-      <c r="H22" s="90" t="inlineStr">
-        <is>
-          <t>Streak</t>
-        </is>
-      </c>
-      <c r="I22" s="91" t="n">
-        <v>101497.85</v>
-      </c>
-      <c r="J22" s="53" t="inlineStr">
-        <is>
-          <t>Canadian Imperial Bank of Commerce a diversified financial institution provides various financial products and services to personal business public sector and institutional clients in Canada the United States and internationally</t>
-        </is>
-      </c>
-      <c r="K22" s="28" t="n"/>
-    </row>
-    <row r="23" ht="24" customHeight="1">
-      <c r="A23" s="28" t="n"/>
-      <c r="B23" s="49" t="n">
-        <v>16</v>
-      </c>
-      <c r="C23" s="30" t="inlineStr">
-        <is>
-          <t>TD</t>
-        </is>
-      </c>
-      <c r="D23" s="31" t="inlineStr">
-        <is>
-          <t>The Toronto-Dominion Bank</t>
-        </is>
-      </c>
-      <c r="E23" s="32" t="inlineStr">
-        <is>
-          <t>Financials</t>
-        </is>
-      </c>
-      <c r="F23" s="32" t="inlineStr">
-        <is>
-          <t>Banks</t>
-        </is>
-      </c>
-      <c r="G23" s="89" t="n">
-        <v>0.323</v>
-      </c>
-      <c r="H23" s="92" t="inlineStr">
-        <is>
-          <t>New</t>
-        </is>
-      </c>
-      <c r="I23" s="93" t="n">
-        <v>189567.97</v>
-      </c>
-      <c r="J23" s="54" t="inlineStr">
-        <is>
-          <t>The Toronto-Dominion Bank together with its subsidiaries provides various financial products and services in Canada the United States and internationally</t>
-        </is>
-      </c>
-      <c r="K23" s="28" t="n"/>
-    </row>
-    <row r="24" ht="24" customHeight="1">
-      <c r="A24" s="36" t="n"/>
-      <c r="B24" s="48" t="n">
-        <v>17</v>
-      </c>
-      <c r="C24" s="38" t="inlineStr">
-        <is>
-          <t>EQB</t>
-        </is>
-      </c>
-      <c r="D24" s="39" t="inlineStr">
-        <is>
-          <t>EQB Inc.</t>
-        </is>
-      </c>
-      <c r="E24" s="40" t="inlineStr">
-        <is>
-          <t>Financials</t>
-        </is>
-      </c>
-      <c r="F24" s="40" t="inlineStr">
-        <is>
-          <t>Banks</t>
-        </is>
-      </c>
-      <c r="G24" s="89" t="n">
-        <v>0.317</v>
-      </c>
-      <c r="H24" s="90" t="inlineStr">
-        <is>
-          <t>New</t>
-        </is>
-      </c>
-      <c r="I24" s="91" t="n">
-        <v>3018.47</v>
-      </c>
-      <c r="J24" s="53" t="inlineStr">
-        <is>
-          <t>EQB Inc through its subsidiary Equitable Bank provides personal and commercial banking services to retail and commercial customers in Canada</t>
-        </is>
-      </c>
-      <c r="K24" s="36" t="n"/>
-    </row>
-    <row r="25" ht="24" customHeight="1">
-      <c r="A25" s="28" t="n"/>
-      <c r="B25" s="49" t="n">
-        <v>18</v>
-      </c>
-      <c r="C25" s="30" t="inlineStr">
-        <is>
-          <t>PPL</t>
-        </is>
-      </c>
-      <c r="D25" s="31" t="inlineStr">
-        <is>
-          <t>Pembina Pipeline Corporation</t>
-        </is>
-      </c>
-      <c r="E25" s="32" t="inlineStr">
-        <is>
-          <t>Energy</t>
-        </is>
-      </c>
-      <c r="F25" s="32" t="inlineStr">
-        <is>
-          <t>Oil Gas and Consumable Fuels</t>
-        </is>
-      </c>
-      <c r="G25" s="89" t="n">
-        <v>0.31</v>
-      </c>
-      <c r="H25" s="92" t="inlineStr">
-        <is>
-          <t>New</t>
-        </is>
-      </c>
-      <c r="I25" s="93" t="n">
-        <v>28518.97</v>
-      </c>
-      <c r="J25" s="54" t="inlineStr">
-        <is>
-          <t>Pembina Pipeline Corporation provides energy transportation and midstream services</t>
-        </is>
-      </c>
       <c r="K25" s="28" t="n"/>
     </row>
-    <row r="26" ht="20.4" customHeight="1">
+    <row r="26" ht="45" customHeight="1">
       <c r="A26" s="36" t="n"/>
-      <c r="B26" s="48" t="n">
-        <v>19</v>
+      <c r="B26" s="48" t="inlineStr">
+        <is>
+          <t>🔁</t>
+        </is>
       </c>
       <c r="C26" s="38" t="inlineStr">
         <is>
@@ -2352,653 +2410,681 @@
       </c>
       <c r="K26" s="36" t="n"/>
     </row>
-    <row r="27" ht="24" customHeight="1">
+    <row r="27" ht="45" customHeight="1">
       <c r="A27" s="36" t="n"/>
-      <c r="B27" s="49" t="n">
-        <v>20</v>
+      <c r="B27" s="49" t="inlineStr">
+        <is>
+          <t>🔁</t>
+        </is>
       </c>
       <c r="C27" s="30" t="inlineStr">
         <is>
+          <t>DXT</t>
+        </is>
+      </c>
+      <c r="D27" s="31" t="inlineStr">
+        <is>
+          <t>Dexterra Group Inc.</t>
+        </is>
+      </c>
+      <c r="E27" s="32" t="inlineStr">
+        <is>
+          <t>Industrials</t>
+        </is>
+      </c>
+      <c r="F27" s="32" t="inlineStr">
+        <is>
+          <t>Commercial Services and Supplies</t>
+        </is>
+      </c>
+      <c r="G27" s="89" t="n">
+        <v>0.234</v>
+      </c>
+      <c r="H27" s="92" t="inlineStr">
+        <is>
+          <t>Repeat</t>
+        </is>
+      </c>
+      <c r="I27" s="93" t="n">
+        <v>576.85</v>
+      </c>
+      <c r="J27" s="54" t="inlineStr">
+        <is>
+          <t>Dexterra Group Inc engages in the provision of support services for the creation management and operation of infrastructure in Canada</t>
+        </is>
+      </c>
+      <c r="K27" s="36" t="n"/>
+    </row>
+    <row r="28" ht="45" customHeight="1">
+      <c r="A28" s="28" t="n"/>
+      <c r="B28" s="48" t="inlineStr">
+        <is>
+          <t>🔁</t>
+        </is>
+      </c>
+      <c r="C28" s="38" t="inlineStr">
+        <is>
+          <t>BNS</t>
+        </is>
+      </c>
+      <c r="D28" s="39" t="inlineStr">
+        <is>
+          <t>The Bank of Nova Scotia</t>
+        </is>
+      </c>
+      <c r="E28" s="40" t="inlineStr">
+        <is>
+          <t>Financials</t>
+        </is>
+      </c>
+      <c r="F28" s="40" t="inlineStr">
+        <is>
+          <t>Banks</t>
+        </is>
+      </c>
+      <c r="G28" s="89" t="n">
+        <v>0.227</v>
+      </c>
+      <c r="H28" s="90" t="inlineStr">
+        <is>
+          <t>Repeat</t>
+        </is>
+      </c>
+      <c r="I28" s="91" t="n">
+        <v>100391.39</v>
+      </c>
+      <c r="J28" s="53" t="inlineStr">
+        <is>
+          <t>The Bank of Nova Scotia provides various banking products and services in Canada the United States Mexico Peru Chile Colombia the Caribbean and Central America and internationally</t>
+        </is>
+      </c>
+      <c r="K28" s="28" t="n"/>
+    </row>
+    <row r="29" ht="45" customHeight="1">
+      <c r="A29" s="36" t="n"/>
+      <c r="B29" s="49" t="inlineStr">
+        <is>
+          <t>🔁</t>
+        </is>
+      </c>
+      <c r="C29" s="30" t="inlineStr">
+        <is>
+          <t>TOY</t>
+        </is>
+      </c>
+      <c r="D29" s="31" t="inlineStr">
+        <is>
+          <t>Spin Master Corp.</t>
+        </is>
+      </c>
+      <c r="E29" s="32" t="inlineStr">
+        <is>
+          <t>Consumer Discretionary</t>
+        </is>
+      </c>
+      <c r="F29" s="32" t="inlineStr">
+        <is>
+          <t>Leisure Products</t>
+        </is>
+      </c>
+      <c r="G29" s="89" t="n">
+        <v>0.174</v>
+      </c>
+      <c r="H29" s="92" t="inlineStr">
+        <is>
+          <t>Repeat</t>
+        </is>
+      </c>
+      <c r="I29" s="93" t="n">
+        <v>1330.28</v>
+      </c>
+      <c r="J29" s="54" t="inlineStr">
+        <is>
+          <t>Spin Master Corp a children’s entertainment company engages in the creation design manufacture licensing and marketing of various toys entertainment products and digital games in North America Europe and internationally</t>
+        </is>
+      </c>
+      <c r="K29" s="36" t="n"/>
+    </row>
+    <row r="30" ht="45" customHeight="1">
+      <c r="A30" s="36" t="n"/>
+      <c r="B30" s="48" t="inlineStr">
+        <is>
+          <t>🔁</t>
+        </is>
+      </c>
+      <c r="C30" s="38" t="inlineStr">
+        <is>
+          <t>DFY</t>
+        </is>
+      </c>
+      <c r="D30" s="39" t="inlineStr">
+        <is>
+          <t>Definity Financial Corporation</t>
+        </is>
+      </c>
+      <c r="E30" s="40" t="inlineStr">
+        <is>
+          <t>Financials</t>
+        </is>
+      </c>
+      <c r="F30" s="40" t="inlineStr">
+        <is>
+          <t>Insurance</t>
+        </is>
+      </c>
+      <c r="G30" s="89" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="H30" s="90" t="inlineStr">
+        <is>
+          <t>Repeat</t>
+        </is>
+      </c>
+      <c r="I30" s="91" t="n">
+        <v>6226.62</v>
+      </c>
+      <c r="J30" s="53" t="inlineStr">
+        <is>
+          <t>Definity Financial Corporation together with its subsidiaries offers property and casualty insurance products in Canada</t>
+        </is>
+      </c>
+      <c r="K30" s="36" t="n"/>
+    </row>
+    <row r="31" ht="45" customHeight="1">
+      <c r="A31" s="28" t="n"/>
+      <c r="B31" s="49" t="inlineStr">
+        <is>
+          <t>🔥</t>
+        </is>
+      </c>
+      <c r="C31" s="30" t="inlineStr">
+        <is>
+          <t>BDT</t>
+        </is>
+      </c>
+      <c r="D31" s="31" t="inlineStr">
+        <is>
+          <t>Bird Construction Inc.</t>
+        </is>
+      </c>
+      <c r="E31" s="32" t="inlineStr">
+        <is>
+          <t>Industrials</t>
+        </is>
+      </c>
+      <c r="F31" s="32" t="inlineStr">
+        <is>
+          <t>Construction and Engineering</t>
+        </is>
+      </c>
+      <c r="G31" s="89" t="n">
+        <v>1.627</v>
+      </c>
+      <c r="H31" s="92" t="inlineStr">
+        <is>
+          <t>Streak</t>
+        </is>
+      </c>
+      <c r="I31" s="93" t="n">
+        <v>2358.79</v>
+      </c>
+      <c r="J31" s="54" t="inlineStr">
+        <is>
+          <t>Bird Construction Inc provides construction services in Canada</t>
+        </is>
+      </c>
+      <c r="K31" s="28" t="n"/>
+    </row>
+    <row r="32" ht="45" customHeight="1">
+      <c r="A32" s="36" t="n"/>
+      <c r="B32" s="48" t="inlineStr">
+        <is>
+          <t>🔥</t>
+        </is>
+      </c>
+      <c r="C32" s="38" t="inlineStr">
+        <is>
+          <t>DRX</t>
+        </is>
+      </c>
+      <c r="D32" s="39" t="inlineStr">
+        <is>
+          <t>ADF Group Inc.</t>
+        </is>
+      </c>
+      <c r="E32" s="40" t="inlineStr">
+        <is>
+          <t>Materials</t>
+        </is>
+      </c>
+      <c r="F32" s="40" t="inlineStr">
+        <is>
+          <t>Metals and Mining</t>
+        </is>
+      </c>
+      <c r="G32" s="89" t="n">
+        <v>1.162</v>
+      </c>
+      <c r="H32" s="90" t="inlineStr">
+        <is>
+          <t>Streak</t>
+        </is>
+      </c>
+      <c r="I32" s="91" t="n">
+        <v>284.57</v>
+      </c>
+      <c r="J32" s="53" t="inlineStr">
+        <is>
+          <t>ADF Group Inc engages in the design and engineering of connections including industrial coatings in Canada and the United States</t>
+        </is>
+      </c>
+      <c r="K32" s="36" t="n"/>
+    </row>
+    <row r="33" ht="45" customHeight="1">
+      <c r="A33" s="28" t="n"/>
+      <c r="B33" s="49" t="inlineStr">
+        <is>
+          <t>🔥</t>
+        </is>
+      </c>
+      <c r="C33" s="30" t="inlineStr">
+        <is>
+          <t>KBL</t>
+        </is>
+      </c>
+      <c r="D33" s="31" t="inlineStr">
+        <is>
+          <t>K-Bro Linen Inc.</t>
+        </is>
+      </c>
+      <c r="E33" s="32" t="inlineStr">
+        <is>
+          <t>Industrials</t>
+        </is>
+      </c>
+      <c r="F33" s="32" t="inlineStr">
+        <is>
+          <t>Commercial Services and Supplies</t>
+        </is>
+      </c>
+      <c r="G33" s="89" t="n">
+        <v>0.38</v>
+      </c>
+      <c r="H33" s="92" t="inlineStr">
+        <is>
+          <t>Streak</t>
+        </is>
+      </c>
+      <c r="I33" s="93" t="n">
+        <v>390.27</v>
+      </c>
+      <c r="J33" s="54" t="inlineStr">
+        <is>
+          <t>K-Bro Linen Inc together with its subsidiaries provides laundry and linen services to healthcare organizations hotels and other commercial accounts in Canada and the United Kingdom</t>
+        </is>
+      </c>
+      <c r="K33" s="28" t="n"/>
+    </row>
+    <row r="34" ht="45" customHeight="1">
+      <c r="A34" s="36" t="n"/>
+      <c r="B34" s="48" t="inlineStr">
+        <is>
+          <t>🔥</t>
+        </is>
+      </c>
+      <c r="C34" s="38" t="inlineStr">
+        <is>
+          <t>BMO</t>
+        </is>
+      </c>
+      <c r="D34" s="39" t="inlineStr">
+        <is>
+          <t>Bank of Montreal</t>
+        </is>
+      </c>
+      <c r="E34" s="40" t="inlineStr">
+        <is>
+          <t>Financials</t>
+        </is>
+      </c>
+      <c r="F34" s="40" t="inlineStr">
+        <is>
+          <t>Banks</t>
+        </is>
+      </c>
+      <c r="G34" s="89" t="n">
+        <v>0.36</v>
+      </c>
+      <c r="H34" s="90" t="inlineStr">
+        <is>
+          <t>Streak</t>
+        </is>
+      </c>
+      <c r="I34" s="91" t="n">
+        <v>116001.23</v>
+      </c>
+      <c r="J34" s="53" t="inlineStr">
+        <is>
+          <t>Bank of Montreal engages in the provision of diversified financial services primarily in North America</t>
+        </is>
+      </c>
+      <c r="K34" s="36" t="n"/>
+    </row>
+    <row r="35" ht="45" customHeight="1">
+      <c r="A35" s="28" t="n"/>
+      <c r="B35" s="49" t="inlineStr">
+        <is>
+          <t>🔥</t>
+        </is>
+      </c>
+      <c r="C35" s="30" t="inlineStr">
+        <is>
+          <t>SLF</t>
+        </is>
+      </c>
+      <c r="D35" s="31" t="inlineStr">
+        <is>
+          <t>Sun Life Financial Inc.</t>
+        </is>
+      </c>
+      <c r="E35" s="32" t="inlineStr">
+        <is>
+          <t>Financials</t>
+        </is>
+      </c>
+      <c r="F35" s="32" t="inlineStr">
+        <is>
+          <t>Insurance</t>
+        </is>
+      </c>
+      <c r="G35" s="89" t="n">
+        <v>0.336</v>
+      </c>
+      <c r="H35" s="92" t="inlineStr">
+        <is>
+          <t>Streak</t>
+        </is>
+      </c>
+      <c r="I35" s="93" t="n">
+        <v>41467.31</v>
+      </c>
+      <c r="J35" s="54" t="inlineStr">
+        <is>
+          <t>Sun Life Financial Inc a financial services company provides asset management wealth insurance and health solutions to individual and institutional customers in Canada the United States the United Kingdom Ireland Hong Kong the Philippines Japan Indonesia India China Australia Singapore Vietnam Malaysia and Bermuda</t>
+        </is>
+      </c>
+      <c r="K35" s="28" t="n"/>
+    </row>
+    <row r="36" ht="45" customHeight="1">
+      <c r="A36" s="36" t="n"/>
+      <c r="B36" s="48" t="inlineStr">
+        <is>
+          <t>🔥</t>
+        </is>
+      </c>
+      <c r="C36" s="38" t="inlineStr">
+        <is>
+          <t>CNR</t>
+        </is>
+      </c>
+      <c r="D36" s="39" t="inlineStr">
+        <is>
+          <t>Canadian National Railway Company</t>
+        </is>
+      </c>
+      <c r="E36" s="40" t="inlineStr">
+        <is>
+          <t>Industrials</t>
+        </is>
+      </c>
+      <c r="F36" s="40" t="inlineStr">
+        <is>
+          <t>Ground Transportation</t>
+        </is>
+      </c>
+      <c r="G36" s="89" t="n">
+        <v>0.327</v>
+      </c>
+      <c r="H36" s="90" t="inlineStr">
+        <is>
+          <t>Streak</t>
+        </is>
+      </c>
+      <c r="I36" s="91" t="n">
+        <v>72839.50999999999</v>
+      </c>
+      <c r="J36" s="53" t="inlineStr">
+        <is>
+          <t>Canadian National Railway Company together with its subsidiaries engages in the rail intermodal trucking and related transportation businesses in Canada and the United States</t>
+        </is>
+      </c>
+      <c r="K36" s="36" t="n"/>
+    </row>
+    <row r="37" ht="45" customHeight="1">
+      <c r="A37" s="28" t="n"/>
+      <c r="B37" s="49" t="inlineStr">
+        <is>
+          <t>🔥</t>
+        </is>
+      </c>
+      <c r="C37" s="30" t="inlineStr">
+        <is>
+          <t>CM</t>
+        </is>
+      </c>
+      <c r="D37" s="31" t="inlineStr">
+        <is>
+          <t>Canadian Imperial Bank of Commerce</t>
+        </is>
+      </c>
+      <c r="E37" s="32" t="inlineStr">
+        <is>
+          <t>Financials</t>
+        </is>
+      </c>
+      <c r="F37" s="32" t="inlineStr">
+        <is>
+          <t>Banks</t>
+        </is>
+      </c>
+      <c r="G37" s="89" t="n">
+        <v>0.324</v>
+      </c>
+      <c r="H37" s="92" t="inlineStr">
+        <is>
+          <t>Streak</t>
+        </is>
+      </c>
+      <c r="I37" s="93" t="n">
+        <v>101497.85</v>
+      </c>
+      <c r="J37" s="54" t="inlineStr">
+        <is>
+          <t>Canadian Imperial Bank of Commerce a diversified financial institution provides various financial products and services to personal business public sector and institutional clients in Canada the United States and internationally</t>
+        </is>
+      </c>
+      <c r="K37" s="28" t="n"/>
+    </row>
+    <row r="38" ht="45" customHeight="1">
+      <c r="A38" s="36" t="n"/>
+      <c r="B38" s="48" t="inlineStr">
+        <is>
+          <t>🔥</t>
+        </is>
+      </c>
+      <c r="C38" s="38" t="inlineStr">
+        <is>
           <t>RY</t>
         </is>
       </c>
-      <c r="D27" s="31" t="inlineStr">
+      <c r="D38" s="39" t="inlineStr">
         <is>
           <t>Royal Bank of Canada</t>
         </is>
       </c>
-      <c r="E27" s="32" t="inlineStr">
+      <c r="E38" s="40" t="inlineStr">
         <is>
           <t>Financials</t>
         </is>
       </c>
-      <c r="F27" s="32" t="inlineStr">
+      <c r="F38" s="40" t="inlineStr">
         <is>
           <t>Banks</t>
         </is>
       </c>
-      <c r="G27" s="89" t="n">
+      <c r="G38" s="89" t="n">
         <v>0.297</v>
       </c>
-      <c r="H27" s="92" t="inlineStr">
+      <c r="H38" s="90" t="inlineStr">
         <is>
           <t>Streak</t>
         </is>
       </c>
-      <c r="I27" s="93" t="n">
+      <c r="I38" s="91" t="n">
         <v>275998.42</v>
       </c>
-      <c r="J27" s="54" t="inlineStr">
+      <c r="J38" s="53" t="inlineStr">
         <is>
           <t>Royal Bank of Canada operates as a diversified financial service company worldwide</t>
         </is>
       </c>
-      <c r="K27" s="36" t="n"/>
-    </row>
-    <row r="28" ht="20.4" customHeight="1">
-      <c r="A28" s="28" t="n"/>
-      <c r="B28" s="48" t="n">
-        <v>21</v>
-      </c>
-      <c r="C28" s="38" t="inlineStr">
-        <is>
-          <t>CP</t>
-        </is>
-      </c>
-      <c r="D28" s="39" t="inlineStr">
-        <is>
-          <t>Canadian Pacific Kansas City Limited</t>
-        </is>
-      </c>
-      <c r="E28" s="40" t="inlineStr">
-        <is>
-          <t>Industrials</t>
-        </is>
-      </c>
-      <c r="F28" s="40" t="inlineStr">
-        <is>
-          <t>Ground Transportation</t>
-        </is>
-      </c>
-      <c r="G28" s="89" t="n">
-        <v>0.295</v>
-      </c>
-      <c r="H28" s="90" t="inlineStr">
-        <is>
-          <t>New</t>
-        </is>
-      </c>
-      <c r="I28" s="91" t="n">
-        <v>79823.21000000001</v>
-      </c>
-      <c r="J28" s="53" t="inlineStr">
-        <is>
-          <t>Canadian Pacific Kansas City Limited together with its subsidiaries owns and operates a transcontinental freight railway in Canada the United States and Mexico</t>
-        </is>
-      </c>
-      <c r="K28" s="28" t="n"/>
-    </row>
-    <row r="29" ht="24" customHeight="1">
-      <c r="A29" s="36" t="n"/>
-      <c r="B29" s="49" t="n">
-        <v>22</v>
-      </c>
-      <c r="C29" s="30" t="inlineStr">
-        <is>
-          <t>CU</t>
-        </is>
-      </c>
-      <c r="D29" s="31" t="inlineStr">
-        <is>
-          <t>Canadian Utilities Limited</t>
-        </is>
-      </c>
-      <c r="E29" s="32" t="inlineStr">
-        <is>
-          <t>Utilities</t>
-        </is>
-      </c>
-      <c r="F29" s="32" t="inlineStr">
-        <is>
-          <t>Multi-Utilities</t>
-        </is>
-      </c>
-      <c r="G29" s="89" t="n">
-        <v>0.266</v>
-      </c>
-      <c r="H29" s="92" t="inlineStr">
-        <is>
-          <t>New</t>
-        </is>
-      </c>
-      <c r="I29" s="93" t="n">
-        <v>10045.65</v>
-      </c>
-      <c r="J29" s="54" t="inlineStr">
-        <is>
-          <t>Canadian Utilities Limited together with its subsidiaries engages in the electricity natural gas renewables pipelines and liquids businesses in Canada Australia and internationally</t>
-        </is>
-      </c>
-      <c r="K29" s="36" t="n"/>
-    </row>
-    <row r="30" ht="30.6" customHeight="1">
-      <c r="A30" s="36" t="n"/>
-      <c r="B30" s="48" t="n">
-        <v>23</v>
-      </c>
-      <c r="C30" s="38" t="inlineStr">
-        <is>
-          <t>CF</t>
-        </is>
-      </c>
-      <c r="D30" s="39" t="inlineStr">
-        <is>
-          <t>Canaccord Genuity Group Inc.</t>
-        </is>
-      </c>
-      <c r="E30" s="40" t="inlineStr">
+      <c r="K38" s="36" t="n"/>
+    </row>
+    <row r="39" ht="45" customHeight="1">
+      <c r="A39" s="28" t="n"/>
+      <c r="B39" s="49" t="inlineStr">
+        <is>
+          <t>🔥</t>
+        </is>
+      </c>
+      <c r="C39" s="30" t="inlineStr">
+        <is>
+          <t>IAG</t>
+        </is>
+      </c>
+      <c r="D39" s="31" t="inlineStr">
+        <is>
+          <t>iA Financial Corporation Inc.</t>
+        </is>
+      </c>
+      <c r="E39" s="32" t="inlineStr">
         <is>
           <t>Financials</t>
         </is>
       </c>
-      <c r="F30" s="40" t="inlineStr">
-        <is>
-          <t>Capital Markets</t>
-        </is>
-      </c>
-      <c r="G30" s="89" t="n">
-        <v>0.265</v>
-      </c>
-      <c r="H30" s="90" t="inlineStr">
-        <is>
-          <t>New</t>
-        </is>
-      </c>
-      <c r="I30" s="91" t="n">
-        <v>976.67</v>
-      </c>
-      <c r="J30" s="53" t="inlineStr">
-        <is>
-          <t>Canaccord Genuity Group Inc operates as a full-service investment dealer in Canada the United States the United Kingdom Europe Crown Dependencies and Australia</t>
-        </is>
-      </c>
-      <c r="K30" s="36" t="n"/>
-    </row>
-    <row r="31" ht="30.6" customHeight="1">
-      <c r="A31" s="28" t="n"/>
-      <c r="B31" s="49" t="n">
-        <v>24</v>
-      </c>
-      <c r="C31" s="30" t="inlineStr">
-        <is>
-          <t>BDGI</t>
-        </is>
-      </c>
-      <c r="D31" s="31" t="inlineStr">
-        <is>
-          <t>Badger Infrastructure Solutions Ltd.</t>
-        </is>
-      </c>
-      <c r="E31" s="32" t="inlineStr">
-        <is>
-          <t>Industrials</t>
-        </is>
-      </c>
-      <c r="F31" s="32" t="inlineStr">
-        <is>
-          <t>Construction and Engineering</t>
-        </is>
-      </c>
-      <c r="G31" s="89" t="n">
-        <v>0.254</v>
-      </c>
-      <c r="H31" s="92" t="inlineStr">
-        <is>
-          <t>New</t>
-        </is>
-      </c>
-      <c r="I31" s="93" t="n">
-        <v>2215.94</v>
-      </c>
-      <c r="J31" s="54" t="inlineStr">
-        <is>
-          <t>Badger Infrastructure Solutions Ltd provides non-destructive excavating and related services to utilities industrial construction transportation and other industries in Canada and the United States</t>
-        </is>
-      </c>
-      <c r="K31" s="28" t="n"/>
-    </row>
-    <row r="32" ht="24" customHeight="1">
-      <c r="A32" s="36" t="n"/>
-      <c r="B32" s="48" t="n">
-        <v>25</v>
-      </c>
-      <c r="C32" s="38" t="inlineStr">
-        <is>
-          <t>IAG</t>
-        </is>
-      </c>
-      <c r="D32" s="39" t="inlineStr">
-        <is>
-          <t>iA Financial Corporation Inc.</t>
-        </is>
-      </c>
-      <c r="E32" s="40" t="inlineStr">
-        <is>
-          <t>Financials</t>
-        </is>
-      </c>
-      <c r="F32" s="40" t="inlineStr">
+      <c r="F39" s="32" t="inlineStr">
         <is>
           <t>Insurance</t>
         </is>
       </c>
-      <c r="G32" s="89" t="n">
+      <c r="G39" s="89" t="n">
         <v>0.238</v>
       </c>
-      <c r="H32" s="90" t="inlineStr">
+      <c r="H39" s="92" t="inlineStr">
         <is>
           <t>Streak</t>
         </is>
       </c>
-      <c r="I32" s="91" t="n">
+      <c r="I39" s="93" t="n">
         <v>11282.66</v>
       </c>
-      <c r="J32" s="53" t="inlineStr">
+      <c r="J39" s="54" t="inlineStr">
         <is>
           <t>iA Financial Corporation Inc provides insurance and wealth management services for individual and group basis in Canada and the United States</t>
         </is>
       </c>
-      <c r="K32" s="36" t="n"/>
-    </row>
-    <row r="33" ht="20.4" customHeight="1">
-      <c r="A33" s="28" t="n"/>
-      <c r="B33" s="49" t="n">
-        <v>26</v>
-      </c>
-      <c r="C33" s="30" t="inlineStr">
-        <is>
-          <t>DXT</t>
-        </is>
-      </c>
-      <c r="D33" s="31" t="inlineStr">
-        <is>
-          <t>Dexterra Group Inc.</t>
-        </is>
-      </c>
-      <c r="E33" s="32" t="inlineStr">
-        <is>
-          <t>Industrials</t>
-        </is>
-      </c>
-      <c r="F33" s="32" t="inlineStr">
-        <is>
-          <t>Commercial Services and Supplies</t>
-        </is>
-      </c>
-      <c r="G33" s="89" t="n">
-        <v>0.234</v>
-      </c>
-      <c r="H33" s="92" t="inlineStr">
-        <is>
-          <t>Repeat</t>
-        </is>
-      </c>
-      <c r="I33" s="93" t="n">
-        <v>576.85</v>
-      </c>
-      <c r="J33" s="54" t="inlineStr">
-        <is>
-          <t>Dexterra Group Inc engages in the provision of support services for the creation management and operation of infrastructure in Canada</t>
-        </is>
-      </c>
-      <c r="K33" s="28" t="n"/>
-    </row>
-    <row r="34" ht="30.6" customHeight="1">
-      <c r="A34" s="36" t="n"/>
-      <c r="B34" s="48" t="n">
-        <v>27</v>
-      </c>
-      <c r="C34" s="38" t="inlineStr">
-        <is>
-          <t>BNS</t>
-        </is>
-      </c>
-      <c r="D34" s="39" t="inlineStr">
-        <is>
-          <t>The Bank of Nova Scotia</t>
-        </is>
-      </c>
-      <c r="E34" s="40" t="inlineStr">
-        <is>
-          <t>Financials</t>
-        </is>
-      </c>
-      <c r="F34" s="40" t="inlineStr">
-        <is>
-          <t>Banks</t>
-        </is>
-      </c>
-      <c r="G34" s="89" t="n">
-        <v>0.227</v>
-      </c>
-      <c r="H34" s="90" t="inlineStr">
-        <is>
-          <t>Repeat</t>
-        </is>
-      </c>
-      <c r="I34" s="91" t="n">
-        <v>100391.39</v>
-      </c>
-      <c r="J34" s="53" t="inlineStr">
-        <is>
-          <t>The Bank of Nova Scotia provides various banking products and services in Canada the United States Mexico Peru Chile Colombia the Caribbean and Central America and internationally</t>
-        </is>
-      </c>
-      <c r="K34" s="36" t="n"/>
-    </row>
-    <row r="35" ht="30.6" customHeight="1">
-      <c r="A35" s="28" t="n"/>
-      <c r="B35" s="49" t="n">
-        <v>28</v>
-      </c>
-      <c r="C35" s="30" t="inlineStr">
-        <is>
-          <t>BDI</t>
-        </is>
-      </c>
-      <c r="D35" s="31" t="inlineStr">
-        <is>
-          <t>Black Diamond Group Limited</t>
-        </is>
-      </c>
-      <c r="E35" s="32" t="inlineStr">
-        <is>
-          <t>Industrials</t>
-        </is>
-      </c>
-      <c r="F35" s="32" t="inlineStr">
-        <is>
-          <t>Commercial Services and Supplies</t>
-        </is>
-      </c>
-      <c r="G35" s="89" t="n">
-        <v>0.22</v>
-      </c>
-      <c r="H35" s="92" t="inlineStr">
-        <is>
-          <t>New</t>
-        </is>
-      </c>
-      <c r="I35" s="93" t="n">
-        <v>927.72</v>
-      </c>
-      <c r="J35" s="54" t="inlineStr">
-        <is>
-          <t>Black Diamond Group Limited provides specialty rentals and industrial services in Canada the United States and Australia</t>
-        </is>
-      </c>
-      <c r="K35" s="28" t="n"/>
-    </row>
-    <row r="36" ht="40.8" customHeight="1">
-      <c r="A36" s="36" t="n"/>
-      <c r="B36" s="48" t="n">
-        <v>29</v>
-      </c>
-      <c r="C36" s="38" t="inlineStr">
-        <is>
-          <t>MFC</t>
-        </is>
-      </c>
-      <c r="D36" s="39" t="inlineStr">
-        <is>
-          <t>Manulife Financial Corporation</t>
-        </is>
-      </c>
-      <c r="E36" s="40" t="inlineStr">
-        <is>
-          <t>Financials</t>
-        </is>
-      </c>
-      <c r="F36" s="40" t="inlineStr">
-        <is>
-          <t>Insurance</t>
-        </is>
-      </c>
-      <c r="G36" s="89" t="n">
-        <v>0.216</v>
-      </c>
-      <c r="H36" s="90" t="inlineStr">
-        <is>
-          <t>New</t>
-        </is>
-      </c>
-      <c r="I36" s="91" t="n">
-        <v>65572.44</v>
-      </c>
-      <c r="J36" s="53" t="inlineStr">
-        <is>
-          <t>Manulife Financial Corporation together with its subsidiaries provides financial products and services in the United States Canada Asia and internationally</t>
-        </is>
-      </c>
-      <c r="K36" s="36" t="n"/>
-    </row>
-    <row r="37" ht="24" customHeight="1">
-      <c r="A37" s="28" t="n"/>
-      <c r="B37" s="49" t="n">
-        <v>30</v>
-      </c>
-      <c r="C37" s="30" t="inlineStr">
+      <c r="K39" s="28" t="n"/>
+    </row>
+    <row r="40" ht="45" customHeight="1">
+      <c r="A40" s="36" t="n"/>
+      <c r="B40" s="106" t="inlineStr">
+        <is>
+          <t>🔥</t>
+        </is>
+      </c>
+      <c r="C40" s="107" t="inlineStr">
         <is>
           <t>IFP</t>
         </is>
       </c>
-      <c r="D37" s="31" t="inlineStr">
+      <c r="D40" s="108" t="inlineStr">
         <is>
           <t>Interfor Corporation</t>
         </is>
       </c>
-      <c r="E37" s="32" t="inlineStr">
+      <c r="E40" s="109" t="inlineStr">
         <is>
           <t>Materials</t>
         </is>
       </c>
-      <c r="F37" s="32" t="inlineStr">
+      <c r="F40" s="109" t="inlineStr">
         <is>
           <t>Paper and Forest Products</t>
         </is>
       </c>
-      <c r="G37" s="89" t="n">
+      <c r="G40" s="110" t="n">
         <v>0.2</v>
       </c>
-      <c r="H37" s="92" t="inlineStr">
+      <c r="H40" s="111" t="inlineStr">
         <is>
           <t>Streak</t>
         </is>
       </c>
-      <c r="I37" s="93" t="n">
+      <c r="I40" s="112" t="n">
         <v>501.72</v>
       </c>
-      <c r="J37" s="54" t="inlineStr">
+      <c r="J40" s="113" t="inlineStr">
         <is>
           <t>Interfor Corporation together with its subsidiaries produces and sells wood products in Canada the United States Japan China Taiwan and internationally</t>
         </is>
       </c>
-      <c r="K37" s="28" t="n"/>
-    </row>
-    <row r="38" ht="20.4" customHeight="1">
-      <c r="A38" s="36" t="n"/>
-      <c r="B38" s="48" t="n">
-        <v>31</v>
-      </c>
-      <c r="C38" s="38" t="inlineStr">
-        <is>
-          <t>TOY</t>
-        </is>
-      </c>
-      <c r="D38" s="39" t="inlineStr">
-        <is>
-          <t>Spin Master Corp.</t>
-        </is>
-      </c>
-      <c r="E38" s="40" t="inlineStr">
-        <is>
-          <t>Consumer Discretionary</t>
-        </is>
-      </c>
-      <c r="F38" s="40" t="inlineStr">
-        <is>
-          <t>Leisure Products</t>
-        </is>
-      </c>
-      <c r="G38" s="89" t="n">
-        <v>0.174</v>
-      </c>
-      <c r="H38" s="90" t="inlineStr">
-        <is>
-          <t>Repeat</t>
-        </is>
-      </c>
-      <c r="I38" s="91" t="n">
-        <v>1330.28</v>
-      </c>
-      <c r="J38" s="53" t="inlineStr">
-        <is>
-          <t>Spin Master Corp a children’s entertainment company engages in the creation design manufacture licensing and marketing of various toys entertainment products and digital games in North America Europe and internationally</t>
-        </is>
-      </c>
-      <c r="K38" s="36" t="n"/>
-    </row>
-    <row r="39" ht="24" customHeight="1">
-      <c r="A39" s="28" t="n"/>
-      <c r="B39" s="49" t="n">
-        <v>32</v>
-      </c>
-      <c r="C39" s="30" t="inlineStr">
-        <is>
-          <t>DBM</t>
-        </is>
-      </c>
-      <c r="D39" s="31" t="inlineStr">
-        <is>
-          <t>Doman Building Materials Group Ltd.</t>
-        </is>
-      </c>
-      <c r="E39" s="32" t="inlineStr">
-        <is>
-          <t>Industrials</t>
-        </is>
-      </c>
-      <c r="F39" s="32" t="inlineStr">
-        <is>
-          <t>Trading Companies and Distributors</t>
-        </is>
-      </c>
-      <c r="G39" s="89" t="n">
-        <v>0.146</v>
-      </c>
-      <c r="H39" s="92" t="inlineStr">
-        <is>
-          <t>New</t>
-        </is>
-      </c>
-      <c r="I39" s="93" t="n">
-        <v>676.4400000000001</v>
-      </c>
-      <c r="J39" s="54" t="inlineStr">
-        <is>
-          <t>Doman Building Materials Group Ltd through its subsidiaries engages in the wholesale distribution of building materials and home renovation products in the United States and Canada</t>
-        </is>
-      </c>
-      <c r="K39" s="28" t="n"/>
-    </row>
-    <row r="40" ht="20.4" customHeight="1">
-      <c r="A40" s="36" t="n"/>
-      <c r="B40" s="106" t="n">
-        <v>33</v>
-      </c>
-      <c r="C40" s="107" t="inlineStr">
-        <is>
-          <t>DFY</t>
-        </is>
-      </c>
-      <c r="D40" s="108" t="inlineStr">
-        <is>
-          <t>Definity Financial Corporation</t>
-        </is>
-      </c>
-      <c r="E40" s="109" t="inlineStr">
-        <is>
-          <t>Financials</t>
-        </is>
-      </c>
-      <c r="F40" s="109" t="inlineStr">
-        <is>
-          <t>Insurance</t>
-        </is>
-      </c>
-      <c r="G40" s="110" t="n">
-        <v>0.08</v>
-      </c>
-      <c r="H40" s="111" t="inlineStr">
-        <is>
-          <t>Repeat</t>
-        </is>
-      </c>
-      <c r="I40" s="112" t="n">
-        <v>6226.62</v>
-      </c>
-      <c r="J40" s="113" t="inlineStr">
-        <is>
-          <t>Definity Financial Corporation together with its subsidiaries offers property and casualty insurance products in Canada</t>
-        </is>
-      </c>
       <c r="K40" s="36" t="n"/>
     </row>
-    <row r="41" ht="15.6" customHeight="1" thickBot="1">
+    <row r="41" ht="8" customHeight="1" thickBot="1">
       <c r="A41" s="68" t="n"/>
-      <c r="B41" s="69" t="n"/>
-      <c r="C41" s="70" t="n"/>
-      <c r="D41" s="71" t="n"/>
-      <c r="E41" s="72" t="n"/>
-      <c r="F41" s="72" t="n"/>
-      <c r="G41" s="94" t="n"/>
-      <c r="H41" s="95" t="n"/>
-      <c r="I41" s="96" t="n"/>
-      <c r="J41" s="74" t="n"/>
+      <c r="B41" s="114" t="n"/>
+      <c r="C41" s="115" t="n"/>
+      <c r="D41" s="116" t="n"/>
+      <c r="E41" s="117" t="n"/>
+      <c r="F41" s="117" t="n"/>
+      <c r="G41" s="118" t="n"/>
+      <c r="H41" s="119" t="n"/>
+      <c r="I41" s="120" t="n"/>
+      <c r="J41" s="121" t="n"/>
       <c r="K41" s="68" t="n"/>
     </row>
     <row r="42" ht="34" customHeight="1">
       <c r="A42" s="43" t="n"/>
-      <c r="B42" s="114" t="inlineStr">
+      <c r="B42" s="122" t="inlineStr">
         <is>
           <t>🔓 Want to know which of these we would actually buy? Start your 14-Day Free Trial at www.5iresearch.ca/bb</t>
         </is>
       </c>
-      <c r="C42" s="115" t="n"/>
-      <c r="D42" s="115" t="n"/>
-      <c r="E42" s="115" t="n"/>
-      <c r="F42" s="115" t="n"/>
-      <c r="G42" s="115" t="n"/>
-      <c r="H42" s="115" t="n"/>
-      <c r="I42" s="115" t="n"/>
-      <c r="J42" s="115" t="n"/>
+      <c r="C42" s="123" t="n"/>
+      <c r="D42" s="123" t="n"/>
+      <c r="E42" s="123" t="n"/>
+      <c r="F42" s="123" t="n"/>
+      <c r="G42" s="123" t="n"/>
+      <c r="H42" s="123" t="n"/>
+      <c r="I42" s="123" t="n"/>
+      <c r="J42" s="123" t="n"/>
       <c r="K42" s="43" t="n"/>
     </row>
     <row r="43" ht="28" customHeight="1" thickBot="1">
       <c r="A43" s="43" t="n"/>
-      <c r="B43" s="116" t="inlineStr">
+      <c r="B43" s="124" t="inlineStr">
         <is>
           <t>Disclosure: While this table does not constitute any formal opinion on names presented, authors may own shares in non-Canadian securities listed above.</t>
         </is>
       </c>
-      <c r="C43" s="117" t="n"/>
-      <c r="D43" s="117" t="n"/>
-      <c r="E43" s="117" t="n"/>
-      <c r="F43" s="117" t="n"/>
-      <c r="G43" s="117" t="n"/>
-      <c r="H43" s="117" t="n"/>
-      <c r="I43" s="117" t="n"/>
-      <c r="J43" s="117" t="n"/>
+      <c r="C43" s="125" t="n"/>
+      <c r="D43" s="125" t="n"/>
+      <c r="E43" s="125" t="n"/>
+      <c r="F43" s="125" t="n"/>
+      <c r="G43" s="125" t="n"/>
+      <c r="H43" s="125" t="n"/>
+      <c r="I43" s="125" t="n"/>
+      <c r="J43" s="125" t="n"/>
       <c r="K43" s="43" t="n"/>
     </row>
     <row r="44" ht="12" customHeight="1">
@@ -3083,7 +3169,7 @@
   <mergeCells count="4">
     <mergeCell ref="B43:J43"/>
     <mergeCell ref="B2:G2"/>
-    <mergeCell ref="H2:I2"/>
+    <mergeCell ref="I2:J2"/>
     <mergeCell ref="B42:J42"/>
   </mergeCells>
   <conditionalFormatting sqref="G8:G40">
@@ -4064,10 +4150,10 @@
           <t>Benchmark Beaters — U.S. Stocks</t>
         </is>
       </c>
-      <c r="H2" s="84" t="n">
-        <v>46224.86266495839</v>
-      </c>
-      <c r="J2" s="83" t="n"/>
+      <c r="H2" s="82" t="n"/>
+      <c r="I2" s="84" t="n">
+        <v>46224.87725170761</v>
+      </c>
     </row>
     <row r="3" ht="3" customHeight="1">
       <c r="A3" s="44" t="n"/>
@@ -4118,21 +4204,17 @@
       <c r="F6" s="24" t="n"/>
       <c r="G6" s="24" t="n"/>
       <c r="H6" s="24" t="n"/>
-      <c r="I6" s="55" t="inlineStr">
+      <c r="I6" s="24" t="n"/>
+      <c r="J6" s="55" t="inlineStr">
         <is>
           <t>Chris White, CFA
 Head of Research</t>
         </is>
       </c>
-      <c r="J6" s="24" t="n"/>
     </row>
     <row r="7" ht="28.05" customHeight="1" thickBot="1">
       <c r="A7" s="26" t="n"/>
-      <c r="B7" s="27" t="inlineStr">
-        <is>
-          <t>#</t>
-        </is>
-      </c>
+      <c r="B7" s="27" t="inlineStr"/>
       <c r="C7" s="27" t="inlineStr">
         <is>
           <t>Ticker</t>
@@ -4175,10 +4257,12 @@
       </c>
       <c r="K7" s="26" t="n"/>
     </row>
-    <row r="8" ht="24" customHeight="1">
+    <row r="8" ht="45" customHeight="1">
       <c r="A8" s="36" t="n"/>
-      <c r="B8" s="48" t="n">
-        <v>1</v>
+      <c r="B8" s="48" t="inlineStr">
+        <is>
+          <t>🆕</t>
+        </is>
       </c>
       <c r="C8" s="38" t="inlineStr">
         <is>
@@ -4218,10 +4302,12 @@
       </c>
       <c r="K8" s="36" t="n"/>
     </row>
-    <row r="9" ht="24" customHeight="1">
+    <row r="9" ht="45" customHeight="1">
       <c r="A9" s="28" t="n"/>
-      <c r="B9" s="49" t="n">
-        <v>2</v>
+      <c r="B9" s="49" t="inlineStr">
+        <is>
+          <t>🆕</t>
+        </is>
       </c>
       <c r="C9" s="30" t="inlineStr">
         <is>
@@ -4261,1384 +4347,1446 @@
       </c>
       <c r="K9" s="28" t="n"/>
     </row>
-    <row r="10" ht="20.4" customHeight="1">
+    <row r="10" ht="45" customHeight="1">
       <c r="A10" s="36" t="n"/>
-      <c r="B10" s="48" t="n">
-        <v>3</v>
+      <c r="B10" s="48" t="inlineStr">
+        <is>
+          <t>🆕</t>
+        </is>
       </c>
       <c r="C10" s="38" t="inlineStr">
         <is>
+          <t>JBHT</t>
+        </is>
+      </c>
+      <c r="D10" s="39" t="inlineStr">
+        <is>
+          <t>J.B. Hunt Transport Services Inc.</t>
+        </is>
+      </c>
+      <c r="E10" s="40" t="inlineStr">
+        <is>
+          <t>Industrials</t>
+        </is>
+      </c>
+      <c r="F10" s="40" t="inlineStr">
+        <is>
+          <t>Ground Transportation</t>
+        </is>
+      </c>
+      <c r="G10" s="89" t="n">
+        <v>0.424</v>
+      </c>
+      <c r="H10" s="90" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="I10" s="91" t="n">
+        <v>26566.73</v>
+      </c>
+      <c r="J10" s="53" t="inlineStr">
+        <is>
+          <t>J</t>
+        </is>
+      </c>
+      <c r="K10" s="36" t="n"/>
+    </row>
+    <row r="11" ht="45" customHeight="1">
+      <c r="A11" s="28" t="n"/>
+      <c r="B11" s="49" t="inlineStr">
+        <is>
+          <t>🆕</t>
+        </is>
+      </c>
+      <c r="C11" s="30" t="inlineStr">
+        <is>
+          <t>GL</t>
+        </is>
+      </c>
+      <c r="D11" s="31" t="inlineStr">
+        <is>
+          <t>Globe Life Inc.</t>
+        </is>
+      </c>
+      <c r="E11" s="32" t="inlineStr">
+        <is>
+          <t>Financials</t>
+        </is>
+      </c>
+      <c r="F11" s="32" t="inlineStr">
+        <is>
+          <t>Insurance</t>
+        </is>
+      </c>
+      <c r="G11" s="89" t="n">
+        <v>0.356</v>
+      </c>
+      <c r="H11" s="92" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="I11" s="93" t="n">
+        <v>12644.53</v>
+      </c>
+      <c r="J11" s="54" t="inlineStr">
+        <is>
+          <t>Globe Life Inc through its subsidiaries provides various life and supplemental health insurance products to lower middle- and middle-income families in the United States</t>
+        </is>
+      </c>
+      <c r="K11" s="28" t="n"/>
+    </row>
+    <row r="12" ht="45" customHeight="1">
+      <c r="A12" s="36" t="n"/>
+      <c r="B12" s="48" t="inlineStr">
+        <is>
+          <t>🆕</t>
+        </is>
+      </c>
+      <c r="C12" s="38" t="inlineStr">
+        <is>
+          <t>WELL</t>
+        </is>
+      </c>
+      <c r="D12" s="39" t="inlineStr">
+        <is>
+          <t>Welltower Inc.</t>
+        </is>
+      </c>
+      <c r="E12" s="40" t="inlineStr">
+        <is>
+          <t>Real Estate</t>
+        </is>
+      </c>
+      <c r="F12" s="40" t="inlineStr">
+        <is>
+          <t>Health Care REITs</t>
+        </is>
+      </c>
+      <c r="G12" s="89" t="n">
+        <v>0.351</v>
+      </c>
+      <c r="H12" s="90" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="I12" s="91" t="n">
+        <v>148209.56</v>
+      </c>
+      <c r="J12" s="53" t="inlineStr">
+        <is>
+          <t>Welltower Inc is a S&amp;P 500 company is positioned at the center of the silver economy focusing on rental housing for aging seniors across the United States United Kingdom and Canada</t>
+        </is>
+      </c>
+      <c r="K12" s="36" t="n"/>
+    </row>
+    <row r="13" ht="45" customHeight="1">
+      <c r="A13" s="28" t="n"/>
+      <c r="B13" s="49" t="inlineStr">
+        <is>
+          <t>🆕</t>
+        </is>
+      </c>
+      <c r="C13" s="30" t="inlineStr">
+        <is>
+          <t>CVS</t>
+        </is>
+      </c>
+      <c r="D13" s="31" t="inlineStr">
+        <is>
+          <t>CVS Health Corporation</t>
+        </is>
+      </c>
+      <c r="E13" s="32" t="inlineStr">
+        <is>
+          <t>Health Care</t>
+        </is>
+      </c>
+      <c r="F13" s="32" t="inlineStr">
+        <is>
+          <t>Health Care Providers and Services</t>
+        </is>
+      </c>
+      <c r="G13" s="89" t="n">
+        <v>0.344</v>
+      </c>
+      <c r="H13" s="92" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="I13" s="93" t="n">
+        <v>125211.85</v>
+      </c>
+      <c r="J13" s="54" t="inlineStr">
+        <is>
+          <t>CVS Health Corporation provides health solutions in the United States</t>
+        </is>
+      </c>
+      <c r="K13" s="28" t="n"/>
+    </row>
+    <row r="14" ht="45" customHeight="1">
+      <c r="A14" s="36" t="n"/>
+      <c r="B14" s="48" t="inlineStr">
+        <is>
+          <t>🆕</t>
+        </is>
+      </c>
+      <c r="C14" s="38" t="inlineStr">
+        <is>
+          <t>TRV</t>
+        </is>
+      </c>
+      <c r="D14" s="39" t="inlineStr">
+        <is>
+          <t>The Travelers Companies Inc.</t>
+        </is>
+      </c>
+      <c r="E14" s="40" t="inlineStr">
+        <is>
+          <t>Financials</t>
+        </is>
+      </c>
+      <c r="F14" s="40" t="inlineStr">
+        <is>
+          <t>Insurance</t>
+        </is>
+      </c>
+      <c r="G14" s="89" t="n">
+        <v>0.341</v>
+      </c>
+      <c r="H14" s="90" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="I14" s="91" t="n">
+        <v>64533.41</v>
+      </c>
+      <c r="J14" s="53" t="inlineStr">
+        <is>
+          <t>The Travelers Companies Inc through its subsidiaries provides a range of commercial and personal property and casualty insurance products and services to businesses government units associations and individuals in the United States Canada and internationally</t>
+        </is>
+      </c>
+      <c r="K14" s="36" t="n"/>
+    </row>
+    <row r="15" ht="45" customHeight="1">
+      <c r="A15" s="28" t="n"/>
+      <c r="B15" s="49" t="inlineStr">
+        <is>
+          <t>🆕</t>
+        </is>
+      </c>
+      <c r="C15" s="30" t="inlineStr">
+        <is>
+          <t>ADM</t>
+        </is>
+      </c>
+      <c r="D15" s="31" t="inlineStr">
+        <is>
+          <t>Archer-Daniels-Midland Company</t>
+        </is>
+      </c>
+      <c r="E15" s="32" t="inlineStr">
+        <is>
+          <t>Consumer Staples</t>
+        </is>
+      </c>
+      <c r="F15" s="32" t="inlineStr">
+        <is>
+          <t>Food Products</t>
+        </is>
+      </c>
+      <c r="G15" s="89" t="n">
+        <v>0.295</v>
+      </c>
+      <c r="H15" s="92" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="I15" s="93" t="n">
+        <v>39380.19</v>
+      </c>
+      <c r="J15" s="54" t="inlineStr">
+        <is>
+          <t>Archer-Daniels-Midland Company provides human and animal nutrition ingredients and solutions in the United States Switzerland the Cayman Islands Brazil Mexico Canada the United Kingdom and internationally</t>
+        </is>
+      </c>
+      <c r="K15" s="28" t="n"/>
+    </row>
+    <row r="16" ht="45" customHeight="1">
+      <c r="A16" s="36" t="n"/>
+      <c r="B16" s="48" t="inlineStr">
+        <is>
+          <t>🆕</t>
+        </is>
+      </c>
+      <c r="C16" s="38" t="inlineStr">
+        <is>
+          <t>DOC</t>
+        </is>
+      </c>
+      <c r="D16" s="39" t="inlineStr">
+        <is>
+          <t>Healthpeak Properties Inc.</t>
+        </is>
+      </c>
+      <c r="E16" s="40" t="inlineStr">
+        <is>
+          <t>Real Estate</t>
+        </is>
+      </c>
+      <c r="F16" s="40" t="inlineStr">
+        <is>
+          <t>Health Care REITs</t>
+        </is>
+      </c>
+      <c r="G16" s="89" t="n">
+        <v>0.292</v>
+      </c>
+      <c r="H16" s="90" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="I16" s="91" t="n">
+        <v>14353.95</v>
+      </c>
+      <c r="J16" s="53" t="inlineStr">
+        <is>
+          <t>Healthpeak Properties Inc is a Standard &amp; Poor’s 500 company that owns operates and develops high-quality real estate focused on healthcare discovery and delivery in the United States</t>
+        </is>
+      </c>
+      <c r="K16" s="36" t="n"/>
+    </row>
+    <row r="17" ht="45" customHeight="1">
+      <c r="A17" s="28" t="n"/>
+      <c r="B17" s="49" t="inlineStr">
+        <is>
+          <t>🆕</t>
+        </is>
+      </c>
+      <c r="C17" s="30" t="inlineStr">
+        <is>
+          <t>GWW</t>
+        </is>
+      </c>
+      <c r="D17" s="31" t="inlineStr">
+        <is>
+          <t>W.W. Grainger Inc.</t>
+        </is>
+      </c>
+      <c r="E17" s="32" t="inlineStr">
+        <is>
+          <t>Industrials</t>
+        </is>
+      </c>
+      <c r="F17" s="32" t="inlineStr">
+        <is>
+          <t>Trading Companies and Distributors</t>
+        </is>
+      </c>
+      <c r="G17" s="89" t="n">
+        <v>0.292</v>
+      </c>
+      <c r="H17" s="92" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="I17" s="93" t="n">
+        <v>62147.38</v>
+      </c>
+      <c r="J17" s="54" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="K17" s="28" t="n"/>
+    </row>
+    <row r="18" ht="45" customHeight="1">
+      <c r="A18" s="36" t="n"/>
+      <c r="B18" s="48" t="inlineStr">
+        <is>
+          <t>🆕</t>
+        </is>
+      </c>
+      <c r="C18" s="38" t="inlineStr">
+        <is>
+          <t>UNP</t>
+        </is>
+      </c>
+      <c r="D18" s="39" t="inlineStr">
+        <is>
+          <t>Union Pacific Corporation</t>
+        </is>
+      </c>
+      <c r="E18" s="40" t="inlineStr">
+        <is>
+          <t>Industrials</t>
+        </is>
+      </c>
+      <c r="F18" s="40" t="inlineStr">
+        <is>
+          <t>Ground Transportation</t>
+        </is>
+      </c>
+      <c r="G18" s="89" t="n">
+        <v>0.29</v>
+      </c>
+      <c r="H18" s="90" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="I18" s="91" t="n">
+        <v>158667.48</v>
+      </c>
+      <c r="J18" s="53" t="inlineStr">
+        <is>
+          <t>Union Pacific Corporation through its subsidiary Union Pacific Railroad Company operates in the railroad business in the United States</t>
+        </is>
+      </c>
+      <c r="K18" s="36" t="n"/>
+    </row>
+    <row r="19" ht="45" customHeight="1">
+      <c r="A19" s="28" t="n"/>
+      <c r="B19" s="49" t="inlineStr">
+        <is>
+          <t>🆕</t>
+        </is>
+      </c>
+      <c r="C19" s="30" t="inlineStr">
+        <is>
+          <t>PFG</t>
+        </is>
+      </c>
+      <c r="D19" s="31" t="inlineStr">
+        <is>
+          <t>Principal Financial Group Inc.</t>
+        </is>
+      </c>
+      <c r="E19" s="32" t="inlineStr">
+        <is>
+          <t>Financials</t>
+        </is>
+      </c>
+      <c r="F19" s="32" t="inlineStr">
+        <is>
+          <t>Insurance</t>
+        </is>
+      </c>
+      <c r="G19" s="89" t="n">
+        <v>0.222</v>
+      </c>
+      <c r="H19" s="92" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="I19" s="93" t="n">
+        <v>23624.19</v>
+      </c>
+      <c r="J19" s="54" t="inlineStr">
+        <is>
+          <t>Principal Financial Group Inc provides retirement asset management and insurance products and services to businesses individuals and institutional clients worldwide</t>
+        </is>
+      </c>
+      <c r="K19" s="28" t="n"/>
+    </row>
+    <row r="20" ht="45" customHeight="1">
+      <c r="A20" s="36" t="n"/>
+      <c r="B20" s="48" t="inlineStr">
+        <is>
+          <t>🆕</t>
+        </is>
+      </c>
+      <c r="C20" s="38" t="inlineStr">
+        <is>
+          <t>XYZ</t>
+        </is>
+      </c>
+      <c r="D20" s="39" t="inlineStr">
+        <is>
+          <t>Block Inc.</t>
+        </is>
+      </c>
+      <c r="E20" s="40" t="inlineStr">
+        <is>
+          <t>Financials</t>
+        </is>
+      </c>
+      <c r="F20" s="40" t="inlineStr">
+        <is>
+          <t>Financial Services</t>
+        </is>
+      </c>
+      <c r="G20" s="89" t="n">
+        <v>0.203</v>
+      </c>
+      <c r="H20" s="90" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="I20" s="91" t="n">
+        <v>40474.89</v>
+      </c>
+      <c r="J20" s="53" t="inlineStr">
+        <is>
+          <t>Block Inc together with its subsidiaries builds ecosystems focused on commerce and financial products and services in the United States and internationally</t>
+        </is>
+      </c>
+      <c r="K20" s="36" t="n"/>
+    </row>
+    <row r="21" ht="45" customHeight="1">
+      <c r="A21" s="28" t="n"/>
+      <c r="B21" s="49" t="inlineStr">
+        <is>
+          <t>🆕</t>
+        </is>
+      </c>
+      <c r="C21" s="30" t="inlineStr">
+        <is>
+          <t>BAC</t>
+        </is>
+      </c>
+      <c r="D21" s="31" t="inlineStr">
+        <is>
+          <t>Bank of America Corporation</t>
+        </is>
+      </c>
+      <c r="E21" s="32" t="inlineStr">
+        <is>
+          <t>Financials</t>
+        </is>
+      </c>
+      <c r="F21" s="32" t="inlineStr">
+        <is>
+          <t>Banks</t>
+        </is>
+      </c>
+      <c r="G21" s="89" t="n">
+        <v>0.197</v>
+      </c>
+      <c r="H21" s="92" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="I21" s="93" t="n">
+        <v>388502.86</v>
+      </c>
+      <c r="J21" s="54" t="inlineStr">
+        <is>
+          <t>Bank of America Corporation through its subsidiaries provides various financial products and services for individual consumers small and middle-market businesses institutional investors large corporations and governments worldwide</t>
+        </is>
+      </c>
+      <c r="K21" s="28" t="n"/>
+    </row>
+    <row r="22" ht="45" customHeight="1">
+      <c r="A22" s="36" t="n"/>
+      <c r="B22" s="48" t="inlineStr">
+        <is>
+          <t>🆕</t>
+        </is>
+      </c>
+      <c r="C22" s="38" t="inlineStr">
+        <is>
+          <t>EG</t>
+        </is>
+      </c>
+      <c r="D22" s="39" t="inlineStr">
+        <is>
+          <t>Everest Group Ltd.</t>
+        </is>
+      </c>
+      <c r="E22" s="40" t="inlineStr">
+        <is>
+          <t>Financials</t>
+        </is>
+      </c>
+      <c r="F22" s="40" t="inlineStr">
+        <is>
+          <t>Insurance</t>
+        </is>
+      </c>
+      <c r="G22" s="89" t="n">
+        <v>0.18</v>
+      </c>
+      <c r="H22" s="90" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="I22" s="91" t="n">
+        <v>13320.91</v>
+      </c>
+      <c r="J22" s="53" t="inlineStr">
+        <is>
+          <t>Everest Group Ltd together with subsidiaries provides reinsurance and insurance products in the United States Europe and internationally</t>
+        </is>
+      </c>
+      <c r="K22" s="36" t="n"/>
+    </row>
+    <row r="23" ht="45" customHeight="1">
+      <c r="A23" s="28" t="n"/>
+      <c r="B23" s="49" t="inlineStr">
+        <is>
+          <t>🆕</t>
+        </is>
+      </c>
+      <c r="C23" s="30" t="inlineStr">
+        <is>
+          <t>CFG</t>
+        </is>
+      </c>
+      <c r="D23" s="31" t="inlineStr">
+        <is>
+          <t>Citizens Financial Group Inc.</t>
+        </is>
+      </c>
+      <c r="E23" s="32" t="inlineStr">
+        <is>
+          <t>Financials</t>
+        </is>
+      </c>
+      <c r="F23" s="32" t="inlineStr">
+        <is>
+          <t>Banks</t>
+        </is>
+      </c>
+      <c r="G23" s="89" t="n">
+        <v>0.166</v>
+      </c>
+      <c r="H23" s="92" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="I23" s="93" t="n">
+        <v>27585.86</v>
+      </c>
+      <c r="J23" s="54" t="inlineStr">
+        <is>
+          <t>Citizens Financial Group Inc operates as the bank holding company that provides retail and commercial banking products and services to individuals small businesses middle-market companies large corporations and institutions in the United States</t>
+        </is>
+      </c>
+      <c r="K23" s="28" t="n"/>
+    </row>
+    <row r="24" ht="45" customHeight="1">
+      <c r="A24" s="36" t="n"/>
+      <c r="B24" s="48" t="inlineStr">
+        <is>
+          <t>🆕</t>
+        </is>
+      </c>
+      <c r="C24" s="38" t="inlineStr">
+        <is>
+          <t>FITB</t>
+        </is>
+      </c>
+      <c r="D24" s="39" t="inlineStr">
+        <is>
+          <t>Fifth Third Bancorp</t>
+        </is>
+      </c>
+      <c r="E24" s="40" t="inlineStr">
+        <is>
+          <t>Financials</t>
+        </is>
+      </c>
+      <c r="F24" s="40" t="inlineStr">
+        <is>
+          <t>Banks</t>
+        </is>
+      </c>
+      <c r="G24" s="89" t="n">
+        <v>0.155</v>
+      </c>
+      <c r="H24" s="90" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="I24" s="91" t="n">
+        <v>47955.66</v>
+      </c>
+      <c r="J24" s="53" t="inlineStr">
+        <is>
+          <t>Fifth Third Bancorp operates as the bank holding company for Fifth Third Bank National Association that provides a range of financial products and services in the United States</t>
+        </is>
+      </c>
+      <c r="K24" s="36" t="n"/>
+    </row>
+    <row r="25" ht="45" customHeight="1">
+      <c r="A25" s="28" t="n"/>
+      <c r="B25" s="49" t="inlineStr">
+        <is>
+          <t>🆕</t>
+        </is>
+      </c>
+      <c r="C25" s="30" t="inlineStr">
+        <is>
+          <t>MNST</t>
+        </is>
+      </c>
+      <c r="D25" s="31" t="inlineStr">
+        <is>
+          <t>Monster Beverage Corporation</t>
+        </is>
+      </c>
+      <c r="E25" s="32" t="inlineStr">
+        <is>
+          <t>Consumer Staples</t>
+        </is>
+      </c>
+      <c r="F25" s="32" t="inlineStr">
+        <is>
+          <t>Beverages</t>
+        </is>
+      </c>
+      <c r="G25" s="89" t="n">
+        <v>0.152</v>
+      </c>
+      <c r="H25" s="92" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="I25" s="93" t="n">
+        <v>89144.46000000001</v>
+      </c>
+      <c r="J25" s="54" t="inlineStr">
+        <is>
+          <t>Monster Beverage Corporation through its subsidiaries engages in development marketing sale and distribution of energy drink beverages and concentrates in the United States and internationally</t>
+        </is>
+      </c>
+      <c r="K25" s="28" t="n"/>
+    </row>
+    <row r="26" ht="45" customHeight="1">
+      <c r="A26" s="36" t="n"/>
+      <c r="B26" s="48" t="inlineStr">
+        <is>
+          <t>🆕</t>
+        </is>
+      </c>
+      <c r="C26" s="38" t="inlineStr">
+        <is>
+          <t>PRU</t>
+        </is>
+      </c>
+      <c r="D26" s="39" t="inlineStr">
+        <is>
+          <t>Prudential Financial Inc.</t>
+        </is>
+      </c>
+      <c r="E26" s="40" t="inlineStr">
+        <is>
+          <t>Financials</t>
+        </is>
+      </c>
+      <c r="F26" s="40" t="inlineStr">
+        <is>
+          <t>Insurance</t>
+        </is>
+      </c>
+      <c r="G26" s="89" t="n">
+        <v>0.131</v>
+      </c>
+      <c r="H26" s="90" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="I26" s="91" t="n">
+        <v>36717.82</v>
+      </c>
+      <c r="J26" s="53" t="inlineStr">
+        <is>
+          <t>Prudential Financial Inc together with its subsidiaries provides financial products and services in the United States Japan and internationally</t>
+        </is>
+      </c>
+      <c r="K26" s="36" t="n"/>
+    </row>
+    <row r="27" ht="45" customHeight="1">
+      <c r="A27" s="28" t="n"/>
+      <c r="B27" s="49" t="inlineStr">
+        <is>
+          <t>🆕</t>
+        </is>
+      </c>
+      <c r="C27" s="30" t="inlineStr">
+        <is>
+          <t>EXPD</t>
+        </is>
+      </c>
+      <c r="D27" s="31" t="inlineStr">
+        <is>
+          <t>Expeditors International of Washington Inc.</t>
+        </is>
+      </c>
+      <c r="E27" s="32" t="inlineStr">
+        <is>
+          <t>Industrials</t>
+        </is>
+      </c>
+      <c r="F27" s="32" t="inlineStr">
+        <is>
+          <t>Air Freight and Logistics</t>
+        </is>
+      </c>
+      <c r="G27" s="89" t="n">
+        <v>0.127</v>
+      </c>
+      <c r="H27" s="92" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="I27" s="93" t="n">
+        <v>21453.67</v>
+      </c>
+      <c r="J27" s="54" t="inlineStr">
+        <is>
+          <t>Expeditors International of Washington Inc together with its subsidiaries provides logistics services in the Americas North Asia South Asia Europe and Middle East Africa and India</t>
+        </is>
+      </c>
+      <c r="K27" s="28" t="n"/>
+    </row>
+    <row r="28" ht="45" customHeight="1">
+      <c r="A28" s="36" t="n"/>
+      <c r="B28" s="48" t="inlineStr">
+        <is>
+          <t>🆕</t>
+        </is>
+      </c>
+      <c r="C28" s="38" t="inlineStr">
+        <is>
+          <t>V</t>
+        </is>
+      </c>
+      <c r="D28" s="39" t="inlineStr">
+        <is>
+          <t>Visa Inc.</t>
+        </is>
+      </c>
+      <c r="E28" s="40" t="inlineStr">
+        <is>
+          <t>Financials</t>
+        </is>
+      </c>
+      <c r="F28" s="40" t="inlineStr">
+        <is>
+          <t>Financial Services</t>
+        </is>
+      </c>
+      <c r="G28" s="89" t="n">
+        <v>0.095</v>
+      </c>
+      <c r="H28" s="90" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="I28" s="91" t="n">
+        <v>612046.08</v>
+      </c>
+      <c r="J28" s="53" t="inlineStr">
+        <is>
+          <t>Visa Inc operates as a payment technology company in the United States and internationally</t>
+        </is>
+      </c>
+      <c r="K28" s="36" t="n"/>
+    </row>
+    <row r="29" ht="45" customHeight="1">
+      <c r="A29" s="28" t="n"/>
+      <c r="B29" s="49" t="inlineStr">
+        <is>
+          <t>🆕</t>
+        </is>
+      </c>
+      <c r="C29" s="30" t="inlineStr">
+        <is>
+          <t>PAYX</t>
+        </is>
+      </c>
+      <c r="D29" s="31" t="inlineStr">
+        <is>
+          <t>Paychex Inc.</t>
+        </is>
+      </c>
+      <c r="E29" s="32" t="inlineStr">
+        <is>
+          <t>Industrials</t>
+        </is>
+      </c>
+      <c r="F29" s="32" t="inlineStr">
+        <is>
+          <t>Professional Services</t>
+        </is>
+      </c>
+      <c r="G29" s="89" t="n">
+        <v>0.075</v>
+      </c>
+      <c r="H29" s="92" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="I29" s="93" t="n">
+        <v>36258.68</v>
+      </c>
+      <c r="J29" s="54" t="inlineStr">
+        <is>
+          <t>Paychex Inc together with its subsidiaries provides human capital management solutions (HCM) for payroll employee benefits human resources (HR) and insurance services for small to medium-sized businesses in the United States Europe and India</t>
+        </is>
+      </c>
+      <c r="K29" s="28" t="n"/>
+    </row>
+    <row r="30" ht="45" customHeight="1">
+      <c r="A30" s="36" t="n"/>
+      <c r="B30" s="48" t="inlineStr">
+        <is>
+          <t>🆕</t>
+        </is>
+      </c>
+      <c r="C30" s="38" t="inlineStr">
+        <is>
+          <t>BXP</t>
+        </is>
+      </c>
+      <c r="D30" s="39" t="inlineStr">
+        <is>
+          <t>BXP Inc.</t>
+        </is>
+      </c>
+      <c r="E30" s="40" t="inlineStr">
+        <is>
+          <t>Real Estate</t>
+        </is>
+      </c>
+      <c r="F30" s="40" t="inlineStr">
+        <is>
+          <t>Office REITs</t>
+        </is>
+      </c>
+      <c r="G30" s="89" t="n">
+        <v>0.068</v>
+      </c>
+      <c r="H30" s="90" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="I30" s="91" t="n">
+        <v>11826.25</v>
+      </c>
+      <c r="J30" s="53" t="inlineStr">
+        <is>
+          <t>BXP Inc (BXP) is the largest publicly traded developer owner and manager of premier workplaces in the United States</t>
+        </is>
+      </c>
+      <c r="K30" s="36" t="n"/>
+    </row>
+    <row r="31" ht="45" customHeight="1">
+      <c r="A31" s="28" t="n"/>
+      <c r="B31" s="49" t="inlineStr">
+        <is>
+          <t>🔁</t>
+        </is>
+      </c>
+      <c r="C31" s="30" t="inlineStr">
+        <is>
           <t>MPC</t>
         </is>
       </c>
-      <c r="D10" s="39" t="inlineStr">
+      <c r="D31" s="31" t="inlineStr">
         <is>
           <t>Marathon Petroleum Corporation</t>
         </is>
       </c>
-      <c r="E10" s="40" t="inlineStr">
+      <c r="E31" s="32" t="inlineStr">
         <is>
           <t>Energy</t>
         </is>
       </c>
-      <c r="F10" s="40" t="inlineStr">
+      <c r="F31" s="32" t="inlineStr">
         <is>
           <t>Oil Gas and Consumable Fuels</t>
         </is>
       </c>
-      <c r="G10" s="89" t="n">
+      <c r="G31" s="89" t="n">
         <v>0.839</v>
       </c>
-      <c r="H10" s="90" t="inlineStr">
+      <c r="H31" s="92" t="inlineStr">
         <is>
           <t>Repeat</t>
         </is>
       </c>
-      <c r="I10" s="91" t="n">
+      <c r="I31" s="93" t="n">
         <v>77721.12</v>
       </c>
-      <c r="J10" s="53" t="inlineStr">
+      <c r="J31" s="54" t="inlineStr">
         <is>
           <t>Marathon Petroleum Corporation together with its subsidiaries operates as an integrated downstream energy company in the United States</t>
         </is>
       </c>
-      <c r="K10" s="36" t="n"/>
-    </row>
-    <row r="11" ht="24" customHeight="1">
-      <c r="A11" s="28" t="n"/>
-      <c r="B11" s="49" t="n">
-        <v>4</v>
-      </c>
-      <c r="C11" s="30" t="inlineStr">
+      <c r="K31" s="28" t="n"/>
+    </row>
+    <row r="32" ht="45" customHeight="1">
+      <c r="A32" s="36" t="n"/>
+      <c r="B32" s="48" t="inlineStr">
+        <is>
+          <t>🔁</t>
+        </is>
+      </c>
+      <c r="C32" s="38" t="inlineStr">
         <is>
           <t>VLO</t>
         </is>
       </c>
-      <c r="D11" s="31" t="inlineStr">
+      <c r="D32" s="39" t="inlineStr">
         <is>
           <t>Valero Energy Corporation</t>
         </is>
       </c>
-      <c r="E11" s="32" t="inlineStr">
+      <c r="E32" s="40" t="inlineStr">
         <is>
           <t>Energy</t>
         </is>
       </c>
-      <c r="F11" s="32" t="inlineStr">
+      <c r="F32" s="40" t="inlineStr">
         <is>
           <t>Oil Gas and Consumable Fuels</t>
         </is>
       </c>
-      <c r="G11" s="89" t="n">
+      <c r="G32" s="89" t="n">
         <v>0.701</v>
       </c>
-      <c r="H11" s="92" t="inlineStr">
+      <c r="H32" s="90" t="inlineStr">
         <is>
           <t>Repeat</t>
         </is>
       </c>
-      <c r="I11" s="93" t="n">
+      <c r="I32" s="91" t="n">
         <v>77190.64999999999</v>
       </c>
-      <c r="J11" s="54" t="inlineStr">
+      <c r="J32" s="53" t="inlineStr">
         <is>
           <t>Valero Energy Corporation manufactures markets and sells petroleum-based and low-carbon liquid transportation fuels and petrochemical products in the United States Canada the United Kingdom Ireland Latin America Mexico Peru and internationally</t>
         </is>
       </c>
-      <c r="K11" s="28" t="n"/>
-    </row>
-    <row r="12" ht="24" customHeight="1">
-      <c r="A12" s="36" t="n"/>
-      <c r="B12" s="48" t="n">
-        <v>5</v>
-      </c>
-      <c r="C12" s="38" t="inlineStr">
+      <c r="K32" s="36" t="n"/>
+    </row>
+    <row r="33" ht="45" customHeight="1">
+      <c r="A33" s="28" t="n"/>
+      <c r="B33" s="49" t="inlineStr">
+        <is>
+          <t>🔁</t>
+        </is>
+      </c>
+      <c r="C33" s="30" t="inlineStr">
         <is>
           <t>STT</t>
         </is>
       </c>
-      <c r="D12" s="39" t="inlineStr">
+      <c r="D33" s="31" t="inlineStr">
         <is>
           <t>State Street Corporation</t>
         </is>
       </c>
-      <c r="E12" s="40" t="inlineStr">
+      <c r="E33" s="32" t="inlineStr">
         <is>
           <t>Financials</t>
         </is>
       </c>
-      <c r="F12" s="40" t="inlineStr">
+      <c r="F33" s="32" t="inlineStr">
         <is>
           <t>Capital Markets</t>
         </is>
       </c>
-      <c r="G12" s="89" t="n">
+      <c r="G33" s="89" t="n">
         <v>0.471</v>
       </c>
-      <c r="H12" s="90" t="inlineStr">
+      <c r="H33" s="92" t="inlineStr">
         <is>
           <t>Repeat</t>
         </is>
       </c>
-      <c r="I12" s="91" t="n">
+      <c r="I33" s="93" t="n">
         <v>44725.83</v>
       </c>
-      <c r="J12" s="53" t="inlineStr">
+      <c r="J33" s="54" t="inlineStr">
         <is>
           <t>State Street Corporation provides various financial products and services to institutional investors</t>
         </is>
       </c>
-      <c r="K12" s="36" t="n"/>
-    </row>
-    <row r="13" ht="20.4" customHeight="1">
-      <c r="A13" s="28" t="n"/>
-      <c r="B13" s="49" t="n">
-        <v>6</v>
-      </c>
-      <c r="C13" s="30" t="inlineStr">
-        <is>
-          <t>JBHT</t>
-        </is>
-      </c>
-      <c r="D13" s="31" t="inlineStr">
-        <is>
-          <t>J.B. Hunt Transport Services Inc.</t>
-        </is>
-      </c>
-      <c r="E13" s="32" t="inlineStr">
+      <c r="K33" s="28" t="n"/>
+    </row>
+    <row r="34" ht="45" customHeight="1">
+      <c r="A34" s="36" t="n"/>
+      <c r="B34" s="48" t="inlineStr">
+        <is>
+          <t>🔁</t>
+        </is>
+      </c>
+      <c r="C34" s="38" t="inlineStr">
+        <is>
+          <t>BNY</t>
+        </is>
+      </c>
+      <c r="D34" s="39" t="inlineStr">
+        <is>
+          <t>The Bank of New York Mellon Corporation</t>
+        </is>
+      </c>
+      <c r="E34" s="40" t="inlineStr">
+        <is>
+          <t>Financials</t>
+        </is>
+      </c>
+      <c r="F34" s="40" t="inlineStr">
+        <is>
+          <t>Capital Markets</t>
+        </is>
+      </c>
+      <c r="G34" s="89" t="n">
+        <v>0.356</v>
+      </c>
+      <c r="H34" s="90" t="inlineStr">
+        <is>
+          <t>Repeat</t>
+        </is>
+      </c>
+      <c r="I34" s="91" t="n">
+        <v>96186.41</v>
+      </c>
+      <c r="J34" s="53" t="inlineStr">
+        <is>
+          <t>The Bank of New York Mellon Corporation provides a range of financial products and services in the United States and internationally</t>
+        </is>
+      </c>
+      <c r="K34" s="36" t="n"/>
+    </row>
+    <row r="35" ht="45" customHeight="1">
+      <c r="A35" s="28" t="n"/>
+      <c r="B35" s="49" t="inlineStr">
+        <is>
+          <t>🔁</t>
+        </is>
+      </c>
+      <c r="C35" s="30" t="inlineStr">
+        <is>
+          <t>AAPL</t>
+        </is>
+      </c>
+      <c r="D35" s="31" t="inlineStr">
+        <is>
+          <t>Apple Inc.</t>
+        </is>
+      </c>
+      <c r="E35" s="32" t="inlineStr">
+        <is>
+          <t>Information Technology</t>
+        </is>
+      </c>
+      <c r="F35" s="32" t="inlineStr">
+        <is>
+          <t>Technology Hardware Storage and Peripherals</t>
+        </is>
+      </c>
+      <c r="G35" s="89" t="n">
+        <v>0.324</v>
+      </c>
+      <c r="H35" s="92" t="inlineStr">
+        <is>
+          <t>Repeat</t>
+        </is>
+      </c>
+      <c r="I35" s="93" t="n">
+        <v>4309578.68</v>
+      </c>
+      <c r="J35" s="54" t="inlineStr">
+        <is>
+          <t>Apple Inc designs manufactures and markets smartphones personal computers tablets wearables and accessories worldwide</t>
+        </is>
+      </c>
+      <c r="K35" s="28" t="n"/>
+    </row>
+    <row r="36" ht="45" customHeight="1">
+      <c r="A36" s="36" t="n"/>
+      <c r="B36" s="48" t="inlineStr">
+        <is>
+          <t>🔁</t>
+        </is>
+      </c>
+      <c r="C36" s="38" t="inlineStr">
+        <is>
+          <t>BBY</t>
+        </is>
+      </c>
+      <c r="D36" s="39" t="inlineStr">
+        <is>
+          <t>Best Buy Co. Inc.</t>
+        </is>
+      </c>
+      <c r="E36" s="40" t="inlineStr">
+        <is>
+          <t>Consumer Discretionary</t>
+        </is>
+      </c>
+      <c r="F36" s="40" t="inlineStr">
+        <is>
+          <t>Specialty Retail</t>
+        </is>
+      </c>
+      <c r="G36" s="89" t="n">
+        <v>0.308</v>
+      </c>
+      <c r="H36" s="90" t="inlineStr">
+        <is>
+          <t>Repeat</t>
+        </is>
+      </c>
+      <c r="I36" s="91" t="n">
+        <v>16078.79</v>
+      </c>
+      <c r="J36" s="53" t="inlineStr">
+        <is>
+          <t>Best Buy Co</t>
+        </is>
+      </c>
+      <c r="K36" s="36" t="n"/>
+    </row>
+    <row r="37" ht="45" customHeight="1">
+      <c r="A37" s="28" t="n"/>
+      <c r="B37" s="49" t="inlineStr">
+        <is>
+          <t>🔁</t>
+        </is>
+      </c>
+      <c r="C37" s="30" t="inlineStr">
+        <is>
+          <t>NTRS</t>
+        </is>
+      </c>
+      <c r="D37" s="31" t="inlineStr">
+        <is>
+          <t>Northern Trust Corporation</t>
+        </is>
+      </c>
+      <c r="E37" s="32" t="inlineStr">
+        <is>
+          <t>Financials</t>
+        </is>
+      </c>
+      <c r="F37" s="32" t="inlineStr">
+        <is>
+          <t>Capital Markets</t>
+        </is>
+      </c>
+      <c r="G37" s="89" t="n">
+        <v>0.258</v>
+      </c>
+      <c r="H37" s="92" t="inlineStr">
+        <is>
+          <t>Repeat</t>
+        </is>
+      </c>
+      <c r="I37" s="93" t="n">
+        <v>30713.22</v>
+      </c>
+      <c r="J37" s="54" t="inlineStr">
+        <is>
+          <t>Northern Trust Corporation a financial holding company provides wealth management asset servicing asset management and banking solutions for corporations institutions families and individuals</t>
+        </is>
+      </c>
+      <c r="K37" s="28" t="n"/>
+    </row>
+    <row r="38" ht="45" customHeight="1">
+      <c r="A38" s="36" t="n"/>
+      <c r="B38" s="48" t="inlineStr">
+        <is>
+          <t>🔁</t>
+        </is>
+      </c>
+      <c r="C38" s="38" t="inlineStr">
+        <is>
+          <t>MET</t>
+        </is>
+      </c>
+      <c r="D38" s="39" t="inlineStr">
+        <is>
+          <t>MetLife Inc.</t>
+        </is>
+      </c>
+      <c r="E38" s="40" t="inlineStr">
+        <is>
+          <t>Financials</t>
+        </is>
+      </c>
+      <c r="F38" s="40" t="inlineStr">
+        <is>
+          <t>Insurance</t>
+        </is>
+      </c>
+      <c r="G38" s="89" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="H38" s="90" t="inlineStr">
+        <is>
+          <t>Repeat</t>
+        </is>
+      </c>
+      <c r="I38" s="91" t="n">
+        <v>55851.6</v>
+      </c>
+      <c r="J38" s="53" t="inlineStr">
+        <is>
+          <t>MetLife Inc a financial services company provides insurance annuities employee benefits and asset management services worldwide</t>
+        </is>
+      </c>
+      <c r="K38" s="36" t="n"/>
+    </row>
+    <row r="39" ht="45" customHeight="1">
+      <c r="A39" s="28" t="n"/>
+      <c r="B39" s="49" t="inlineStr">
+        <is>
+          <t>🔁</t>
+        </is>
+      </c>
+      <c r="C39" s="30" t="inlineStr">
+        <is>
+          <t>GS</t>
+        </is>
+      </c>
+      <c r="D39" s="31" t="inlineStr">
+        <is>
+          <t>The Goldman Sachs Group Inc.</t>
+        </is>
+      </c>
+      <c r="E39" s="32" t="inlineStr">
+        <is>
+          <t>Financials</t>
+        </is>
+      </c>
+      <c r="F39" s="32" t="inlineStr">
+        <is>
+          <t>Capital Markets</t>
+        </is>
+      </c>
+      <c r="G39" s="89" t="n">
+        <v>0.193</v>
+      </c>
+      <c r="H39" s="92" t="inlineStr">
+        <is>
+          <t>Repeat</t>
+        </is>
+      </c>
+      <c r="I39" s="93" t="n">
+        <v>308648.81</v>
+      </c>
+      <c r="J39" s="54" t="inlineStr">
+        <is>
+          <t>The Goldman Sachs Group Inc a financial institution provides a range of financial services for corporations financial institutions governments and individuals in the Americas Europe the Middle East Africa and Asia</t>
+        </is>
+      </c>
+      <c r="K39" s="28" t="n"/>
+    </row>
+    <row r="40" ht="45" customHeight="1">
+      <c r="A40" s="36" t="n"/>
+      <c r="B40" s="106" t="inlineStr">
+        <is>
+          <t>🔥</t>
+        </is>
+      </c>
+      <c r="C40" s="107" t="inlineStr">
+        <is>
+          <t>CSX</t>
+        </is>
+      </c>
+      <c r="D40" s="108" t="inlineStr">
+        <is>
+          <t>CSX Corporation</t>
+        </is>
+      </c>
+      <c r="E40" s="109" t="inlineStr">
         <is>
           <t>Industrials</t>
         </is>
       </c>
-      <c r="F13" s="32" t="inlineStr">
+      <c r="F40" s="109" t="inlineStr">
         <is>
           <t>Ground Transportation</t>
         </is>
       </c>
-      <c r="G13" s="89" t="n">
-        <v>0.424</v>
-      </c>
-      <c r="H13" s="92" t="inlineStr">
-        <is>
-          <t>New</t>
-        </is>
-      </c>
-      <c r="I13" s="93" t="n">
-        <v>26566.73</v>
-      </c>
-      <c r="J13" s="54" t="inlineStr">
-        <is>
-          <t>J</t>
-        </is>
-      </c>
-      <c r="K13" s="28" t="n"/>
-    </row>
-    <row r="14" ht="40.8" customHeight="1">
-      <c r="A14" s="36" t="n"/>
-      <c r="B14" s="48" t="n">
-        <v>7</v>
-      </c>
-      <c r="C14" s="38" t="inlineStr">
-        <is>
-          <t>CSX</t>
-        </is>
-      </c>
-      <c r="D14" s="39" t="inlineStr">
-        <is>
-          <t>CSX Corporation</t>
-        </is>
-      </c>
-      <c r="E14" s="40" t="inlineStr">
-        <is>
-          <t>Industrials</t>
-        </is>
-      </c>
-      <c r="F14" s="40" t="inlineStr">
-        <is>
-          <t>Ground Transportation</t>
-        </is>
-      </c>
-      <c r="G14" s="89" t="n">
+      <c r="G40" s="110" t="n">
         <v>0.37</v>
       </c>
-      <c r="H14" s="90" t="inlineStr">
+      <c r="H40" s="111" t="inlineStr">
         <is>
           <t>Streak</t>
         </is>
       </c>
-      <c r="I14" s="91" t="n">
+      <c r="I40" s="112" t="n">
         <v>86617.14</v>
       </c>
-      <c r="J14" s="53" t="inlineStr">
+      <c r="J40" s="113" t="inlineStr">
         <is>
           <t>CSX Corporation together with its subsidiaries provides rail-based freight transportation services in the United States and Canada</t>
         </is>
       </c>
-      <c r="K14" s="36" t="n"/>
-    </row>
-    <row r="15" ht="30.6" customHeight="1">
-      <c r="A15" s="28" t="n"/>
-      <c r="B15" s="49" t="n">
-        <v>8</v>
-      </c>
-      <c r="C15" s="30" t="inlineStr">
-        <is>
-          <t>BNY</t>
-        </is>
-      </c>
-      <c r="D15" s="31" t="inlineStr">
-        <is>
-          <t>The Bank of New York Mellon Corporation</t>
-        </is>
-      </c>
-      <c r="E15" s="32" t="inlineStr">
-        <is>
-          <t>Financials</t>
-        </is>
-      </c>
-      <c r="F15" s="32" t="inlineStr">
-        <is>
-          <t>Capital Markets</t>
-        </is>
-      </c>
-      <c r="G15" s="89" t="n">
-        <v>0.356</v>
-      </c>
-      <c r="H15" s="92" t="inlineStr">
-        <is>
-          <t>Repeat</t>
-        </is>
-      </c>
-      <c r="I15" s="93" t="n">
-        <v>96186.41</v>
-      </c>
-      <c r="J15" s="54" t="inlineStr">
-        <is>
-          <t>The Bank of New York Mellon Corporation provides a range of financial products and services in the United States and internationally</t>
-        </is>
-      </c>
-      <c r="K15" s="28" t="n"/>
-    </row>
-    <row r="16" ht="24" customHeight="1">
-      <c r="A16" s="36" t="n"/>
-      <c r="B16" s="48" t="n">
-        <v>9</v>
-      </c>
-      <c r="C16" s="38" t="inlineStr">
-        <is>
-          <t>GL</t>
-        </is>
-      </c>
-      <c r="D16" s="39" t="inlineStr">
-        <is>
-          <t>Globe Life Inc.</t>
-        </is>
-      </c>
-      <c r="E16" s="40" t="inlineStr">
-        <is>
-          <t>Financials</t>
-        </is>
-      </c>
-      <c r="F16" s="40" t="inlineStr">
-        <is>
-          <t>Insurance</t>
-        </is>
-      </c>
-      <c r="G16" s="89" t="n">
-        <v>0.356</v>
-      </c>
-      <c r="H16" s="90" t="inlineStr">
-        <is>
-          <t>New</t>
-        </is>
-      </c>
-      <c r="I16" s="91" t="n">
-        <v>12644.53</v>
-      </c>
-      <c r="J16" s="53" t="inlineStr">
-        <is>
-          <t>Globe Life Inc through its subsidiaries provides various life and supplemental health insurance products to lower middle- and middle-income families in the United States</t>
-        </is>
-      </c>
-      <c r="K16" s="36" t="n"/>
-    </row>
-    <row r="17" ht="30.6" customHeight="1">
-      <c r="A17" s="28" t="n"/>
-      <c r="B17" s="49" t="n">
-        <v>10</v>
-      </c>
-      <c r="C17" s="30" t="inlineStr">
-        <is>
-          <t>WELL</t>
-        </is>
-      </c>
-      <c r="D17" s="31" t="inlineStr">
-        <is>
-          <t>Welltower Inc.</t>
-        </is>
-      </c>
-      <c r="E17" s="32" t="inlineStr">
-        <is>
-          <t>Real Estate</t>
-        </is>
-      </c>
-      <c r="F17" s="32" t="inlineStr">
-        <is>
-          <t>Health Care REITs</t>
-        </is>
-      </c>
-      <c r="G17" s="89" t="n">
-        <v>0.351</v>
-      </c>
-      <c r="H17" s="92" t="inlineStr">
-        <is>
-          <t>New</t>
-        </is>
-      </c>
-      <c r="I17" s="93" t="n">
-        <v>148209.56</v>
-      </c>
-      <c r="J17" s="54" t="inlineStr">
-        <is>
-          <t>Welltower Inc is a S&amp;P 500 company is positioned at the center of the silver economy focusing on rental housing for aging seniors across the United States United Kingdom and Canada</t>
-        </is>
-      </c>
-      <c r="K17" s="28" t="n"/>
-    </row>
-    <row r="18" ht="20.4" customHeight="1">
-      <c r="A18" s="36" t="n"/>
-      <c r="B18" s="48" t="n">
-        <v>11</v>
-      </c>
-      <c r="C18" s="38" t="inlineStr">
-        <is>
-          <t>CVS</t>
-        </is>
-      </c>
-      <c r="D18" s="39" t="inlineStr">
-        <is>
-          <t>CVS Health Corporation</t>
-        </is>
-      </c>
-      <c r="E18" s="40" t="inlineStr">
-        <is>
-          <t>Health Care</t>
-        </is>
-      </c>
-      <c r="F18" s="40" t="inlineStr">
-        <is>
-          <t>Health Care Providers and Services</t>
-        </is>
-      </c>
-      <c r="G18" s="89" t="n">
-        <v>0.344</v>
-      </c>
-      <c r="H18" s="90" t="inlineStr">
-        <is>
-          <t>New</t>
-        </is>
-      </c>
-      <c r="I18" s="91" t="n">
-        <v>125211.85</v>
-      </c>
-      <c r="J18" s="53" t="inlineStr">
-        <is>
-          <t>CVS Health Corporation provides health solutions in the United States</t>
-        </is>
-      </c>
-      <c r="K18" s="36" t="n"/>
-    </row>
-    <row r="19" ht="20.4" customHeight="1">
-      <c r="A19" s="28" t="n"/>
-      <c r="B19" s="49" t="n">
-        <v>12</v>
-      </c>
-      <c r="C19" s="30" t="inlineStr">
-        <is>
-          <t>TRV</t>
-        </is>
-      </c>
-      <c r="D19" s="31" t="inlineStr">
-        <is>
-          <t>The Travelers Companies Inc.</t>
-        </is>
-      </c>
-      <c r="E19" s="32" t="inlineStr">
-        <is>
-          <t>Financials</t>
-        </is>
-      </c>
-      <c r="F19" s="32" t="inlineStr">
-        <is>
-          <t>Insurance</t>
-        </is>
-      </c>
-      <c r="G19" s="89" t="n">
-        <v>0.341</v>
-      </c>
-      <c r="H19" s="92" t="inlineStr">
-        <is>
-          <t>New</t>
-        </is>
-      </c>
-      <c r="I19" s="93" t="n">
-        <v>64533.41</v>
-      </c>
-      <c r="J19" s="54" t="inlineStr">
-        <is>
-          <t>The Travelers Companies Inc through its subsidiaries provides a range of commercial and personal property and casualty insurance products and services to businesses government units associations and individuals in the United States Canada and internationally</t>
-        </is>
-      </c>
-      <c r="K19" s="28" t="n"/>
-    </row>
-    <row r="20" ht="24" customHeight="1">
-      <c r="A20" s="36" t="n"/>
-      <c r="B20" s="48" t="n">
-        <v>13</v>
-      </c>
-      <c r="C20" s="38" t="inlineStr">
-        <is>
-          <t>AAPL</t>
-        </is>
-      </c>
-      <c r="D20" s="39" t="inlineStr">
-        <is>
-          <t>Apple Inc.</t>
-        </is>
-      </c>
-      <c r="E20" s="40" t="inlineStr">
-        <is>
-          <t>Information Technology</t>
-        </is>
-      </c>
-      <c r="F20" s="40" t="inlineStr">
-        <is>
-          <t>Technology Hardware Storage and Peripherals</t>
-        </is>
-      </c>
-      <c r="G20" s="89" t="n">
-        <v>0.324</v>
-      </c>
-      <c r="H20" s="90" t="inlineStr">
-        <is>
-          <t>Repeat</t>
-        </is>
-      </c>
-      <c r="I20" s="91" t="n">
-        <v>4309578.68</v>
-      </c>
-      <c r="J20" s="53" t="inlineStr">
-        <is>
-          <t>Apple Inc designs manufactures and markets smartphones personal computers tablets wearables and accessories worldwide</t>
-        </is>
-      </c>
-      <c r="K20" s="36" t="n"/>
-    </row>
-    <row r="21" ht="20.4" customHeight="1">
-      <c r="A21" s="28" t="n"/>
-      <c r="B21" s="49" t="n">
-        <v>14</v>
-      </c>
-      <c r="C21" s="30" t="inlineStr">
-        <is>
-          <t>BBY</t>
-        </is>
-      </c>
-      <c r="D21" s="31" t="inlineStr">
-        <is>
-          <t>Best Buy Co. Inc.</t>
-        </is>
-      </c>
-      <c r="E21" s="32" t="inlineStr">
-        <is>
-          <t>Consumer Discretionary</t>
-        </is>
-      </c>
-      <c r="F21" s="32" t="inlineStr">
-        <is>
-          <t>Specialty Retail</t>
-        </is>
-      </c>
-      <c r="G21" s="89" t="n">
-        <v>0.308</v>
-      </c>
-      <c r="H21" s="92" t="inlineStr">
-        <is>
-          <t>Repeat</t>
-        </is>
-      </c>
-      <c r="I21" s="93" t="n">
-        <v>16078.79</v>
-      </c>
-      <c r="J21" s="54" t="inlineStr">
-        <is>
-          <t>Best Buy Co</t>
-        </is>
-      </c>
-      <c r="K21" s="28" t="n"/>
-    </row>
-    <row r="22" ht="30.6" customHeight="1">
-      <c r="A22" s="36" t="n"/>
-      <c r="B22" s="48" t="n">
-        <v>15</v>
-      </c>
-      <c r="C22" s="38" t="inlineStr">
-        <is>
-          <t>ADM</t>
-        </is>
-      </c>
-      <c r="D22" s="39" t="inlineStr">
-        <is>
-          <t>Archer-Daniels-Midland Company</t>
-        </is>
-      </c>
-      <c r="E22" s="40" t="inlineStr">
-        <is>
-          <t>Consumer Staples</t>
-        </is>
-      </c>
-      <c r="F22" s="40" t="inlineStr">
-        <is>
-          <t>Food Products</t>
-        </is>
-      </c>
-      <c r="G22" s="89" t="n">
-        <v>0.295</v>
-      </c>
-      <c r="H22" s="90" t="inlineStr">
-        <is>
-          <t>New</t>
-        </is>
-      </c>
-      <c r="I22" s="91" t="n">
-        <v>39380.19</v>
-      </c>
-      <c r="J22" s="53" t="inlineStr">
-        <is>
-          <t>Archer-Daniels-Midland Company provides human and animal nutrition ingredients and solutions in the United States Switzerland the Cayman Islands Brazil Mexico Canada the United Kingdom and internationally</t>
-        </is>
-      </c>
-      <c r="K22" s="36" t="n"/>
-    </row>
-    <row r="23" ht="20.4" customHeight="1">
-      <c r="A23" s="28" t="n"/>
-      <c r="B23" s="49" t="n">
-        <v>16</v>
-      </c>
-      <c r="C23" s="30" t="inlineStr">
-        <is>
-          <t>GWW</t>
-        </is>
-      </c>
-      <c r="D23" s="31" t="inlineStr">
-        <is>
-          <t>W.W. Grainger Inc.</t>
-        </is>
-      </c>
-      <c r="E23" s="32" t="inlineStr">
-        <is>
-          <t>Industrials</t>
-        </is>
-      </c>
-      <c r="F23" s="32" t="inlineStr">
-        <is>
-          <t>Trading Companies and Distributors</t>
-        </is>
-      </c>
-      <c r="G23" s="89" t="n">
-        <v>0.292</v>
-      </c>
-      <c r="H23" s="92" t="inlineStr">
-        <is>
-          <t>New</t>
-        </is>
-      </c>
-      <c r="I23" s="93" t="n">
-        <v>62147.38</v>
-      </c>
-      <c r="J23" s="54" t="inlineStr">
-        <is>
-          <t>W</t>
-        </is>
-      </c>
-      <c r="K23" s="28" t="n"/>
-    </row>
-    <row r="24" ht="24" customHeight="1">
-      <c r="A24" s="36" t="n"/>
-      <c r="B24" s="48" t="n">
-        <v>17</v>
-      </c>
-      <c r="C24" s="38" t="inlineStr">
-        <is>
-          <t>DOC</t>
-        </is>
-      </c>
-      <c r="D24" s="39" t="inlineStr">
-        <is>
-          <t>Healthpeak Properties Inc.</t>
-        </is>
-      </c>
-      <c r="E24" s="40" t="inlineStr">
-        <is>
-          <t>Real Estate</t>
-        </is>
-      </c>
-      <c r="F24" s="40" t="inlineStr">
-        <is>
-          <t>Health Care REITs</t>
-        </is>
-      </c>
-      <c r="G24" s="89" t="n">
-        <v>0.292</v>
-      </c>
-      <c r="H24" s="90" t="inlineStr">
-        <is>
-          <t>New</t>
-        </is>
-      </c>
-      <c r="I24" s="91" t="n">
-        <v>14353.95</v>
-      </c>
-      <c r="J24" s="53" t="inlineStr">
-        <is>
-          <t>Healthpeak Properties Inc is a Standard &amp; Poor’s 500 company that owns operates and develops high-quality real estate focused on healthcare discovery and delivery in the United States</t>
-        </is>
-      </c>
-      <c r="K24" s="36" t="n"/>
-    </row>
-    <row r="25" ht="30.6" customHeight="1">
-      <c r="A25" s="28" t="n"/>
-      <c r="B25" s="49" t="n">
-        <v>18</v>
-      </c>
-      <c r="C25" s="30" t="inlineStr">
-        <is>
-          <t>UNP</t>
-        </is>
-      </c>
-      <c r="D25" s="31" t="inlineStr">
-        <is>
-          <t>Union Pacific Corporation</t>
-        </is>
-      </c>
-      <c r="E25" s="32" t="inlineStr">
-        <is>
-          <t>Industrials</t>
-        </is>
-      </c>
-      <c r="F25" s="32" t="inlineStr">
-        <is>
-          <t>Ground Transportation</t>
-        </is>
-      </c>
-      <c r="G25" s="89" t="n">
-        <v>0.29</v>
-      </c>
-      <c r="H25" s="92" t="inlineStr">
-        <is>
-          <t>New</t>
-        </is>
-      </c>
-      <c r="I25" s="93" t="n">
-        <v>158667.48</v>
-      </c>
-      <c r="J25" s="54" t="inlineStr">
-        <is>
-          <t>Union Pacific Corporation through its subsidiary Union Pacific Railroad Company operates in the railroad business in the United States</t>
-        </is>
-      </c>
-      <c r="K25" s="28" t="n"/>
-    </row>
-    <row r="26" ht="30.6" customHeight="1">
-      <c r="A26" s="36" t="n"/>
-      <c r="B26" s="48" t="n">
-        <v>19</v>
-      </c>
-      <c r="C26" s="38" t="inlineStr">
-        <is>
-          <t>NTRS</t>
-        </is>
-      </c>
-      <c r="D26" s="39" t="inlineStr">
-        <is>
-          <t>Northern Trust Corporation</t>
-        </is>
-      </c>
-      <c r="E26" s="40" t="inlineStr">
-        <is>
-          <t>Financials</t>
-        </is>
-      </c>
-      <c r="F26" s="40" t="inlineStr">
-        <is>
-          <t>Capital Markets</t>
-        </is>
-      </c>
-      <c r="G26" s="89" t="n">
-        <v>0.258</v>
-      </c>
-      <c r="H26" s="90" t="inlineStr">
-        <is>
-          <t>Repeat</t>
-        </is>
-      </c>
-      <c r="I26" s="91" t="n">
-        <v>30713.22</v>
-      </c>
-      <c r="J26" s="53" t="inlineStr">
-        <is>
-          <t>Northern Trust Corporation a financial holding company provides wealth management asset servicing asset management and banking solutions for corporations institutions families and individuals</t>
-        </is>
-      </c>
-      <c r="K26" s="36" t="n"/>
-    </row>
-    <row r="27" ht="30.6" customHeight="1">
-      <c r="A27" s="28" t="n"/>
-      <c r="B27" s="49" t="n">
-        <v>20</v>
-      </c>
-      <c r="C27" s="30" t="inlineStr">
-        <is>
-          <t>MET</t>
-        </is>
-      </c>
-      <c r="D27" s="31" t="inlineStr">
-        <is>
-          <t>MetLife Inc.</t>
-        </is>
-      </c>
-      <c r="E27" s="32" t="inlineStr">
-        <is>
-          <t>Financials</t>
-        </is>
-      </c>
-      <c r="F27" s="32" t="inlineStr">
-        <is>
-          <t>Insurance</t>
-        </is>
-      </c>
-      <c r="G27" s="89" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="H27" s="92" t="inlineStr">
-        <is>
-          <t>Repeat</t>
-        </is>
-      </c>
-      <c r="I27" s="93" t="n">
-        <v>55851.6</v>
-      </c>
-      <c r="J27" s="54" t="inlineStr">
-        <is>
-          <t>MetLife Inc a financial services company provides insurance annuities employee benefits and asset management services worldwide</t>
-        </is>
-      </c>
-      <c r="K27" s="28" t="n"/>
-    </row>
-    <row r="28" ht="24" customHeight="1">
-      <c r="A28" s="36" t="n"/>
-      <c r="B28" s="48" t="n">
-        <v>21</v>
-      </c>
-      <c r="C28" s="38" t="inlineStr">
-        <is>
-          <t>PFG</t>
-        </is>
-      </c>
-      <c r="D28" s="39" t="inlineStr">
-        <is>
-          <t>Principal Financial Group Inc.</t>
-        </is>
-      </c>
-      <c r="E28" s="40" t="inlineStr">
-        <is>
-          <t>Financials</t>
-        </is>
-      </c>
-      <c r="F28" s="40" t="inlineStr">
-        <is>
-          <t>Insurance</t>
-        </is>
-      </c>
-      <c r="G28" s="89" t="n">
-        <v>0.222</v>
-      </c>
-      <c r="H28" s="90" t="inlineStr">
-        <is>
-          <t>New</t>
-        </is>
-      </c>
-      <c r="I28" s="91" t="n">
-        <v>23624.19</v>
-      </c>
-      <c r="J28" s="53" t="inlineStr">
-        <is>
-          <t>Principal Financial Group Inc provides retirement asset management and insurance products and services to businesses individuals and institutional clients worldwide</t>
-        </is>
-      </c>
-      <c r="K28" s="36" t="n"/>
-    </row>
-    <row r="29" ht="20.4" customHeight="1">
-      <c r="A29" s="28" t="n"/>
-      <c r="B29" s="49" t="n">
-        <v>22</v>
-      </c>
-      <c r="C29" s="30" t="inlineStr">
-        <is>
-          <t>XYZ</t>
-        </is>
-      </c>
-      <c r="D29" s="31" t="inlineStr">
-        <is>
-          <t>Block Inc.</t>
-        </is>
-      </c>
-      <c r="E29" s="32" t="inlineStr">
-        <is>
-          <t>Financials</t>
-        </is>
-      </c>
-      <c r="F29" s="32" t="inlineStr">
-        <is>
-          <t>Financial Services</t>
-        </is>
-      </c>
-      <c r="G29" s="89" t="n">
-        <v>0.203</v>
-      </c>
-      <c r="H29" s="92" t="inlineStr">
-        <is>
-          <t>New</t>
-        </is>
-      </c>
-      <c r="I29" s="93" t="n">
-        <v>40474.89</v>
-      </c>
-      <c r="J29" s="54" t="inlineStr">
-        <is>
-          <t>Block Inc together with its subsidiaries builds ecosystems focused on commerce and financial products and services in the United States and internationally</t>
-        </is>
-      </c>
-      <c r="K29" s="28" t="n"/>
-    </row>
-    <row r="30">
-      <c r="A30" s="36" t="n"/>
-      <c r="B30" s="48" t="n">
-        <v>23</v>
-      </c>
-      <c r="C30" s="38" t="inlineStr">
-        <is>
-          <t>BAC</t>
-        </is>
-      </c>
-      <c r="D30" s="39" t="inlineStr">
-        <is>
-          <t>Bank of America Corporation</t>
-        </is>
-      </c>
-      <c r="E30" s="40" t="inlineStr">
-        <is>
-          <t>Financials</t>
-        </is>
-      </c>
-      <c r="F30" s="40" t="inlineStr">
-        <is>
-          <t>Banks</t>
-        </is>
-      </c>
-      <c r="G30" s="89" t="n">
-        <v>0.197</v>
-      </c>
-      <c r="H30" s="90" t="inlineStr">
-        <is>
-          <t>New</t>
-        </is>
-      </c>
-      <c r="I30" s="91" t="n">
-        <v>388502.86</v>
-      </c>
-      <c r="J30" s="53" t="inlineStr">
-        <is>
-          <t>Bank of America Corporation through its subsidiaries provides various financial products and services for individual consumers small and middle-market businesses institutional investors large corporations and governments worldwide</t>
-        </is>
-      </c>
-      <c r="K30" s="36" t="n"/>
-    </row>
-    <row r="31">
-      <c r="A31" s="28" t="n"/>
-      <c r="B31" s="49" t="n">
-        <v>24</v>
-      </c>
-      <c r="C31" s="30" t="inlineStr">
-        <is>
-          <t>GS</t>
-        </is>
-      </c>
-      <c r="D31" s="31" t="inlineStr">
-        <is>
-          <t>The Goldman Sachs Group Inc.</t>
-        </is>
-      </c>
-      <c r="E31" s="32" t="inlineStr">
-        <is>
-          <t>Financials</t>
-        </is>
-      </c>
-      <c r="F31" s="32" t="inlineStr">
-        <is>
-          <t>Capital Markets</t>
-        </is>
-      </c>
-      <c r="G31" s="89" t="n">
-        <v>0.193</v>
-      </c>
-      <c r="H31" s="92" t="inlineStr">
-        <is>
-          <t>Repeat</t>
-        </is>
-      </c>
-      <c r="I31" s="93" t="n">
-        <v>308648.81</v>
-      </c>
-      <c r="J31" s="54" t="inlineStr">
-        <is>
-          <t>The Goldman Sachs Group Inc a financial institution provides a range of financial services for corporations financial institutions governments and individuals in the Americas Europe the Middle East Africa and Asia</t>
-        </is>
-      </c>
-      <c r="K31" s="28" t="n"/>
-    </row>
-    <row r="32" ht="24" customHeight="1">
-      <c r="A32" s="36" t="n"/>
-      <c r="B32" s="48" t="n">
-        <v>25</v>
-      </c>
-      <c r="C32" s="38" t="inlineStr">
-        <is>
-          <t>EG</t>
-        </is>
-      </c>
-      <c r="D32" s="39" t="inlineStr">
-        <is>
-          <t>Everest Group Ltd.</t>
-        </is>
-      </c>
-      <c r="E32" s="40" t="inlineStr">
-        <is>
-          <t>Financials</t>
-        </is>
-      </c>
-      <c r="F32" s="40" t="inlineStr">
-        <is>
-          <t>Insurance</t>
-        </is>
-      </c>
-      <c r="G32" s="89" t="n">
-        <v>0.18</v>
-      </c>
-      <c r="H32" s="90" t="inlineStr">
-        <is>
-          <t>New</t>
-        </is>
-      </c>
-      <c r="I32" s="91" t="n">
-        <v>13320.91</v>
-      </c>
-      <c r="J32" s="53" t="inlineStr">
-        <is>
-          <t>Everest Group Ltd together with subsidiaries provides reinsurance and insurance products in the United States Europe and internationally</t>
-        </is>
-      </c>
-      <c r="K32" s="36" t="n"/>
-    </row>
-    <row r="33" ht="20.4" customHeight="1">
-      <c r="A33" s="28" t="n"/>
-      <c r="B33" s="49" t="n">
-        <v>26</v>
-      </c>
-      <c r="C33" s="30" t="inlineStr">
-        <is>
-          <t>CFG</t>
-        </is>
-      </c>
-      <c r="D33" s="31" t="inlineStr">
-        <is>
-          <t>Citizens Financial Group Inc.</t>
-        </is>
-      </c>
-      <c r="E33" s="32" t="inlineStr">
-        <is>
-          <t>Financials</t>
-        </is>
-      </c>
-      <c r="F33" s="32" t="inlineStr">
-        <is>
-          <t>Banks</t>
-        </is>
-      </c>
-      <c r="G33" s="89" t="n">
-        <v>0.166</v>
-      </c>
-      <c r="H33" s="92" t="inlineStr">
-        <is>
-          <t>New</t>
-        </is>
-      </c>
-      <c r="I33" s="93" t="n">
-        <v>27585.86</v>
-      </c>
-      <c r="J33" s="54" t="inlineStr">
-        <is>
-          <t>Citizens Financial Group Inc operates as the bank holding company that provides retail and commercial banking products and services to individuals small businesses middle-market companies large corporations and institutions in the United States</t>
-        </is>
-      </c>
-      <c r="K33" s="28" t="n"/>
-    </row>
-    <row r="34" ht="24" customHeight="1">
-      <c r="A34" s="36" t="n"/>
-      <c r="B34" s="48" t="n">
-        <v>27</v>
-      </c>
-      <c r="C34" s="38" t="inlineStr">
-        <is>
-          <t>FITB</t>
-        </is>
-      </c>
-      <c r="D34" s="39" t="inlineStr">
-        <is>
-          <t>Fifth Third Bancorp</t>
-        </is>
-      </c>
-      <c r="E34" s="40" t="inlineStr">
-        <is>
-          <t>Financials</t>
-        </is>
-      </c>
-      <c r="F34" s="40" t="inlineStr">
-        <is>
-          <t>Banks</t>
-        </is>
-      </c>
-      <c r="G34" s="89" t="n">
-        <v>0.155</v>
-      </c>
-      <c r="H34" s="90" t="inlineStr">
-        <is>
-          <t>New</t>
-        </is>
-      </c>
-      <c r="I34" s="91" t="n">
-        <v>47955.66</v>
-      </c>
-      <c r="J34" s="53" t="inlineStr">
-        <is>
-          <t>Fifth Third Bancorp operates as the bank holding company for Fifth Third Bank National Association that provides a range of financial products and services in the United States</t>
-        </is>
-      </c>
-      <c r="K34" s="36" t="n"/>
-    </row>
-    <row r="35" ht="20.4" customHeight="1">
-      <c r="A35" s="28" t="n"/>
-      <c r="B35" s="49" t="n">
-        <v>28</v>
-      </c>
-      <c r="C35" s="30" t="inlineStr">
-        <is>
-          <t>MNST</t>
-        </is>
-      </c>
-      <c r="D35" s="31" t="inlineStr">
-        <is>
-          <t>Monster Beverage Corporation</t>
-        </is>
-      </c>
-      <c r="E35" s="32" t="inlineStr">
-        <is>
-          <t>Consumer Staples</t>
-        </is>
-      </c>
-      <c r="F35" s="32" t="inlineStr">
-        <is>
-          <t>Beverages</t>
-        </is>
-      </c>
-      <c r="G35" s="89" t="n">
-        <v>0.152</v>
-      </c>
-      <c r="H35" s="92" t="inlineStr">
-        <is>
-          <t>New</t>
-        </is>
-      </c>
-      <c r="I35" s="93" t="n">
-        <v>89144.46000000001</v>
-      </c>
-      <c r="J35" s="54" t="inlineStr">
-        <is>
-          <t>Monster Beverage Corporation through its subsidiaries engages in development marketing sale and distribution of energy drink beverages and concentrates in the United States and internationally</t>
-        </is>
-      </c>
-      <c r="K35" s="28" t="n"/>
-    </row>
-    <row r="36" ht="30.6" customHeight="1">
-      <c r="A36" s="36" t="n"/>
-      <c r="B36" s="48" t="n">
-        <v>29</v>
-      </c>
-      <c r="C36" s="38" t="inlineStr">
-        <is>
-          <t>PRU</t>
-        </is>
-      </c>
-      <c r="D36" s="39" t="inlineStr">
-        <is>
-          <t>Prudential Financial Inc.</t>
-        </is>
-      </c>
-      <c r="E36" s="40" t="inlineStr">
-        <is>
-          <t>Financials</t>
-        </is>
-      </c>
-      <c r="F36" s="40" t="inlineStr">
-        <is>
-          <t>Insurance</t>
-        </is>
-      </c>
-      <c r="G36" s="89" t="n">
-        <v>0.131</v>
-      </c>
-      <c r="H36" s="90" t="inlineStr">
-        <is>
-          <t>New</t>
-        </is>
-      </c>
-      <c r="I36" s="91" t="n">
-        <v>36717.82</v>
-      </c>
-      <c r="J36" s="53" t="inlineStr">
-        <is>
-          <t>Prudential Financial Inc together with its subsidiaries provides financial products and services in the United States Japan and internationally</t>
-        </is>
-      </c>
-      <c r="K36" s="36" t="n"/>
-    </row>
-    <row r="37" ht="30.6" customHeight="1">
-      <c r="A37" s="28" t="n"/>
-      <c r="B37" s="49" t="n">
-        <v>30</v>
-      </c>
-      <c r="C37" s="30" t="inlineStr">
-        <is>
-          <t>EXPD</t>
-        </is>
-      </c>
-      <c r="D37" s="31" t="inlineStr">
-        <is>
-          <t>Expeditors International of Washington Inc.</t>
-        </is>
-      </c>
-      <c r="E37" s="32" t="inlineStr">
-        <is>
-          <t>Industrials</t>
-        </is>
-      </c>
-      <c r="F37" s="32" t="inlineStr">
-        <is>
-          <t>Air Freight and Logistics</t>
-        </is>
-      </c>
-      <c r="G37" s="89" t="n">
-        <v>0.127</v>
-      </c>
-      <c r="H37" s="92" t="inlineStr">
-        <is>
-          <t>New</t>
-        </is>
-      </c>
-      <c r="I37" s="93" t="n">
-        <v>21453.67</v>
-      </c>
-      <c r="J37" s="54" t="inlineStr">
-        <is>
-          <t>Expeditors International of Washington Inc together with its subsidiaries provides logistics services in the Americas North Asia South Asia Europe and Middle East Africa and India</t>
-        </is>
-      </c>
-      <c r="K37" s="28" t="n"/>
-    </row>
-    <row r="38" ht="20.4" customHeight="1">
-      <c r="A38" s="36" t="n"/>
-      <c r="B38" s="48" t="n">
-        <v>31</v>
-      </c>
-      <c r="C38" s="38" t="inlineStr">
-        <is>
-          <t>V</t>
-        </is>
-      </c>
-      <c r="D38" s="39" t="inlineStr">
-        <is>
-          <t>Visa Inc.</t>
-        </is>
-      </c>
-      <c r="E38" s="40" t="inlineStr">
-        <is>
-          <t>Financials</t>
-        </is>
-      </c>
-      <c r="F38" s="40" t="inlineStr">
-        <is>
-          <t>Financial Services</t>
-        </is>
-      </c>
-      <c r="G38" s="89" t="n">
-        <v>0.095</v>
-      </c>
-      <c r="H38" s="90" t="inlineStr">
-        <is>
-          <t>New</t>
-        </is>
-      </c>
-      <c r="I38" s="91" t="n">
-        <v>612046.08</v>
-      </c>
-      <c r="J38" s="53" t="inlineStr">
-        <is>
-          <t>Visa Inc operates as a payment technology company in the United States and internationally</t>
-        </is>
-      </c>
-      <c r="K38" s="36" t="n"/>
-    </row>
-    <row r="39" ht="24" customHeight="1">
-      <c r="A39" s="28" t="n"/>
-      <c r="B39" s="49" t="n">
-        <v>32</v>
-      </c>
-      <c r="C39" s="30" t="inlineStr">
-        <is>
-          <t>PAYX</t>
-        </is>
-      </c>
-      <c r="D39" s="31" t="inlineStr">
-        <is>
-          <t>Paychex Inc.</t>
-        </is>
-      </c>
-      <c r="E39" s="32" t="inlineStr">
-        <is>
-          <t>Industrials</t>
-        </is>
-      </c>
-      <c r="F39" s="32" t="inlineStr">
-        <is>
-          <t>Professional Services</t>
-        </is>
-      </c>
-      <c r="G39" s="89" t="n">
-        <v>0.075</v>
-      </c>
-      <c r="H39" s="92" t="inlineStr">
-        <is>
-          <t>New</t>
-        </is>
-      </c>
-      <c r="I39" s="93" t="n">
-        <v>36258.68</v>
-      </c>
-      <c r="J39" s="54" t="inlineStr">
-        <is>
-          <t>Paychex Inc together with its subsidiaries provides human capital management solutions (HCM) for payroll employee benefits human resources (HR) and insurance services for small to medium-sized businesses in the United States Europe and India</t>
-        </is>
-      </c>
-      <c r="K39" s="28" t="n"/>
-    </row>
-    <row r="40" ht="24" customHeight="1">
-      <c r="A40" s="36" t="n"/>
-      <c r="B40" s="106" t="n">
-        <v>33</v>
-      </c>
-      <c r="C40" s="107" t="inlineStr">
-        <is>
-          <t>BXP</t>
-        </is>
-      </c>
-      <c r="D40" s="108" t="inlineStr">
-        <is>
-          <t>BXP Inc.</t>
-        </is>
-      </c>
-      <c r="E40" s="109" t="inlineStr">
-        <is>
-          <t>Real Estate</t>
-        </is>
-      </c>
-      <c r="F40" s="109" t="inlineStr">
-        <is>
-          <t>Office REITs</t>
-        </is>
-      </c>
-      <c r="G40" s="110" t="n">
-        <v>0.068</v>
-      </c>
-      <c r="H40" s="111" t="inlineStr">
-        <is>
-          <t>New</t>
-        </is>
-      </c>
-      <c r="I40" s="112" t="n">
-        <v>11826.25</v>
-      </c>
-      <c r="J40" s="113" t="inlineStr">
-        <is>
-          <t>BXP Inc (BXP) is the largest publicly traded developer owner and manager of premier workplaces in the United States</t>
-        </is>
-      </c>
       <c r="K40" s="36" t="n"/>
     </row>
-    <row r="41" ht="30.6" customHeight="1">
+    <row r="41" ht="8" customHeight="1">
       <c r="A41" s="28" t="n"/>
-      <c r="B41" s="49" t="n"/>
-      <c r="C41" s="30" t="n"/>
-      <c r="D41" s="31" t="n"/>
-      <c r="E41" s="32" t="n"/>
-      <c r="F41" s="32" t="n"/>
-      <c r="G41" s="89" t="n"/>
-      <c r="H41" s="92" t="n"/>
-      <c r="I41" s="93" t="n"/>
-      <c r="J41" s="54" t="n"/>
+      <c r="B41" s="114" t="n"/>
+      <c r="C41" s="115" t="n"/>
+      <c r="D41" s="116" t="n"/>
+      <c r="E41" s="117" t="n"/>
+      <c r="F41" s="117" t="n"/>
+      <c r="G41" s="118" t="n"/>
+      <c r="H41" s="119" t="n"/>
+      <c r="I41" s="120" t="n"/>
+      <c r="J41" s="121" t="n"/>
       <c r="K41" s="28" t="n"/>
     </row>
     <row r="42" ht="34" customHeight="1" thickBot="1">
       <c r="A42" s="75" t="n"/>
-      <c r="B42" s="114" t="inlineStr">
+      <c r="B42" s="122" t="inlineStr">
         <is>
           <t>🔓 Want to know which of these we would actually buy? Start your 14-Day Free Trial at www.5iresearch.ca/bb</t>
         </is>
       </c>
-      <c r="C42" s="115" t="n"/>
-      <c r="D42" s="115" t="n"/>
-      <c r="E42" s="115" t="n"/>
-      <c r="F42" s="115" t="n"/>
-      <c r="G42" s="115" t="n"/>
-      <c r="H42" s="115" t="n"/>
-      <c r="I42" s="115" t="n"/>
-      <c r="J42" s="115" t="n"/>
+      <c r="C42" s="123" t="n"/>
+      <c r="D42" s="123" t="n"/>
+      <c r="E42" s="123" t="n"/>
+      <c r="F42" s="123" t="n"/>
+      <c r="G42" s="123" t="n"/>
+      <c r="H42" s="123" t="n"/>
+      <c r="I42" s="123" t="n"/>
+      <c r="J42" s="123" t="n"/>
       <c r="K42" s="75" t="n"/>
     </row>
     <row r="43" ht="28" customHeight="1">
       <c r="A43" s="43" t="n"/>
-      <c r="B43" s="116" t="inlineStr">
+      <c r="B43" s="124" t="inlineStr">
         <is>
           <t>Disclosure: While this table does not constitute any formal opinion on names presented, authors may own shares in non-Canadian securities listed above.</t>
         </is>
       </c>
-      <c r="C43" s="117" t="n"/>
-      <c r="D43" s="117" t="n"/>
-      <c r="E43" s="117" t="n"/>
-      <c r="F43" s="117" t="n"/>
-      <c r="G43" s="117" t="n"/>
-      <c r="H43" s="117" t="n"/>
-      <c r="I43" s="117" t="n"/>
-      <c r="J43" s="117" t="n"/>
+      <c r="C43" s="125" t="n"/>
+      <c r="D43" s="125" t="n"/>
+      <c r="E43" s="125" t="n"/>
+      <c r="F43" s="125" t="n"/>
+      <c r="G43" s="125" t="n"/>
+      <c r="H43" s="125" t="n"/>
+      <c r="I43" s="125" t="n"/>
+      <c r="J43" s="125" t="n"/>
       <c r="K43" s="43" t="n"/>
     </row>
     <row r="44" ht="15.6" customHeight="1" thickBot="1">
@@ -5723,7 +5871,7 @@
   <mergeCells count="4">
     <mergeCell ref="B43:J43"/>
     <mergeCell ref="B2:G2"/>
-    <mergeCell ref="H2:I2"/>
+    <mergeCell ref="I2:J2"/>
     <mergeCell ref="B42:J42"/>
   </mergeCells>
   <conditionalFormatting sqref="G8:G40">

--- a/outputs/benchmark-beaters/Benchmark_Beaters_2026-07-21.xlsx
+++ b/outputs/benchmark-beaters/Benchmark_Beaters_2026-07-21.xlsx
@@ -34,7 +34,7 @@
     <numFmt numFmtId="166" formatCode="[&gt;=1000]&quot;$&quot;#0.0,&quot;B&quot;;[&gt;=100]&quot;$&quot;#0.0,&quot;B&quot;;&quot;$&quot;#0.0"/>
     <numFmt numFmtId="167" formatCode="[$-F800]dddd\,\ mmmm\ dd\,\ yyyy"/>
   </numFmts>
-  <fonts count="28">
+  <fonts count="29">
     <font>
       <name val="Aptos Narrow"/>
       <family val="2"/>
@@ -216,6 +216,11 @@
     </font>
     <font>
       <b val="1"/>
+      <color rgb="FFFFFFFF"/>
+      <sz val="7"/>
+    </font>
+    <font>
+      <b val="1"/>
       <color rgb="FFC67A29"/>
       <sz val="10"/>
     </font>
@@ -225,7 +230,7 @@
       <sz val="10"/>
     </font>
   </fonts>
-  <fills count="18">
+  <fills count="21">
     <fill>
       <patternFill/>
     </fill>
@@ -306,6 +311,21 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFFFF3CD"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF2E86DE"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF8E44AD"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC0392B"/>
       </patternFill>
     </fill>
     <fill>
@@ -507,7 +527,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="126">
+  <cellXfs count="129">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
@@ -776,7 +796,16 @@
     <xf numFmtId="166" fontId="19" fillId="8" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="15" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="26" fillId="16" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="17" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="18" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="18" borderId="15" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="17" fillId="8" borderId="15" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -824,14 +853,14 @@
     <xf numFmtId="0" fontId="22" fillId="0" borderId="16" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="16" borderId="17" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="27" fillId="19" borderId="17" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="16" borderId="17" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="27" fillId="17" borderId="16" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="19" borderId="17" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="28" fillId="20" borderId="16" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="17" borderId="16" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="20" borderId="16" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1387,7 +1416,7 @@
     <row r="2" ht="15.6" customHeight="1">
       <c r="A2" s="22" t="n"/>
       <c r="B2" s="21" t="n">
-        <v>46224.87725170761</v>
+        <v>46224.90155205015</v>
       </c>
       <c r="C2" s="22" t="n"/>
     </row>
@@ -1413,7 +1442,7 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="1.21875" customWidth="1" style="11" min="1" max="1"/>
-    <col width="5.44140625" customWidth="1" style="11" min="2" max="2"/>
+    <col width="8.5" customWidth="1" style="11" min="2" max="2"/>
     <col width="10" customWidth="1" style="14" min="3" max="3"/>
     <col width="26" customWidth="1" style="15" min="4" max="4"/>
     <col width="16" customWidth="1" style="14" min="5" max="5"/>
@@ -1450,7 +1479,7 @@
       </c>
       <c r="H2" s="82" t="n"/>
       <c r="I2" s="84" t="n">
-        <v>46224.87725170761</v>
+        <v>46224.90155205015</v>
       </c>
     </row>
     <row r="3" ht="3" customHeight="1">
@@ -1555,11 +1584,11 @@
       </c>
       <c r="K7" s="26" t="n"/>
     </row>
-    <row r="8" ht="45" customHeight="1">
+    <row r="8" ht="50" customHeight="1">
       <c r="A8" s="36" t="n"/>
-      <c r="B8" s="48" t="inlineStr">
-        <is>
-          <t>🆕</t>
+      <c r="B8" s="106" t="inlineStr">
+        <is>
+          <t>NEW</t>
         </is>
       </c>
       <c r="C8" s="38" t="inlineStr">
@@ -1600,11 +1629,11 @@
       </c>
       <c r="K8" s="36" t="n"/>
     </row>
-    <row r="9" ht="45" customHeight="1">
+    <row r="9" ht="50" customHeight="1">
       <c r="A9" s="28" t="n"/>
-      <c r="B9" s="49" t="inlineStr">
-        <is>
-          <t>🆕</t>
+      <c r="B9" s="106" t="inlineStr">
+        <is>
+          <t>NEW</t>
         </is>
       </c>
       <c r="C9" s="30" t="inlineStr">
@@ -1645,11 +1674,11 @@
       </c>
       <c r="K9" s="28" t="n"/>
     </row>
-    <row r="10" ht="45" customHeight="1">
+    <row r="10" ht="67" customHeight="1">
       <c r="A10" s="36" t="n"/>
-      <c r="B10" s="48" t="inlineStr">
-        <is>
-          <t>🆕</t>
+      <c r="B10" s="106" t="inlineStr">
+        <is>
+          <t>NEW</t>
         </is>
       </c>
       <c r="C10" s="38" t="inlineStr">
@@ -1690,11 +1719,11 @@
       </c>
       <c r="K10" s="36" t="n"/>
     </row>
-    <row r="11" ht="45" customHeight="1">
+    <row r="11" ht="50" customHeight="1">
       <c r="A11" s="28" t="n"/>
-      <c r="B11" s="49" t="inlineStr">
-        <is>
-          <t>🆕</t>
+      <c r="B11" s="106" t="inlineStr">
+        <is>
+          <t>NEW</t>
         </is>
       </c>
       <c r="C11" s="30" t="inlineStr">
@@ -1735,11 +1764,11 @@
       </c>
       <c r="K11" s="28" t="n"/>
     </row>
-    <row r="12" ht="45" customHeight="1">
+    <row r="12" ht="67" customHeight="1">
       <c r="A12" s="36" t="n"/>
-      <c r="B12" s="48" t="inlineStr">
-        <is>
-          <t>🆕</t>
+      <c r="B12" s="106" t="inlineStr">
+        <is>
+          <t>NEW</t>
         </is>
       </c>
       <c r="C12" s="38" t="inlineStr">
@@ -1780,11 +1809,11 @@
       </c>
       <c r="K12" s="36" t="n"/>
     </row>
-    <row r="13" ht="45" customHeight="1">
+    <row r="13" ht="50" customHeight="1">
       <c r="A13" s="28" t="n"/>
-      <c r="B13" s="49" t="inlineStr">
-        <is>
-          <t>🆕</t>
+      <c r="B13" s="106" t="inlineStr">
+        <is>
+          <t>NEW</t>
         </is>
       </c>
       <c r="C13" s="30" t="inlineStr">
@@ -1825,11 +1854,11 @@
       </c>
       <c r="K13" s="28" t="n"/>
     </row>
-    <row r="14" ht="45" customHeight="1">
+    <row r="14" ht="50" customHeight="1">
       <c r="A14" s="36" t="n"/>
-      <c r="B14" s="48" t="inlineStr">
-        <is>
-          <t>🆕</t>
+      <c r="B14" s="106" t="inlineStr">
+        <is>
+          <t>NEW</t>
         </is>
       </c>
       <c r="C14" s="38" t="inlineStr">
@@ -1870,11 +1899,11 @@
       </c>
       <c r="K14" s="36" t="n"/>
     </row>
-    <row r="15" ht="45" customHeight="1">
+    <row r="15" ht="67" customHeight="1">
       <c r="A15" s="28" t="n"/>
-      <c r="B15" s="49" t="inlineStr">
-        <is>
-          <t>🆕</t>
+      <c r="B15" s="106" t="inlineStr">
+        <is>
+          <t>NEW</t>
         </is>
       </c>
       <c r="C15" s="30" t="inlineStr">
@@ -1915,11 +1944,11 @@
       </c>
       <c r="K15" s="28" t="n"/>
     </row>
-    <row r="16" ht="45" customHeight="1">
+    <row r="16" ht="67" customHeight="1">
       <c r="A16" s="28" t="n"/>
-      <c r="B16" s="48" t="inlineStr">
-        <is>
-          <t>🆕</t>
+      <c r="B16" s="106" t="inlineStr">
+        <is>
+          <t>NEW</t>
         </is>
       </c>
       <c r="C16" s="38" t="inlineStr">
@@ -1960,11 +1989,11 @@
       </c>
       <c r="K16" s="28" t="n"/>
     </row>
-    <row r="17" ht="45" customHeight="1">
+    <row r="17" ht="67" customHeight="1">
       <c r="A17" s="36" t="n"/>
-      <c r="B17" s="49" t="inlineStr">
-        <is>
-          <t>🆕</t>
+      <c r="B17" s="106" t="inlineStr">
+        <is>
+          <t>NEW</t>
         </is>
       </c>
       <c r="C17" s="30" t="inlineStr">
@@ -2005,11 +2034,11 @@
       </c>
       <c r="K17" s="36" t="n"/>
     </row>
-    <row r="18" ht="45" customHeight="1">
+    <row r="18" ht="67" customHeight="1">
       <c r="A18" s="28" t="n"/>
-      <c r="B18" s="48" t="inlineStr">
-        <is>
-          <t>🆕</t>
+      <c r="B18" s="106" t="inlineStr">
+        <is>
+          <t>NEW</t>
         </is>
       </c>
       <c r="C18" s="38" t="inlineStr">
@@ -2050,11 +2079,11 @@
       </c>
       <c r="K18" s="28" t="n"/>
     </row>
-    <row r="19" ht="45" customHeight="1">
+    <row r="19" ht="50" customHeight="1">
       <c r="A19" s="36" t="n"/>
-      <c r="B19" s="49" t="inlineStr">
-        <is>
-          <t>🆕</t>
+      <c r="B19" s="106" t="inlineStr">
+        <is>
+          <t>NEW</t>
         </is>
       </c>
       <c r="C19" s="30" t="inlineStr">
@@ -2095,11 +2124,11 @@
       </c>
       <c r="K19" s="36" t="n"/>
     </row>
-    <row r="20" ht="45" customHeight="1">
+    <row r="20" ht="67" customHeight="1">
       <c r="A20" s="28" t="n"/>
-      <c r="B20" s="48" t="inlineStr">
-        <is>
-          <t>🆕</t>
+      <c r="B20" s="106" t="inlineStr">
+        <is>
+          <t>NEW</t>
         </is>
       </c>
       <c r="C20" s="38" t="inlineStr">
@@ -2140,11 +2169,11 @@
       </c>
       <c r="K20" s="28" t="n"/>
     </row>
-    <row r="21" ht="45" customHeight="1">
+    <row r="21" ht="67" customHeight="1">
       <c r="A21" s="36" t="n"/>
-      <c r="B21" s="49" t="inlineStr">
-        <is>
-          <t>🆕</t>
+      <c r="B21" s="106" t="inlineStr">
+        <is>
+          <t>NEW</t>
         </is>
       </c>
       <c r="C21" s="30" t="inlineStr">
@@ -2185,11 +2214,11 @@
       </c>
       <c r="K21" s="36" t="n"/>
     </row>
-    <row r="22" ht="45" customHeight="1">
+    <row r="22" ht="84" customHeight="1">
       <c r="A22" s="28" t="n"/>
-      <c r="B22" s="48" t="inlineStr">
-        <is>
-          <t>🔁</t>
+      <c r="B22" s="107" t="inlineStr">
+        <is>
+          <t>RPT</t>
         </is>
       </c>
       <c r="C22" s="38" t="inlineStr">
@@ -2230,11 +2259,11 @@
       </c>
       <c r="K22" s="28" t="n"/>
     </row>
-    <row r="23" ht="45" customHeight="1">
+    <row r="23" ht="50" customHeight="1">
       <c r="A23" s="28" t="n"/>
-      <c r="B23" s="49" t="inlineStr">
-        <is>
-          <t>🔁</t>
+      <c r="B23" s="107" t="inlineStr">
+        <is>
+          <t>RPT</t>
         </is>
       </c>
       <c r="C23" s="30" t="inlineStr">
@@ -2275,11 +2304,11 @@
       </c>
       <c r="K23" s="28" t="n"/>
     </row>
-    <row r="24" ht="45" customHeight="1">
+    <row r="24" ht="50" customHeight="1">
       <c r="A24" s="36" t="n"/>
-      <c r="B24" s="48" t="inlineStr">
-        <is>
-          <t>🔁</t>
+      <c r="B24" s="107" t="inlineStr">
+        <is>
+          <t>RPT</t>
         </is>
       </c>
       <c r="C24" s="38" t="inlineStr">
@@ -2320,11 +2349,11 @@
       </c>
       <c r="K24" s="36" t="n"/>
     </row>
-    <row r="25" ht="45" customHeight="1">
+    <row r="25" ht="50" customHeight="1">
       <c r="A25" s="28" t="n"/>
-      <c r="B25" s="49" t="inlineStr">
-        <is>
-          <t>🔁</t>
+      <c r="B25" s="107" t="inlineStr">
+        <is>
+          <t>RPT</t>
         </is>
       </c>
       <c r="C25" s="30" t="inlineStr">
@@ -2365,11 +2394,11 @@
       </c>
       <c r="K25" s="28" t="n"/>
     </row>
-    <row r="26" ht="45" customHeight="1">
+    <row r="26" ht="50" customHeight="1">
       <c r="A26" s="36" t="n"/>
-      <c r="B26" s="48" t="inlineStr">
-        <is>
-          <t>🔁</t>
+      <c r="B26" s="107" t="inlineStr">
+        <is>
+          <t>RPT</t>
         </is>
       </c>
       <c r="C26" s="38" t="inlineStr">
@@ -2410,11 +2439,11 @@
       </c>
       <c r="K26" s="36" t="n"/>
     </row>
-    <row r="27" ht="45" customHeight="1">
+    <row r="27" ht="50" customHeight="1">
       <c r="A27" s="36" t="n"/>
-      <c r="B27" s="49" t="inlineStr">
-        <is>
-          <t>🔁</t>
+      <c r="B27" s="107" t="inlineStr">
+        <is>
+          <t>RPT</t>
         </is>
       </c>
       <c r="C27" s="30" t="inlineStr">
@@ -2455,11 +2484,11 @@
       </c>
       <c r="K27" s="36" t="n"/>
     </row>
-    <row r="28" ht="45" customHeight="1">
+    <row r="28" ht="67" customHeight="1">
       <c r="A28" s="28" t="n"/>
-      <c r="B28" s="48" t="inlineStr">
-        <is>
-          <t>🔁</t>
+      <c r="B28" s="107" t="inlineStr">
+        <is>
+          <t>RPT</t>
         </is>
       </c>
       <c r="C28" s="38" t="inlineStr">
@@ -2500,11 +2529,11 @@
       </c>
       <c r="K28" s="28" t="n"/>
     </row>
-    <row r="29" ht="45" customHeight="1">
+    <row r="29" ht="67" customHeight="1">
       <c r="A29" s="36" t="n"/>
-      <c r="B29" s="49" t="inlineStr">
-        <is>
-          <t>🔁</t>
+      <c r="B29" s="107" t="inlineStr">
+        <is>
+          <t>RPT</t>
         </is>
       </c>
       <c r="C29" s="30" t="inlineStr">
@@ -2545,11 +2574,11 @@
       </c>
       <c r="K29" s="36" t="n"/>
     </row>
-    <row r="30" ht="45" customHeight="1">
+    <row r="30" ht="50" customHeight="1">
       <c r="A30" s="36" t="n"/>
-      <c r="B30" s="48" t="inlineStr">
-        <is>
-          <t>🔁</t>
+      <c r="B30" s="107" t="inlineStr">
+        <is>
+          <t>RPT</t>
         </is>
       </c>
       <c r="C30" s="38" t="inlineStr">
@@ -2590,11 +2619,11 @@
       </c>
       <c r="K30" s="36" t="n"/>
     </row>
-    <row r="31" ht="45" customHeight="1">
+    <row r="31" ht="50" customHeight="1">
       <c r="A31" s="28" t="n"/>
-      <c r="B31" s="49" t="inlineStr">
-        <is>
-          <t>🔥</t>
+      <c r="B31" s="108" t="inlineStr">
+        <is>
+          <t>STRK</t>
         </is>
       </c>
       <c r="C31" s="30" t="inlineStr">
@@ -2635,11 +2664,11 @@
       </c>
       <c r="K31" s="28" t="n"/>
     </row>
-    <row r="32" ht="45" customHeight="1">
+    <row r="32" ht="50" customHeight="1">
       <c r="A32" s="36" t="n"/>
-      <c r="B32" s="48" t="inlineStr">
-        <is>
-          <t>🔥</t>
+      <c r="B32" s="108" t="inlineStr">
+        <is>
+          <t>STRK</t>
         </is>
       </c>
       <c r="C32" s="38" t="inlineStr">
@@ -2680,11 +2709,11 @@
       </c>
       <c r="K32" s="36" t="n"/>
     </row>
-    <row r="33" ht="45" customHeight="1">
+    <row r="33" ht="67" customHeight="1">
       <c r="A33" s="28" t="n"/>
-      <c r="B33" s="49" t="inlineStr">
-        <is>
-          <t>🔥</t>
+      <c r="B33" s="108" t="inlineStr">
+        <is>
+          <t>STRK</t>
         </is>
       </c>
       <c r="C33" s="30" t="inlineStr">
@@ -2725,11 +2754,11 @@
       </c>
       <c r="K33" s="28" t="n"/>
     </row>
-    <row r="34" ht="45" customHeight="1">
+    <row r="34" ht="50" customHeight="1">
       <c r="A34" s="36" t="n"/>
-      <c r="B34" s="48" t="inlineStr">
-        <is>
-          <t>🔥</t>
+      <c r="B34" s="108" t="inlineStr">
+        <is>
+          <t>STRK</t>
         </is>
       </c>
       <c r="C34" s="38" t="inlineStr">
@@ -2770,11 +2799,11 @@
       </c>
       <c r="K34" s="36" t="n"/>
     </row>
-    <row r="35" ht="45" customHeight="1">
+    <row r="35" ht="101" customHeight="1">
       <c r="A35" s="28" t="n"/>
-      <c r="B35" s="49" t="inlineStr">
-        <is>
-          <t>🔥</t>
+      <c r="B35" s="108" t="inlineStr">
+        <is>
+          <t>STRK</t>
         </is>
       </c>
       <c r="C35" s="30" t="inlineStr">
@@ -2815,11 +2844,11 @@
       </c>
       <c r="K35" s="28" t="n"/>
     </row>
-    <row r="36" ht="45" customHeight="1">
+    <row r="36" ht="67" customHeight="1">
       <c r="A36" s="36" t="n"/>
-      <c r="B36" s="48" t="inlineStr">
-        <is>
-          <t>🔥</t>
+      <c r="B36" s="108" t="inlineStr">
+        <is>
+          <t>STRK</t>
         </is>
       </c>
       <c r="C36" s="38" t="inlineStr">
@@ -2860,11 +2889,11 @@
       </c>
       <c r="K36" s="36" t="n"/>
     </row>
-    <row r="37" ht="45" customHeight="1">
+    <row r="37" ht="84" customHeight="1">
       <c r="A37" s="28" t="n"/>
-      <c r="B37" s="49" t="inlineStr">
-        <is>
-          <t>🔥</t>
+      <c r="B37" s="108" t="inlineStr">
+        <is>
+          <t>STRK</t>
         </is>
       </c>
       <c r="C37" s="30" t="inlineStr">
@@ -2905,11 +2934,11 @@
       </c>
       <c r="K37" s="28" t="n"/>
     </row>
-    <row r="38" ht="45" customHeight="1">
+    <row r="38" ht="50" customHeight="1">
       <c r="A38" s="36" t="n"/>
-      <c r="B38" s="48" t="inlineStr">
-        <is>
-          <t>🔥</t>
+      <c r="B38" s="108" t="inlineStr">
+        <is>
+          <t>STRK</t>
         </is>
       </c>
       <c r="C38" s="38" t="inlineStr">
@@ -2950,11 +2979,11 @@
       </c>
       <c r="K38" s="36" t="n"/>
     </row>
-    <row r="39" ht="45" customHeight="1">
+    <row r="39" ht="50" customHeight="1">
       <c r="A39" s="28" t="n"/>
-      <c r="B39" s="49" t="inlineStr">
-        <is>
-          <t>🔥</t>
+      <c r="B39" s="108" t="inlineStr">
+        <is>
+          <t>STRK</t>
         </is>
       </c>
       <c r="C39" s="30" t="inlineStr">
@@ -2995,45 +3024,45 @@
       </c>
       <c r="K39" s="28" t="n"/>
     </row>
-    <row r="40" ht="45" customHeight="1">
+    <row r="40" ht="67" customHeight="1">
       <c r="A40" s="36" t="n"/>
-      <c r="B40" s="106" t="inlineStr">
-        <is>
-          <t>🔥</t>
-        </is>
-      </c>
-      <c r="C40" s="107" t="inlineStr">
+      <c r="B40" s="109" t="inlineStr">
+        <is>
+          <t>STRK</t>
+        </is>
+      </c>
+      <c r="C40" s="110" t="inlineStr">
         <is>
           <t>IFP</t>
         </is>
       </c>
-      <c r="D40" s="108" t="inlineStr">
+      <c r="D40" s="111" t="inlineStr">
         <is>
           <t>Interfor Corporation</t>
         </is>
       </c>
-      <c r="E40" s="109" t="inlineStr">
+      <c r="E40" s="112" t="inlineStr">
         <is>
           <t>Materials</t>
         </is>
       </c>
-      <c r="F40" s="109" t="inlineStr">
+      <c r="F40" s="112" t="inlineStr">
         <is>
           <t>Paper and Forest Products</t>
         </is>
       </c>
-      <c r="G40" s="110" t="n">
+      <c r="G40" s="113" t="n">
         <v>0.2</v>
       </c>
-      <c r="H40" s="111" t="inlineStr">
+      <c r="H40" s="114" t="inlineStr">
         <is>
           <t>Streak</t>
         </is>
       </c>
-      <c r="I40" s="112" t="n">
+      <c r="I40" s="115" t="n">
         <v>501.72</v>
       </c>
-      <c r="J40" s="113" t="inlineStr">
+      <c r="J40" s="116" t="inlineStr">
         <is>
           <t>Interfor Corporation together with its subsidiaries produces and sells wood products in Canada the United States Japan China Taiwan and internationally</t>
         </is>
@@ -3042,49 +3071,49 @@
     </row>
     <row r="41" ht="8" customHeight="1" thickBot="1">
       <c r="A41" s="68" t="n"/>
-      <c r="B41" s="114" t="n"/>
-      <c r="C41" s="115" t="n"/>
-      <c r="D41" s="116" t="n"/>
-      <c r="E41" s="117" t="n"/>
-      <c r="F41" s="117" t="n"/>
-      <c r="G41" s="118" t="n"/>
-      <c r="H41" s="119" t="n"/>
-      <c r="I41" s="120" t="n"/>
-      <c r="J41" s="121" t="n"/>
+      <c r="B41" s="117" t="n"/>
+      <c r="C41" s="118" t="n"/>
+      <c r="D41" s="119" t="n"/>
+      <c r="E41" s="120" t="n"/>
+      <c r="F41" s="120" t="n"/>
+      <c r="G41" s="121" t="n"/>
+      <c r="H41" s="122" t="n"/>
+      <c r="I41" s="123" t="n"/>
+      <c r="J41" s="124" t="n"/>
       <c r="K41" s="68" t="n"/>
     </row>
     <row r="42" ht="34" customHeight="1">
       <c r="A42" s="43" t="n"/>
-      <c r="B42" s="122" t="inlineStr">
+      <c r="B42" s="125" t="inlineStr">
         <is>
           <t>🔓 Want to know which of these we would actually buy? Start your 14-Day Free Trial at www.5iresearch.ca/bb</t>
         </is>
       </c>
-      <c r="C42" s="123" t="n"/>
-      <c r="D42" s="123" t="n"/>
-      <c r="E42" s="123" t="n"/>
-      <c r="F42" s="123" t="n"/>
-      <c r="G42" s="123" t="n"/>
-      <c r="H42" s="123" t="n"/>
-      <c r="I42" s="123" t="n"/>
-      <c r="J42" s="123" t="n"/>
+      <c r="C42" s="126" t="n"/>
+      <c r="D42" s="126" t="n"/>
+      <c r="E42" s="126" t="n"/>
+      <c r="F42" s="126" t="n"/>
+      <c r="G42" s="126" t="n"/>
+      <c r="H42" s="126" t="n"/>
+      <c r="I42" s="126" t="n"/>
+      <c r="J42" s="126" t="n"/>
       <c r="K42" s="43" t="n"/>
     </row>
     <row r="43" ht="28" customHeight="1" thickBot="1">
       <c r="A43" s="43" t="n"/>
-      <c r="B43" s="124" t="inlineStr">
+      <c r="B43" s="127" t="inlineStr">
         <is>
           <t>Disclosure: While this table does not constitute any formal opinion on names presented, authors may own shares in non-Canadian securities listed above.</t>
         </is>
       </c>
-      <c r="C43" s="125" t="n"/>
-      <c r="D43" s="125" t="n"/>
-      <c r="E43" s="125" t="n"/>
-      <c r="F43" s="125" t="n"/>
-      <c r="G43" s="125" t="n"/>
-      <c r="H43" s="125" t="n"/>
-      <c r="I43" s="125" t="n"/>
-      <c r="J43" s="125" t="n"/>
+      <c r="C43" s="128" t="n"/>
+      <c r="D43" s="128" t="n"/>
+      <c r="E43" s="128" t="n"/>
+      <c r="F43" s="128" t="n"/>
+      <c r="G43" s="128" t="n"/>
+      <c r="H43" s="128" t="n"/>
+      <c r="I43" s="128" t="n"/>
+      <c r="J43" s="128" t="n"/>
       <c r="K43" s="43" t="n"/>
     </row>
     <row r="44" ht="12" customHeight="1">
@@ -4115,7 +4144,7 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="1.21875" customWidth="1" style="11" min="1" max="1"/>
-    <col width="5.44140625" customWidth="1" style="11" min="2" max="2"/>
+    <col width="8.5" customWidth="1" style="11" min="2" max="2"/>
     <col width="10" customWidth="1" style="14" min="3" max="3"/>
     <col width="26" customWidth="1" style="15" min="4" max="4"/>
     <col width="16" customWidth="1" style="14" min="5" max="5"/>
@@ -4152,7 +4181,7 @@
       </c>
       <c r="H2" s="82" t="n"/>
       <c r="I2" s="84" t="n">
-        <v>46224.87725170761</v>
+        <v>46224.90155205015</v>
       </c>
     </row>
     <row r="3" ht="3" customHeight="1">
@@ -4257,11 +4286,11 @@
       </c>
       <c r="K7" s="26" t="n"/>
     </row>
-    <row r="8" ht="45" customHeight="1">
+    <row r="8" ht="50" customHeight="1">
       <c r="A8" s="36" t="n"/>
-      <c r="B8" s="48" t="inlineStr">
-        <is>
-          <t>🆕</t>
+      <c r="B8" s="106" t="inlineStr">
+        <is>
+          <t>NEW</t>
         </is>
       </c>
       <c r="C8" s="38" t="inlineStr">
@@ -4302,11 +4331,11 @@
       </c>
       <c r="K8" s="36" t="n"/>
     </row>
-    <row r="9" ht="45" customHeight="1">
+    <row r="9" ht="50" customHeight="1">
       <c r="A9" s="28" t="n"/>
-      <c r="B9" s="49" t="inlineStr">
-        <is>
-          <t>🆕</t>
+      <c r="B9" s="106" t="inlineStr">
+        <is>
+          <t>NEW</t>
         </is>
       </c>
       <c r="C9" s="30" t="inlineStr">
@@ -4347,11 +4376,11 @@
       </c>
       <c r="K9" s="28" t="n"/>
     </row>
-    <row r="10" ht="45" customHeight="1">
+    <row r="10" ht="50" customHeight="1">
       <c r="A10" s="36" t="n"/>
-      <c r="B10" s="48" t="inlineStr">
-        <is>
-          <t>🆕</t>
+      <c r="B10" s="106" t="inlineStr">
+        <is>
+          <t>NEW</t>
         </is>
       </c>
       <c r="C10" s="38" t="inlineStr">
@@ -4392,11 +4421,11 @@
       </c>
       <c r="K10" s="36" t="n"/>
     </row>
-    <row r="11" ht="45" customHeight="1">
+    <row r="11" ht="67" customHeight="1">
       <c r="A11" s="28" t="n"/>
-      <c r="B11" s="49" t="inlineStr">
-        <is>
-          <t>🆕</t>
+      <c r="B11" s="106" t="inlineStr">
+        <is>
+          <t>NEW</t>
         </is>
       </c>
       <c r="C11" s="30" t="inlineStr">
@@ -4437,11 +4466,11 @@
       </c>
       <c r="K11" s="28" t="n"/>
     </row>
-    <row r="12" ht="45" customHeight="1">
+    <row r="12" ht="67" customHeight="1">
       <c r="A12" s="36" t="n"/>
-      <c r="B12" s="48" t="inlineStr">
-        <is>
-          <t>🆕</t>
+      <c r="B12" s="106" t="inlineStr">
+        <is>
+          <t>NEW</t>
         </is>
       </c>
       <c r="C12" s="38" t="inlineStr">
@@ -4482,11 +4511,11 @@
       </c>
       <c r="K12" s="36" t="n"/>
     </row>
-    <row r="13" ht="45" customHeight="1">
+    <row r="13" ht="50" customHeight="1">
       <c r="A13" s="28" t="n"/>
-      <c r="B13" s="49" t="inlineStr">
-        <is>
-          <t>🆕</t>
+      <c r="B13" s="106" t="inlineStr">
+        <is>
+          <t>NEW</t>
         </is>
       </c>
       <c r="C13" s="30" t="inlineStr">
@@ -4527,11 +4556,11 @@
       </c>
       <c r="K13" s="28" t="n"/>
     </row>
-    <row r="14" ht="45" customHeight="1">
+    <row r="14" ht="84" customHeight="1">
       <c r="A14" s="36" t="n"/>
-      <c r="B14" s="48" t="inlineStr">
-        <is>
-          <t>🆕</t>
+      <c r="B14" s="106" t="inlineStr">
+        <is>
+          <t>NEW</t>
         </is>
       </c>
       <c r="C14" s="38" t="inlineStr">
@@ -4572,11 +4601,11 @@
       </c>
       <c r="K14" s="36" t="n"/>
     </row>
-    <row r="15" ht="45" customHeight="1">
+    <row r="15" ht="67" customHeight="1">
       <c r="A15" s="28" t="n"/>
-      <c r="B15" s="49" t="inlineStr">
-        <is>
-          <t>🆕</t>
+      <c r="B15" s="106" t="inlineStr">
+        <is>
+          <t>NEW</t>
         </is>
       </c>
       <c r="C15" s="30" t="inlineStr">
@@ -4617,11 +4646,11 @@
       </c>
       <c r="K15" s="28" t="n"/>
     </row>
-    <row r="16" ht="45" customHeight="1">
+    <row r="16" ht="67" customHeight="1">
       <c r="A16" s="36" t="n"/>
-      <c r="B16" s="48" t="inlineStr">
-        <is>
-          <t>🆕</t>
+      <c r="B16" s="106" t="inlineStr">
+        <is>
+          <t>NEW</t>
         </is>
       </c>
       <c r="C16" s="38" t="inlineStr">
@@ -4662,11 +4691,11 @@
       </c>
       <c r="K16" s="36" t="n"/>
     </row>
-    <row r="17" ht="45" customHeight="1">
+    <row r="17" ht="33" customHeight="1">
       <c r="A17" s="28" t="n"/>
-      <c r="B17" s="49" t="inlineStr">
-        <is>
-          <t>🆕</t>
+      <c r="B17" s="106" t="inlineStr">
+        <is>
+          <t>NEW</t>
         </is>
       </c>
       <c r="C17" s="30" t="inlineStr">
@@ -4707,11 +4736,11 @@
       </c>
       <c r="K17" s="28" t="n"/>
     </row>
-    <row r="18" ht="45" customHeight="1">
+    <row r="18" ht="50" customHeight="1">
       <c r="A18" s="36" t="n"/>
-      <c r="B18" s="48" t="inlineStr">
-        <is>
-          <t>🆕</t>
+      <c r="B18" s="106" t="inlineStr">
+        <is>
+          <t>NEW</t>
         </is>
       </c>
       <c r="C18" s="38" t="inlineStr">
@@ -4752,11 +4781,11 @@
       </c>
       <c r="K18" s="36" t="n"/>
     </row>
-    <row r="19" ht="45" customHeight="1">
+    <row r="19" ht="67" customHeight="1">
       <c r="A19" s="28" t="n"/>
-      <c r="B19" s="49" t="inlineStr">
-        <is>
-          <t>🆕</t>
+      <c r="B19" s="106" t="inlineStr">
+        <is>
+          <t>NEW</t>
         </is>
       </c>
       <c r="C19" s="30" t="inlineStr">
@@ -4797,11 +4826,11 @@
       </c>
       <c r="K19" s="28" t="n"/>
     </row>
-    <row r="20" ht="45" customHeight="1">
+    <row r="20" ht="67" customHeight="1">
       <c r="A20" s="36" t="n"/>
-      <c r="B20" s="48" t="inlineStr">
-        <is>
-          <t>🆕</t>
+      <c r="B20" s="106" t="inlineStr">
+        <is>
+          <t>NEW</t>
         </is>
       </c>
       <c r="C20" s="38" t="inlineStr">
@@ -4842,11 +4871,11 @@
       </c>
       <c r="K20" s="36" t="n"/>
     </row>
-    <row r="21" ht="45" customHeight="1">
+    <row r="21" ht="84" customHeight="1">
       <c r="A21" s="28" t="n"/>
-      <c r="B21" s="49" t="inlineStr">
-        <is>
-          <t>🆕</t>
+      <c r="B21" s="106" t="inlineStr">
+        <is>
+          <t>NEW</t>
         </is>
       </c>
       <c r="C21" s="30" t="inlineStr">
@@ -4887,11 +4916,11 @@
       </c>
       <c r="K21" s="28" t="n"/>
     </row>
-    <row r="22" ht="45" customHeight="1">
+    <row r="22" ht="50" customHeight="1">
       <c r="A22" s="36" t="n"/>
-      <c r="B22" s="48" t="inlineStr">
-        <is>
-          <t>🆕</t>
+      <c r="B22" s="106" t="inlineStr">
+        <is>
+          <t>NEW</t>
         </is>
       </c>
       <c r="C22" s="38" t="inlineStr">
@@ -4932,11 +4961,11 @@
       </c>
       <c r="K22" s="36" t="n"/>
     </row>
-    <row r="23" ht="45" customHeight="1">
+    <row r="23" ht="84" customHeight="1">
       <c r="A23" s="28" t="n"/>
-      <c r="B23" s="49" t="inlineStr">
-        <is>
-          <t>🆕</t>
+      <c r="B23" s="106" t="inlineStr">
+        <is>
+          <t>NEW</t>
         </is>
       </c>
       <c r="C23" s="30" t="inlineStr">
@@ -4977,11 +5006,11 @@
       </c>
       <c r="K23" s="28" t="n"/>
     </row>
-    <row r="24" ht="45" customHeight="1">
+    <row r="24" ht="67" customHeight="1">
       <c r="A24" s="36" t="n"/>
-      <c r="B24" s="48" t="inlineStr">
-        <is>
-          <t>🆕</t>
+      <c r="B24" s="106" t="inlineStr">
+        <is>
+          <t>NEW</t>
         </is>
       </c>
       <c r="C24" s="38" t="inlineStr">
@@ -5022,11 +5051,11 @@
       </c>
       <c r="K24" s="36" t="n"/>
     </row>
-    <row r="25" ht="45" customHeight="1">
+    <row r="25" ht="67" customHeight="1">
       <c r="A25" s="28" t="n"/>
-      <c r="B25" s="49" t="inlineStr">
-        <is>
-          <t>🆕</t>
+      <c r="B25" s="106" t="inlineStr">
+        <is>
+          <t>NEW</t>
         </is>
       </c>
       <c r="C25" s="30" t="inlineStr">
@@ -5067,11 +5096,11 @@
       </c>
       <c r="K25" s="28" t="n"/>
     </row>
-    <row r="26" ht="45" customHeight="1">
+    <row r="26" ht="50" customHeight="1">
       <c r="A26" s="36" t="n"/>
-      <c r="B26" s="48" t="inlineStr">
-        <is>
-          <t>🆕</t>
+      <c r="B26" s="106" t="inlineStr">
+        <is>
+          <t>NEW</t>
         </is>
       </c>
       <c r="C26" s="38" t="inlineStr">
@@ -5112,11 +5141,11 @@
       </c>
       <c r="K26" s="36" t="n"/>
     </row>
-    <row r="27" ht="45" customHeight="1">
+    <row r="27" ht="67" customHeight="1">
       <c r="A27" s="28" t="n"/>
-      <c r="B27" s="49" t="inlineStr">
-        <is>
-          <t>🆕</t>
+      <c r="B27" s="106" t="inlineStr">
+        <is>
+          <t>NEW</t>
         </is>
       </c>
       <c r="C27" s="30" t="inlineStr">
@@ -5157,11 +5186,11 @@
       </c>
       <c r="K27" s="28" t="n"/>
     </row>
-    <row r="28" ht="45" customHeight="1">
+    <row r="28" ht="50" customHeight="1">
       <c r="A28" s="36" t="n"/>
-      <c r="B28" s="48" t="inlineStr">
-        <is>
-          <t>🆕</t>
+      <c r="B28" s="106" t="inlineStr">
+        <is>
+          <t>NEW</t>
         </is>
       </c>
       <c r="C28" s="38" t="inlineStr">
@@ -5202,11 +5231,11 @@
       </c>
       <c r="K28" s="36" t="n"/>
     </row>
-    <row r="29" ht="45" customHeight="1">
+    <row r="29" ht="84" customHeight="1">
       <c r="A29" s="28" t="n"/>
-      <c r="B29" s="49" t="inlineStr">
-        <is>
-          <t>🆕</t>
+      <c r="B29" s="106" t="inlineStr">
+        <is>
+          <t>NEW</t>
         </is>
       </c>
       <c r="C29" s="30" t="inlineStr">
@@ -5247,11 +5276,11 @@
       </c>
       <c r="K29" s="28" t="n"/>
     </row>
-    <row r="30" ht="45" customHeight="1">
+    <row r="30" ht="50" customHeight="1">
       <c r="A30" s="36" t="n"/>
-      <c r="B30" s="48" t="inlineStr">
-        <is>
-          <t>🆕</t>
+      <c r="B30" s="106" t="inlineStr">
+        <is>
+          <t>NEW</t>
         </is>
       </c>
       <c r="C30" s="38" t="inlineStr">
@@ -5292,11 +5321,11 @@
       </c>
       <c r="K30" s="36" t="n"/>
     </row>
-    <row r="31" ht="45" customHeight="1">
+    <row r="31" ht="50" customHeight="1">
       <c r="A31" s="28" t="n"/>
-      <c r="B31" s="49" t="inlineStr">
-        <is>
-          <t>🔁</t>
+      <c r="B31" s="107" t="inlineStr">
+        <is>
+          <t>RPT</t>
         </is>
       </c>
       <c r="C31" s="30" t="inlineStr">
@@ -5337,11 +5366,11 @@
       </c>
       <c r="K31" s="28" t="n"/>
     </row>
-    <row r="32" ht="45" customHeight="1">
+    <row r="32" ht="84" customHeight="1">
       <c r="A32" s="36" t="n"/>
-      <c r="B32" s="48" t="inlineStr">
-        <is>
-          <t>🔁</t>
+      <c r="B32" s="107" t="inlineStr">
+        <is>
+          <t>RPT</t>
         </is>
       </c>
       <c r="C32" s="38" t="inlineStr">
@@ -5382,11 +5411,11 @@
       </c>
       <c r="K32" s="36" t="n"/>
     </row>
-    <row r="33" ht="45" customHeight="1">
+    <row r="33" ht="50" customHeight="1">
       <c r="A33" s="28" t="n"/>
-      <c r="B33" s="49" t="inlineStr">
-        <is>
-          <t>🔁</t>
+      <c r="B33" s="107" t="inlineStr">
+        <is>
+          <t>RPT</t>
         </is>
       </c>
       <c r="C33" s="30" t="inlineStr">
@@ -5427,11 +5456,11 @@
       </c>
       <c r="K33" s="28" t="n"/>
     </row>
-    <row r="34" ht="45" customHeight="1">
+    <row r="34" ht="50" customHeight="1">
       <c r="A34" s="36" t="n"/>
-      <c r="B34" s="48" t="inlineStr">
-        <is>
-          <t>🔁</t>
+      <c r="B34" s="107" t="inlineStr">
+        <is>
+          <t>RPT</t>
         </is>
       </c>
       <c r="C34" s="38" t="inlineStr">
@@ -5472,11 +5501,11 @@
       </c>
       <c r="K34" s="36" t="n"/>
     </row>
-    <row r="35" ht="45" customHeight="1">
+    <row r="35" ht="50" customHeight="1">
       <c r="A35" s="28" t="n"/>
-      <c r="B35" s="49" t="inlineStr">
-        <is>
-          <t>🔁</t>
+      <c r="B35" s="107" t="inlineStr">
+        <is>
+          <t>RPT</t>
         </is>
       </c>
       <c r="C35" s="30" t="inlineStr">
@@ -5517,11 +5546,11 @@
       </c>
       <c r="K35" s="28" t="n"/>
     </row>
-    <row r="36" ht="45" customHeight="1">
+    <row r="36" ht="33" customHeight="1">
       <c r="A36" s="36" t="n"/>
-      <c r="B36" s="48" t="inlineStr">
-        <is>
-          <t>🔁</t>
+      <c r="B36" s="107" t="inlineStr">
+        <is>
+          <t>RPT</t>
         </is>
       </c>
       <c r="C36" s="38" t="inlineStr">
@@ -5562,11 +5591,11 @@
       </c>
       <c r="K36" s="36" t="n"/>
     </row>
-    <row r="37" ht="45" customHeight="1">
+    <row r="37" ht="67" customHeight="1">
       <c r="A37" s="28" t="n"/>
-      <c r="B37" s="49" t="inlineStr">
-        <is>
-          <t>🔁</t>
+      <c r="B37" s="107" t="inlineStr">
+        <is>
+          <t>RPT</t>
         </is>
       </c>
       <c r="C37" s="30" t="inlineStr">
@@ -5607,11 +5636,11 @@
       </c>
       <c r="K37" s="28" t="n"/>
     </row>
-    <row r="38" ht="45" customHeight="1">
+    <row r="38" ht="50" customHeight="1">
       <c r="A38" s="36" t="n"/>
-      <c r="B38" s="48" t="inlineStr">
-        <is>
-          <t>🔁</t>
+      <c r="B38" s="107" t="inlineStr">
+        <is>
+          <t>RPT</t>
         </is>
       </c>
       <c r="C38" s="38" t="inlineStr">
@@ -5652,11 +5681,11 @@
       </c>
       <c r="K38" s="36" t="n"/>
     </row>
-    <row r="39" ht="45" customHeight="1">
+    <row r="39" ht="67" customHeight="1">
       <c r="A39" s="28" t="n"/>
-      <c r="B39" s="49" t="inlineStr">
-        <is>
-          <t>🔁</t>
+      <c r="B39" s="107" t="inlineStr">
+        <is>
+          <t>RPT</t>
         </is>
       </c>
       <c r="C39" s="30" t="inlineStr">
@@ -5697,45 +5726,45 @@
       </c>
       <c r="K39" s="28" t="n"/>
     </row>
-    <row r="40" ht="45" customHeight="1">
+    <row r="40" ht="50" customHeight="1">
       <c r="A40" s="36" t="n"/>
-      <c r="B40" s="106" t="inlineStr">
-        <is>
-          <t>🔥</t>
-        </is>
-      </c>
-      <c r="C40" s="107" t="inlineStr">
+      <c r="B40" s="109" t="inlineStr">
+        <is>
+          <t>STRK</t>
+        </is>
+      </c>
+      <c r="C40" s="110" t="inlineStr">
         <is>
           <t>CSX</t>
         </is>
       </c>
-      <c r="D40" s="108" t="inlineStr">
+      <c r="D40" s="111" t="inlineStr">
         <is>
           <t>CSX Corporation</t>
         </is>
       </c>
-      <c r="E40" s="109" t="inlineStr">
+      <c r="E40" s="112" t="inlineStr">
         <is>
           <t>Industrials</t>
         </is>
       </c>
-      <c r="F40" s="109" t="inlineStr">
+      <c r="F40" s="112" t="inlineStr">
         <is>
           <t>Ground Transportation</t>
         </is>
       </c>
-      <c r="G40" s="110" t="n">
+      <c r="G40" s="113" t="n">
         <v>0.37</v>
       </c>
-      <c r="H40" s="111" t="inlineStr">
+      <c r="H40" s="114" t="inlineStr">
         <is>
           <t>Streak</t>
         </is>
       </c>
-      <c r="I40" s="112" t="n">
+      <c r="I40" s="115" t="n">
         <v>86617.14</v>
       </c>
-      <c r="J40" s="113" t="inlineStr">
+      <c r="J40" s="116" t="inlineStr">
         <is>
           <t>CSX Corporation together with its subsidiaries provides rail-based freight transportation services in the United States and Canada</t>
         </is>
@@ -5744,49 +5773,49 @@
     </row>
     <row r="41" ht="8" customHeight="1">
       <c r="A41" s="28" t="n"/>
-      <c r="B41" s="114" t="n"/>
-      <c r="C41" s="115" t="n"/>
-      <c r="D41" s="116" t="n"/>
-      <c r="E41" s="117" t="n"/>
-      <c r="F41" s="117" t="n"/>
-      <c r="G41" s="118" t="n"/>
-      <c r="H41" s="119" t="n"/>
-      <c r="I41" s="120" t="n"/>
-      <c r="J41" s="121" t="n"/>
+      <c r="B41" s="117" t="n"/>
+      <c r="C41" s="118" t="n"/>
+      <c r="D41" s="119" t="n"/>
+      <c r="E41" s="120" t="n"/>
+      <c r="F41" s="120" t="n"/>
+      <c r="G41" s="121" t="n"/>
+      <c r="H41" s="122" t="n"/>
+      <c r="I41" s="123" t="n"/>
+      <c r="J41" s="124" t="n"/>
       <c r="K41" s="28" t="n"/>
     </row>
     <row r="42" ht="34" customHeight="1" thickBot="1">
       <c r="A42" s="75" t="n"/>
-      <c r="B42" s="122" t="inlineStr">
+      <c r="B42" s="125" t="inlineStr">
         <is>
           <t>🔓 Want to know which of these we would actually buy? Start your 14-Day Free Trial at www.5iresearch.ca/bb</t>
         </is>
       </c>
-      <c r="C42" s="123" t="n"/>
-      <c r="D42" s="123" t="n"/>
-      <c r="E42" s="123" t="n"/>
-      <c r="F42" s="123" t="n"/>
-      <c r="G42" s="123" t="n"/>
-      <c r="H42" s="123" t="n"/>
-      <c r="I42" s="123" t="n"/>
-      <c r="J42" s="123" t="n"/>
+      <c r="C42" s="126" t="n"/>
+      <c r="D42" s="126" t="n"/>
+      <c r="E42" s="126" t="n"/>
+      <c r="F42" s="126" t="n"/>
+      <c r="G42" s="126" t="n"/>
+      <c r="H42" s="126" t="n"/>
+      <c r="I42" s="126" t="n"/>
+      <c r="J42" s="126" t="n"/>
       <c r="K42" s="75" t="n"/>
     </row>
     <row r="43" ht="28" customHeight="1">
       <c r="A43" s="43" t="n"/>
-      <c r="B43" s="124" t="inlineStr">
+      <c r="B43" s="127" t="inlineStr">
         <is>
           <t>Disclosure: While this table does not constitute any formal opinion on names presented, authors may own shares in non-Canadian securities listed above.</t>
         </is>
       </c>
-      <c r="C43" s="125" t="n"/>
-      <c r="D43" s="125" t="n"/>
-      <c r="E43" s="125" t="n"/>
-      <c r="F43" s="125" t="n"/>
-      <c r="G43" s="125" t="n"/>
-      <c r="H43" s="125" t="n"/>
-      <c r="I43" s="125" t="n"/>
-      <c r="J43" s="125" t="n"/>
+      <c r="C43" s="128" t="n"/>
+      <c r="D43" s="128" t="n"/>
+      <c r="E43" s="128" t="n"/>
+      <c r="F43" s="128" t="n"/>
+      <c r="G43" s="128" t="n"/>
+      <c r="H43" s="128" t="n"/>
+      <c r="I43" s="128" t="n"/>
+      <c r="J43" s="128" t="n"/>
       <c r="K43" s="43" t="n"/>
     </row>
     <row r="44" ht="15.6" customHeight="1" thickBot="1">
